--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>25.1572</v>
+        <v>23.5588</v>
       </c>
       <c r="C2" t="n">
-        <v>42.2318</v>
+        <v>25.5156</v>
       </c>
       <c r="D2" t="n">
-        <v>57.3346</v>
+        <v>55.899</v>
       </c>
       <c r="E2" t="n">
-        <v>20.7887</v>
+        <v>19.3314</v>
       </c>
       <c r="F2" t="n">
-        <v>39.5651</v>
+        <v>35.937</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0192</v>
+        <v>22.2423</v>
       </c>
       <c r="C3" t="n">
-        <v>41.6799</v>
+        <v>24.94</v>
       </c>
       <c r="D3" t="n">
-        <v>56.2625</v>
+        <v>55.1945</v>
       </c>
       <c r="E3" t="n">
-        <v>20.2727</v>
+        <v>18.7453</v>
       </c>
       <c r="F3" t="n">
-        <v>39.2357</v>
+        <v>35.4287</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>24.1894</v>
+        <v>21.2111</v>
       </c>
       <c r="C4" t="n">
-        <v>40.9992</v>
+        <v>24.466</v>
       </c>
       <c r="D4" t="n">
-        <v>55.8829</v>
+        <v>54.7185</v>
       </c>
       <c r="E4" t="n">
-        <v>19.7495</v>
+        <v>18.3133</v>
       </c>
       <c r="F4" t="n">
-        <v>38.6216</v>
+        <v>34.9254</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>23.0382</v>
+        <v>20.6457</v>
       </c>
       <c r="C5" t="n">
-        <v>40.5649</v>
+        <v>23.9408</v>
       </c>
       <c r="D5" t="n">
-        <v>55.3956</v>
+        <v>54.294</v>
       </c>
       <c r="E5" t="n">
-        <v>19.7071</v>
+        <v>17.9738</v>
       </c>
       <c r="F5" t="n">
-        <v>38.4077</v>
+        <v>34.6134</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.9887</v>
+        <v>20.668</v>
       </c>
       <c r="C6" t="n">
-        <v>39.9929</v>
+        <v>24.1069</v>
       </c>
       <c r="D6" t="n">
-        <v>54.752</v>
+        <v>53.8598</v>
       </c>
       <c r="E6" t="n">
-        <v>18.9307</v>
+        <v>17.6348</v>
       </c>
       <c r="F6" t="n">
-        <v>38.1155</v>
+        <v>34.4065</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>23.3609</v>
+        <v>20.589</v>
       </c>
       <c r="C7" t="n">
-        <v>39.7766</v>
+        <v>23.1348</v>
       </c>
       <c r="D7" t="n">
-        <v>70.16630000000001</v>
+        <v>68.986</v>
       </c>
       <c r="E7" t="n">
-        <v>18.7042</v>
+        <v>17.3741</v>
       </c>
       <c r="F7" t="n">
-        <v>38.0618</v>
+        <v>34.2784</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>22.6363</v>
+        <v>20.0563</v>
       </c>
       <c r="C8" t="n">
-        <v>39.3238</v>
+        <v>31.9857</v>
       </c>
       <c r="D8" t="n">
-        <v>68.8539</v>
+        <v>67.4682</v>
       </c>
       <c r="E8" t="n">
-        <v>18.7594</v>
+        <v>17.4603</v>
       </c>
       <c r="F8" t="n">
-        <v>38.4305</v>
+        <v>34.1338</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>22.508</v>
+        <v>20.1423</v>
       </c>
       <c r="C9" t="n">
-        <v>39.5349</v>
+        <v>31.2302</v>
       </c>
       <c r="D9" t="n">
-        <v>67.6134</v>
+        <v>66.0025</v>
       </c>
       <c r="E9" t="n">
-        <v>27.998</v>
+        <v>25.8625</v>
       </c>
       <c r="F9" t="n">
-        <v>46.2522</v>
+        <v>41.7421</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>32.0603</v>
+        <v>28.6427</v>
       </c>
       <c r="C10" t="n">
-        <v>48.4857</v>
+        <v>31.6326</v>
       </c>
       <c r="D10" t="n">
-        <v>66.2804</v>
+        <v>64.777</v>
       </c>
       <c r="E10" t="n">
-        <v>27.1248</v>
+        <v>25.0106</v>
       </c>
       <c r="F10" t="n">
-        <v>45.3637</v>
+        <v>40.8032</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>30.7034</v>
+        <v>28.51</v>
       </c>
       <c r="C11" t="n">
-        <v>47.4394</v>
+        <v>29.5519</v>
       </c>
       <c r="D11" t="n">
-        <v>65.1211</v>
+        <v>63.662</v>
       </c>
       <c r="E11" t="n">
-        <v>26.0965</v>
+        <v>24.142</v>
       </c>
       <c r="F11" t="n">
-        <v>43.8307</v>
+        <v>39.7736</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>29.2139</v>
+        <v>26.7585</v>
       </c>
       <c r="C12" t="n">
-        <v>46.717</v>
+        <v>28.8842</v>
       </c>
       <c r="D12" t="n">
-        <v>64.0153</v>
+        <v>62.5898</v>
       </c>
       <c r="E12" t="n">
-        <v>25.2661</v>
+        <v>23.3695</v>
       </c>
       <c r="F12" t="n">
-        <v>42.9505</v>
+        <v>38.9293</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>28.9149</v>
+        <v>26.1129</v>
       </c>
       <c r="C13" t="n">
-        <v>45.6568</v>
+        <v>28.2319</v>
       </c>
       <c r="D13" t="n">
-        <v>63.1462</v>
+        <v>61.7757</v>
       </c>
       <c r="E13" t="n">
-        <v>24.3217</v>
+        <v>22.6654</v>
       </c>
       <c r="F13" t="n">
-        <v>42.0843</v>
+        <v>38.1381</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>27.5528</v>
+        <v>25.6063</v>
       </c>
       <c r="C14" t="n">
-        <v>44.7286</v>
+        <v>27.4816</v>
       </c>
       <c r="D14" t="n">
-        <v>62.1723</v>
+        <v>60.9783</v>
       </c>
       <c r="E14" t="n">
-        <v>23.532</v>
+        <v>21.985</v>
       </c>
       <c r="F14" t="n">
-        <v>41.2695</v>
+        <v>37.3997</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>27.1804</v>
+        <v>24.7123</v>
       </c>
       <c r="C15" t="n">
-        <v>44.5709</v>
+        <v>26.8261</v>
       </c>
       <c r="D15" t="n">
-        <v>61.6618</v>
+        <v>60.2183</v>
       </c>
       <c r="E15" t="n">
-        <v>22.9939</v>
+        <v>21.3705</v>
       </c>
       <c r="F15" t="n">
-        <v>40.5517</v>
+        <v>36.7189</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>26.3905</v>
+        <v>24.2906</v>
       </c>
       <c r="C16" t="n">
-        <v>43.9653</v>
+        <v>26.2781</v>
       </c>
       <c r="D16" t="n">
-        <v>61.078</v>
+        <v>59.6626</v>
       </c>
       <c r="E16" t="n">
-        <v>22.4133</v>
+        <v>20.817</v>
       </c>
       <c r="F16" t="n">
-        <v>40.0287</v>
+        <v>36.1123</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>25.6809</v>
+        <v>23.3297</v>
       </c>
       <c r="C17" t="n">
-        <v>43.6887</v>
+        <v>25.6546</v>
       </c>
       <c r="D17" t="n">
-        <v>60.5039</v>
+        <v>59.2295</v>
       </c>
       <c r="E17" t="n">
-        <v>21.8042</v>
+        <v>20.2577</v>
       </c>
       <c r="F17" t="n">
-        <v>39.7854</v>
+        <v>35.5821</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.6154</v>
+        <v>23.0523</v>
       </c>
       <c r="C18" t="n">
-        <v>42.3566</v>
+        <v>25.2392</v>
       </c>
       <c r="D18" t="n">
-        <v>60.1315</v>
+        <v>58.6434</v>
       </c>
       <c r="E18" t="n">
-        <v>21.2547</v>
+        <v>19.8355</v>
       </c>
       <c r="F18" t="n">
-        <v>39.3909</v>
+        <v>35.0886</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>24.3601</v>
+        <v>22.1401</v>
       </c>
       <c r="C19" t="n">
-        <v>41.7633</v>
+        <v>24.7307</v>
       </c>
       <c r="D19" t="n">
-        <v>59.41</v>
+        <v>57.905</v>
       </c>
       <c r="E19" t="n">
-        <v>20.8112</v>
+        <v>19.3902</v>
       </c>
       <c r="F19" t="n">
-        <v>38.0803</v>
+        <v>34.621</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.8545</v>
+        <v>21.7361</v>
       </c>
       <c r="C20" t="n">
-        <v>40.8281</v>
+        <v>24.3434</v>
       </c>
       <c r="D20" t="n">
-        <v>59.0357</v>
+        <v>57.6325</v>
       </c>
       <c r="E20" t="n">
-        <v>20.4738</v>
+        <v>19.0616</v>
       </c>
       <c r="F20" t="n">
-        <v>37.91</v>
+        <v>34.2988</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>23.0922</v>
+        <v>21.717</v>
       </c>
       <c r="C21" t="n">
-        <v>40.3686</v>
+        <v>24.0185</v>
       </c>
       <c r="D21" t="n">
-        <v>76.41419999999999</v>
+        <v>75.3214</v>
       </c>
       <c r="E21" t="n">
-        <v>20.4611</v>
+        <v>18.9609</v>
       </c>
       <c r="F21" t="n">
-        <v>37.9169</v>
+        <v>34.1548</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>23.0714</v>
+        <v>21.2987</v>
       </c>
       <c r="C22" t="n">
-        <v>40.1262</v>
+        <v>32.8778</v>
       </c>
       <c r="D22" t="n">
-        <v>74.89870000000001</v>
+        <v>73.71469999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>20.4199</v>
+        <v>19.1112</v>
       </c>
       <c r="F22" t="n">
-        <v>37.9326</v>
+        <v>34.4647</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>23.8027</v>
+        <v>22.191</v>
       </c>
       <c r="C23" t="n">
-        <v>40.6808</v>
+        <v>31.9726</v>
       </c>
       <c r="D23" t="n">
-        <v>73.59</v>
+        <v>72.3198</v>
       </c>
       <c r="E23" t="n">
-        <v>29.4441</v>
+        <v>27.555</v>
       </c>
       <c r="F23" t="n">
-        <v>46.3324</v>
+        <v>42.3144</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>31.6232</v>
+        <v>29.9788</v>
       </c>
       <c r="C24" t="n">
-        <v>50.244</v>
+        <v>31.2672</v>
       </c>
       <c r="D24" t="n">
-        <v>72.384</v>
+        <v>70.952</v>
       </c>
       <c r="E24" t="n">
-        <v>28.4455</v>
+        <v>26.6614</v>
       </c>
       <c r="F24" t="n">
-        <v>45.3113</v>
+        <v>41.416</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>31.6026</v>
+        <v>28.7755</v>
       </c>
       <c r="C25" t="n">
-        <v>49.7243</v>
+        <v>30.6068</v>
       </c>
       <c r="D25" t="n">
-        <v>71.0802</v>
+        <v>69.7743</v>
       </c>
       <c r="E25" t="n">
-        <v>27.476</v>
+        <v>25.7417</v>
       </c>
       <c r="F25" t="n">
-        <v>44.4009</v>
+        <v>40.4998</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>30.5636</v>
+        <v>27.4878</v>
       </c>
       <c r="C26" t="n">
-        <v>48.2071</v>
+        <v>29.6774</v>
       </c>
       <c r="D26" t="n">
-        <v>69.9436</v>
+        <v>68.6121</v>
       </c>
       <c r="E26" t="n">
-        <v>26.6729</v>
+        <v>24.873</v>
       </c>
       <c r="F26" t="n">
-        <v>43.5326</v>
+        <v>39.7246</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>29.3422</v>
+        <v>26.9574</v>
       </c>
       <c r="C27" t="n">
-        <v>47.2231</v>
+        <v>28.9993</v>
       </c>
       <c r="D27" t="n">
-        <v>68.9449</v>
+        <v>67.6579</v>
       </c>
       <c r="E27" t="n">
-        <v>25.9269</v>
+        <v>24.1193</v>
       </c>
       <c r="F27" t="n">
-        <v>42.6114</v>
+        <v>38.8999</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>28.3717</v>
+        <v>26.095</v>
       </c>
       <c r="C28" t="n">
-        <v>46.2542</v>
+        <v>28.2208</v>
       </c>
       <c r="D28" t="n">
-        <v>67.94929999999999</v>
+        <v>66.5275</v>
       </c>
       <c r="E28" t="n">
-        <v>25.1118</v>
+        <v>23.3228</v>
       </c>
       <c r="F28" t="n">
-        <v>41.8227</v>
+        <v>38.199</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>28.3026</v>
+        <v>25.6295</v>
       </c>
       <c r="C29" t="n">
-        <v>45.5909</v>
+        <v>27.6032</v>
       </c>
       <c r="D29" t="n">
-        <v>67.23779999999999</v>
+        <v>65.87739999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2116</v>
+        <v>22.6967</v>
       </c>
       <c r="F29" t="n">
-        <v>41.3369</v>
+        <v>37.5494</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>27.3852</v>
+        <v>24.3794</v>
       </c>
       <c r="C30" t="n">
-        <v>44.65</v>
+        <v>26.9297</v>
       </c>
       <c r="D30" t="n">
-        <v>66.3289</v>
+        <v>65.0548</v>
       </c>
       <c r="E30" t="n">
-        <v>23.5148</v>
+        <v>22.0813</v>
       </c>
       <c r="F30" t="n">
-        <v>40.8158</v>
+        <v>36.9483</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>26.0195</v>
+        <v>24.1833</v>
       </c>
       <c r="C31" t="n">
-        <v>43.9441</v>
+        <v>26.3784</v>
       </c>
       <c r="D31" t="n">
-        <v>65.7471</v>
+        <v>64.5689</v>
       </c>
       <c r="E31" t="n">
-        <v>22.8742</v>
+        <v>21.4797</v>
       </c>
       <c r="F31" t="n">
-        <v>40.1959</v>
+        <v>36.4158</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.3843</v>
+        <v>23.1349</v>
       </c>
       <c r="C32" t="n">
-        <v>43.4102</v>
+        <v>25.8462</v>
       </c>
       <c r="D32" t="n">
-        <v>65.5063</v>
+        <v>64.0545</v>
       </c>
       <c r="E32" t="n">
-        <v>22.3127</v>
+        <v>20.9592</v>
       </c>
       <c r="F32" t="n">
-        <v>39.6669</v>
+        <v>35.9897</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.6577</v>
+        <v>22.9916</v>
       </c>
       <c r="C33" t="n">
-        <v>42.7759</v>
+        <v>25.3766</v>
       </c>
       <c r="D33" t="n">
-        <v>64.79049999999999</v>
+        <v>63.7146</v>
       </c>
       <c r="E33" t="n">
-        <v>21.8229</v>
+        <v>20.4734</v>
       </c>
       <c r="F33" t="n">
-        <v>39.6183</v>
+        <v>35.5363</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.6854</v>
+        <v>22.567</v>
       </c>
       <c r="C34" t="n">
-        <v>42.3548</v>
+        <v>24.9378</v>
       </c>
       <c r="D34" t="n">
-        <v>64.19889999999999</v>
+        <v>62.7489</v>
       </c>
       <c r="E34" t="n">
-        <v>21.4329</v>
+        <v>20.1561</v>
       </c>
       <c r="F34" t="n">
-        <v>39.0607</v>
+        <v>35.1992</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.8746</v>
+        <v>22.0409</v>
       </c>
       <c r="C35" t="n">
-        <v>42.3207</v>
+        <v>24.5716</v>
       </c>
       <c r="D35" t="n">
-        <v>82.6816</v>
+        <v>81.2471</v>
       </c>
       <c r="E35" t="n">
-        <v>21.1731</v>
+        <v>19.9346</v>
       </c>
       <c r="F35" t="n">
-        <v>38.9119</v>
+        <v>35.1297</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.4551</v>
+        <v>21.6053</v>
       </c>
       <c r="C36" t="n">
-        <v>41.4888</v>
+        <v>24.2764</v>
       </c>
       <c r="D36" t="n">
-        <v>80.9297</v>
+        <v>79.4748</v>
       </c>
       <c r="E36" t="n">
-        <v>21.2399</v>
+        <v>19.824</v>
       </c>
       <c r="F36" t="n">
-        <v>38.8989</v>
+        <v>34.9167</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.4835</v>
+        <v>21.6157</v>
       </c>
       <c r="C37" t="n">
-        <v>41.3417</v>
+        <v>32.805</v>
       </c>
       <c r="D37" t="n">
-        <v>79.29340000000001</v>
+        <v>77.9415</v>
       </c>
       <c r="E37" t="n">
-        <v>30.4967</v>
+        <v>28.7308</v>
       </c>
       <c r="F37" t="n">
-        <v>47.7575</v>
+        <v>43.1991</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>32.4391</v>
+        <v>29.831</v>
       </c>
       <c r="C38" t="n">
-        <v>51.2495</v>
+        <v>32.0419</v>
       </c>
       <c r="D38" t="n">
-        <v>77.90940000000001</v>
+        <v>76.3518</v>
       </c>
       <c r="E38" t="n">
-        <v>29.5006</v>
+        <v>27.854</v>
       </c>
       <c r="F38" t="n">
-        <v>46.8662</v>
+        <v>42.3764</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>31.778</v>
+        <v>28.9144</v>
       </c>
       <c r="C39" t="n">
-        <v>50.167</v>
+        <v>31.3786</v>
       </c>
       <c r="D39" t="n">
-        <v>76.4084</v>
+        <v>75.17440000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>28.6515</v>
+        <v>26.7761</v>
       </c>
       <c r="F39" t="n">
-        <v>45.8871</v>
+        <v>41.5157</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>30.9971</v>
+        <v>27.948</v>
       </c>
       <c r="C40" t="n">
-        <v>49.3471</v>
+        <v>30.573</v>
       </c>
       <c r="D40" t="n">
-        <v>75.1478</v>
+        <v>73.8785</v>
       </c>
       <c r="E40" t="n">
-        <v>27.6826</v>
+        <v>25.9662</v>
       </c>
       <c r="F40" t="n">
-        <v>44.8166</v>
+        <v>41.0786</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>29.9723</v>
+        <v>27.3259</v>
       </c>
       <c r="C41" t="n">
-        <v>48.2695</v>
+        <v>29.9709</v>
       </c>
       <c r="D41" t="n">
-        <v>73.86579999999999</v>
+        <v>72.5873</v>
       </c>
       <c r="E41" t="n">
-        <v>26.7791</v>
+        <v>25.1799</v>
       </c>
       <c r="F41" t="n">
-        <v>43.952</v>
+        <v>40.6134</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>29.424</v>
+        <v>26.1604</v>
       </c>
       <c r="C42" t="n">
-        <v>47.807</v>
+        <v>29.3068</v>
       </c>
       <c r="D42" t="n">
-        <v>72.9477</v>
+        <v>71.8244</v>
       </c>
       <c r="E42" t="n">
-        <v>26.0056</v>
+        <v>24.4673</v>
       </c>
       <c r="F42" t="n">
-        <v>43.0007</v>
+        <v>39.647</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>28.59</v>
+        <v>25.7887</v>
       </c>
       <c r="C43" t="n">
-        <v>47.0449</v>
+        <v>28.7671</v>
       </c>
       <c r="D43" t="n">
-        <v>71.9226</v>
+        <v>70.556</v>
       </c>
       <c r="E43" t="n">
-        <v>25.2565</v>
+        <v>23.7262</v>
       </c>
       <c r="F43" t="n">
-        <v>42.1553</v>
+        <v>38.8831</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>28.1655</v>
+        <v>25.6772</v>
       </c>
       <c r="C44" t="n">
-        <v>46.2968</v>
+        <v>28.1519</v>
       </c>
       <c r="D44" t="n">
-        <v>71.0671</v>
+        <v>69.8647</v>
       </c>
       <c r="E44" t="n">
-        <v>24.561</v>
+        <v>23.2409</v>
       </c>
       <c r="F44" t="n">
-        <v>41.4517</v>
+        <v>38.3048</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>27.2817</v>
+        <v>24.3356</v>
       </c>
       <c r="C45" t="n">
-        <v>45.4653</v>
+        <v>27.6204</v>
       </c>
       <c r="D45" t="n">
-        <v>70.3212</v>
+        <v>69.1857</v>
       </c>
       <c r="E45" t="n">
-        <v>23.9202</v>
+        <v>22.5074</v>
       </c>
       <c r="F45" t="n">
-        <v>40.8285</v>
+        <v>37.4818</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>27.2595</v>
+        <v>24.9492</v>
       </c>
       <c r="C46" t="n">
-        <v>44.7184</v>
+        <v>27.1089</v>
       </c>
       <c r="D46" t="n">
-        <v>69.6658</v>
+        <v>68.58929999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>23.3226</v>
+        <v>21.9941</v>
       </c>
       <c r="F46" t="n">
-        <v>40.3664</v>
+        <v>37.0315</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>25.6294</v>
+        <v>24.0494</v>
       </c>
       <c r="C47" t="n">
-        <v>44.2619</v>
+        <v>26.475</v>
       </c>
       <c r="D47" t="n">
-        <v>69.1289</v>
+        <v>68.1266</v>
       </c>
       <c r="E47" t="n">
-        <v>22.7868</v>
+        <v>21.5266</v>
       </c>
       <c r="F47" t="n">
-        <v>39.9171</v>
+        <v>36.615</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>25.5338</v>
+        <v>23.3229</v>
       </c>
       <c r="C48" t="n">
-        <v>43.6192</v>
+        <v>26.0786</v>
       </c>
       <c r="D48" t="n">
-        <v>68.60890000000001</v>
+        <v>67.42700000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>22.3338</v>
+        <v>21.1534</v>
       </c>
       <c r="F48" t="n">
-        <v>39.6295</v>
+        <v>36.3054</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>24.3155</v>
+        <v>23.0748</v>
       </c>
       <c r="C49" t="n">
-        <v>43.1849</v>
+        <v>25.8577</v>
       </c>
       <c r="D49" t="n">
-        <v>68.2616</v>
+        <v>67.01390000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>22.0784</v>
+        <v>20.8879</v>
       </c>
       <c r="F49" t="n">
-        <v>39.4354</v>
+        <v>36.0212</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>24.747</v>
+        <v>22.0871</v>
       </c>
       <c r="C50" t="n">
-        <v>42.848</v>
+        <v>25.5713</v>
       </c>
       <c r="D50" t="n">
-        <v>85.6953</v>
+        <v>84.27509999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>21.9125</v>
+        <v>20.7177</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4139</v>
+        <v>36.0404</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>24.0854</v>
+        <v>22.539</v>
       </c>
       <c r="C51" t="n">
-        <v>42.7201</v>
+        <v>34.0587</v>
       </c>
       <c r="D51" t="n">
-        <v>83.9622</v>
+        <v>82.6862</v>
       </c>
       <c r="E51" t="n">
-        <v>31.7112</v>
+        <v>29.8984</v>
       </c>
       <c r="F51" t="n">
-        <v>48.7533</v>
+        <v>45.2972</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>24.7438</v>
+        <v>22.3596</v>
       </c>
       <c r="C52" t="n">
-        <v>42.6018</v>
+        <v>33.4281</v>
       </c>
       <c r="D52" t="n">
-        <v>82.3749</v>
+        <v>81.0198</v>
       </c>
       <c r="E52" t="n">
-        <v>30.7706</v>
+        <v>28.9505</v>
       </c>
       <c r="F52" t="n">
-        <v>47.8528</v>
+        <v>44.332</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>33.4921</v>
+        <v>30.6619</v>
       </c>
       <c r="C53" t="n">
-        <v>52.7188</v>
+        <v>32.8591</v>
       </c>
       <c r="D53" t="n">
-        <v>80.7726</v>
+        <v>79.58410000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>29.8216</v>
+        <v>28.5168</v>
       </c>
       <c r="F53" t="n">
-        <v>46.9044</v>
+        <v>43.5665</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>32.4814</v>
+        <v>29.4638</v>
       </c>
       <c r="C54" t="n">
-        <v>51.883</v>
+        <v>32.1337</v>
       </c>
       <c r="D54" t="n">
-        <v>79.43859999999999</v>
+        <v>78.22920000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>29.0609</v>
+        <v>27.5416</v>
       </c>
       <c r="F54" t="n">
-        <v>46.0277</v>
+        <v>42.7679</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>31.2558</v>
+        <v>29.0458</v>
       </c>
       <c r="C55" t="n">
-        <v>50.9596</v>
+        <v>31.5838</v>
       </c>
       <c r="D55" t="n">
-        <v>78.2073</v>
+        <v>76.9434</v>
       </c>
       <c r="E55" t="n">
-        <v>28.1718</v>
+        <v>26.5611</v>
       </c>
       <c r="F55" t="n">
-        <v>45.1148</v>
+        <v>42.0276</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>30.3511</v>
+        <v>27.6301</v>
       </c>
       <c r="C56" t="n">
-        <v>50.2692</v>
+        <v>30.8023</v>
       </c>
       <c r="D56" t="n">
-        <v>77.0476</v>
+        <v>75.9241</v>
       </c>
       <c r="E56" t="n">
-        <v>27.3487</v>
+        <v>25.6747</v>
       </c>
       <c r="F56" t="n">
-        <v>44.4719</v>
+        <v>41.1871</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>29.8691</v>
+        <v>27.3041</v>
       </c>
       <c r="C57" t="n">
-        <v>49.3509</v>
+        <v>30.3317</v>
       </c>
       <c r="D57" t="n">
-        <v>75.8967</v>
+        <v>74.7608</v>
       </c>
       <c r="E57" t="n">
-        <v>26.6247</v>
+        <v>25.0522</v>
       </c>
       <c r="F57" t="n">
-        <v>43.5627</v>
+        <v>40.7161</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.9213</v>
+        <v>26.9208</v>
       </c>
       <c r="C58" t="n">
-        <v>48.4058</v>
+        <v>29.7647</v>
       </c>
       <c r="D58" t="n">
-        <v>74.9405</v>
+        <v>74.0911</v>
       </c>
       <c r="E58" t="n">
-        <v>25.9673</v>
+        <v>24.4889</v>
       </c>
       <c r="F58" t="n">
-        <v>42.9518</v>
+        <v>40.0966</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.8605</v>
+        <v>26.0511</v>
       </c>
       <c r="C59" t="n">
-        <v>47.7399</v>
+        <v>29.2287</v>
       </c>
       <c r="D59" t="n">
-        <v>74.1263</v>
+        <v>73.0108</v>
       </c>
       <c r="E59" t="n">
-        <v>25.232</v>
+        <v>23.8807</v>
       </c>
       <c r="F59" t="n">
-        <v>42.2698</v>
+        <v>39.5909</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>27.0413</v>
+        <v>25.2036</v>
       </c>
       <c r="C60" t="n">
-        <v>47.1785</v>
+        <v>28.5737</v>
       </c>
       <c r="D60" t="n">
-        <v>73.4654</v>
+        <v>72.5744</v>
       </c>
       <c r="E60" t="n">
-        <v>24.7379</v>
+        <v>23.526</v>
       </c>
       <c r="F60" t="n">
-        <v>41.7305</v>
+        <v>39.0607</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.6164</v>
+        <v>25.06</v>
       </c>
       <c r="C61" t="n">
-        <v>46.6129</v>
+        <v>28.3179</v>
       </c>
       <c r="D61" t="n">
-        <v>72.6348</v>
+        <v>71.6361</v>
       </c>
       <c r="E61" t="n">
-        <v>24.0682</v>
+        <v>23.07</v>
       </c>
       <c r="F61" t="n">
-        <v>41.3269</v>
+        <v>38.6967</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.4174</v>
+        <v>24.3299</v>
       </c>
       <c r="C62" t="n">
-        <v>46.0561</v>
+        <v>27.7562</v>
       </c>
       <c r="D62" t="n">
-        <v>72.053</v>
+        <v>71.02370000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>23.7687</v>
+        <v>22.4173</v>
       </c>
       <c r="F62" t="n">
-        <v>40.9107</v>
+        <v>38.414</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>26.0025</v>
+        <v>23.9949</v>
       </c>
       <c r="C63" t="n">
-        <v>45.5291</v>
+        <v>27.3967</v>
       </c>
       <c r="D63" t="n">
-        <v>71.45189999999999</v>
+        <v>70.5359</v>
       </c>
       <c r="E63" t="n">
-        <v>23.3927</v>
+        <v>22.273</v>
       </c>
       <c r="F63" t="n">
-        <v>40.6288</v>
+        <v>38.3677</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.4005</v>
+        <v>23.6307</v>
       </c>
       <c r="C64" t="n">
-        <v>45.1824</v>
+        <v>27.3454</v>
       </c>
       <c r="D64" t="n">
-        <v>92.30419999999999</v>
+        <v>91.46169999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>23.1511</v>
+        <v>21.936</v>
       </c>
       <c r="F64" t="n">
-        <v>40.5925</v>
+        <v>38.246</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.1058</v>
+        <v>23.629</v>
       </c>
       <c r="C65" t="n">
-        <v>45.1557</v>
+        <v>37.0477</v>
       </c>
       <c r="D65" t="n">
-        <v>90.4376</v>
+        <v>89.88509999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>23.2597</v>
+        <v>22.1738</v>
       </c>
       <c r="F65" t="n">
-        <v>40.8185</v>
+        <v>38.4061</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.3653</v>
+        <v>23.3531</v>
       </c>
       <c r="C66" t="n">
-        <v>45.3325</v>
+        <v>36.2636</v>
       </c>
       <c r="D66" t="n">
-        <v>88.67959999999999</v>
+        <v>88.0257</v>
       </c>
       <c r="E66" t="n">
-        <v>35.5814</v>
+        <v>34.5632</v>
       </c>
       <c r="F66" t="n">
-        <v>51.7682</v>
+        <v>48.5341</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>40.9538</v>
+        <v>41.4774</v>
       </c>
       <c r="C67" t="n">
-        <v>61.4325</v>
+        <v>35.6639</v>
       </c>
       <c r="D67" t="n">
-        <v>87.18519999999999</v>
+        <v>86.10680000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>34.325</v>
+        <v>33.6216</v>
       </c>
       <c r="F67" t="n">
-        <v>51.2002</v>
+        <v>47.9436</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.1023</v>
+        <v>37.7614</v>
       </c>
       <c r="C68" t="n">
-        <v>60.7015</v>
+        <v>35.2219</v>
       </c>
       <c r="D68" t="n">
-        <v>85.49250000000001</v>
+        <v>84.8599</v>
       </c>
       <c r="E68" t="n">
-        <v>33.6202</v>
+        <v>32.7812</v>
       </c>
       <c r="F68" t="n">
-        <v>50.6211</v>
+        <v>47.3921</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>38.0945</v>
+        <v>37.4995</v>
       </c>
       <c r="C69" t="n">
-        <v>59.7455</v>
+        <v>34.9647</v>
       </c>
       <c r="D69" t="n">
-        <v>84.3809</v>
+        <v>83.08580000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>32.5891</v>
+        <v>31.9774</v>
       </c>
       <c r="F69" t="n">
-        <v>49.9472</v>
+        <v>46.2507</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>38.8467</v>
+        <v>37.7612</v>
       </c>
       <c r="C70" t="n">
-        <v>59.1388</v>
+        <v>34.6632</v>
       </c>
       <c r="D70" t="n">
-        <v>83.2788</v>
+        <v>81.9395</v>
       </c>
       <c r="E70" t="n">
-        <v>31.9186</v>
+        <v>31.1227</v>
       </c>
       <c r="F70" t="n">
-        <v>49.1811</v>
+        <v>46.0535</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>37.1091</v>
+        <v>35.5738</v>
       </c>
       <c r="C71" t="n">
-        <v>58.4558</v>
+        <v>34.3745</v>
       </c>
       <c r="D71" t="n">
-        <v>82.4577</v>
+        <v>81.2754</v>
       </c>
       <c r="E71" t="n">
-        <v>31.0039</v>
+        <v>30.6093</v>
       </c>
       <c r="F71" t="n">
-        <v>48.4413</v>
+        <v>45.3781</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.2916</v>
+        <v>36.1842</v>
       </c>
       <c r="C72" t="n">
-        <v>57.4812</v>
+        <v>34.0235</v>
       </c>
       <c r="D72" t="n">
-        <v>81.875</v>
+        <v>80.60290000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>30.1208</v>
+        <v>29.9707</v>
       </c>
       <c r="F72" t="n">
-        <v>47.8906</v>
+        <v>44.8571</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>34.3132</v>
+        <v>36.1182</v>
       </c>
       <c r="C73" t="n">
-        <v>56.8107</v>
+        <v>33.5817</v>
       </c>
       <c r="D73" t="n">
-        <v>81.8317</v>
+        <v>80.5099</v>
       </c>
       <c r="E73" t="n">
-        <v>29.7005</v>
+        <v>29.2892</v>
       </c>
       <c r="F73" t="n">
-        <v>47.3093</v>
+        <v>44.3619</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>34.2879</v>
+        <v>33.1063</v>
       </c>
       <c r="C74" t="n">
-        <v>56.3192</v>
+        <v>33.4002</v>
       </c>
       <c r="D74" t="n">
-        <v>81.3386</v>
+        <v>80.2373</v>
       </c>
       <c r="E74" t="n">
-        <v>28.8857</v>
+        <v>28.7123</v>
       </c>
       <c r="F74" t="n">
-        <v>46.7514</v>
+        <v>43.8902</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>36.1179</v>
+        <v>32.6904</v>
       </c>
       <c r="C75" t="n">
-        <v>55.6696</v>
+        <v>33.2159</v>
       </c>
       <c r="D75" t="n">
-        <v>80.8323</v>
+        <v>78.9396</v>
       </c>
       <c r="E75" t="n">
-        <v>28.5797</v>
+        <v>28.2407</v>
       </c>
       <c r="F75" t="n">
-        <v>46.2518</v>
+        <v>43.5131</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>35.4353</v>
+        <v>31.985</v>
       </c>
       <c r="C76" t="n">
-        <v>55.1569</v>
+        <v>32.7188</v>
       </c>
       <c r="D76" t="n">
-        <v>80.7967</v>
+        <v>78.9936</v>
       </c>
       <c r="E76" t="n">
-        <v>27.8944</v>
+        <v>27.702</v>
       </c>
       <c r="F76" t="n">
-        <v>45.9044</v>
+        <v>43.2851</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.242</v>
+        <v>32.006</v>
       </c>
       <c r="C77" t="n">
-        <v>54.9788</v>
+        <v>32.4308</v>
       </c>
       <c r="D77" t="n">
-        <v>81.0899</v>
+        <v>79.1074</v>
       </c>
       <c r="E77" t="n">
-        <v>27.6512</v>
+        <v>27.3609</v>
       </c>
       <c r="F77" t="n">
-        <v>45.6749</v>
+        <v>43.162</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.4697</v>
+        <v>32.9198</v>
       </c>
       <c r="C78" t="n">
-        <v>54.6275</v>
+        <v>32.1055</v>
       </c>
       <c r="D78" t="n">
-        <v>130.598</v>
+        <v>129.291</v>
       </c>
       <c r="E78" t="n">
-        <v>27.1586</v>
+        <v>27.0037</v>
       </c>
       <c r="F78" t="n">
-        <v>45.5745</v>
+        <v>43.0763</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>32.7365</v>
+        <v>31.713</v>
       </c>
       <c r="C79" t="n">
-        <v>54.7109</v>
+        <v>42.1969</v>
       </c>
       <c r="D79" t="n">
-        <v>128.437</v>
+        <v>127.068</v>
       </c>
       <c r="E79" t="n">
-        <v>27.2633</v>
+        <v>26.8836</v>
       </c>
       <c r="F79" t="n">
-        <v>45.6865</v>
+        <v>43.2751</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>33.5617</v>
+        <v>31.6675</v>
       </c>
       <c r="C80" t="n">
-        <v>54.4357</v>
+        <v>42.9679</v>
       </c>
       <c r="D80" t="n">
-        <v>126.654</v>
+        <v>124.931</v>
       </c>
       <c r="E80" t="n">
-        <v>42.8842</v>
+        <v>42.9688</v>
       </c>
       <c r="F80" t="n">
-        <v>75.1378</v>
+        <v>70.03959999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>46.6824</v>
+        <v>45.1475</v>
       </c>
       <c r="C81" t="n">
-        <v>90.2311</v>
+        <v>43.3601</v>
       </c>
       <c r="D81" t="n">
-        <v>124.844</v>
+        <v>123.43</v>
       </c>
       <c r="E81" t="n">
-        <v>42.3972</v>
+        <v>42.5992</v>
       </c>
       <c r="F81" t="n">
-        <v>76.72490000000001</v>
+        <v>70.87909999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>46.7125</v>
+        <v>39.7614</v>
       </c>
       <c r="C82" t="n">
-        <v>92.1811</v>
+        <v>43.6142</v>
       </c>
       <c r="D82" t="n">
-        <v>123.467</v>
+        <v>122.943</v>
       </c>
       <c r="E82" t="n">
-        <v>41.6646</v>
+        <v>41.7245</v>
       </c>
       <c r="F82" t="n">
-        <v>76.5956</v>
+        <v>70.3047</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>43.7176</v>
+        <v>43.2805</v>
       </c>
       <c r="C83" t="n">
-        <v>90.83459999999999</v>
+        <v>44.0344</v>
       </c>
       <c r="D83" t="n">
-        <v>122.359</v>
+        <v>122.006</v>
       </c>
       <c r="E83" t="n">
-        <v>40.5787</v>
+        <v>40.7714</v>
       </c>
       <c r="F83" t="n">
-        <v>75.685</v>
+        <v>69.2903</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>45.0354</v>
+        <v>42.6612</v>
       </c>
       <c r="C84" t="n">
-        <v>90.70869999999999</v>
+        <v>44.1724</v>
       </c>
       <c r="D84" t="n">
-        <v>121.853</v>
+        <v>121.315</v>
       </c>
       <c r="E84" t="n">
-        <v>39.8746</v>
+        <v>40.0211</v>
       </c>
       <c r="F84" t="n">
-        <v>74.1157</v>
+        <v>68.2466</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>43.8591</v>
+        <v>44.4629</v>
       </c>
       <c r="C85" t="n">
-        <v>89.13120000000001</v>
+        <v>44.1799</v>
       </c>
       <c r="D85" t="n">
-        <v>121.181</v>
+        <v>121.323</v>
       </c>
       <c r="E85" t="n">
-        <v>38.9207</v>
+        <v>39.1326</v>
       </c>
       <c r="F85" t="n">
-        <v>72.82810000000001</v>
+        <v>67.1046</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>44.7823</v>
+        <v>44.6037</v>
       </c>
       <c r="C86" t="n">
-        <v>87.64490000000001</v>
+        <v>44.3595</v>
       </c>
       <c r="D86" t="n">
-        <v>121.091</v>
+        <v>121.315</v>
       </c>
       <c r="E86" t="n">
-        <v>38.0336</v>
+        <v>38.1551</v>
       </c>
       <c r="F86" t="n">
-        <v>71.36360000000001</v>
+        <v>65.7795</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>46.0224</v>
+        <v>39.6804</v>
       </c>
       <c r="C87" t="n">
-        <v>86.43899999999999</v>
+        <v>43.9088</v>
       </c>
       <c r="D87" t="n">
-        <v>121.747</v>
+        <v>121.301</v>
       </c>
       <c r="E87" t="n">
-        <v>37.2117</v>
+        <v>37.551</v>
       </c>
       <c r="F87" t="n">
-        <v>70.0658</v>
+        <v>64.9894</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>41.5491</v>
+        <v>41.2426</v>
       </c>
       <c r="C88" t="n">
-        <v>85.31359999999999</v>
+        <v>43.3167</v>
       </c>
       <c r="D88" t="n">
-        <v>121.663</v>
+        <v>121.627</v>
       </c>
       <c r="E88" t="n">
-        <v>36.4375</v>
+        <v>36.6122</v>
       </c>
       <c r="F88" t="n">
-        <v>68.8398</v>
+        <v>63.5952</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>42.9138</v>
+        <v>38.8768</v>
       </c>
       <c r="C89" t="n">
-        <v>83.8656</v>
+        <v>42.5463</v>
       </c>
       <c r="D89" t="n">
-        <v>122.751</v>
+        <v>120.425</v>
       </c>
       <c r="E89" t="n">
-        <v>35.6909</v>
+        <v>34.1097</v>
       </c>
       <c r="F89" t="n">
-        <v>67.7586</v>
+        <v>61.638</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>43.3241</v>
+        <v>38.8805</v>
       </c>
       <c r="C90" t="n">
-        <v>82.6375</v>
+        <v>42.9602</v>
       </c>
       <c r="D90" t="n">
-        <v>123.989</v>
+        <v>122.03</v>
       </c>
       <c r="E90" t="n">
-        <v>34.9046</v>
+        <v>33.7253</v>
       </c>
       <c r="F90" t="n">
-        <v>66.4276</v>
+        <v>61.1623</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>40.1084</v>
+        <v>38.1283</v>
       </c>
       <c r="C91" t="n">
-        <v>81.9859</v>
+        <v>42.6926</v>
       </c>
       <c r="D91" t="n">
-        <v>125.384</v>
+        <v>123.332</v>
       </c>
       <c r="E91" t="n">
-        <v>34.309</v>
+        <v>33.0671</v>
       </c>
       <c r="F91" t="n">
-        <v>65.5201</v>
+        <v>61.0827</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>40.1601</v>
+        <v>37.731</v>
       </c>
       <c r="C92" t="n">
-        <v>80.8947</v>
+        <v>42.4632</v>
       </c>
       <c r="D92" t="n">
-        <v>186.345</v>
+        <v>184.143</v>
       </c>
       <c r="E92" t="n">
-        <v>33.8049</v>
+        <v>32.1436</v>
       </c>
       <c r="F92" t="n">
-        <v>64.57380000000001</v>
+        <v>60.1271</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>39.4582</v>
+        <v>35.9448</v>
       </c>
       <c r="C93" t="n">
-        <v>80.2002</v>
+        <v>42.3889</v>
       </c>
       <c r="D93" t="n">
-        <v>185.902</v>
+        <v>183.719</v>
       </c>
       <c r="E93" t="n">
-        <v>33.4024</v>
+        <v>32.2704</v>
       </c>
       <c r="F93" t="n">
-        <v>64.75369999999999</v>
+        <v>59.3226</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>38.4131</v>
+        <v>37.0673</v>
       </c>
       <c r="C94" t="n">
-        <v>79.6285</v>
+        <v>75.2766</v>
       </c>
       <c r="D94" t="n">
-        <v>184.877</v>
+        <v>182.394</v>
       </c>
       <c r="E94" t="n">
-        <v>54.799</v>
+        <v>63.5378</v>
       </c>
       <c r="F94" t="n">
-        <v>118.875</v>
+        <v>117.858</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>59.8165</v>
+        <v>69.7568</v>
       </c>
       <c r="C95" t="n">
-        <v>129.153</v>
+        <v>75.40430000000001</v>
       </c>
       <c r="D95" t="n">
-        <v>183.592</v>
+        <v>181.404</v>
       </c>
       <c r="E95" t="n">
-        <v>54.2785</v>
+        <v>62.6033</v>
       </c>
       <c r="F95" t="n">
-        <v>118.712</v>
+        <v>116.641</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>61.1444</v>
+        <v>68.3663</v>
       </c>
       <c r="C96" t="n">
-        <v>127.891</v>
+        <v>74.6913</v>
       </c>
       <c r="D96" t="n">
-        <v>183.241</v>
+        <v>180.268</v>
       </c>
       <c r="E96" t="n">
-        <v>52.9125</v>
+        <v>60.9498</v>
       </c>
       <c r="F96" t="n">
-        <v>117.434</v>
+        <v>114.932</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>60.2784</v>
+        <v>66.63590000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>127.661</v>
+        <v>73.7413</v>
       </c>
       <c r="D97" t="n">
-        <v>182.047</v>
+        <v>179.575</v>
       </c>
       <c r="E97" t="n">
-        <v>51.9756</v>
+        <v>59.5133</v>
       </c>
       <c r="F97" t="n">
-        <v>115.795</v>
+        <v>112.231</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>57.9241</v>
+        <v>64.62479999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>125.024</v>
+        <v>73.0979</v>
       </c>
       <c r="D98" t="n">
-        <v>181.3</v>
+        <v>179.562</v>
       </c>
       <c r="E98" t="n">
-        <v>50.5038</v>
+        <v>57.7507</v>
       </c>
       <c r="F98" t="n">
-        <v>113.883</v>
+        <v>109.939</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>55.8888</v>
+        <v>64.1641</v>
       </c>
       <c r="C99" t="n">
-        <v>122.481</v>
+        <v>72.24760000000001</v>
       </c>
       <c r="D99" t="n">
-        <v>180.97</v>
+        <v>179.718</v>
       </c>
       <c r="E99" t="n">
-        <v>49.3891</v>
+        <v>56.1934</v>
       </c>
       <c r="F99" t="n">
-        <v>111.939</v>
+        <v>107.996</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>55.8178</v>
+        <v>61.18</v>
       </c>
       <c r="C100" t="n">
-        <v>120.826</v>
+        <v>71.49160000000001</v>
       </c>
       <c r="D100" t="n">
-        <v>180.893</v>
+        <v>179.781</v>
       </c>
       <c r="E100" t="n">
-        <v>48.3737</v>
+        <v>54.8333</v>
       </c>
       <c r="F100" t="n">
-        <v>110.501</v>
+        <v>106.515</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>55.042</v>
+        <v>60.2753</v>
       </c>
       <c r="C101" t="n">
-        <v>119.461</v>
+        <v>70.68389999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>181.616</v>
+        <v>179.767</v>
       </c>
       <c r="E101" t="n">
-        <v>47.2207</v>
+        <v>53.5763</v>
       </c>
       <c r="F101" t="n">
-        <v>108.638</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>55.0762</v>
+        <v>59.4749</v>
       </c>
       <c r="C102" t="n">
-        <v>119.619</v>
+        <v>70.0904</v>
       </c>
       <c r="D102" t="n">
-        <v>182.209</v>
+        <v>180.723</v>
       </c>
       <c r="E102" t="n">
-        <v>46.3183</v>
+        <v>52.2299</v>
       </c>
       <c r="F102" t="n">
-        <v>107.107</v>
+        <v>103.744</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>51.8503</v>
+        <v>58.9262</v>
       </c>
       <c r="C103" t="n">
-        <v>115.956</v>
+        <v>69.2676</v>
       </c>
       <c r="D103" t="n">
-        <v>183.499</v>
+        <v>182.016</v>
       </c>
       <c r="E103" t="n">
-        <v>45.3979</v>
+        <v>50.9843</v>
       </c>
       <c r="F103" t="n">
-        <v>105.781</v>
+        <v>103.204</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>50.8827</v>
+        <v>56.9001</v>
       </c>
       <c r="C104" t="n">
-        <v>114.904</v>
+        <v>68.63939999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>184.723</v>
+        <v>183.113</v>
       </c>
       <c r="E104" t="n">
-        <v>44.5701</v>
+        <v>49.8365</v>
       </c>
       <c r="F104" t="n">
-        <v>102.649</v>
+        <v>98.30549999999999</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>52.5057</v>
+        <v>56.5388</v>
       </c>
       <c r="C105" t="n">
-        <v>115.009</v>
+        <v>68.1675</v>
       </c>
       <c r="D105" t="n">
-        <v>186.338</v>
+        <v>184.755</v>
       </c>
       <c r="E105" t="n">
-        <v>43.8262</v>
+        <v>48.7927</v>
       </c>
       <c r="F105" t="n">
-        <v>102.875</v>
+        <v>97.0549</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>50.6933</v>
+        <v>55.4845</v>
       </c>
       <c r="C106" t="n">
-        <v>114.264</v>
+        <v>67.49720000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>188.073</v>
+        <v>186.031</v>
       </c>
       <c r="E106" t="n">
-        <v>43.0906</v>
+        <v>48.0078</v>
       </c>
       <c r="F106" t="n">
-        <v>100.472</v>
+        <v>97.8077</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>50.1437</v>
+        <v>55.8497</v>
       </c>
       <c r="C107" t="n">
-        <v>112.914</v>
+        <v>66.9967</v>
       </c>
       <c r="D107" t="n">
-        <v>252.685</v>
+        <v>250.126</v>
       </c>
       <c r="E107" t="n">
-        <v>42.5652</v>
+        <v>47.0954</v>
       </c>
       <c r="F107" t="n">
-        <v>98.4423</v>
+        <v>100.269</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>49.6432</v>
+        <v>53.5732</v>
       </c>
       <c r="C108" t="n">
-        <v>112.276</v>
+        <v>101.615</v>
       </c>
       <c r="D108" t="n">
-        <v>250.116</v>
+        <v>245.403</v>
       </c>
       <c r="E108" t="n">
-        <v>64.92910000000001</v>
+        <v>80.1908</v>
       </c>
       <c r="F108" t="n">
-        <v>264.75</v>
+        <v>249.405</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>49.2711</v>
+        <v>55.2626</v>
       </c>
       <c r="C109" t="n">
-        <v>111.597</v>
+        <v>100.158</v>
       </c>
       <c r="D109" t="n">
-        <v>247.706</v>
+        <v>243.905</v>
       </c>
       <c r="E109" t="n">
-        <v>64.2546</v>
+        <v>68.1611</v>
       </c>
       <c r="F109" t="n">
-        <v>266.384</v>
+        <v>250.537</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>73.785</v>
+        <v>85.58199999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>290.058</v>
+        <v>99.2634</v>
       </c>
       <c r="D110" t="n">
-        <v>245.886</v>
+        <v>241.893</v>
       </c>
       <c r="E110" t="n">
-        <v>62.8088</v>
+        <v>76.7495</v>
       </c>
       <c r="F110" t="n">
-        <v>266.701</v>
+        <v>249.769</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>70.9776</v>
+        <v>84.654</v>
       </c>
       <c r="C111" t="n">
-        <v>290.647</v>
+        <v>97.7055</v>
       </c>
       <c r="D111" t="n">
-        <v>244.371</v>
+        <v>242.847</v>
       </c>
       <c r="E111" t="n">
-        <v>57.436</v>
+        <v>74.74939999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>267.289</v>
+        <v>250.92</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>69.931</v>
+        <v>76.30929999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>290.057</v>
+        <v>84.753</v>
       </c>
       <c r="D112" t="n">
-        <v>242.869</v>
+        <v>239.415</v>
       </c>
       <c r="E112" t="n">
-        <v>56.2648</v>
+        <v>63.5683</v>
       </c>
       <c r="F112" t="n">
-        <v>268.449</v>
+        <v>250.632</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>69.49720000000001</v>
+        <v>81.01739999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>290.376</v>
+        <v>94.7307</v>
       </c>
       <c r="D113" t="n">
-        <v>243.755</v>
+        <v>238.083</v>
       </c>
       <c r="E113" t="n">
-        <v>58.9213</v>
+        <v>70.7529</v>
       </c>
       <c r="F113" t="n">
-        <v>268.731</v>
+        <v>250.254</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>62.2672</v>
+        <v>79.1262</v>
       </c>
       <c r="C114" t="n">
-        <v>289.85</v>
+        <v>93.51730000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>245.627</v>
+        <v>243.717</v>
       </c>
       <c r="E114" t="n">
-        <v>57.7278</v>
+        <v>60.8844</v>
       </c>
       <c r="F114" t="n">
-        <v>267.197</v>
+        <v>250.892</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>62.0897</v>
+        <v>76.8733</v>
       </c>
       <c r="C115" t="n">
-        <v>288.931</v>
+        <v>92.16160000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>248.681</v>
+        <v>245.946</v>
       </c>
       <c r="E115" t="n">
-        <v>56.8058</v>
+        <v>67.2987</v>
       </c>
       <c r="F115" t="n">
-        <v>269.558</v>
+        <v>250.649</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>62.9389</v>
+        <v>70.42910000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>290.481</v>
+        <v>81.6228</v>
       </c>
       <c r="D116" t="n">
-        <v>246.77</v>
+        <v>250.516</v>
       </c>
       <c r="E116" t="n">
-        <v>55.6349</v>
+        <v>65.5928</v>
       </c>
       <c r="F116" t="n">
-        <v>268.855</v>
+        <v>250.338</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>64.0973</v>
+        <v>73.7642</v>
       </c>
       <c r="C117" t="n">
-        <v>290.701</v>
+        <v>89.79219999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>248.929</v>
+        <v>246.732</v>
       </c>
       <c r="E117" t="n">
-        <v>54.6976</v>
+        <v>64.30710000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>270.059</v>
+        <v>249.247</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>62.9089</v>
+        <v>72.64239999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>290.46</v>
+        <v>88.6401</v>
       </c>
       <c r="D118" t="n">
-        <v>242.352</v>
+        <v>237.553</v>
       </c>
       <c r="E118" t="n">
-        <v>50.6006</v>
+        <v>56.0581</v>
       </c>
       <c r="F118" t="n">
-        <v>224.593</v>
+        <v>229.201</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>59.1125</v>
+        <v>66.7132</v>
       </c>
       <c r="C119" t="n">
-        <v>147.009</v>
+        <v>79.5889</v>
       </c>
       <c r="D119" t="n">
-        <v>242.597</v>
+        <v>238.611</v>
       </c>
       <c r="E119" t="n">
-        <v>49.8972</v>
+        <v>55.1619</v>
       </c>
       <c r="F119" t="n">
-        <v>225.388</v>
+        <v>227.049</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>61.3222</v>
+        <v>69.3141</v>
       </c>
       <c r="C120" t="n">
-        <v>290.362</v>
+        <v>86.8</v>
       </c>
       <c r="D120" t="n">
-        <v>244.096</v>
+        <v>239.674</v>
       </c>
       <c r="E120" t="n">
-        <v>49.1461</v>
+        <v>54.133</v>
       </c>
       <c r="F120" t="n">
-        <v>247.959</v>
+        <v>251.365</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>58.7155</v>
+        <v>64.0008</v>
       </c>
       <c r="C121" t="n">
-        <v>290.548</v>
+        <v>78.4348</v>
       </c>
       <c r="D121" t="n">
-        <v>316.061</v>
+        <v>315.934</v>
       </c>
       <c r="E121" t="n">
-        <v>48.7583</v>
+        <v>53.5267</v>
       </c>
       <c r="F121" t="n">
-        <v>224.349</v>
+        <v>205.649</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>57.3635</v>
+        <v>66.44</v>
       </c>
       <c r="C122" t="n">
-        <v>291.56</v>
+        <v>120.192</v>
       </c>
       <c r="D122" t="n">
-        <v>312.122</v>
+        <v>310.87</v>
       </c>
       <c r="E122" t="n">
-        <v>48.2664</v>
+        <v>52.6925</v>
       </c>
       <c r="F122" t="n">
-        <v>273.299</v>
+        <v>204.357</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>57.6881</v>
+        <v>61.261</v>
       </c>
       <c r="C123" t="n">
-        <v>292.25</v>
+        <v>111.866</v>
       </c>
       <c r="D123" t="n">
-        <v>307.665</v>
+        <v>306.17</v>
       </c>
       <c r="E123" t="n">
-        <v>70.0082</v>
+        <v>85.34010000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>327.589</v>
+        <v>302.065</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>79.261</v>
+        <v>96.6476</v>
       </c>
       <c r="C124" t="n">
-        <v>356.844</v>
+        <v>117.761</v>
       </c>
       <c r="D124" t="n">
-        <v>304.319</v>
+        <v>302.838</v>
       </c>
       <c r="E124" t="n">
-        <v>68.9726</v>
+        <v>83.471</v>
       </c>
       <c r="F124" t="n">
-        <v>326.973</v>
+        <v>299.893</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>80.0364</v>
+        <v>92.07989999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>353.079</v>
+        <v>110.131</v>
       </c>
       <c r="D125" t="n">
-        <v>301.094</v>
+        <v>299.226</v>
       </c>
       <c r="E125" t="n">
-        <v>68.087</v>
+        <v>86.66459999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>326.272</v>
+        <v>299.914</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>79.26600000000001</v>
+        <v>89.8086</v>
       </c>
       <c r="C126" t="n">
-        <v>353.671</v>
+        <v>108.895</v>
       </c>
       <c r="D126" t="n">
-        <v>298.32</v>
+        <v>296.387</v>
       </c>
       <c r="E126" t="n">
-        <v>66.77800000000001</v>
+        <v>80.3205</v>
       </c>
       <c r="F126" t="n">
-        <v>325.662</v>
+        <v>298.669</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>77.07940000000001</v>
+        <v>88.96980000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>352.258</v>
+        <v>107.787</v>
       </c>
       <c r="D127" t="n">
-        <v>295.974</v>
+        <v>293.923</v>
       </c>
       <c r="E127" t="n">
-        <v>65.9375</v>
+        <v>78.8901</v>
       </c>
       <c r="F127" t="n">
-        <v>324.943</v>
+        <v>297.595</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>73.83969999999999</v>
+        <v>86.2443</v>
       </c>
       <c r="C128" t="n">
-        <v>350.517</v>
+        <v>106.803</v>
       </c>
       <c r="D128" t="n">
-        <v>294.082</v>
+        <v>291.719</v>
       </c>
       <c r="E128" t="n">
-        <v>65.8961</v>
+        <v>77.449</v>
       </c>
       <c r="F128" t="n">
-        <v>324.51</v>
+        <v>297.049</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>72.1682</v>
+        <v>83.7449</v>
       </c>
       <c r="C129" t="n">
-        <v>349.304</v>
+        <v>105.815</v>
       </c>
       <c r="D129" t="n">
-        <v>292.389</v>
+        <v>290.216</v>
       </c>
       <c r="E129" t="n">
-        <v>65.1504</v>
+        <v>76.19450000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>323.396</v>
+        <v>296.454</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>74.0534</v>
+        <v>86.39879999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>348.802</v>
+        <v>109.648</v>
       </c>
       <c r="D130" t="n">
-        <v>291.206</v>
+        <v>288.512</v>
       </c>
       <c r="E130" t="n">
-        <v>66.25620000000001</v>
+        <v>74.8603</v>
       </c>
       <c r="F130" t="n">
-        <v>323.171</v>
+        <v>295.64</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>73.173</v>
+        <v>81.1934</v>
       </c>
       <c r="C131" t="n">
-        <v>346.442</v>
+        <v>103.84</v>
       </c>
       <c r="D131" t="n">
-        <v>290.534</v>
+        <v>287.235</v>
       </c>
       <c r="E131" t="n">
-        <v>63.7877</v>
+        <v>73.76390000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>323.123</v>
+        <v>294.5</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>71.5853</v>
+        <v>79.8869</v>
       </c>
       <c r="C132" t="n">
-        <v>343.368</v>
+        <v>103.023</v>
       </c>
       <c r="D132" t="n">
-        <v>289.963</v>
+        <v>286.709</v>
       </c>
       <c r="E132" t="n">
-        <v>62.1984</v>
+        <v>72.70269999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>322.842</v>
+        <v>294.319</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>70.748</v>
+        <v>78.3597</v>
       </c>
       <c r="C133" t="n">
-        <v>346.198</v>
+        <v>102.223</v>
       </c>
       <c r="D133" t="n">
-        <v>289.814</v>
+        <v>286.228</v>
       </c>
       <c r="E133" t="n">
-        <v>62.0086</v>
+        <v>71.58280000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>323.258</v>
+        <v>294.341</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>69.99550000000001</v>
+        <v>78.5365</v>
       </c>
       <c r="C134" t="n">
-        <v>344.201</v>
+        <v>101.419</v>
       </c>
       <c r="D134" t="n">
-        <v>287.571</v>
+        <v>283.545</v>
       </c>
       <c r="E134" t="n">
-        <v>59.5929</v>
+        <v>64.599</v>
       </c>
       <c r="F134" t="n">
-        <v>297.815</v>
+        <v>267.278</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>69.6782</v>
+        <v>76.12609999999999</v>
       </c>
       <c r="C135" t="n">
-        <v>344.019</v>
+        <v>100.931</v>
       </c>
       <c r="D135" t="n">
-        <v>362.524</v>
+        <v>360.815</v>
       </c>
       <c r="E135" t="n">
-        <v>59.1027</v>
+        <v>64.0338</v>
       </c>
       <c r="F135" t="n">
-        <v>296.703</v>
+        <v>241.325</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>69.0198</v>
+        <v>71.29340000000001</v>
       </c>
       <c r="C136" t="n">
-        <v>343.1</v>
+        <v>127.718</v>
       </c>
       <c r="D136" t="n">
-        <v>356.395</v>
+        <v>354.187</v>
       </c>
       <c r="E136" t="n">
-        <v>58.8049</v>
+        <v>63.5893</v>
       </c>
       <c r="F136" t="n">
-        <v>322.376</v>
+        <v>292.202</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>68.03279999999999</v>
+        <v>75.82859999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>341.3</v>
+        <v>133.398</v>
       </c>
       <c r="D137" t="n">
-        <v>350.969</v>
+        <v>348.79</v>
       </c>
       <c r="E137" t="n">
-        <v>79.8981</v>
+        <v>96.2437</v>
       </c>
       <c r="F137" t="n">
-        <v>376.071</v>
+        <v>342.074</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>90.67310000000001</v>
+        <v>106.253</v>
       </c>
       <c r="C138" t="n">
-        <v>402.821</v>
+        <v>133.267</v>
       </c>
       <c r="D138" t="n">
-        <v>346.279</v>
+        <v>343.912</v>
       </c>
       <c r="E138" t="n">
-        <v>79.2881</v>
+        <v>94.62130000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>374.533</v>
+        <v>340.835</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>89.02979999999999</v>
+        <v>99.2362</v>
       </c>
       <c r="C139" t="n">
-        <v>398.264</v>
+        <v>125.217</v>
       </c>
       <c r="D139" t="n">
-        <v>341.294</v>
+        <v>339.029</v>
       </c>
       <c r="E139" t="n">
-        <v>78.65770000000001</v>
+        <v>93.1434</v>
       </c>
       <c r="F139" t="n">
-        <v>373.555</v>
+        <v>339.852</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>85.40009999999999</v>
+        <v>99.1387</v>
       </c>
       <c r="C140" t="n">
-        <v>394.567</v>
+        <v>124.176</v>
       </c>
       <c r="D140" t="n">
-        <v>337.309</v>
+        <v>335.261</v>
       </c>
       <c r="E140" t="n">
-        <v>77.82680000000001</v>
+        <v>92.0159</v>
       </c>
       <c r="F140" t="n">
-        <v>371.518</v>
+        <v>337.812</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>86.57680000000001</v>
+        <v>98.7256</v>
       </c>
       <c r="C141" t="n">
-        <v>394.022</v>
+        <v>123.283</v>
       </c>
       <c r="D141" t="n">
-        <v>333.751</v>
+        <v>333.055</v>
       </c>
       <c r="E141" t="n">
-        <v>77.13630000000001</v>
+        <v>90.5753</v>
       </c>
       <c r="F141" t="n">
-        <v>369.981</v>
+        <v>336.826</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>85.1566</v>
+        <v>96.2328</v>
       </c>
       <c r="C142" t="n">
-        <v>391.054</v>
+        <v>122.394</v>
       </c>
       <c r="D142" t="n">
-        <v>332.86</v>
+        <v>331.709</v>
       </c>
       <c r="E142" t="n">
-        <v>78.4967</v>
+        <v>89.25020000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>367.482</v>
+        <v>334.713</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>81.3877</v>
+        <v>97.8466</v>
       </c>
       <c r="C143" t="n">
-        <v>390.058</v>
+        <v>127.234</v>
       </c>
       <c r="D143" t="n">
-        <v>330.407</v>
+        <v>329.572</v>
       </c>
       <c r="E143" t="n">
-        <v>77.8546</v>
+        <v>88.06019999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>366.332</v>
+        <v>333.671</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>22.0318</v>
+        <v>21.9934</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6135</v>
+        <v>24.5602</v>
       </c>
       <c r="D2" t="n">
-        <v>55.9228</v>
+        <v>55.5444</v>
       </c>
       <c r="E2" t="n">
-        <v>19.1419</v>
+        <v>17.7881</v>
       </c>
       <c r="F2" t="n">
-        <v>35.452</v>
+        <v>33.1749</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>21.283</v>
+        <v>21.2522</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0796</v>
+        <v>24.0409</v>
       </c>
       <c r="D3" t="n">
-        <v>55.3634</v>
+        <v>54.9582</v>
       </c>
       <c r="E3" t="n">
-        <v>18.5589</v>
+        <v>17.3404</v>
       </c>
       <c r="F3" t="n">
-        <v>34.9529</v>
+        <v>32.7684</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>20.6656</v>
+        <v>21.8406</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5676</v>
+        <v>23.5642</v>
       </c>
       <c r="D4" t="n">
-        <v>54.8809</v>
+        <v>54.3843</v>
       </c>
       <c r="E4" t="n">
-        <v>18.1156</v>
+        <v>16.9211</v>
       </c>
       <c r="F4" t="n">
-        <v>34.6296</v>
+        <v>32.4289</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>20.2759</v>
+        <v>20.1757</v>
       </c>
       <c r="C5" t="n">
-        <v>23.1886</v>
+        <v>23.1293</v>
       </c>
       <c r="D5" t="n">
-        <v>54.5019</v>
+        <v>53.9922</v>
       </c>
       <c r="E5" t="n">
-        <v>17.737</v>
+        <v>16.4774</v>
       </c>
       <c r="F5" t="n">
-        <v>34.3046</v>
+        <v>32.1985</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>19.5719</v>
+        <v>19.9644</v>
       </c>
       <c r="C6" t="n">
-        <v>22.7926</v>
+        <v>22.7078</v>
       </c>
       <c r="D6" t="n">
-        <v>54.1457</v>
+        <v>53.5434</v>
       </c>
       <c r="E6" t="n">
-        <v>17.4542</v>
+        <v>16.1408</v>
       </c>
       <c r="F6" t="n">
-        <v>34.1351</v>
+        <v>32.0154</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.609</v>
+        <v>19.3009</v>
       </c>
       <c r="C7" t="n">
-        <v>22.4244</v>
+        <v>22.4729</v>
       </c>
       <c r="D7" t="n">
-        <v>69.3836</v>
+        <v>68.40389999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>17.3732</v>
+        <v>24.816</v>
       </c>
       <c r="F7" t="n">
-        <v>34.0214</v>
+        <v>40.0229</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>19.4443</v>
+        <v>18.6565</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8725</v>
+        <v>30.8272</v>
       </c>
       <c r="D8" t="n">
-        <v>67.6855</v>
+        <v>66.7346</v>
       </c>
       <c r="E8" t="n">
-        <v>17.6092</v>
+        <v>24.0086</v>
       </c>
       <c r="F8" t="n">
-        <v>34.2659</v>
+        <v>39.0589</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>19.3683</v>
+        <v>20.0213</v>
       </c>
       <c r="C9" t="n">
-        <v>30.0496</v>
+        <v>30.0232</v>
       </c>
       <c r="D9" t="n">
-        <v>66.48999999999999</v>
+        <v>65.50279999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>26.0607</v>
+        <v>23.1875</v>
       </c>
       <c r="F9" t="n">
-        <v>41.818</v>
+        <v>38.2137</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>28.2466</v>
+        <v>27.8693</v>
       </c>
       <c r="C10" t="n">
-        <v>29.2645</v>
+        <v>29.2583</v>
       </c>
       <c r="D10" t="n">
-        <v>65.2166</v>
+        <v>64.2872</v>
       </c>
       <c r="E10" t="n">
-        <v>25.1478</v>
+        <v>22.3892</v>
       </c>
       <c r="F10" t="n">
-        <v>40.9324</v>
+        <v>37.4646</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>26.7106</v>
+        <v>26.8201</v>
       </c>
       <c r="C11" t="n">
-        <v>28.7545</v>
+        <v>28.4893</v>
       </c>
       <c r="D11" t="n">
-        <v>64.1754</v>
+        <v>63.2296</v>
       </c>
       <c r="E11" t="n">
-        <v>24.3186</v>
+        <v>21.7052</v>
       </c>
       <c r="F11" t="n">
-        <v>39.9316</v>
+        <v>36.7042</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>25.7249</v>
+        <v>26.424</v>
       </c>
       <c r="C12" t="n">
-        <v>27.8196</v>
+        <v>27.7822</v>
       </c>
       <c r="D12" t="n">
-        <v>62.9326</v>
+        <v>62.2078</v>
       </c>
       <c r="E12" t="n">
-        <v>23.5207</v>
+        <v>20.9803</v>
       </c>
       <c r="F12" t="n">
-        <v>39.1161</v>
+        <v>35.9356</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.4673</v>
+        <v>25.354</v>
       </c>
       <c r="C13" t="n">
-        <v>27.1561</v>
+        <v>27.1131</v>
       </c>
       <c r="D13" t="n">
-        <v>61.9114</v>
+        <v>61.2707</v>
       </c>
       <c r="E13" t="n">
-        <v>22.6951</v>
+        <v>20.3349</v>
       </c>
       <c r="F13" t="n">
-        <v>38.3164</v>
+        <v>35.3111</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.3703</v>
+        <v>24.6202</v>
       </c>
       <c r="C14" t="n">
-        <v>26.524</v>
+        <v>26.4804</v>
       </c>
       <c r="D14" t="n">
-        <v>61.044</v>
+        <v>60.4603</v>
       </c>
       <c r="E14" t="n">
-        <v>22.013</v>
+        <v>19.7278</v>
       </c>
       <c r="F14" t="n">
-        <v>37.5559</v>
+        <v>34.7402</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.6828</v>
+        <v>23.6829</v>
       </c>
       <c r="C15" t="n">
-        <v>25.8829</v>
+        <v>25.8541</v>
       </c>
       <c r="D15" t="n">
-        <v>60.4097</v>
+        <v>60.0404</v>
       </c>
       <c r="E15" t="n">
-        <v>21.3115</v>
+        <v>19.2548</v>
       </c>
       <c r="F15" t="n">
-        <v>36.9132</v>
+        <v>34.197</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.0097</v>
+        <v>23.0995</v>
       </c>
       <c r="C16" t="n">
-        <v>25.3071</v>
+        <v>25.2678</v>
       </c>
       <c r="D16" t="n">
-        <v>59.857</v>
+        <v>59.3326</v>
       </c>
       <c r="E16" t="n">
-        <v>20.7239</v>
+        <v>18.6709</v>
       </c>
       <c r="F16" t="n">
-        <v>36.3806</v>
+        <v>33.7295</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.2688</v>
+        <v>22.3261</v>
       </c>
       <c r="C17" t="n">
-        <v>24.7681</v>
+        <v>24.7375</v>
       </c>
       <c r="D17" t="n">
-        <v>59.3353</v>
+        <v>58.8758</v>
       </c>
       <c r="E17" t="n">
-        <v>20.147</v>
+        <v>18.2122</v>
       </c>
       <c r="F17" t="n">
-        <v>35.8501</v>
+        <v>33.2784</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>22.0452</v>
+        <v>21.5681</v>
       </c>
       <c r="C18" t="n">
-        <v>24.2619</v>
+        <v>24.2655</v>
       </c>
       <c r="D18" t="n">
-        <v>58.645</v>
+        <v>58.289</v>
       </c>
       <c r="E18" t="n">
-        <v>19.6856</v>
+        <v>17.7804</v>
       </c>
       <c r="F18" t="n">
-        <v>35.2107</v>
+        <v>32.8928</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.3004</v>
+        <v>21.3614</v>
       </c>
       <c r="C19" t="n">
-        <v>23.8288</v>
+        <v>23.791</v>
       </c>
       <c r="D19" t="n">
-        <v>57.8964</v>
+        <v>57.5843</v>
       </c>
       <c r="E19" t="n">
-        <v>19.2949</v>
+        <v>17.4099</v>
       </c>
       <c r="F19" t="n">
-        <v>34.9159</v>
+        <v>32.5671</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>20.8941</v>
+        <v>21.1523</v>
       </c>
       <c r="C20" t="n">
-        <v>23.4323</v>
+        <v>23.3959</v>
       </c>
       <c r="D20" t="n">
-        <v>57.5572</v>
+        <v>57.2591</v>
       </c>
       <c r="E20" t="n">
-        <v>18.9865</v>
+        <v>17.1034</v>
       </c>
       <c r="F20" t="n">
-        <v>34.5664</v>
+        <v>32.3978</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.5094</v>
+        <v>20.5584</v>
       </c>
       <c r="C21" t="n">
-        <v>23.1348</v>
+        <v>23.2487</v>
       </c>
       <c r="D21" t="n">
-        <v>75.14790000000001</v>
+        <v>74.7681</v>
       </c>
       <c r="E21" t="n">
-        <v>18.8797</v>
+        <v>25.8668</v>
       </c>
       <c r="F21" t="n">
-        <v>34.3565</v>
+        <v>40.3189</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.3865</v>
+        <v>20.5422</v>
       </c>
       <c r="C22" t="n">
-        <v>31.5937</v>
+        <v>31.5413</v>
       </c>
       <c r="D22" t="n">
-        <v>73.70820000000001</v>
+        <v>73.2394</v>
       </c>
       <c r="E22" t="n">
-        <v>18.9836</v>
+        <v>24.9675</v>
       </c>
       <c r="F22" t="n">
-        <v>34.4135</v>
+        <v>39.4555</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>20.1789</v>
+        <v>20.4223</v>
       </c>
       <c r="C23" t="n">
-        <v>30.8211</v>
+        <v>30.7577</v>
       </c>
       <c r="D23" t="n">
-        <v>72.2704</v>
+        <v>71.87009999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>27.368</v>
+        <v>24.1316</v>
       </c>
       <c r="F23" t="n">
-        <v>42.4163</v>
+        <v>38.6305</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>28.8116</v>
+        <v>29.1625</v>
       </c>
       <c r="C24" t="n">
-        <v>30.0423</v>
+        <v>29.9883</v>
       </c>
       <c r="D24" t="n">
-        <v>70.9076</v>
+        <v>70.48309999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>26.4951</v>
+        <v>23.3379</v>
       </c>
       <c r="F24" t="n">
-        <v>41.3347</v>
+        <v>37.8792</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>27.631</v>
+        <v>28.2541</v>
       </c>
       <c r="C25" t="n">
-        <v>29.2751</v>
+        <v>29.2142</v>
       </c>
       <c r="D25" t="n">
-        <v>69.82599999999999</v>
+        <v>69.26560000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>25.5618</v>
+        <v>22.599</v>
       </c>
       <c r="F25" t="n">
-        <v>40.5638</v>
+        <v>37.1332</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>27.0157</v>
+        <v>26.5894</v>
       </c>
       <c r="C26" t="n">
-        <v>28.5897</v>
+        <v>28.5071</v>
       </c>
       <c r="D26" t="n">
-        <v>68.62139999999999</v>
+        <v>68.0813</v>
       </c>
       <c r="E26" t="n">
-        <v>24.7204</v>
+        <v>21.9917</v>
       </c>
       <c r="F26" t="n">
-        <v>39.608</v>
+        <v>36.8555</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>25.9595</v>
+        <v>25.9328</v>
       </c>
       <c r="C27" t="n">
-        <v>27.8575</v>
+        <v>27.8395</v>
       </c>
       <c r="D27" t="n">
-        <v>67.7253</v>
+        <v>67.1341</v>
       </c>
       <c r="E27" t="n">
-        <v>23.9336</v>
+        <v>21.2597</v>
       </c>
       <c r="F27" t="n">
-        <v>38.7726</v>
+        <v>36.2357</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.2419</v>
+        <v>25.1505</v>
       </c>
       <c r="C28" t="n">
-        <v>27.332</v>
+        <v>27.1783</v>
       </c>
       <c r="D28" t="n">
-        <v>66.4592</v>
+        <v>66.1707</v>
       </c>
       <c r="E28" t="n">
-        <v>23.2441</v>
+        <v>20.5789</v>
       </c>
       <c r="F28" t="n">
-        <v>37.9847</v>
+        <v>35.594</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>24.32</v>
+        <v>24.3988</v>
       </c>
       <c r="C29" t="n">
-        <v>26.6185</v>
+        <v>26.5639</v>
       </c>
       <c r="D29" t="n">
-        <v>65.75020000000001</v>
+        <v>65.53279999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>22.5063</v>
+        <v>20.0119</v>
       </c>
       <c r="F29" t="n">
-        <v>37.347</v>
+        <v>35.0334</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>24.2128</v>
+        <v>23.682</v>
       </c>
       <c r="C30" t="n">
-        <v>26.1124</v>
+        <v>25.9886</v>
       </c>
       <c r="D30" t="n">
-        <v>64.91030000000001</v>
+        <v>64.73950000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>21.8338</v>
+        <v>19.4759</v>
       </c>
       <c r="F30" t="n">
-        <v>36.6859</v>
+        <v>34.4996</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.3581</v>
+        <v>23.4814</v>
       </c>
       <c r="C31" t="n">
-        <v>25.4944</v>
+        <v>25.5436</v>
       </c>
       <c r="D31" t="n">
-        <v>64.3847</v>
+        <v>64.23820000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>21.2598</v>
+        <v>18.9369</v>
       </c>
       <c r="F31" t="n">
-        <v>35.8889</v>
+        <v>33.4259</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>23.3569</v>
+        <v>23.088</v>
       </c>
       <c r="C32" t="n">
-        <v>24.9902</v>
+        <v>24.935</v>
       </c>
       <c r="D32" t="n">
-        <v>63.9628</v>
+        <v>63.7921</v>
       </c>
       <c r="E32" t="n">
-        <v>20.6359</v>
+        <v>18.5284</v>
       </c>
       <c r="F32" t="n">
-        <v>35.4311</v>
+        <v>33.0628</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>21.9728</v>
+        <v>22.5296</v>
       </c>
       <c r="C33" t="n">
-        <v>24.5511</v>
+        <v>24.4765</v>
       </c>
       <c r="D33" t="n">
-        <v>63.5619</v>
+        <v>63.3981</v>
       </c>
       <c r="E33" t="n">
-        <v>20.2569</v>
+        <v>18.2369</v>
       </c>
       <c r="F33" t="n">
-        <v>35.0811</v>
+        <v>32.9699</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>22.1148</v>
+        <v>22.0765</v>
       </c>
       <c r="C34" t="n">
-        <v>24.146</v>
+        <v>24.0534</v>
       </c>
       <c r="D34" t="n">
-        <v>62.9094</v>
+        <v>62.6302</v>
       </c>
       <c r="E34" t="n">
-        <v>19.8222</v>
+        <v>17.8635</v>
       </c>
       <c r="F34" t="n">
-        <v>34.7473</v>
+        <v>32.7486</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>21.46</v>
+        <v>21.7739</v>
       </c>
       <c r="C35" t="n">
-        <v>23.8228</v>
+        <v>23.7449</v>
       </c>
       <c r="D35" t="n">
-        <v>81.3021</v>
+        <v>81.0187</v>
       </c>
       <c r="E35" t="n">
-        <v>19.7023</v>
+        <v>26.765</v>
       </c>
       <c r="F35" t="n">
-        <v>34.6884</v>
+        <v>41.3487</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>21.1324</v>
+        <v>21.2461</v>
       </c>
       <c r="C36" t="n">
-        <v>23.5671</v>
+        <v>23.4766</v>
       </c>
       <c r="D36" t="n">
-        <v>79.6296</v>
+        <v>79.30410000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>19.4338</v>
+        <v>25.9468</v>
       </c>
       <c r="F36" t="n">
-        <v>34.6578</v>
+        <v>40.5407</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>20.7794</v>
+        <v>21.0891</v>
       </c>
       <c r="C37" t="n">
-        <v>31.6419</v>
+        <v>31.6155</v>
       </c>
       <c r="D37" t="n">
-        <v>78.1374</v>
+        <v>77.74809999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>28.1915</v>
+        <v>25.1025</v>
       </c>
       <c r="F37" t="n">
-        <v>43.4371</v>
+        <v>39.7476</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>29.4218</v>
+        <v>29.7262</v>
       </c>
       <c r="C38" t="n">
-        <v>30.9534</v>
+        <v>30.8865</v>
       </c>
       <c r="D38" t="n">
-        <v>76.5565</v>
+        <v>76.2804</v>
       </c>
       <c r="E38" t="n">
-        <v>27.2638</v>
+        <v>24.2994</v>
       </c>
       <c r="F38" t="n">
-        <v>42.6646</v>
+        <v>39.0996</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>28.1554</v>
+        <v>27.9831</v>
       </c>
       <c r="C39" t="n">
-        <v>30.5538</v>
+        <v>30.1737</v>
       </c>
       <c r="D39" t="n">
-        <v>75.2253</v>
+        <v>74.9294</v>
       </c>
       <c r="E39" t="n">
-        <v>26.3952</v>
+        <v>23.5899</v>
       </c>
       <c r="F39" t="n">
-        <v>41.7394</v>
+        <v>38.2814</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>27.6759</v>
+        <v>27.147</v>
       </c>
       <c r="C40" t="n">
-        <v>29.4612</v>
+        <v>29.362</v>
       </c>
       <c r="D40" t="n">
-        <v>74.0136</v>
+        <v>73.7295</v>
       </c>
       <c r="E40" t="n">
-        <v>25.6176</v>
+        <v>22.9433</v>
       </c>
       <c r="F40" t="n">
-        <v>40.8233</v>
+        <v>37.616</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.5075</v>
+        <v>26.4175</v>
       </c>
       <c r="C41" t="n">
-        <v>29.0264</v>
+        <v>28.914</v>
       </c>
       <c r="D41" t="n">
-        <v>72.80370000000001</v>
+        <v>72.6504</v>
       </c>
       <c r="E41" t="n">
-        <v>24.7986</v>
+        <v>22.2205</v>
       </c>
       <c r="F41" t="n">
-        <v>39.9256</v>
+        <v>36.9418</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>25.8495</v>
+        <v>25.4461</v>
       </c>
       <c r="C42" t="n">
-        <v>28.1983</v>
+        <v>28.2786</v>
       </c>
       <c r="D42" t="n">
-        <v>71.9311</v>
+        <v>71.65600000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>24.0729</v>
+        <v>21.6317</v>
       </c>
       <c r="F42" t="n">
-        <v>39.2993</v>
+        <v>36.3862</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>25.1136</v>
+        <v>24.9394</v>
       </c>
       <c r="C43" t="n">
-        <v>27.8322</v>
+        <v>27.8197</v>
       </c>
       <c r="D43" t="n">
-        <v>70.7976</v>
+        <v>70.5638</v>
       </c>
       <c r="E43" t="n">
-        <v>23.3607</v>
+        <v>21.1325</v>
       </c>
       <c r="F43" t="n">
-        <v>38.671</v>
+        <v>35.8681</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.4723</v>
+        <v>24.2299</v>
       </c>
       <c r="C44" t="n">
-        <v>27.0689</v>
+        <v>27.1042</v>
       </c>
       <c r="D44" t="n">
-        <v>69.96380000000001</v>
+        <v>69.7383</v>
       </c>
       <c r="E44" t="n">
-        <v>22.7635</v>
+        <v>20.512</v>
       </c>
       <c r="F44" t="n">
-        <v>38.0006</v>
+        <v>35.4109</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>23.4127</v>
+        <v>24.1041</v>
       </c>
       <c r="C45" t="n">
-        <v>26.7741</v>
+        <v>26.739</v>
       </c>
       <c r="D45" t="n">
-        <v>69.3231</v>
+        <v>69.0624</v>
       </c>
       <c r="E45" t="n">
-        <v>22.1345</v>
+        <v>20.154</v>
       </c>
       <c r="F45" t="n">
-        <v>37.4631</v>
+        <v>35.0628</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>23.4241</v>
+        <v>23.1144</v>
       </c>
       <c r="C46" t="n">
-        <v>26.0683</v>
+        <v>26.3236</v>
       </c>
       <c r="D46" t="n">
-        <v>68.749</v>
+        <v>68.5322</v>
       </c>
       <c r="E46" t="n">
-        <v>21.5951</v>
+        <v>19.6525</v>
       </c>
       <c r="F46" t="n">
-        <v>37.0596</v>
+        <v>34.6684</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.5865</v>
+        <v>22.519</v>
       </c>
       <c r="C47" t="n">
-        <v>25.5734</v>
+        <v>25.8256</v>
       </c>
       <c r="D47" t="n">
-        <v>68.3171</v>
+        <v>68.09650000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>21.1393</v>
+        <v>19.3098</v>
       </c>
       <c r="F47" t="n">
-        <v>36.6271</v>
+        <v>34.3822</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>22.1438</v>
+        <v>22.0713</v>
       </c>
       <c r="C48" t="n">
-        <v>25.1721</v>
+        <v>25.0324</v>
       </c>
       <c r="D48" t="n">
-        <v>67.5275</v>
+        <v>67.348</v>
       </c>
       <c r="E48" t="n">
-        <v>20.7898</v>
+        <v>18.7606</v>
       </c>
       <c r="F48" t="n">
-        <v>36.3393</v>
+        <v>34.1697</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>21.5163</v>
+        <v>22.2564</v>
       </c>
       <c r="C49" t="n">
-        <v>25.1364</v>
+        <v>25.1591</v>
       </c>
       <c r="D49" t="n">
-        <v>67.1866</v>
+        <v>66.9586</v>
       </c>
       <c r="E49" t="n">
-        <v>20.4325</v>
+        <v>18.5383</v>
       </c>
       <c r="F49" t="n">
-        <v>36.1064</v>
+        <v>33.9992</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.6089</v>
+        <v>21.2606</v>
       </c>
       <c r="C50" t="n">
-        <v>24.5552</v>
+        <v>24.8256</v>
       </c>
       <c r="D50" t="n">
-        <v>84.4294</v>
+        <v>84.2265</v>
       </c>
       <c r="E50" t="n">
-        <v>20.3781</v>
+        <v>27.098</v>
       </c>
       <c r="F50" t="n">
-        <v>36.0326</v>
+        <v>42.002</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>21.2149</v>
+        <v>22.1644</v>
       </c>
       <c r="C51" t="n">
-        <v>32.6941</v>
+        <v>32.8373</v>
       </c>
       <c r="D51" t="n">
-        <v>82.744</v>
+        <v>82.486</v>
       </c>
       <c r="E51" t="n">
-        <v>29.715</v>
+        <v>26.4024</v>
       </c>
       <c r="F51" t="n">
-        <v>45.0506</v>
+        <v>41.7029</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>21.965</v>
+        <v>22.0485</v>
       </c>
       <c r="C52" t="n">
-        <v>32.2564</v>
+        <v>32.0839</v>
       </c>
       <c r="D52" t="n">
-        <v>81.1206</v>
+        <v>80.8522</v>
       </c>
       <c r="E52" t="n">
-        <v>28.4822</v>
+        <v>25.5061</v>
       </c>
       <c r="F52" t="n">
-        <v>43.8948</v>
+        <v>40.5896</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.9404</v>
+        <v>29.1209</v>
       </c>
       <c r="C53" t="n">
-        <v>31.4141</v>
+        <v>31.2902</v>
       </c>
       <c r="D53" t="n">
-        <v>79.5605</v>
+        <v>79.3396</v>
       </c>
       <c r="E53" t="n">
-        <v>27.8864</v>
+        <v>24.8044</v>
       </c>
       <c r="F53" t="n">
-        <v>43.1273</v>
+        <v>39.8397</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>29.6565</v>
+        <v>28.5446</v>
       </c>
       <c r="C54" t="n">
-        <v>30.7484</v>
+        <v>30.7512</v>
       </c>
       <c r="D54" t="n">
-        <v>78.1961</v>
+        <v>77.93980000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>26.9309</v>
+        <v>24.1286</v>
       </c>
       <c r="F54" t="n">
-        <v>42.3069</v>
+        <v>39.3138</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>28.7715</v>
+        <v>27.8911</v>
       </c>
       <c r="C55" t="n">
-        <v>30.2181</v>
+        <v>30.198</v>
       </c>
       <c r="D55" t="n">
-        <v>76.9328</v>
+        <v>76.7193</v>
       </c>
       <c r="E55" t="n">
-        <v>25.8518</v>
+        <v>23.4383</v>
       </c>
       <c r="F55" t="n">
-        <v>41.4373</v>
+        <v>38.648</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>27.5694</v>
+        <v>26.7259</v>
       </c>
       <c r="C56" t="n">
-        <v>29.6949</v>
+        <v>29.5313</v>
       </c>
       <c r="D56" t="n">
-        <v>75.8938</v>
+        <v>75.717</v>
       </c>
       <c r="E56" t="n">
-        <v>25.1384</v>
+        <v>22.7854</v>
       </c>
       <c r="F56" t="n">
-        <v>40.7269</v>
+        <v>38.014</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.9036</v>
+        <v>26.0914</v>
       </c>
       <c r="C57" t="n">
-        <v>29.0469</v>
+        <v>29.1165</v>
       </c>
       <c r="D57" t="n">
-        <v>74.6495</v>
+        <v>74.52589999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>24.458</v>
+        <v>22.5272</v>
       </c>
       <c r="F57" t="n">
-        <v>40.0632</v>
+        <v>37.5708</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>26.2245</v>
+        <v>25.3202</v>
       </c>
       <c r="C58" t="n">
-        <v>28.6065</v>
+        <v>28.6538</v>
       </c>
       <c r="D58" t="n">
-        <v>73.8408</v>
+        <v>73.72</v>
       </c>
       <c r="E58" t="n">
-        <v>23.9003</v>
+        <v>21.6024</v>
       </c>
       <c r="F58" t="n">
-        <v>39.4495</v>
+        <v>37.1717</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>25.3106</v>
+        <v>24.7189</v>
       </c>
       <c r="C59" t="n">
-        <v>28.052</v>
+        <v>28.1211</v>
       </c>
       <c r="D59" t="n">
-        <v>73.01009999999999</v>
+        <v>72.8754</v>
       </c>
       <c r="E59" t="n">
-        <v>23.4402</v>
+        <v>21.376</v>
       </c>
       <c r="F59" t="n">
-        <v>38.9336</v>
+        <v>36.7213</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>25.1131</v>
+        <v>24.5541</v>
       </c>
       <c r="C60" t="n">
-        <v>27.7208</v>
+        <v>27.8861</v>
       </c>
       <c r="D60" t="n">
-        <v>72.3479</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>22.7809</v>
+        <v>20.7062</v>
       </c>
       <c r="F60" t="n">
-        <v>38.3578</v>
+        <v>36.2941</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>24.5224</v>
+        <v>23.618</v>
       </c>
       <c r="C61" t="n">
-        <v>26.8573</v>
+        <v>27.3004</v>
       </c>
       <c r="D61" t="n">
-        <v>71.5665</v>
+        <v>71.4765</v>
       </c>
       <c r="E61" t="n">
-        <v>22.4967</v>
+        <v>20.3048</v>
       </c>
       <c r="F61" t="n">
-        <v>37.8723</v>
+        <v>35.9572</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>24.0174</v>
+        <v>23.3571</v>
       </c>
       <c r="C62" t="n">
-        <v>26.4887</v>
+        <v>26.9696</v>
       </c>
       <c r="D62" t="n">
-        <v>70.9723</v>
+        <v>70.822</v>
       </c>
       <c r="E62" t="n">
-        <v>21.9453</v>
+        <v>19.9293</v>
       </c>
       <c r="F62" t="n">
-        <v>37.5424</v>
+        <v>35.7446</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>23.5991</v>
+        <v>22.7965</v>
       </c>
       <c r="C63" t="n">
-        <v>26.1757</v>
+        <v>26.5597</v>
       </c>
       <c r="D63" t="n">
-        <v>70.4966</v>
+        <v>70.4614</v>
       </c>
       <c r="E63" t="n">
-        <v>21.5704</v>
+        <v>19.8085</v>
       </c>
       <c r="F63" t="n">
-        <v>37.297</v>
+        <v>35.6451</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>23.0006</v>
+        <v>22.554</v>
       </c>
       <c r="C64" t="n">
-        <v>25.8648</v>
+        <v>26.5172</v>
       </c>
       <c r="D64" t="n">
-        <v>92.6211</v>
+        <v>91.5206</v>
       </c>
       <c r="E64" t="n">
-        <v>21.3505</v>
+        <v>31.191</v>
       </c>
       <c r="F64" t="n">
-        <v>37.3813</v>
+        <v>45.0562</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>22.7675</v>
+        <v>22.2205</v>
       </c>
       <c r="C65" t="n">
-        <v>35.0156</v>
+        <v>34.8028</v>
       </c>
       <c r="D65" t="n">
-        <v>90.2697</v>
+        <v>89.4492</v>
       </c>
       <c r="E65" t="n">
-        <v>21.3479</v>
+        <v>30.9373</v>
       </c>
       <c r="F65" t="n">
-        <v>37.5657</v>
+        <v>44.5048</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.7011</v>
+        <v>22.7987</v>
       </c>
       <c r="C66" t="n">
-        <v>34.5645</v>
+        <v>34.4268</v>
       </c>
       <c r="D66" t="n">
-        <v>88.422</v>
+        <v>87.6255</v>
       </c>
       <c r="E66" t="n">
-        <v>33.775</v>
+        <v>29.6446</v>
       </c>
       <c r="F66" t="n">
-        <v>48.2747</v>
+        <v>43.9795</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>38.7193</v>
+        <v>35.5545</v>
       </c>
       <c r="C67" t="n">
-        <v>34.1228</v>
+        <v>34.0506</v>
       </c>
       <c r="D67" t="n">
-        <v>86.7192</v>
+        <v>85.9258</v>
       </c>
       <c r="E67" t="n">
-        <v>33.0074</v>
+        <v>29.6446</v>
       </c>
       <c r="F67" t="n">
-        <v>47.7335</v>
+        <v>43.4572</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>37.8351</v>
+        <v>36.3011</v>
       </c>
       <c r="C68" t="n">
-        <v>33.7791</v>
+        <v>33.5892</v>
       </c>
       <c r="D68" t="n">
-        <v>85.24169999999999</v>
+        <v>84.4666</v>
       </c>
       <c r="E68" t="n">
-        <v>32.1675</v>
+        <v>28.7771</v>
       </c>
       <c r="F68" t="n">
-        <v>47.0989</v>
+        <v>42.7934</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>36.8311</v>
+        <v>36.8016</v>
       </c>
       <c r="C69" t="n">
-        <v>33.4933</v>
+        <v>33.164</v>
       </c>
       <c r="D69" t="n">
-        <v>83.79900000000001</v>
+        <v>82.9896</v>
       </c>
       <c r="E69" t="n">
-        <v>31.3947</v>
+        <v>28.1827</v>
       </c>
       <c r="F69" t="n">
-        <v>46.537</v>
+        <v>42.1699</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>35.6655</v>
+        <v>35.1034</v>
       </c>
       <c r="C70" t="n">
-        <v>33.2633</v>
+        <v>32.9377</v>
       </c>
       <c r="D70" t="n">
-        <v>83.08750000000001</v>
+        <v>81.9622</v>
       </c>
       <c r="E70" t="n">
-        <v>30.6628</v>
+        <v>27.5742</v>
       </c>
       <c r="F70" t="n">
-        <v>45.8754</v>
+        <v>41.6717</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>35.4261</v>
+        <v>33.7056</v>
       </c>
       <c r="C71" t="n">
-        <v>32.9415</v>
+        <v>32.542</v>
       </c>
       <c r="D71" t="n">
-        <v>82.4045</v>
+        <v>81.1234</v>
       </c>
       <c r="E71" t="n">
-        <v>29.9793</v>
+        <v>27.2026</v>
       </c>
       <c r="F71" t="n">
-        <v>45.1063</v>
+        <v>41.3721</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.2384</v>
+        <v>33.8739</v>
       </c>
       <c r="C72" t="n">
-        <v>32.5941</v>
+        <v>32.5327</v>
       </c>
       <c r="D72" t="n">
-        <v>82.0557</v>
+        <v>80.81870000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>29.2329</v>
+        <v>27.6867</v>
       </c>
       <c r="F72" t="n">
-        <v>44.5763</v>
+        <v>40.9399</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>32.8418</v>
+        <v>33.0043</v>
       </c>
       <c r="C73" t="n">
-        <v>32.5356</v>
+        <v>32.0792</v>
       </c>
       <c r="D73" t="n">
-        <v>81.7535</v>
+        <v>80.52549999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>28.6765</v>
+        <v>26.8001</v>
       </c>
       <c r="F73" t="n">
-        <v>44.1715</v>
+        <v>40.6487</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>33.1567</v>
+        <v>32.6702</v>
       </c>
       <c r="C74" t="n">
-        <v>31.8604</v>
+        <v>31.685</v>
       </c>
       <c r="D74" t="n">
-        <v>81.30329999999999</v>
+        <v>80.1122</v>
       </c>
       <c r="E74" t="n">
-        <v>28.1988</v>
+        <v>26.2689</v>
       </c>
       <c r="F74" t="n">
-        <v>43.6503</v>
+        <v>40.336</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>33.0645</v>
+        <v>32.6978</v>
       </c>
       <c r="C75" t="n">
-        <v>31.616</v>
+        <v>31.3028</v>
       </c>
       <c r="D75" t="n">
-        <v>80.09439999999999</v>
+        <v>79.2243</v>
       </c>
       <c r="E75" t="n">
-        <v>27.5974</v>
+        <v>25.9117</v>
       </c>
       <c r="F75" t="n">
-        <v>43.3107</v>
+        <v>40.0237</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>32.5417</v>
+        <v>30.9901</v>
       </c>
       <c r="C76" t="n">
-        <v>31.3526</v>
+        <v>31.0599</v>
       </c>
       <c r="D76" t="n">
-        <v>80.2364</v>
+        <v>79.3182</v>
       </c>
       <c r="E76" t="n">
-        <v>27.2024</v>
+        <v>25.434</v>
       </c>
       <c r="F76" t="n">
-        <v>42.9678</v>
+        <v>39.8716</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>32.0453</v>
+        <v>31.8039</v>
       </c>
       <c r="C77" t="n">
-        <v>31.1276</v>
+        <v>30.825</v>
       </c>
       <c r="D77" t="n">
-        <v>80.71380000000001</v>
+        <v>79.5686</v>
       </c>
       <c r="E77" t="n">
-        <v>26.6457</v>
+        <v>25.016</v>
       </c>
       <c r="F77" t="n">
-        <v>42.7206</v>
+        <v>39.7962</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>31.8032</v>
+        <v>29.5948</v>
       </c>
       <c r="C78" t="n">
-        <v>30.8468</v>
+        <v>30.5145</v>
       </c>
       <c r="D78" t="n">
-        <v>131.275</v>
+        <v>129.884</v>
       </c>
       <c r="E78" t="n">
-        <v>26.1557</v>
+        <v>42.6725</v>
       </c>
       <c r="F78" t="n">
-        <v>42.6951</v>
+        <v>64.271</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>30.1677</v>
+        <v>34.1335</v>
       </c>
       <c r="C79" t="n">
-        <v>40.6028</v>
+        <v>40.0359</v>
       </c>
       <c r="D79" t="n">
-        <v>129.036</v>
+        <v>127.717</v>
       </c>
       <c r="E79" t="n">
-        <v>26.1577</v>
+        <v>41.5168</v>
       </c>
       <c r="F79" t="n">
-        <v>42.7973</v>
+        <v>64.4679</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>31.3107</v>
+        <v>34.4213</v>
       </c>
       <c r="C80" t="n">
-        <v>41.2128</v>
+        <v>40.8749</v>
       </c>
       <c r="D80" t="n">
-        <v>127.073</v>
+        <v>125.922</v>
       </c>
       <c r="E80" t="n">
-        <v>42.4292</v>
+        <v>40.7784</v>
       </c>
       <c r="F80" t="n">
-        <v>67.9765</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>48.0132</v>
+        <v>48.4515</v>
       </c>
       <c r="C81" t="n">
-        <v>41.8014</v>
+        <v>41.3051</v>
       </c>
       <c r="D81" t="n">
-        <v>125.409</v>
+        <v>124.348</v>
       </c>
       <c r="E81" t="n">
-        <v>41.8457</v>
+        <v>40.0837</v>
       </c>
       <c r="F81" t="n">
-        <v>68.1118</v>
+        <v>63.7509</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>48.67</v>
+        <v>44.5188</v>
       </c>
       <c r="C82" t="n">
-        <v>41.9331</v>
+        <v>41.4416</v>
       </c>
       <c r="D82" t="n">
-        <v>124.11</v>
+        <v>123.047</v>
       </c>
       <c r="E82" t="n">
-        <v>40.7454</v>
+        <v>39.2175</v>
       </c>
       <c r="F82" t="n">
-        <v>68.96850000000001</v>
+        <v>63.2264</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>44.6998</v>
+        <v>45.094</v>
       </c>
       <c r="C83" t="n">
-        <v>42.2839</v>
+        <v>41.7452</v>
       </c>
       <c r="D83" t="n">
-        <v>123.147</v>
+        <v>122.118</v>
       </c>
       <c r="E83" t="n">
-        <v>40.0361</v>
+        <v>38.3025</v>
       </c>
       <c r="F83" t="n">
-        <v>66.8639</v>
+        <v>62.224</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>46.2553</v>
+        <v>43.3546</v>
       </c>
       <c r="C84" t="n">
-        <v>42.4685</v>
+        <v>41.8178</v>
       </c>
       <c r="D84" t="n">
-        <v>124.366</v>
+        <v>121.714</v>
       </c>
       <c r="E84" t="n">
-        <v>39.2776</v>
+        <v>37.5625</v>
       </c>
       <c r="F84" t="n">
-        <v>65.9971</v>
+        <v>61.3095</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>45.0632</v>
+        <v>43.7032</v>
       </c>
       <c r="C85" t="n">
-        <v>42.6288</v>
+        <v>41.9802</v>
       </c>
       <c r="D85" t="n">
-        <v>124.124</v>
+        <v>121.528</v>
       </c>
       <c r="E85" t="n">
-        <v>38.3555</v>
+        <v>36.4379</v>
       </c>
       <c r="F85" t="n">
-        <v>64.90170000000001</v>
+        <v>60.4233</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>45.6631</v>
+        <v>40.6545</v>
       </c>
       <c r="C86" t="n">
-        <v>42.7048</v>
+        <v>42.2901</v>
       </c>
       <c r="D86" t="n">
-        <v>124.149</v>
+        <v>121.657</v>
       </c>
       <c r="E86" t="n">
-        <v>37.4151</v>
+        <v>35.7048</v>
       </c>
       <c r="F86" t="n">
-        <v>64.27200000000001</v>
+        <v>59.6879</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>43.0214</v>
+        <v>43.5113</v>
       </c>
       <c r="C87" t="n">
-        <v>42.5688</v>
+        <v>41.9542</v>
       </c>
       <c r="D87" t="n">
-        <v>124.266</v>
+        <v>121.673</v>
       </c>
       <c r="E87" t="n">
-        <v>36.7378</v>
+        <v>34.9237</v>
       </c>
       <c r="F87" t="n">
-        <v>62.9769</v>
+        <v>58.6359</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>40.2802</v>
+        <v>40.7871</v>
       </c>
       <c r="C88" t="n">
-        <v>42.6642</v>
+        <v>41.7772</v>
       </c>
       <c r="D88" t="n">
-        <v>124.843</v>
+        <v>122.385</v>
       </c>
       <c r="E88" t="n">
-        <v>35.9323</v>
+        <v>33.9052</v>
       </c>
       <c r="F88" t="n">
-        <v>62.5441</v>
+        <v>57.7249</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>41.7823</v>
+        <v>40.9563</v>
       </c>
       <c r="C89" t="n">
-        <v>42.3732</v>
+        <v>41.7202</v>
       </c>
       <c r="D89" t="n">
-        <v>124.945</v>
+        <v>122.557</v>
       </c>
       <c r="E89" t="n">
-        <v>35.1256</v>
+        <v>33.4103</v>
       </c>
       <c r="F89" t="n">
-        <v>60.5744</v>
+        <v>56.9516</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>41.8441</v>
+        <v>41.8803</v>
       </c>
       <c r="C90" t="n">
-        <v>42.276</v>
+        <v>41.9767</v>
       </c>
       <c r="D90" t="n">
-        <v>126.301</v>
+        <v>123.861</v>
       </c>
       <c r="E90" t="n">
-        <v>34.2204</v>
+        <v>32.9812</v>
       </c>
       <c r="F90" t="n">
-        <v>60.2833</v>
+        <v>56.1705</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>40.4947</v>
+        <v>39.328</v>
       </c>
       <c r="C91" t="n">
-        <v>42.0725</v>
+        <v>41.9288</v>
       </c>
       <c r="D91" t="n">
-        <v>126.966</v>
+        <v>125.316</v>
       </c>
       <c r="E91" t="n">
-        <v>33.7158</v>
+        <v>32.4275</v>
       </c>
       <c r="F91" t="n">
-        <v>59.4657</v>
+        <v>55.7581</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>40.1539</v>
+        <v>37.5296</v>
       </c>
       <c r="C92" t="n">
-        <v>41.9803</v>
+        <v>41.8408</v>
       </c>
       <c r="D92" t="n">
-        <v>190.673</v>
+        <v>188.077</v>
       </c>
       <c r="E92" t="n">
-        <v>33.2239</v>
+        <v>66.52800000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>58.9784</v>
+        <v>90.5993</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>40.2192</v>
+        <v>41.7438</v>
       </c>
       <c r="C93" t="n">
-        <v>41.8652</v>
+        <v>41.5806</v>
       </c>
       <c r="D93" t="n">
-        <v>190.064</v>
+        <v>188.03</v>
       </c>
       <c r="E93" t="n">
-        <v>32.8654</v>
+        <v>65.4671</v>
       </c>
       <c r="F93" t="n">
-        <v>58.8563</v>
+        <v>84.6443</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>39.5467</v>
+        <v>40.2259</v>
       </c>
       <c r="C94" t="n">
-        <v>74.8032</v>
+        <v>74.92449999999999</v>
       </c>
       <c r="D94" t="n">
-        <v>186.706</v>
+        <v>186.534</v>
       </c>
       <c r="E94" t="n">
-        <v>64.48909999999999</v>
+        <v>63.8007</v>
       </c>
       <c r="F94" t="n">
-        <v>89.5724</v>
+        <v>84.33710000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>71.8236</v>
+        <v>70.5562</v>
       </c>
       <c r="C95" t="n">
-        <v>74.60169999999999</v>
+        <v>74.7358</v>
       </c>
       <c r="D95" t="n">
-        <v>184.604</v>
+        <v>185.34</v>
       </c>
       <c r="E95" t="n">
-        <v>63.3709</v>
+        <v>62.1657</v>
       </c>
       <c r="F95" t="n">
-        <v>90.242</v>
+        <v>82.44840000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>72.99639999999999</v>
+        <v>72.8533</v>
       </c>
       <c r="C96" t="n">
-        <v>74.0444</v>
+        <v>73.94929999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>183.903</v>
+        <v>184.342</v>
       </c>
       <c r="E96" t="n">
-        <v>61.8063</v>
+        <v>60.518</v>
       </c>
       <c r="F96" t="n">
-        <v>91.21210000000001</v>
+        <v>81.85469999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>67.20950000000001</v>
+        <v>71.3421</v>
       </c>
       <c r="C97" t="n">
-        <v>73.09699999999999</v>
+        <v>73.11320000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>184.224</v>
+        <v>183.718</v>
       </c>
       <c r="E97" t="n">
-        <v>60.3659</v>
+        <v>58.6237</v>
       </c>
       <c r="F97" t="n">
-        <v>88.8275</v>
+        <v>84.4645</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>68.18600000000001</v>
+        <v>68.5287</v>
       </c>
       <c r="C98" t="n">
-        <v>72.44159999999999</v>
+        <v>72.3749</v>
       </c>
       <c r="D98" t="n">
-        <v>183.863</v>
+        <v>183.263</v>
       </c>
       <c r="E98" t="n">
-        <v>58.5834</v>
+        <v>57.2089</v>
       </c>
       <c r="F98" t="n">
-        <v>87.6891</v>
+        <v>83.38209999999999</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>63.2215</v>
+        <v>65.2651</v>
       </c>
       <c r="C99" t="n">
-        <v>71.71129999999999</v>
+        <v>71.64190000000001</v>
       </c>
       <c r="D99" t="n">
-        <v>184.282</v>
+        <v>182.949</v>
       </c>
       <c r="E99" t="n">
-        <v>56.9807</v>
+        <v>55.5781</v>
       </c>
       <c r="F99" t="n">
-        <v>85.8014</v>
+        <v>83.0231</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>64.7405</v>
+        <v>66.97239999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>71.276</v>
+        <v>71.0498</v>
       </c>
       <c r="D100" t="n">
-        <v>184.535</v>
+        <v>183.487</v>
       </c>
       <c r="E100" t="n">
-        <v>55.4754</v>
+        <v>54.1794</v>
       </c>
       <c r="F100" t="n">
-        <v>85.6512</v>
+        <v>80.75920000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>65.27630000000001</v>
+        <v>62.7937</v>
       </c>
       <c r="C101" t="n">
-        <v>70.41200000000001</v>
+        <v>70.40560000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>184.876</v>
+        <v>183.31</v>
       </c>
       <c r="E101" t="n">
-        <v>54.1066</v>
+        <v>52.6966</v>
       </c>
       <c r="F101" t="n">
-        <v>84.7555</v>
+        <v>80.48220000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>62.2696</v>
+        <v>61.2009</v>
       </c>
       <c r="C102" t="n">
-        <v>69.7967</v>
+        <v>69.75149999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>185.67</v>
+        <v>184.417</v>
       </c>
       <c r="E102" t="n">
-        <v>52.7115</v>
+        <v>51.444</v>
       </c>
       <c r="F102" t="n">
-        <v>83.74890000000001</v>
+        <v>79.42440000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>60.6898</v>
+        <v>62.4</v>
       </c>
       <c r="C103" t="n">
-        <v>69.12390000000001</v>
+        <v>69.0924</v>
       </c>
       <c r="D103" t="n">
-        <v>186.808</v>
+        <v>186.178</v>
       </c>
       <c r="E103" t="n">
-        <v>51.4328</v>
+        <v>50.2487</v>
       </c>
       <c r="F103" t="n">
-        <v>82.7864</v>
+        <v>81.7625</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>61.0267</v>
+        <v>60.5847</v>
       </c>
       <c r="C104" t="n">
-        <v>68.4182</v>
+        <v>68.4264</v>
       </c>
       <c r="D104" t="n">
-        <v>187.851</v>
+        <v>187.276</v>
       </c>
       <c r="E104" t="n">
-        <v>50.3019</v>
+        <v>49.1888</v>
       </c>
       <c r="F104" t="n">
-        <v>82.5869</v>
+        <v>78.5656</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>59.6331</v>
+        <v>59.6217</v>
       </c>
       <c r="C105" t="n">
-        <v>68.0076</v>
+        <v>67.8085</v>
       </c>
       <c r="D105" t="n">
-        <v>189.75</v>
+        <v>188.536</v>
       </c>
       <c r="E105" t="n">
-        <v>49.1781</v>
+        <v>48.1035</v>
       </c>
       <c r="F105" t="n">
-        <v>81.5462</v>
+        <v>88.4114</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>58.3314</v>
+        <v>60.6705</v>
       </c>
       <c r="C106" t="n">
-        <v>67.3738</v>
+        <v>67.24720000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>191.468</v>
+        <v>190.117</v>
       </c>
       <c r="E106" t="n">
-        <v>48.2526</v>
+        <v>47.1964</v>
       </c>
       <c r="F106" t="n">
-        <v>86.9286</v>
+        <v>88.81699999999999</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>56.1315</v>
+        <v>56.3445</v>
       </c>
       <c r="C107" t="n">
-        <v>66.91679999999999</v>
+        <v>66.7252</v>
       </c>
       <c r="D107" t="n">
-        <v>261.249</v>
+        <v>257.867</v>
       </c>
       <c r="E107" t="n">
-        <v>47.2336</v>
+        <v>82.2307</v>
       </c>
       <c r="F107" t="n">
-        <v>80.55329999999999</v>
+        <v>242.986</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>56.2936</v>
+        <v>57.1275</v>
       </c>
       <c r="C108" t="n">
-        <v>101.662</v>
+        <v>101.11</v>
       </c>
       <c r="D108" t="n">
-        <v>256.348</v>
+        <v>254.644</v>
       </c>
       <c r="E108" t="n">
-        <v>80.72199999999999</v>
+        <v>80.2868</v>
       </c>
       <c r="F108" t="n">
-        <v>246.939</v>
+        <v>243.846</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>57.1778</v>
+        <v>46.0195</v>
       </c>
       <c r="C109" t="n">
-        <v>100.518</v>
+        <v>86.9158</v>
       </c>
       <c r="D109" t="n">
-        <v>254.005</v>
+        <v>252.014</v>
       </c>
       <c r="E109" t="n">
-        <v>79.4383</v>
+        <v>78.07989999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>248.469</v>
+        <v>243.921</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>87.9614</v>
+        <v>88.0175</v>
       </c>
       <c r="C110" t="n">
-        <v>99.51220000000001</v>
+        <v>99.2788</v>
       </c>
       <c r="D110" t="n">
-        <v>251.673</v>
+        <v>250.129</v>
       </c>
       <c r="E110" t="n">
-        <v>75.8596</v>
+        <v>76.1836</v>
       </c>
       <c r="F110" t="n">
-        <v>240.247</v>
+        <v>244.25</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>84.5136</v>
+        <v>74.7809</v>
       </c>
       <c r="C111" t="n">
-        <v>96.40170000000001</v>
+        <v>85.4789</v>
       </c>
       <c r="D111" t="n">
-        <v>241.339</v>
+        <v>250.553</v>
       </c>
       <c r="E111" t="n">
-        <v>73.81489999999999</v>
+        <v>73.5228</v>
       </c>
       <c r="F111" t="n">
-        <v>241.401</v>
+        <v>244.998</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>77.2662</v>
+        <v>82.9881</v>
       </c>
       <c r="C112" t="n">
-        <v>83.35420000000001</v>
+        <v>96.32899999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>239.946</v>
+        <v>247.383</v>
       </c>
       <c r="E112" t="n">
-        <v>71.8584</v>
+        <v>62.7303</v>
       </c>
       <c r="F112" t="n">
-        <v>242.49</v>
+        <v>245.276</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>73.143</v>
+        <v>82.72239999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>82.4136</v>
+        <v>95.0821</v>
       </c>
       <c r="D113" t="n">
-        <v>240.994</v>
+        <v>248.671</v>
       </c>
       <c r="E113" t="n">
-        <v>61.2105</v>
+        <v>61.3175</v>
       </c>
       <c r="F113" t="n">
-        <v>242.958</v>
+        <v>245.594</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>71.6981</v>
+        <v>78.10169999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>81.8702</v>
+        <v>93.6534</v>
       </c>
       <c r="D114" t="n">
-        <v>244.299</v>
+        <v>247.567</v>
       </c>
       <c r="E114" t="n">
-        <v>68.0485</v>
+        <v>68.1221</v>
       </c>
       <c r="F114" t="n">
-        <v>244.492</v>
+        <v>246.511</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>74.39230000000001</v>
+        <v>78.4181</v>
       </c>
       <c r="C115" t="n">
-        <v>91.08839999999999</v>
+        <v>92.47929999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>250.102</v>
+        <v>255.07</v>
       </c>
       <c r="E115" t="n">
-        <v>66.30889999999999</v>
+        <v>66.48569999999999</v>
       </c>
       <c r="F115" t="n">
-        <v>243.782</v>
+        <v>246.118</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>75.13809999999999</v>
+        <v>68.40479999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>89.8124</v>
+        <v>81.5891</v>
       </c>
       <c r="D116" t="n">
-        <v>242.229</v>
+        <v>259.178</v>
       </c>
       <c r="E116" t="n">
-        <v>64.53619999999999</v>
+        <v>64.8314</v>
       </c>
       <c r="F116" t="n">
-        <v>243.918</v>
+        <v>247.109</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>72.7871</v>
+        <v>74.8263</v>
       </c>
       <c r="C117" t="n">
-        <v>88.6763</v>
+        <v>90.1234</v>
       </c>
       <c r="D117" t="n">
-        <v>251.519</v>
+        <v>259.96</v>
       </c>
       <c r="E117" t="n">
-        <v>63.1387</v>
+        <v>63.4213</v>
       </c>
       <c r="F117" t="n">
-        <v>243.106</v>
+        <v>246.949</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>65.6728</v>
+        <v>72.9761</v>
       </c>
       <c r="C118" t="n">
-        <v>78.7949</v>
+        <v>89.0651</v>
       </c>
       <c r="D118" t="n">
-        <v>237.823</v>
+        <v>244.732</v>
       </c>
       <c r="E118" t="n">
-        <v>55.1218</v>
+        <v>55.023</v>
       </c>
       <c r="F118" t="n">
-        <v>242.793</v>
+        <v>247.501</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>69.5167</v>
+        <v>71.512</v>
       </c>
       <c r="C119" t="n">
-        <v>86.48909999999999</v>
+        <v>87.976</v>
       </c>
       <c r="D119" t="n">
-        <v>238.883</v>
+        <v>245.412</v>
       </c>
       <c r="E119" t="n">
-        <v>53.914</v>
+        <v>54.2677</v>
       </c>
       <c r="F119" t="n">
-        <v>222.089</v>
+        <v>101.906</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>61.1344</v>
+        <v>69.4834</v>
       </c>
       <c r="C120" t="n">
-        <v>77.7512</v>
+        <v>87.0966</v>
       </c>
       <c r="D120" t="n">
-        <v>239.757</v>
+        <v>246.617</v>
       </c>
       <c r="E120" t="n">
-        <v>53.0327</v>
+        <v>53.3536</v>
       </c>
       <c r="F120" t="n">
-        <v>220.945</v>
+        <v>151.905</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>60.6189</v>
+        <v>69.36969999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>77.1692</v>
+        <v>86.1307</v>
       </c>
       <c r="D121" t="n">
-        <v>316.55</v>
+        <v>325.488</v>
       </c>
       <c r="E121" t="n">
-        <v>52.1849</v>
+        <v>88.5763</v>
       </c>
       <c r="F121" t="n">
-        <v>223.455</v>
+        <v>295.432</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>61.929</v>
+        <v>61.1764</v>
       </c>
       <c r="C122" t="n">
-        <v>111.349</v>
+        <v>113.204</v>
       </c>
       <c r="D122" t="n">
-        <v>311.34</v>
+        <v>320.607</v>
       </c>
       <c r="E122" t="n">
-        <v>51.5317</v>
+        <v>86.6969</v>
       </c>
       <c r="F122" t="n">
-        <v>199.428</v>
+        <v>295.43</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>60.8276</v>
+        <v>62.0775</v>
       </c>
       <c r="C123" t="n">
-        <v>110.321</v>
+        <v>112.144</v>
       </c>
       <c r="D123" t="n">
-        <v>306.895</v>
+        <v>316.196</v>
       </c>
       <c r="E123" t="n">
-        <v>83.8659</v>
+        <v>84.9915</v>
       </c>
       <c r="F123" t="n">
-        <v>289.733</v>
+        <v>295.154</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>92.5351</v>
+        <v>93.1514</v>
       </c>
       <c r="C124" t="n">
-        <v>109.922</v>
+        <v>111.843</v>
       </c>
       <c r="D124" t="n">
-        <v>303.601</v>
+        <v>312.508</v>
       </c>
       <c r="E124" t="n">
-        <v>82.1648</v>
+        <v>83.4071</v>
       </c>
       <c r="F124" t="n">
-        <v>289.011</v>
+        <v>293.747</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>88.92829999999999</v>
+        <v>96.6307</v>
       </c>
       <c r="C125" t="n">
-        <v>108.644</v>
+        <v>116.826</v>
       </c>
       <c r="D125" t="n">
-        <v>299.987</v>
+        <v>308.967</v>
       </c>
       <c r="E125" t="n">
-        <v>80.5271</v>
+        <v>81.5624</v>
       </c>
       <c r="F125" t="n">
-        <v>289.29</v>
+        <v>294.405</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>88.9464</v>
+        <v>89.5472</v>
       </c>
       <c r="C126" t="n">
-        <v>107.591</v>
+        <v>109.493</v>
       </c>
       <c r="D126" t="n">
-        <v>297.235</v>
+        <v>305.98</v>
       </c>
       <c r="E126" t="n">
-        <v>78.9366</v>
+        <v>84.70050000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>288.037</v>
+        <v>293.624</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>86.76009999999999</v>
+        <v>92.9491</v>
       </c>
       <c r="C127" t="n">
-        <v>106.523</v>
+        <v>114.087</v>
       </c>
       <c r="D127" t="n">
-        <v>294.396</v>
+        <v>303.263</v>
       </c>
       <c r="E127" t="n">
-        <v>77.25060000000001</v>
+        <v>78.3489</v>
       </c>
       <c r="F127" t="n">
-        <v>287.364</v>
+        <v>292.584</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>84.2542</v>
+        <v>86.7213</v>
       </c>
       <c r="C128" t="n">
-        <v>105.49</v>
+        <v>107.531</v>
       </c>
       <c r="D128" t="n">
-        <v>292.128</v>
+        <v>301</v>
       </c>
       <c r="E128" t="n">
-        <v>75.8687</v>
+        <v>77.0727</v>
       </c>
       <c r="F128" t="n">
-        <v>287.475</v>
+        <v>292.825</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>83.26009999999999</v>
+        <v>88.6069</v>
       </c>
       <c r="C129" t="n">
-        <v>104.467</v>
+        <v>111.664</v>
       </c>
       <c r="D129" t="n">
-        <v>290.335</v>
+        <v>298.846</v>
       </c>
       <c r="E129" t="n">
-        <v>74.5168</v>
+        <v>75.5311</v>
       </c>
       <c r="F129" t="n">
-        <v>286.499</v>
+        <v>292.439</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>80.7899</v>
+        <v>87.74979999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>103.467</v>
+        <v>110.595</v>
       </c>
       <c r="D130" t="n">
-        <v>288.871</v>
+        <v>297.544</v>
       </c>
       <c r="E130" t="n">
-        <v>73.0659</v>
+        <v>74.1828</v>
       </c>
       <c r="F130" t="n">
-        <v>286.339</v>
+        <v>291.946</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>80.9576</v>
+        <v>81.9689</v>
       </c>
       <c r="C131" t="n">
-        <v>102.605</v>
+        <v>104.947</v>
       </c>
       <c r="D131" t="n">
-        <v>287.752</v>
+        <v>296.426</v>
       </c>
       <c r="E131" t="n">
-        <v>71.9216</v>
+        <v>73.0475</v>
       </c>
       <c r="F131" t="n">
-        <v>286.543</v>
+        <v>291.825</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>79.9422</v>
+        <v>81.96939999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>101.933</v>
+        <v>104.129</v>
       </c>
       <c r="D132" t="n">
-        <v>287.108</v>
+        <v>295.646</v>
       </c>
       <c r="E132" t="n">
-        <v>70.8865</v>
+        <v>75.4265</v>
       </c>
       <c r="F132" t="n">
-        <v>286.306</v>
+        <v>291.969</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>71.7625</v>
+        <v>77.0275</v>
       </c>
       <c r="C133" t="n">
-        <v>92.31059999999999</v>
+        <v>94.5334</v>
       </c>
       <c r="D133" t="n">
-        <v>287.634</v>
+        <v>295.359</v>
       </c>
       <c r="E133" t="n">
-        <v>69.7715</v>
+        <v>70.9892</v>
       </c>
       <c r="F133" t="n">
-        <v>286.012</v>
+        <v>292.421</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>78.057</v>
+        <v>80.3351</v>
       </c>
       <c r="C134" t="n">
-        <v>100.443</v>
+        <v>102.79</v>
       </c>
       <c r="D134" t="n">
-        <v>282.033</v>
+        <v>290.168</v>
       </c>
       <c r="E134" t="n">
-        <v>68.79649999999999</v>
+        <v>63.9023</v>
       </c>
       <c r="F134" t="n">
-        <v>286.062</v>
+        <v>240.008</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>76.5617</v>
+        <v>77.96729999999999</v>
       </c>
       <c r="C135" t="n">
-        <v>99.7814</v>
+        <v>102.071</v>
       </c>
       <c r="D135" t="n">
-        <v>361.669</v>
+        <v>372.588</v>
       </c>
       <c r="E135" t="n">
-        <v>62.1727</v>
+        <v>99.6489</v>
       </c>
       <c r="F135" t="n">
-        <v>260.176</v>
+        <v>335.635</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>75.0026</v>
+        <v>77.1909</v>
       </c>
       <c r="C136" t="n">
-        <v>133.623</v>
+        <v>135.457</v>
       </c>
       <c r="D136" t="n">
-        <v>355.313</v>
+        <v>365.77</v>
       </c>
       <c r="E136" t="n">
-        <v>61.6108</v>
+        <v>97.8896</v>
       </c>
       <c r="F136" t="n">
-        <v>285.554</v>
+        <v>335.104</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>74.5715</v>
+        <v>76.7955</v>
       </c>
       <c r="C137" t="n">
-        <v>132.352</v>
+        <v>133.918</v>
       </c>
       <c r="D137" t="n">
-        <v>349.814</v>
+        <v>360.358</v>
       </c>
       <c r="E137" t="n">
-        <v>94.3673</v>
+        <v>95.8712</v>
       </c>
       <c r="F137" t="n">
-        <v>326.24</v>
+        <v>335.483</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>99.2368</v>
+        <v>109.359</v>
       </c>
       <c r="C138" t="n">
-        <v>124.705</v>
+        <v>134.988</v>
       </c>
       <c r="D138" t="n">
-        <v>345.881</v>
+        <v>354.863</v>
       </c>
       <c r="E138" t="n">
-        <v>92.8784</v>
+        <v>94.6071</v>
       </c>
       <c r="F138" t="n">
-        <v>325.018</v>
+        <v>334.57</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>101.462</v>
+        <v>102.817</v>
       </c>
       <c r="C139" t="n">
-        <v>123.955</v>
+        <v>126.756</v>
       </c>
       <c r="D139" t="n">
-        <v>339.726</v>
+        <v>350.226</v>
       </c>
       <c r="E139" t="n">
-        <v>91.21550000000001</v>
+        <v>93.18510000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>326.695</v>
+        <v>333.898</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>102.488</v>
+        <v>105.811</v>
       </c>
       <c r="C140" t="n">
-        <v>129.528</v>
+        <v>132.435</v>
       </c>
       <c r="D140" t="n">
-        <v>335.156</v>
+        <v>345.617</v>
       </c>
       <c r="E140" t="n">
-        <v>89.6434</v>
+        <v>96.2071</v>
       </c>
       <c r="F140" t="n">
-        <v>325.557</v>
+        <v>332.379</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>95.7452</v>
+        <v>103.914</v>
       </c>
       <c r="C141" t="n">
-        <v>122.361</v>
+        <v>131.42</v>
       </c>
       <c r="D141" t="n">
-        <v>331.812</v>
+        <v>343.787</v>
       </c>
       <c r="E141" t="n">
-        <v>88.3437</v>
+        <v>94.5018</v>
       </c>
       <c r="F141" t="n">
-        <v>324.388</v>
+        <v>332.558</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>95.3185</v>
+        <v>98.8753</v>
       </c>
       <c r="C142" t="n">
-        <v>121.592</v>
+        <v>124.649</v>
       </c>
       <c r="D142" t="n">
-        <v>332.381</v>
+        <v>343.885</v>
       </c>
       <c r="E142" t="n">
-        <v>86.7683</v>
+        <v>92.5523</v>
       </c>
       <c r="F142" t="n">
-        <v>323.073</v>
+        <v>331.032</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>97.15860000000001</v>
+        <v>100.418</v>
       </c>
       <c r="C143" t="n">
-        <v>126.135</v>
+        <v>129.406</v>
       </c>
       <c r="D143" t="n">
-        <v>330.262</v>
+        <v>341.782</v>
       </c>
       <c r="E143" t="n">
-        <v>85.6636</v>
+        <v>87.4093</v>
       </c>
       <c r="F143" t="n">
-        <v>322.481</v>
+        <v>329.533</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>21.9934</v>
+        <v>21.9872</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5602</v>
+        <v>24.5498</v>
       </c>
       <c r="D2" t="n">
-        <v>55.5444</v>
+        <v>55.5978</v>
       </c>
       <c r="E2" t="n">
-        <v>17.7881</v>
+        <v>17.8594</v>
       </c>
       <c r="F2" t="n">
-        <v>33.1749</v>
+        <v>33.2854</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>21.2522</v>
+        <v>21.2014</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0409</v>
+        <v>24.0394</v>
       </c>
       <c r="D3" t="n">
-        <v>54.9582</v>
+        <v>54.9375</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3404</v>
+        <v>17.3214</v>
       </c>
       <c r="F3" t="n">
-        <v>32.7684</v>
+        <v>32.8241</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>21.8406</v>
+        <v>20.8022</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5642</v>
+        <v>23.5692</v>
       </c>
       <c r="D4" t="n">
-        <v>54.3843</v>
+        <v>54.4251</v>
       </c>
       <c r="E4" t="n">
-        <v>16.9211</v>
+        <v>16.8468</v>
       </c>
       <c r="F4" t="n">
-        <v>32.4289</v>
+        <v>32.4482</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>20.1757</v>
+        <v>19.9354</v>
       </c>
       <c r="C5" t="n">
-        <v>23.1293</v>
+        <v>23.1373</v>
       </c>
       <c r="D5" t="n">
-        <v>53.9922</v>
+        <v>54.0899</v>
       </c>
       <c r="E5" t="n">
-        <v>16.4774</v>
+        <v>16.5517</v>
       </c>
       <c r="F5" t="n">
-        <v>32.1985</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>19.9644</v>
+        <v>19.5174</v>
       </c>
       <c r="C6" t="n">
-        <v>22.7078</v>
+        <v>22.782</v>
       </c>
       <c r="D6" t="n">
-        <v>53.5434</v>
+        <v>53.7664</v>
       </c>
       <c r="E6" t="n">
-        <v>16.1408</v>
+        <v>16.1915</v>
       </c>
       <c r="F6" t="n">
-        <v>32.0154</v>
+        <v>32.0745</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3009</v>
+        <v>19.4681</v>
       </c>
       <c r="C7" t="n">
-        <v>22.4729</v>
+        <v>22.4352</v>
       </c>
       <c r="D7" t="n">
-        <v>68.40389999999999</v>
+        <v>68.313</v>
       </c>
       <c r="E7" t="n">
-        <v>24.816</v>
+        <v>24.8336</v>
       </c>
       <c r="F7" t="n">
-        <v>40.0229</v>
+        <v>39.9945</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>18.6565</v>
+        <v>19.0642</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8272</v>
+        <v>30.9108</v>
       </c>
       <c r="D8" t="n">
-        <v>66.7346</v>
+        <v>66.8045</v>
       </c>
       <c r="E8" t="n">
-        <v>24.0086</v>
+        <v>24.0159</v>
       </c>
       <c r="F8" t="n">
-        <v>39.0589</v>
+        <v>39.1177</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>20.0213</v>
+        <v>19.7905</v>
       </c>
       <c r="C9" t="n">
-        <v>30.0232</v>
+        <v>30.1068</v>
       </c>
       <c r="D9" t="n">
-        <v>65.50279999999999</v>
+        <v>65.42619999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>23.1875</v>
+        <v>23.2447</v>
       </c>
       <c r="F9" t="n">
-        <v>38.2137</v>
+        <v>38.232</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.8693</v>
+        <v>27.6998</v>
       </c>
       <c r="C10" t="n">
-        <v>29.2583</v>
+        <v>29.3328</v>
       </c>
       <c r="D10" t="n">
-        <v>64.2872</v>
+        <v>64.2878</v>
       </c>
       <c r="E10" t="n">
-        <v>22.3892</v>
+        <v>22.5165</v>
       </c>
       <c r="F10" t="n">
-        <v>37.4646</v>
+        <v>37.4748</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>26.8201</v>
+        <v>27.0436</v>
       </c>
       <c r="C11" t="n">
-        <v>28.4893</v>
+        <v>28.551</v>
       </c>
       <c r="D11" t="n">
-        <v>63.2296</v>
+        <v>63.1545</v>
       </c>
       <c r="E11" t="n">
-        <v>21.7052</v>
+        <v>21.6661</v>
       </c>
       <c r="F11" t="n">
-        <v>36.7042</v>
+        <v>36.7035</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.424</v>
+        <v>25.9947</v>
       </c>
       <c r="C12" t="n">
-        <v>27.7822</v>
+        <v>27.8441</v>
       </c>
       <c r="D12" t="n">
-        <v>62.2078</v>
+        <v>62.1073</v>
       </c>
       <c r="E12" t="n">
-        <v>20.9803</v>
+        <v>21.6807</v>
       </c>
       <c r="F12" t="n">
-        <v>35.9356</v>
+        <v>36.0131</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.354</v>
+        <v>24.9958</v>
       </c>
       <c r="C13" t="n">
-        <v>27.1131</v>
+        <v>27.4012</v>
       </c>
       <c r="D13" t="n">
-        <v>61.2707</v>
+        <v>61.2146</v>
       </c>
       <c r="E13" t="n">
-        <v>20.3349</v>
+        <v>20.3681</v>
       </c>
       <c r="F13" t="n">
-        <v>35.3111</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.6202</v>
+        <v>24.431</v>
       </c>
       <c r="C14" t="n">
-        <v>26.4804</v>
+        <v>26.4852</v>
       </c>
       <c r="D14" t="n">
-        <v>60.4603</v>
+        <v>60.5545</v>
       </c>
       <c r="E14" t="n">
-        <v>19.7278</v>
+        <v>19.8553</v>
       </c>
       <c r="F14" t="n">
-        <v>34.7402</v>
+        <v>34.867</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.6829</v>
+        <v>23.9156</v>
       </c>
       <c r="C15" t="n">
-        <v>25.8541</v>
+        <v>25.88</v>
       </c>
       <c r="D15" t="n">
-        <v>60.0404</v>
+        <v>59.9313</v>
       </c>
       <c r="E15" t="n">
-        <v>19.2548</v>
+        <v>19.2391</v>
       </c>
       <c r="F15" t="n">
-        <v>34.197</v>
+        <v>34.2551</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.0995</v>
+        <v>23.1265</v>
       </c>
       <c r="C16" t="n">
-        <v>25.2678</v>
+        <v>25.3096</v>
       </c>
       <c r="D16" t="n">
-        <v>59.3326</v>
+        <v>59.5355</v>
       </c>
       <c r="E16" t="n">
-        <v>18.6709</v>
+        <v>18.7085</v>
       </c>
       <c r="F16" t="n">
-        <v>33.7295</v>
+        <v>33.7923</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.3261</v>
+        <v>22.445</v>
       </c>
       <c r="C17" t="n">
-        <v>24.7375</v>
+        <v>24.789</v>
       </c>
       <c r="D17" t="n">
-        <v>58.8758</v>
+        <v>58.9085</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2122</v>
+        <v>18.285</v>
       </c>
       <c r="F17" t="n">
-        <v>33.2784</v>
+        <v>33.357</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>21.5681</v>
+        <v>22.3345</v>
       </c>
       <c r="C18" t="n">
-        <v>24.2655</v>
+        <v>24.3301</v>
       </c>
       <c r="D18" t="n">
-        <v>58.289</v>
+        <v>58.1433</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7804</v>
+        <v>17.7996</v>
       </c>
       <c r="F18" t="n">
-        <v>32.8928</v>
+        <v>32.9549</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.3614</v>
+        <v>21.2592</v>
       </c>
       <c r="C19" t="n">
-        <v>23.791</v>
+        <v>23.81</v>
       </c>
       <c r="D19" t="n">
-        <v>57.5843</v>
+        <v>57.5989</v>
       </c>
       <c r="E19" t="n">
-        <v>17.4099</v>
+        <v>17.428</v>
       </c>
       <c r="F19" t="n">
-        <v>32.5671</v>
+        <v>32.6395</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>21.1523</v>
+        <v>21.2506</v>
       </c>
       <c r="C20" t="n">
-        <v>23.3959</v>
+        <v>23.4437</v>
       </c>
       <c r="D20" t="n">
-        <v>57.2591</v>
+        <v>57.262</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1034</v>
+        <v>17.1412</v>
       </c>
       <c r="F20" t="n">
-        <v>32.3978</v>
+        <v>32.5117</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.5584</v>
+        <v>20.3226</v>
       </c>
       <c r="C21" t="n">
-        <v>23.2487</v>
+        <v>23.2276</v>
       </c>
       <c r="D21" t="n">
-        <v>74.7681</v>
+        <v>74.8485</v>
       </c>
       <c r="E21" t="n">
-        <v>25.8668</v>
+        <v>26.1173</v>
       </c>
       <c r="F21" t="n">
-        <v>40.3189</v>
+        <v>40.6407</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.5422</v>
+        <v>20.4398</v>
       </c>
       <c r="C22" t="n">
-        <v>31.5413</v>
+        <v>31.5361</v>
       </c>
       <c r="D22" t="n">
-        <v>73.2394</v>
+        <v>73.3068</v>
       </c>
       <c r="E22" t="n">
-        <v>24.9675</v>
+        <v>25.0293</v>
       </c>
       <c r="F22" t="n">
-        <v>39.4555</v>
+        <v>39.7287</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>20.4223</v>
+        <v>20.5869</v>
       </c>
       <c r="C23" t="n">
-        <v>30.7577</v>
+        <v>30.8055</v>
       </c>
       <c r="D23" t="n">
-        <v>71.87009999999999</v>
+        <v>71.9371</v>
       </c>
       <c r="E23" t="n">
-        <v>24.1316</v>
+        <v>24.147</v>
       </c>
       <c r="F23" t="n">
-        <v>38.6305</v>
+        <v>38.9231</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>29.1625</v>
+        <v>28.6314</v>
       </c>
       <c r="C24" t="n">
-        <v>29.9883</v>
+        <v>30.0204</v>
       </c>
       <c r="D24" t="n">
-        <v>70.48309999999999</v>
+        <v>70.55289999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>23.3379</v>
+        <v>23.4209</v>
       </c>
       <c r="F24" t="n">
-        <v>37.8792</v>
+        <v>38.1336</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>28.2541</v>
+        <v>27.5531</v>
       </c>
       <c r="C25" t="n">
-        <v>29.2142</v>
+        <v>29.2816</v>
       </c>
       <c r="D25" t="n">
-        <v>69.26560000000001</v>
+        <v>69.3922</v>
       </c>
       <c r="E25" t="n">
-        <v>22.599</v>
+        <v>22.6517</v>
       </c>
       <c r="F25" t="n">
-        <v>37.1332</v>
+        <v>37.3404</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>26.5894</v>
+        <v>26.6666</v>
       </c>
       <c r="C26" t="n">
-        <v>28.5071</v>
+        <v>28.5512</v>
       </c>
       <c r="D26" t="n">
-        <v>68.0813</v>
+        <v>68.176</v>
       </c>
       <c r="E26" t="n">
-        <v>21.9917</v>
+        <v>21.9369</v>
       </c>
       <c r="F26" t="n">
-        <v>36.8555</v>
+        <v>36.8916</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>25.9328</v>
+        <v>26.7545</v>
       </c>
       <c r="C27" t="n">
-        <v>27.8395</v>
+        <v>27.8766</v>
       </c>
       <c r="D27" t="n">
-        <v>67.1341</v>
+        <v>67.2779</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2597</v>
+        <v>21.2567</v>
       </c>
       <c r="F27" t="n">
-        <v>36.2357</v>
+        <v>36.1754</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.1505</v>
+        <v>25.1544</v>
       </c>
       <c r="C28" t="n">
-        <v>27.1783</v>
+        <v>27.1816</v>
       </c>
       <c r="D28" t="n">
-        <v>66.1707</v>
+        <v>66.2531</v>
       </c>
       <c r="E28" t="n">
-        <v>20.5789</v>
+        <v>20.545</v>
       </c>
       <c r="F28" t="n">
-        <v>35.594</v>
+        <v>35.5852</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>24.3988</v>
+        <v>25.1351</v>
       </c>
       <c r="C29" t="n">
-        <v>26.5639</v>
+        <v>26.6113</v>
       </c>
       <c r="D29" t="n">
-        <v>65.53279999999999</v>
+        <v>65.598</v>
       </c>
       <c r="E29" t="n">
-        <v>20.0119</v>
+        <v>20.0441</v>
       </c>
       <c r="F29" t="n">
-        <v>35.0334</v>
+        <v>35.0673</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>23.682</v>
+        <v>23.6969</v>
       </c>
       <c r="C30" t="n">
-        <v>25.9886</v>
+        <v>25.9774</v>
       </c>
       <c r="D30" t="n">
-        <v>64.73950000000001</v>
+        <v>64.71210000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>19.4759</v>
+        <v>19.4224</v>
       </c>
       <c r="F30" t="n">
-        <v>34.4996</v>
+        <v>34.5054</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.4814</v>
+        <v>23.0198</v>
       </c>
       <c r="C31" t="n">
-        <v>25.5436</v>
+        <v>25.4201</v>
       </c>
       <c r="D31" t="n">
-        <v>64.23820000000001</v>
+        <v>64.1968</v>
       </c>
       <c r="E31" t="n">
-        <v>18.9369</v>
+        <v>18.9366</v>
       </c>
       <c r="F31" t="n">
-        <v>33.4259</v>
+        <v>33.4575</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>23.088</v>
+        <v>23.5076</v>
       </c>
       <c r="C32" t="n">
-        <v>24.935</v>
+        <v>24.9702</v>
       </c>
       <c r="D32" t="n">
-        <v>63.7921</v>
+        <v>63.7702</v>
       </c>
       <c r="E32" t="n">
-        <v>18.5284</v>
+        <v>18.5058</v>
       </c>
       <c r="F32" t="n">
-        <v>33.0628</v>
+        <v>33.3341</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>22.5296</v>
+        <v>22.6226</v>
       </c>
       <c r="C33" t="n">
-        <v>24.4765</v>
+        <v>24.5439</v>
       </c>
       <c r="D33" t="n">
-        <v>63.3981</v>
+        <v>63.4031</v>
       </c>
       <c r="E33" t="n">
-        <v>18.2369</v>
+        <v>18.1673</v>
       </c>
       <c r="F33" t="n">
-        <v>32.9699</v>
+        <v>32.9385</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>22.0765</v>
+        <v>22.0426</v>
       </c>
       <c r="C34" t="n">
-        <v>24.0534</v>
+        <v>24.0999</v>
       </c>
       <c r="D34" t="n">
-        <v>62.6302</v>
+        <v>62.7091</v>
       </c>
       <c r="E34" t="n">
-        <v>17.8635</v>
+        <v>17.8552</v>
       </c>
       <c r="F34" t="n">
-        <v>32.7486</v>
+        <v>32.7567</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>21.7739</v>
+        <v>21.1077</v>
       </c>
       <c r="C35" t="n">
-        <v>23.7449</v>
+        <v>23.7587</v>
       </c>
       <c r="D35" t="n">
-        <v>81.0187</v>
+        <v>80.97709999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>26.765</v>
+        <v>26.6007</v>
       </c>
       <c r="F35" t="n">
-        <v>41.3487</v>
+        <v>41.4983</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>21.2461</v>
+        <v>21.2048</v>
       </c>
       <c r="C36" t="n">
-        <v>23.4766</v>
+        <v>23.4848</v>
       </c>
       <c r="D36" t="n">
-        <v>79.30410000000001</v>
+        <v>79.3026</v>
       </c>
       <c r="E36" t="n">
-        <v>25.9468</v>
+        <v>25.7688</v>
       </c>
       <c r="F36" t="n">
-        <v>40.5407</v>
+        <v>40.7226</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>21.0891</v>
+        <v>20.6637</v>
       </c>
       <c r="C37" t="n">
-        <v>31.6155</v>
+        <v>31.784</v>
       </c>
       <c r="D37" t="n">
-        <v>77.74809999999999</v>
+        <v>77.7668</v>
       </c>
       <c r="E37" t="n">
-        <v>25.1025</v>
+        <v>24.9616</v>
       </c>
       <c r="F37" t="n">
-        <v>39.7476</v>
+        <v>39.9404</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>29.7262</v>
+        <v>29.4554</v>
       </c>
       <c r="C38" t="n">
-        <v>30.8865</v>
+        <v>30.8393</v>
       </c>
       <c r="D38" t="n">
-        <v>76.2804</v>
+        <v>76.2316</v>
       </c>
       <c r="E38" t="n">
-        <v>24.2994</v>
+        <v>24.2023</v>
       </c>
       <c r="F38" t="n">
-        <v>39.0996</v>
+        <v>39.3209</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>27.9831</v>
+        <v>28.5735</v>
       </c>
       <c r="C39" t="n">
-        <v>30.1737</v>
+        <v>30.225</v>
       </c>
       <c r="D39" t="n">
-        <v>74.9294</v>
+        <v>74.9838</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5899</v>
+        <v>23.5269</v>
       </c>
       <c r="F39" t="n">
-        <v>38.2814</v>
+        <v>38.3909</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>27.147</v>
+        <v>27.6938</v>
       </c>
       <c r="C40" t="n">
-        <v>29.362</v>
+        <v>29.5018</v>
       </c>
       <c r="D40" t="n">
-        <v>73.7295</v>
+        <v>73.78959999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>22.9433</v>
+        <v>22.7724</v>
       </c>
       <c r="F40" t="n">
-        <v>37.616</v>
+        <v>37.5663</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.4175</v>
+        <v>26.7043</v>
       </c>
       <c r="C41" t="n">
-        <v>28.914</v>
+        <v>28.7812</v>
       </c>
       <c r="D41" t="n">
-        <v>72.6504</v>
+        <v>72.5397</v>
       </c>
       <c r="E41" t="n">
-        <v>22.2205</v>
+        <v>22.1176</v>
       </c>
       <c r="F41" t="n">
-        <v>36.9418</v>
+        <v>36.994</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>25.4461</v>
+        <v>25.6332</v>
       </c>
       <c r="C42" t="n">
-        <v>28.2786</v>
+        <v>28.2673</v>
       </c>
       <c r="D42" t="n">
-        <v>71.65600000000001</v>
+        <v>71.79300000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>21.6317</v>
+        <v>21.5425</v>
       </c>
       <c r="F42" t="n">
-        <v>36.3862</v>
+        <v>36.4268</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>24.9394</v>
+        <v>25.3158</v>
       </c>
       <c r="C43" t="n">
-        <v>27.8197</v>
+        <v>27.5544</v>
       </c>
       <c r="D43" t="n">
-        <v>70.5638</v>
+        <v>70.4302</v>
       </c>
       <c r="E43" t="n">
-        <v>21.1325</v>
+        <v>20.9435</v>
       </c>
       <c r="F43" t="n">
-        <v>35.8681</v>
+        <v>35.9084</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.2299</v>
+        <v>24.385</v>
       </c>
       <c r="C44" t="n">
-        <v>27.1042</v>
+        <v>26.9849</v>
       </c>
       <c r="D44" t="n">
-        <v>69.7383</v>
+        <v>69.7152</v>
       </c>
       <c r="E44" t="n">
-        <v>20.512</v>
+        <v>20.5102</v>
       </c>
       <c r="F44" t="n">
-        <v>35.4109</v>
+        <v>35.3897</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>24.1041</v>
+        <v>23.7284</v>
       </c>
       <c r="C45" t="n">
-        <v>26.739</v>
+        <v>26.67</v>
       </c>
       <c r="D45" t="n">
-        <v>69.0624</v>
+        <v>69.11790000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>20.154</v>
+        <v>19.9416</v>
       </c>
       <c r="F45" t="n">
-        <v>35.0628</v>
+        <v>34.9247</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>23.1144</v>
+        <v>23.0855</v>
       </c>
       <c r="C46" t="n">
-        <v>26.3236</v>
+        <v>26.1393</v>
       </c>
       <c r="D46" t="n">
-        <v>68.5322</v>
+        <v>68.4836</v>
       </c>
       <c r="E46" t="n">
-        <v>19.6525</v>
+        <v>19.454</v>
       </c>
       <c r="F46" t="n">
-        <v>34.6684</v>
+        <v>34.5347</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.519</v>
+        <v>22.3674</v>
       </c>
       <c r="C47" t="n">
-        <v>25.8256</v>
+        <v>25.5549</v>
       </c>
       <c r="D47" t="n">
-        <v>68.09650000000001</v>
+        <v>68.0423</v>
       </c>
       <c r="E47" t="n">
-        <v>19.3098</v>
+        <v>19.145</v>
       </c>
       <c r="F47" t="n">
-        <v>34.3822</v>
+        <v>34.1671</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>22.0713</v>
+        <v>21.9338</v>
       </c>
       <c r="C48" t="n">
-        <v>25.0324</v>
+        <v>25.202</v>
       </c>
       <c r="D48" t="n">
-        <v>67.348</v>
+        <v>67.3022</v>
       </c>
       <c r="E48" t="n">
-        <v>18.7606</v>
+        <v>18.8746</v>
       </c>
       <c r="F48" t="n">
-        <v>34.1697</v>
+        <v>33.9605</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>22.2564</v>
+        <v>21.9172</v>
       </c>
       <c r="C49" t="n">
-        <v>25.1591</v>
+        <v>24.9245</v>
       </c>
       <c r="D49" t="n">
-        <v>66.9586</v>
+        <v>66.94710000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>18.5383</v>
+        <v>18.5346</v>
       </c>
       <c r="F49" t="n">
-        <v>33.9992</v>
+        <v>33.8528</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.2606</v>
+        <v>21.2269</v>
       </c>
       <c r="C50" t="n">
-        <v>24.8256</v>
+        <v>24.5387</v>
       </c>
       <c r="D50" t="n">
-        <v>84.2265</v>
+        <v>84.20050000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>27.098</v>
+        <v>27.2401</v>
       </c>
       <c r="F50" t="n">
-        <v>42.002</v>
+        <v>42.3185</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>22.1644</v>
+        <v>21.1522</v>
       </c>
       <c r="C51" t="n">
-        <v>32.8373</v>
+        <v>32.7221</v>
       </c>
       <c r="D51" t="n">
-        <v>82.486</v>
+        <v>82.4426</v>
       </c>
       <c r="E51" t="n">
-        <v>26.4024</v>
+        <v>26.5743</v>
       </c>
       <c r="F51" t="n">
-        <v>41.7029</v>
+        <v>41.4397</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>22.0485</v>
+        <v>21.2064</v>
       </c>
       <c r="C52" t="n">
-        <v>32.0839</v>
+        <v>32.019</v>
       </c>
       <c r="D52" t="n">
-        <v>80.8522</v>
+        <v>80.8591</v>
       </c>
       <c r="E52" t="n">
-        <v>25.5061</v>
+        <v>25.5398</v>
       </c>
       <c r="F52" t="n">
-        <v>40.5896</v>
+        <v>40.4598</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.1209</v>
+        <v>29.4242</v>
       </c>
       <c r="C53" t="n">
-        <v>31.2902</v>
+        <v>31.4286</v>
       </c>
       <c r="D53" t="n">
-        <v>79.3396</v>
+        <v>79.3202</v>
       </c>
       <c r="E53" t="n">
-        <v>24.8044</v>
+        <v>24.9043</v>
       </c>
       <c r="F53" t="n">
-        <v>39.8397</v>
+        <v>39.9431</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>28.5446</v>
+        <v>28.6398</v>
       </c>
       <c r="C54" t="n">
-        <v>30.7512</v>
+        <v>30.827</v>
       </c>
       <c r="D54" t="n">
-        <v>77.93980000000001</v>
+        <v>77.9648</v>
       </c>
       <c r="E54" t="n">
-        <v>24.1286</v>
+        <v>24.2389</v>
       </c>
       <c r="F54" t="n">
-        <v>39.3138</v>
+        <v>39.2644</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>27.8911</v>
+        <v>28.005</v>
       </c>
       <c r="C55" t="n">
-        <v>30.198</v>
+        <v>30.2691</v>
       </c>
       <c r="D55" t="n">
-        <v>76.7193</v>
+        <v>76.7525</v>
       </c>
       <c r="E55" t="n">
-        <v>23.4383</v>
+        <v>23.5031</v>
       </c>
       <c r="F55" t="n">
-        <v>38.648</v>
+        <v>38.5641</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>26.7259</v>
+        <v>27.4461</v>
       </c>
       <c r="C56" t="n">
-        <v>29.5313</v>
+        <v>29.6066</v>
       </c>
       <c r="D56" t="n">
-        <v>75.717</v>
+        <v>75.6412</v>
       </c>
       <c r="E56" t="n">
-        <v>22.7854</v>
+        <v>22.8702</v>
       </c>
       <c r="F56" t="n">
-        <v>38.014</v>
+        <v>37.9039</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.0914</v>
+        <v>26.4455</v>
       </c>
       <c r="C57" t="n">
-        <v>29.1165</v>
+        <v>29.1528</v>
       </c>
       <c r="D57" t="n">
-        <v>74.52589999999999</v>
+        <v>74.50920000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>22.5272</v>
+        <v>22.3774</v>
       </c>
       <c r="F57" t="n">
-        <v>37.5708</v>
+        <v>37.4155</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>25.3202</v>
+        <v>26.0101</v>
       </c>
       <c r="C58" t="n">
-        <v>28.6538</v>
+        <v>28.4267</v>
       </c>
       <c r="D58" t="n">
-        <v>73.72</v>
+        <v>73.6883</v>
       </c>
       <c r="E58" t="n">
-        <v>21.6024</v>
+        <v>21.7868</v>
       </c>
       <c r="F58" t="n">
-        <v>37.1717</v>
+        <v>36.9598</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>24.7189</v>
+        <v>25.3231</v>
       </c>
       <c r="C59" t="n">
-        <v>28.1211</v>
+        <v>27.7192</v>
       </c>
       <c r="D59" t="n">
-        <v>72.8754</v>
+        <v>72.7941</v>
       </c>
       <c r="E59" t="n">
-        <v>21.376</v>
+        <v>21.2503</v>
       </c>
       <c r="F59" t="n">
-        <v>36.7213</v>
+        <v>36.4689</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>24.5541</v>
+        <v>24.2224</v>
       </c>
       <c r="C60" t="n">
-        <v>27.8861</v>
+        <v>27.3294</v>
       </c>
       <c r="D60" t="n">
-        <v>72.20999999999999</v>
+        <v>72.20310000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>20.7062</v>
+        <v>20.8063</v>
       </c>
       <c r="F60" t="n">
-        <v>36.2941</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>23.618</v>
+        <v>23.7656</v>
       </c>
       <c r="C61" t="n">
-        <v>27.3004</v>
+        <v>27.1922</v>
       </c>
       <c r="D61" t="n">
-        <v>71.4765</v>
+        <v>71.44450000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>20.3048</v>
+        <v>20.4182</v>
       </c>
       <c r="F61" t="n">
-        <v>35.9572</v>
+        <v>35.7579</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>23.3571</v>
+        <v>23.416</v>
       </c>
       <c r="C62" t="n">
-        <v>26.9696</v>
+        <v>26.5103</v>
       </c>
       <c r="D62" t="n">
-        <v>70.822</v>
+        <v>70.85380000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>19.9293</v>
+        <v>20.0701</v>
       </c>
       <c r="F62" t="n">
-        <v>35.7446</v>
+        <v>35.5105</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>22.7965</v>
+        <v>23.1922</v>
       </c>
       <c r="C63" t="n">
-        <v>26.5597</v>
+        <v>26.5806</v>
       </c>
       <c r="D63" t="n">
-        <v>70.4614</v>
+        <v>70.4594</v>
       </c>
       <c r="E63" t="n">
-        <v>19.8085</v>
+        <v>19.8099</v>
       </c>
       <c r="F63" t="n">
-        <v>35.6451</v>
+        <v>35.369</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>22.554</v>
+        <v>22.7457</v>
       </c>
       <c r="C64" t="n">
-        <v>26.5172</v>
+        <v>26.0198</v>
       </c>
       <c r="D64" t="n">
-        <v>91.5206</v>
+        <v>91.5795</v>
       </c>
       <c r="E64" t="n">
-        <v>31.191</v>
+        <v>33.1484</v>
       </c>
       <c r="F64" t="n">
-        <v>45.0562</v>
+        <v>45.1853</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>22.2205</v>
+        <v>22.5982</v>
       </c>
       <c r="C65" t="n">
-        <v>34.8028</v>
+        <v>35.4152</v>
       </c>
       <c r="D65" t="n">
-        <v>89.4492</v>
+        <v>89.3963</v>
       </c>
       <c r="E65" t="n">
-        <v>30.9373</v>
+        <v>32.447</v>
       </c>
       <c r="F65" t="n">
-        <v>44.5048</v>
+        <v>44.6922</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.7987</v>
+        <v>22.6007</v>
       </c>
       <c r="C66" t="n">
-        <v>34.4268</v>
+        <v>34.8461</v>
       </c>
       <c r="D66" t="n">
-        <v>87.6255</v>
+        <v>87.5857</v>
       </c>
       <c r="E66" t="n">
-        <v>29.6446</v>
+        <v>31.7201</v>
       </c>
       <c r="F66" t="n">
-        <v>43.9795</v>
+        <v>44.1212</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>35.5545</v>
+        <v>38.4989</v>
       </c>
       <c r="C67" t="n">
-        <v>34.0506</v>
+        <v>34.3178</v>
       </c>
       <c r="D67" t="n">
-        <v>85.9258</v>
+        <v>85.95820000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>29.6446</v>
+        <v>30.8482</v>
       </c>
       <c r="F67" t="n">
-        <v>43.4572</v>
+        <v>43.303</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>36.3011</v>
+        <v>37.0806</v>
       </c>
       <c r="C68" t="n">
-        <v>33.5892</v>
+        <v>33.9235</v>
       </c>
       <c r="D68" t="n">
-        <v>84.4666</v>
+        <v>84.47369999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>28.7771</v>
+        <v>29.9357</v>
       </c>
       <c r="F68" t="n">
-        <v>42.7934</v>
+        <v>43.0578</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>36.8016</v>
+        <v>36.606</v>
       </c>
       <c r="C69" t="n">
-        <v>33.164</v>
+        <v>33.694</v>
       </c>
       <c r="D69" t="n">
-        <v>82.9896</v>
+        <v>83.1525</v>
       </c>
       <c r="E69" t="n">
-        <v>28.1827</v>
+        <v>29.6414</v>
       </c>
       <c r="F69" t="n">
-        <v>42.1699</v>
+        <v>42.509</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>35.1034</v>
+        <v>35.9793</v>
       </c>
       <c r="C70" t="n">
-        <v>32.9377</v>
+        <v>33.4179</v>
       </c>
       <c r="D70" t="n">
-        <v>81.9622</v>
+        <v>82.1876</v>
       </c>
       <c r="E70" t="n">
-        <v>27.5742</v>
+        <v>28.7421</v>
       </c>
       <c r="F70" t="n">
-        <v>41.6717</v>
+        <v>41.9115</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>33.7056</v>
+        <v>35.2145</v>
       </c>
       <c r="C71" t="n">
-        <v>32.542</v>
+        <v>32.744</v>
       </c>
       <c r="D71" t="n">
-        <v>81.1234</v>
+        <v>81.4949</v>
       </c>
       <c r="E71" t="n">
-        <v>27.2026</v>
+        <v>28.0449</v>
       </c>
       <c r="F71" t="n">
-        <v>41.3721</v>
+        <v>41.4742</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>33.8739</v>
+        <v>33.3155</v>
       </c>
       <c r="C72" t="n">
-        <v>32.5327</v>
+        <v>32.6514</v>
       </c>
       <c r="D72" t="n">
-        <v>80.81870000000001</v>
+        <v>81.1058</v>
       </c>
       <c r="E72" t="n">
-        <v>27.6867</v>
+        <v>27.4154</v>
       </c>
       <c r="F72" t="n">
-        <v>40.9399</v>
+        <v>41.0953</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>33.0043</v>
+        <v>31.6419</v>
       </c>
       <c r="C73" t="n">
-        <v>32.0792</v>
+        <v>32.1968</v>
       </c>
       <c r="D73" t="n">
-        <v>80.52549999999999</v>
+        <v>80.8027</v>
       </c>
       <c r="E73" t="n">
-        <v>26.8001</v>
+        <v>26.8941</v>
       </c>
       <c r="F73" t="n">
-        <v>40.6487</v>
+        <v>40.7224</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>32.6702</v>
+        <v>32.8813</v>
       </c>
       <c r="C74" t="n">
-        <v>31.685</v>
+        <v>31.684</v>
       </c>
       <c r="D74" t="n">
-        <v>80.1122</v>
+        <v>80.35899999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>26.2689</v>
+        <v>26.5563</v>
       </c>
       <c r="F74" t="n">
-        <v>40.336</v>
+        <v>40.4008</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>32.6978</v>
+        <v>32.1114</v>
       </c>
       <c r="C75" t="n">
-        <v>31.3028</v>
+        <v>31.6625</v>
       </c>
       <c r="D75" t="n">
-        <v>79.2243</v>
+        <v>78.96729999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>25.9117</v>
+        <v>26.0218</v>
       </c>
       <c r="F75" t="n">
-        <v>40.0237</v>
+        <v>40.1572</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>30.9901</v>
+        <v>31.9179</v>
       </c>
       <c r="C76" t="n">
-        <v>31.0599</v>
+        <v>31.2469</v>
       </c>
       <c r="D76" t="n">
-        <v>79.3182</v>
+        <v>78.97369999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>25.434</v>
+        <v>25.2625</v>
       </c>
       <c r="F76" t="n">
-        <v>39.8716</v>
+        <v>39.9673</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>31.8039</v>
+        <v>32.3128</v>
       </c>
       <c r="C77" t="n">
-        <v>30.825</v>
+        <v>30.8857</v>
       </c>
       <c r="D77" t="n">
-        <v>79.5686</v>
+        <v>79.3053</v>
       </c>
       <c r="E77" t="n">
-        <v>25.016</v>
+        <v>25.1217</v>
       </c>
       <c r="F77" t="n">
-        <v>39.7962</v>
+        <v>39.963</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>29.5948</v>
+        <v>31.1892</v>
       </c>
       <c r="C78" t="n">
-        <v>30.5145</v>
+        <v>30.8638</v>
       </c>
       <c r="D78" t="n">
-        <v>129.884</v>
+        <v>129.808</v>
       </c>
       <c r="E78" t="n">
-        <v>42.6725</v>
+        <v>42.5405</v>
       </c>
       <c r="F78" t="n">
-        <v>64.271</v>
+        <v>64.3704</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>34.1335</v>
+        <v>34.3289</v>
       </c>
       <c r="C79" t="n">
-        <v>40.0359</v>
+        <v>40.6761</v>
       </c>
       <c r="D79" t="n">
-        <v>127.717</v>
+        <v>127.657</v>
       </c>
       <c r="E79" t="n">
-        <v>41.5168</v>
+        <v>41.9682</v>
       </c>
       <c r="F79" t="n">
-        <v>64.4679</v>
+        <v>64.5635</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>34.4213</v>
+        <v>32.4596</v>
       </c>
       <c r="C80" t="n">
-        <v>40.8749</v>
+        <v>41.2865</v>
       </c>
       <c r="D80" t="n">
-        <v>125.922</v>
+        <v>125.645</v>
       </c>
       <c r="E80" t="n">
-        <v>40.7784</v>
+        <v>41.2457</v>
       </c>
       <c r="F80" t="n">
-        <v>64.13</v>
+        <v>64.53789999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>48.4515</v>
+        <v>45.5792</v>
       </c>
       <c r="C81" t="n">
-        <v>41.3051</v>
+        <v>41.7564</v>
       </c>
       <c r="D81" t="n">
-        <v>124.348</v>
+        <v>124.161</v>
       </c>
       <c r="E81" t="n">
-        <v>40.0837</v>
+        <v>40.5971</v>
       </c>
       <c r="F81" t="n">
-        <v>63.7509</v>
+        <v>64.0117</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>44.5188</v>
+        <v>49.9322</v>
       </c>
       <c r="C82" t="n">
-        <v>41.4416</v>
+        <v>41.9557</v>
       </c>
       <c r="D82" t="n">
-        <v>123.047</v>
+        <v>122.844</v>
       </c>
       <c r="E82" t="n">
-        <v>39.2175</v>
+        <v>39.686</v>
       </c>
       <c r="F82" t="n">
-        <v>63.2264</v>
+        <v>63.4076</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>45.094</v>
+        <v>44.2949</v>
       </c>
       <c r="C83" t="n">
-        <v>41.7452</v>
+        <v>42.1867</v>
       </c>
       <c r="D83" t="n">
-        <v>122.118</v>
+        <v>122.044</v>
       </c>
       <c r="E83" t="n">
-        <v>38.3025</v>
+        <v>38.689</v>
       </c>
       <c r="F83" t="n">
-        <v>62.224</v>
+        <v>62.5588</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.3546</v>
+        <v>43.4612</v>
       </c>
       <c r="C84" t="n">
-        <v>41.8178</v>
+        <v>42.3608</v>
       </c>
       <c r="D84" t="n">
-        <v>121.714</v>
+        <v>121.726</v>
       </c>
       <c r="E84" t="n">
-        <v>37.5625</v>
+        <v>37.9377</v>
       </c>
       <c r="F84" t="n">
-        <v>61.3095</v>
+        <v>62.4521</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>43.7032</v>
+        <v>43.6533</v>
       </c>
       <c r="C85" t="n">
-        <v>41.9802</v>
+        <v>42.5424</v>
       </c>
       <c r="D85" t="n">
-        <v>121.528</v>
+        <v>121.269</v>
       </c>
       <c r="E85" t="n">
-        <v>36.4379</v>
+        <v>37.1704</v>
       </c>
       <c r="F85" t="n">
-        <v>60.4233</v>
+        <v>60.1118</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>40.6545</v>
+        <v>44.8508</v>
       </c>
       <c r="C86" t="n">
-        <v>42.2901</v>
+        <v>42.5668</v>
       </c>
       <c r="D86" t="n">
-        <v>121.657</v>
+        <v>121.13</v>
       </c>
       <c r="E86" t="n">
-        <v>35.7048</v>
+        <v>36.2378</v>
       </c>
       <c r="F86" t="n">
-        <v>59.6879</v>
+        <v>59.6952</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>43.5113</v>
+        <v>44.3963</v>
       </c>
       <c r="C87" t="n">
-        <v>41.9542</v>
+        <v>42.6145</v>
       </c>
       <c r="D87" t="n">
-        <v>121.673</v>
+        <v>121.348</v>
       </c>
       <c r="E87" t="n">
-        <v>34.9237</v>
+        <v>35.3856</v>
       </c>
       <c r="F87" t="n">
-        <v>58.6359</v>
+        <v>58.7467</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>40.7871</v>
+        <v>43.2017</v>
       </c>
       <c r="C88" t="n">
-        <v>41.7772</v>
+        <v>42.4694</v>
       </c>
       <c r="D88" t="n">
-        <v>122.385</v>
+        <v>122.016</v>
       </c>
       <c r="E88" t="n">
-        <v>33.9052</v>
+        <v>34.6435</v>
       </c>
       <c r="F88" t="n">
-        <v>57.7249</v>
+        <v>57.5131</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>40.9563</v>
+        <v>42.6516</v>
       </c>
       <c r="C89" t="n">
-        <v>41.7202</v>
+        <v>42.3497</v>
       </c>
       <c r="D89" t="n">
-        <v>122.557</v>
+        <v>122.217</v>
       </c>
       <c r="E89" t="n">
-        <v>33.4103</v>
+        <v>33.9358</v>
       </c>
       <c r="F89" t="n">
-        <v>56.9516</v>
+        <v>56.8299</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>41.8803</v>
+        <v>41.3734</v>
       </c>
       <c r="C90" t="n">
-        <v>41.9767</v>
+        <v>42.2929</v>
       </c>
       <c r="D90" t="n">
-        <v>123.861</v>
+        <v>123.669</v>
       </c>
       <c r="E90" t="n">
-        <v>32.9812</v>
+        <v>33.2845</v>
       </c>
       <c r="F90" t="n">
-        <v>56.1705</v>
+        <v>56.0231</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>39.328</v>
+        <v>38.6674</v>
       </c>
       <c r="C91" t="n">
-        <v>41.9288</v>
+        <v>42.2348</v>
       </c>
       <c r="D91" t="n">
-        <v>125.316</v>
+        <v>125.112</v>
       </c>
       <c r="E91" t="n">
-        <v>32.4275</v>
+        <v>32.5015</v>
       </c>
       <c r="F91" t="n">
-        <v>55.7581</v>
+        <v>56.5223</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>37.5296</v>
+        <v>41.0918</v>
       </c>
       <c r="C92" t="n">
-        <v>41.8408</v>
+        <v>41.8793</v>
       </c>
       <c r="D92" t="n">
-        <v>188.077</v>
+        <v>188.643</v>
       </c>
       <c r="E92" t="n">
-        <v>66.52800000000001</v>
+        <v>66.66589999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>90.5993</v>
+        <v>86.4931</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>41.7438</v>
+        <v>39.6301</v>
       </c>
       <c r="C93" t="n">
-        <v>41.5806</v>
+        <v>41.7387</v>
       </c>
       <c r="D93" t="n">
-        <v>188.03</v>
+        <v>187.974</v>
       </c>
       <c r="E93" t="n">
-        <v>65.4671</v>
+        <v>65.5107</v>
       </c>
       <c r="F93" t="n">
-        <v>84.6443</v>
+        <v>86.361</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>40.2259</v>
+        <v>40.3101</v>
       </c>
       <c r="C94" t="n">
-        <v>74.92449999999999</v>
+        <v>75.1439</v>
       </c>
       <c r="D94" t="n">
-        <v>186.534</v>
+        <v>186.773</v>
       </c>
       <c r="E94" t="n">
-        <v>63.8007</v>
+        <v>63.9477</v>
       </c>
       <c r="F94" t="n">
-        <v>84.33710000000001</v>
+        <v>86.001</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>70.5562</v>
+        <v>68.84699999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>74.7358</v>
+        <v>74.6908</v>
       </c>
       <c r="D95" t="n">
-        <v>185.34</v>
+        <v>185.074</v>
       </c>
       <c r="E95" t="n">
-        <v>62.1657</v>
+        <v>62.3056</v>
       </c>
       <c r="F95" t="n">
-        <v>82.44840000000001</v>
+        <v>86.3874</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>72.8533</v>
+        <v>73.55500000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>73.94929999999999</v>
+        <v>74.0656</v>
       </c>
       <c r="D96" t="n">
-        <v>184.342</v>
+        <v>183.592</v>
       </c>
       <c r="E96" t="n">
-        <v>60.518</v>
+        <v>60.6393</v>
       </c>
       <c r="F96" t="n">
-        <v>81.85469999999999</v>
+        <v>85.6121</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>71.3421</v>
+        <v>69.4781</v>
       </c>
       <c r="C97" t="n">
-        <v>73.11320000000001</v>
+        <v>73.31610000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>183.718</v>
+        <v>183.094</v>
       </c>
       <c r="E97" t="n">
-        <v>58.6237</v>
+        <v>59.1645</v>
       </c>
       <c r="F97" t="n">
-        <v>84.4645</v>
+        <v>84.7732</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>68.5287</v>
+        <v>69.7003</v>
       </c>
       <c r="C98" t="n">
-        <v>72.3749</v>
+        <v>72.54089999999999</v>
       </c>
       <c r="D98" t="n">
-        <v>183.263</v>
+        <v>182.904</v>
       </c>
       <c r="E98" t="n">
-        <v>57.2089</v>
+        <v>57.4514</v>
       </c>
       <c r="F98" t="n">
-        <v>83.38209999999999</v>
+        <v>83.7509</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>65.2651</v>
+        <v>66.3391</v>
       </c>
       <c r="C99" t="n">
-        <v>71.64190000000001</v>
+        <v>71.8283</v>
       </c>
       <c r="D99" t="n">
-        <v>182.949</v>
+        <v>182.991</v>
       </c>
       <c r="E99" t="n">
-        <v>55.5781</v>
+        <v>56.0634</v>
       </c>
       <c r="F99" t="n">
-        <v>83.0231</v>
+        <v>82.6902</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>66.97239999999999</v>
+        <v>65.38939999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>71.0498</v>
+        <v>71.11709999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>183.487</v>
+        <v>183.342</v>
       </c>
       <c r="E100" t="n">
-        <v>54.1794</v>
+        <v>54.6705</v>
       </c>
       <c r="F100" t="n">
-        <v>80.75920000000001</v>
+        <v>81.6306</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>62.7937</v>
+        <v>63.903</v>
       </c>
       <c r="C101" t="n">
-        <v>70.40560000000001</v>
+        <v>70.4199</v>
       </c>
       <c r="D101" t="n">
-        <v>183.31</v>
+        <v>183.583</v>
       </c>
       <c r="E101" t="n">
-        <v>52.6966</v>
+        <v>53.1029</v>
       </c>
       <c r="F101" t="n">
-        <v>80.48220000000001</v>
+        <v>81.8524</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>61.2009</v>
+        <v>64.4054</v>
       </c>
       <c r="C102" t="n">
-        <v>69.75149999999999</v>
+        <v>69.7235</v>
       </c>
       <c r="D102" t="n">
-        <v>184.417</v>
+        <v>184.948</v>
       </c>
       <c r="E102" t="n">
-        <v>51.444</v>
+        <v>51.9585</v>
       </c>
       <c r="F102" t="n">
-        <v>79.42440000000001</v>
+        <v>83.0304</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>62.4</v>
+        <v>62.0098</v>
       </c>
       <c r="C103" t="n">
-        <v>69.0924</v>
+        <v>69.1713</v>
       </c>
       <c r="D103" t="n">
-        <v>186.178</v>
+        <v>185.927</v>
       </c>
       <c r="E103" t="n">
-        <v>50.2487</v>
+        <v>50.7776</v>
       </c>
       <c r="F103" t="n">
-        <v>81.7625</v>
+        <v>79.10080000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>60.5847</v>
+        <v>57.3017</v>
       </c>
       <c r="C104" t="n">
-        <v>68.4264</v>
+        <v>68.679</v>
       </c>
       <c r="D104" t="n">
-        <v>187.276</v>
+        <v>187.329</v>
       </c>
       <c r="E104" t="n">
-        <v>49.1888</v>
+        <v>49.5311</v>
       </c>
       <c r="F104" t="n">
-        <v>78.5656</v>
+        <v>79.3681</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>59.6217</v>
+        <v>60.5518</v>
       </c>
       <c r="C105" t="n">
-        <v>67.8085</v>
+        <v>68.02509999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>188.536</v>
+        <v>188.975</v>
       </c>
       <c r="E105" t="n">
-        <v>48.1035</v>
+        <v>48.5636</v>
       </c>
       <c r="F105" t="n">
-        <v>88.4114</v>
+        <v>81.83799999999999</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>60.6705</v>
+        <v>58.7272</v>
       </c>
       <c r="C106" t="n">
-        <v>67.24720000000001</v>
+        <v>67.532</v>
       </c>
       <c r="D106" t="n">
-        <v>190.117</v>
+        <v>190.982</v>
       </c>
       <c r="E106" t="n">
-        <v>47.1964</v>
+        <v>47.6281</v>
       </c>
       <c r="F106" t="n">
-        <v>88.81699999999999</v>
+        <v>83.5792</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>56.3445</v>
+        <v>57.3235</v>
       </c>
       <c r="C107" t="n">
-        <v>66.7252</v>
+        <v>67.0565</v>
       </c>
       <c r="D107" t="n">
-        <v>257.867</v>
+        <v>258.492</v>
       </c>
       <c r="E107" t="n">
-        <v>82.2307</v>
+        <v>71.3485</v>
       </c>
       <c r="F107" t="n">
-        <v>242.986</v>
+        <v>242.525</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>57.1275</v>
+        <v>56.7287</v>
       </c>
       <c r="C108" t="n">
-        <v>101.11</v>
+        <v>101.164</v>
       </c>
       <c r="D108" t="n">
-        <v>254.644</v>
+        <v>255.572</v>
       </c>
       <c r="E108" t="n">
-        <v>80.2868</v>
+        <v>80.8869</v>
       </c>
       <c r="F108" t="n">
-        <v>243.846</v>
+        <v>242.725</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>46.0195</v>
+        <v>54.6241</v>
       </c>
       <c r="C109" t="n">
-        <v>86.9158</v>
+        <v>100.272</v>
       </c>
       <c r="D109" t="n">
-        <v>252.014</v>
+        <v>253.196</v>
       </c>
       <c r="E109" t="n">
-        <v>78.07989999999999</v>
+        <v>68.1871</v>
       </c>
       <c r="F109" t="n">
-        <v>243.921</v>
+        <v>244.458</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>88.0175</v>
+        <v>88.5742</v>
       </c>
       <c r="C110" t="n">
-        <v>99.2788</v>
+        <v>99.5183</v>
       </c>
       <c r="D110" t="n">
-        <v>250.129</v>
+        <v>250.745</v>
       </c>
       <c r="E110" t="n">
-        <v>76.1836</v>
+        <v>66.70440000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>244.25</v>
+        <v>245.353</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>74.7809</v>
+        <v>85.5184</v>
       </c>
       <c r="C111" t="n">
-        <v>85.4789</v>
+        <v>98.0688</v>
       </c>
       <c r="D111" t="n">
-        <v>250.553</v>
+        <v>249.368</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5228</v>
+        <v>65.0561</v>
       </c>
       <c r="F111" t="n">
-        <v>244.998</v>
+        <v>245.529</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>82.9881</v>
+        <v>78.009</v>
       </c>
       <c r="C112" t="n">
-        <v>96.32899999999999</v>
+        <v>84.8403</v>
       </c>
       <c r="D112" t="n">
-        <v>247.383</v>
+        <v>248.088</v>
       </c>
       <c r="E112" t="n">
-        <v>62.7303</v>
+        <v>63.4093</v>
       </c>
       <c r="F112" t="n">
-        <v>245.276</v>
+        <v>246.088</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>82.72239999999999</v>
+        <v>75.2183</v>
       </c>
       <c r="C113" t="n">
-        <v>95.0821</v>
+        <v>83.9357</v>
       </c>
       <c r="D113" t="n">
-        <v>248.671</v>
+        <v>249.476</v>
       </c>
       <c r="E113" t="n">
-        <v>61.3175</v>
+        <v>70.5029</v>
       </c>
       <c r="F113" t="n">
-        <v>245.594</v>
+        <v>247.015</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>78.10169999999999</v>
+        <v>72.8083</v>
       </c>
       <c r="C114" t="n">
-        <v>93.6534</v>
+        <v>83.2597</v>
       </c>
       <c r="D114" t="n">
-        <v>247.567</v>
+        <v>260.9</v>
       </c>
       <c r="E114" t="n">
-        <v>68.1221</v>
+        <v>68.93470000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>246.511</v>
+        <v>247.667</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>78.4181</v>
+        <v>68.46720000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>92.47929999999999</v>
+        <v>82.455</v>
       </c>
       <c r="D115" t="n">
-        <v>255.07</v>
+        <v>260.256</v>
       </c>
       <c r="E115" t="n">
-        <v>66.48569999999999</v>
+        <v>59.4306</v>
       </c>
       <c r="F115" t="n">
-        <v>246.118</v>
+        <v>248.028</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>68.40479999999999</v>
+        <v>75.33280000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>81.5891</v>
+        <v>91.4726</v>
       </c>
       <c r="D116" t="n">
-        <v>259.178</v>
+        <v>260.473</v>
       </c>
       <c r="E116" t="n">
-        <v>64.8314</v>
+        <v>65.7667</v>
       </c>
       <c r="F116" t="n">
-        <v>247.109</v>
+        <v>247.641</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>74.8263</v>
+        <v>75.0367</v>
       </c>
       <c r="C117" t="n">
-        <v>90.1234</v>
+        <v>90.3986</v>
       </c>
       <c r="D117" t="n">
-        <v>259.96</v>
+        <v>261.109</v>
       </c>
       <c r="E117" t="n">
-        <v>63.4213</v>
+        <v>64.23860000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>246.949</v>
+        <v>248.926</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>72.9761</v>
+        <v>73.1713</v>
       </c>
       <c r="C118" t="n">
-        <v>89.0651</v>
+        <v>89.179</v>
       </c>
       <c r="D118" t="n">
-        <v>244.732</v>
+        <v>245.95</v>
       </c>
       <c r="E118" t="n">
-        <v>55.023</v>
+        <v>56.0158</v>
       </c>
       <c r="F118" t="n">
-        <v>247.501</v>
+        <v>249.237</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>71.512</v>
+        <v>65.943</v>
       </c>
       <c r="C119" t="n">
-        <v>87.976</v>
+        <v>79.86</v>
       </c>
       <c r="D119" t="n">
-        <v>245.412</v>
+        <v>247.187</v>
       </c>
       <c r="E119" t="n">
-        <v>54.2677</v>
+        <v>55.0717</v>
       </c>
       <c r="F119" t="n">
-        <v>101.906</v>
+        <v>226.486</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>69.4834</v>
+        <v>65.6811</v>
       </c>
       <c r="C120" t="n">
-        <v>87.0966</v>
+        <v>79.47450000000001</v>
       </c>
       <c r="D120" t="n">
-        <v>246.617</v>
+        <v>248.298</v>
       </c>
       <c r="E120" t="n">
-        <v>53.3536</v>
+        <v>54.2927</v>
       </c>
       <c r="F120" t="n">
-        <v>151.905</v>
+        <v>152.728</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>69.36969999999999</v>
+        <v>68.5248</v>
       </c>
       <c r="C121" t="n">
-        <v>86.1307</v>
+        <v>86.4761</v>
       </c>
       <c r="D121" t="n">
-        <v>325.488</v>
+        <v>327.873</v>
       </c>
       <c r="E121" t="n">
-        <v>88.5763</v>
+        <v>89.5879</v>
       </c>
       <c r="F121" t="n">
-        <v>295.432</v>
+        <v>297</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>61.1764</v>
+        <v>63.433</v>
       </c>
       <c r="C122" t="n">
-        <v>113.204</v>
+        <v>113.842</v>
       </c>
       <c r="D122" t="n">
-        <v>320.607</v>
+        <v>322.329</v>
       </c>
       <c r="E122" t="n">
-        <v>86.6969</v>
+        <v>87.7047</v>
       </c>
       <c r="F122" t="n">
-        <v>295.43</v>
+        <v>296.054</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>62.0775</v>
+        <v>61.8563</v>
       </c>
       <c r="C123" t="n">
-        <v>112.144</v>
+        <v>112.454</v>
       </c>
       <c r="D123" t="n">
-        <v>316.196</v>
+        <v>317.847</v>
       </c>
       <c r="E123" t="n">
-        <v>84.9915</v>
+        <v>85.82689999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>295.154</v>
+        <v>296.208</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>93.1514</v>
+        <v>99.15560000000001</v>
       </c>
       <c r="C124" t="n">
-        <v>111.843</v>
+        <v>118.662</v>
       </c>
       <c r="D124" t="n">
-        <v>312.508</v>
+        <v>314.821</v>
       </c>
       <c r="E124" t="n">
-        <v>83.4071</v>
+        <v>84.2867</v>
       </c>
       <c r="F124" t="n">
-        <v>293.747</v>
+        <v>295.935</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>96.6307</v>
+        <v>97.61799999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>116.826</v>
+        <v>117.307</v>
       </c>
       <c r="D125" t="n">
-        <v>308.967</v>
+        <v>302.023</v>
       </c>
       <c r="E125" t="n">
-        <v>81.5624</v>
+        <v>85.5368</v>
       </c>
       <c r="F125" t="n">
-        <v>294.405</v>
+        <v>287.183</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>89.5472</v>
+        <v>92.20350000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>109.493</v>
+        <v>113.502</v>
       </c>
       <c r="D126" t="n">
-        <v>305.98</v>
+        <v>298.987</v>
       </c>
       <c r="E126" t="n">
-        <v>84.70050000000001</v>
+        <v>81.11499999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>293.624</v>
+        <v>295.207</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>92.9491</v>
+        <v>90.23220000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>114.087</v>
+        <v>108.939</v>
       </c>
       <c r="D127" t="n">
-        <v>303.263</v>
+        <v>305.544</v>
       </c>
       <c r="E127" t="n">
-        <v>78.3489</v>
+        <v>83.7457</v>
       </c>
       <c r="F127" t="n">
-        <v>292.584</v>
+        <v>294.566</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>86.7213</v>
+        <v>91.3182</v>
       </c>
       <c r="C128" t="n">
-        <v>107.531</v>
+        <v>113.39</v>
       </c>
       <c r="D128" t="n">
-        <v>301</v>
+        <v>303.114</v>
       </c>
       <c r="E128" t="n">
-        <v>77.0727</v>
+        <v>78.1327</v>
       </c>
       <c r="F128" t="n">
-        <v>292.825</v>
+        <v>294.131</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>88.6069</v>
+        <v>83.8685</v>
       </c>
       <c r="C129" t="n">
-        <v>111.664</v>
+        <v>106.984</v>
       </c>
       <c r="D129" t="n">
-        <v>298.846</v>
+        <v>301.101</v>
       </c>
       <c r="E129" t="n">
-        <v>75.5311</v>
+        <v>76.6763</v>
       </c>
       <c r="F129" t="n">
-        <v>292.439</v>
+        <v>293.528</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>87.74979999999999</v>
+        <v>82.80200000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>110.595</v>
+        <v>106.136</v>
       </c>
       <c r="D130" t="n">
-        <v>297.544</v>
+        <v>299.38</v>
       </c>
       <c r="E130" t="n">
-        <v>74.1828</v>
+        <v>75.44329999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>291.946</v>
+        <v>293.349</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>81.9689</v>
+        <v>82.66840000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>104.947</v>
+        <v>105.338</v>
       </c>
       <c r="D131" t="n">
-        <v>296.426</v>
+        <v>298.356</v>
       </c>
       <c r="E131" t="n">
-        <v>73.0475</v>
+        <v>74.1562</v>
       </c>
       <c r="F131" t="n">
-        <v>291.825</v>
+        <v>293.755</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>81.96939999999999</v>
+        <v>81.9049</v>
       </c>
       <c r="C132" t="n">
-        <v>104.129</v>
+        <v>104.491</v>
       </c>
       <c r="D132" t="n">
-        <v>295.646</v>
+        <v>297.497</v>
       </c>
       <c r="E132" t="n">
-        <v>75.4265</v>
+        <v>73.1027</v>
       </c>
       <c r="F132" t="n">
-        <v>291.969</v>
+        <v>292.97</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>77.0275</v>
+        <v>80.41330000000001</v>
       </c>
       <c r="C133" t="n">
-        <v>94.5334</v>
+        <v>103.71</v>
       </c>
       <c r="D133" t="n">
-        <v>295.359</v>
+        <v>297.007</v>
       </c>
       <c r="E133" t="n">
-        <v>70.9892</v>
+        <v>72.04900000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>292.421</v>
+        <v>293.383</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>80.3351</v>
+        <v>80.14619999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>102.79</v>
+        <v>103.142</v>
       </c>
       <c r="D134" t="n">
-        <v>290.168</v>
+        <v>293.249</v>
       </c>
       <c r="E134" t="n">
-        <v>63.9023</v>
+        <v>64.98609999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>240.008</v>
+        <v>240.181</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>77.96729999999999</v>
+        <v>78.42310000000001</v>
       </c>
       <c r="C135" t="n">
-        <v>102.071</v>
+        <v>102.499</v>
       </c>
       <c r="D135" t="n">
-        <v>372.588</v>
+        <v>375.021</v>
       </c>
       <c r="E135" t="n">
-        <v>99.6489</v>
+        <v>100.67</v>
       </c>
       <c r="F135" t="n">
-        <v>335.635</v>
+        <v>338.855</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>77.1909</v>
+        <v>77.9896</v>
       </c>
       <c r="C136" t="n">
-        <v>135.457</v>
+        <v>136.466</v>
       </c>
       <c r="D136" t="n">
-        <v>365.77</v>
+        <v>368.38</v>
       </c>
       <c r="E136" t="n">
-        <v>97.8896</v>
+        <v>98.75409999999999</v>
       </c>
       <c r="F136" t="n">
-        <v>335.104</v>
+        <v>335.862</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>76.7955</v>
+        <v>77.0624</v>
       </c>
       <c r="C137" t="n">
-        <v>133.918</v>
+        <v>135.33</v>
       </c>
       <c r="D137" t="n">
-        <v>360.358</v>
+        <v>362.398</v>
       </c>
       <c r="E137" t="n">
-        <v>95.8712</v>
+        <v>96.9136</v>
       </c>
       <c r="F137" t="n">
-        <v>335.483</v>
+        <v>336.236</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>109.359</v>
+        <v>109.415</v>
       </c>
       <c r="C138" t="n">
-        <v>134.988</v>
+        <v>134.908</v>
       </c>
       <c r="D138" t="n">
-        <v>354.863</v>
+        <v>357.926</v>
       </c>
       <c r="E138" t="n">
-        <v>94.6071</v>
+        <v>95.11279999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>334.57</v>
+        <v>333.616</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>102.817</v>
+        <v>107.497</v>
       </c>
       <c r="C139" t="n">
-        <v>126.756</v>
+        <v>133.623</v>
       </c>
       <c r="D139" t="n">
-        <v>350.226</v>
+        <v>352.298</v>
       </c>
       <c r="E139" t="n">
-        <v>93.18510000000001</v>
+        <v>93.58710000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>333.898</v>
+        <v>334.124</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>105.811</v>
+        <v>102.222</v>
       </c>
       <c r="C140" t="n">
-        <v>132.435</v>
+        <v>124.877</v>
       </c>
       <c r="D140" t="n">
-        <v>345.617</v>
+        <v>337.17</v>
       </c>
       <c r="E140" t="n">
-        <v>96.2071</v>
+        <v>94.6936</v>
       </c>
       <c r="F140" t="n">
-        <v>332.379</v>
+        <v>323.713</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>103.914</v>
+        <v>100.879</v>
       </c>
       <c r="C141" t="n">
-        <v>131.42</v>
+        <v>128.837</v>
       </c>
       <c r="D141" t="n">
-        <v>343.787</v>
+        <v>335.189</v>
       </c>
       <c r="E141" t="n">
-        <v>94.5018</v>
+        <v>88.7714</v>
       </c>
       <c r="F141" t="n">
-        <v>332.558</v>
+        <v>321.619</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>98.8753</v>
+        <v>95.73690000000001</v>
       </c>
       <c r="C142" t="n">
-        <v>124.649</v>
+        <v>121.542</v>
       </c>
       <c r="D142" t="n">
-        <v>343.885</v>
+        <v>332.606</v>
       </c>
       <c r="E142" t="n">
-        <v>92.5523</v>
+        <v>87.19499999999999</v>
       </c>
       <c r="F142" t="n">
-        <v>331.032</v>
+        <v>320.15</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>100.418</v>
+        <v>93.99209999999999</v>
       </c>
       <c r="C143" t="n">
-        <v>129.406</v>
+        <v>120.839</v>
       </c>
       <c r="D143" t="n">
-        <v>341.782</v>
+        <v>329.527</v>
       </c>
       <c r="E143" t="n">
-        <v>87.4093</v>
+        <v>85.8742</v>
       </c>
       <c r="F143" t="n">
-        <v>329.533</v>
+        <v>319.358</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>21.9872</v>
+        <v>22.0351</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5498</v>
+        <v>24.6058</v>
       </c>
       <c r="D2" t="n">
-        <v>55.5978</v>
+        <v>56.0545</v>
       </c>
       <c r="E2" t="n">
-        <v>17.8594</v>
+        <v>17.8695</v>
       </c>
       <c r="F2" t="n">
-        <v>33.2854</v>
+        <v>33.3511</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>21.2014</v>
+        <v>20.9369</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0394</v>
+        <v>24.1827</v>
       </c>
       <c r="D3" t="n">
-        <v>54.9375</v>
+        <v>55.3951</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3214</v>
+        <v>17.3667</v>
       </c>
       <c r="F3" t="n">
-        <v>32.8241</v>
+        <v>32.9122</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>20.8022</v>
+        <v>20.7245</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5692</v>
+        <v>23.5574</v>
       </c>
       <c r="D4" t="n">
-        <v>54.4251</v>
+        <v>54.9393</v>
       </c>
       <c r="E4" t="n">
-        <v>16.8468</v>
+        <v>16.8864</v>
       </c>
       <c r="F4" t="n">
-        <v>32.4482</v>
+        <v>32.5201</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>19.9354</v>
+        <v>20.6427</v>
       </c>
       <c r="C5" t="n">
-        <v>23.1373</v>
+        <v>23.128</v>
       </c>
       <c r="D5" t="n">
-        <v>54.0899</v>
+        <v>54.7189</v>
       </c>
       <c r="E5" t="n">
-        <v>16.5517</v>
+        <v>16.4808</v>
       </c>
       <c r="F5" t="n">
-        <v>32.2</v>
+        <v>32.2774</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>19.5174</v>
+        <v>19.9836</v>
       </c>
       <c r="C6" t="n">
-        <v>22.782</v>
+        <v>22.8309</v>
       </c>
       <c r="D6" t="n">
-        <v>53.7664</v>
+        <v>54.1771</v>
       </c>
       <c r="E6" t="n">
-        <v>16.1915</v>
+        <v>16.1572</v>
       </c>
       <c r="F6" t="n">
-        <v>32.0745</v>
+        <v>32.2166</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.4681</v>
+        <v>19.5328</v>
       </c>
       <c r="C7" t="n">
-        <v>22.4352</v>
+        <v>22.4742</v>
       </c>
       <c r="D7" t="n">
-        <v>68.313</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>24.8336</v>
+        <v>24.8705</v>
       </c>
       <c r="F7" t="n">
-        <v>39.9945</v>
+        <v>40.2158</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>19.0642</v>
+        <v>19.4204</v>
       </c>
       <c r="C8" t="n">
-        <v>30.9108</v>
+        <v>30.8984</v>
       </c>
       <c r="D8" t="n">
-        <v>66.8045</v>
+        <v>67.4871</v>
       </c>
       <c r="E8" t="n">
-        <v>24.0159</v>
+        <v>23.8497</v>
       </c>
       <c r="F8" t="n">
-        <v>39.1177</v>
+        <v>39.135</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>19.7905</v>
+        <v>19.3386</v>
       </c>
       <c r="C9" t="n">
-        <v>30.1068</v>
+        <v>30.204</v>
       </c>
       <c r="D9" t="n">
-        <v>65.42619999999999</v>
+        <v>66.18600000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>23.2447</v>
+        <v>23.1555</v>
       </c>
       <c r="F9" t="n">
-        <v>38.232</v>
+        <v>38.4809</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.6998</v>
+        <v>27.8275</v>
       </c>
       <c r="C10" t="n">
-        <v>29.3328</v>
+        <v>29.3113</v>
       </c>
       <c r="D10" t="n">
-        <v>64.2878</v>
+        <v>65.0448</v>
       </c>
       <c r="E10" t="n">
-        <v>22.5165</v>
+        <v>22.456</v>
       </c>
       <c r="F10" t="n">
-        <v>37.4748</v>
+        <v>37.5369</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.0436</v>
+        <v>26.8415</v>
       </c>
       <c r="C11" t="n">
-        <v>28.551</v>
+        <v>28.5718</v>
       </c>
       <c r="D11" t="n">
-        <v>63.1545</v>
+        <v>63.9498</v>
       </c>
       <c r="E11" t="n">
-        <v>21.6661</v>
+        <v>21.6489</v>
       </c>
       <c r="F11" t="n">
-        <v>36.7035</v>
+        <v>36.7401</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>25.9947</v>
+        <v>26.5671</v>
       </c>
       <c r="C12" t="n">
-        <v>27.8441</v>
+        <v>27.9195</v>
       </c>
       <c r="D12" t="n">
-        <v>62.1073</v>
+        <v>62.8664</v>
       </c>
       <c r="E12" t="n">
-        <v>21.6807</v>
+        <v>20.9942</v>
       </c>
       <c r="F12" t="n">
-        <v>36.0131</v>
+        <v>36.0316</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>24.9958</v>
+        <v>25.8246</v>
       </c>
       <c r="C13" t="n">
-        <v>27.4012</v>
+        <v>27.1604</v>
       </c>
       <c r="D13" t="n">
-        <v>61.2146</v>
+        <v>61.936</v>
       </c>
       <c r="E13" t="n">
-        <v>20.3681</v>
+        <v>20.3522</v>
       </c>
       <c r="F13" t="n">
-        <v>35.4</v>
+        <v>35.4327</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.431</v>
+        <v>24.8562</v>
       </c>
       <c r="C14" t="n">
-        <v>26.4852</v>
+        <v>26.4963</v>
       </c>
       <c r="D14" t="n">
-        <v>60.5545</v>
+        <v>61.132</v>
       </c>
       <c r="E14" t="n">
-        <v>19.8553</v>
+        <v>19.6879</v>
       </c>
       <c r="F14" t="n">
-        <v>34.867</v>
+        <v>34.8531</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.9156</v>
+        <v>23.9588</v>
       </c>
       <c r="C15" t="n">
-        <v>25.88</v>
+        <v>25.9205</v>
       </c>
       <c r="D15" t="n">
-        <v>59.9313</v>
+        <v>60.7427</v>
       </c>
       <c r="E15" t="n">
-        <v>19.2391</v>
+        <v>19.1905</v>
       </c>
       <c r="F15" t="n">
-        <v>34.2551</v>
+        <v>34.2805</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.1265</v>
+        <v>23.2494</v>
       </c>
       <c r="C16" t="n">
-        <v>25.3096</v>
+        <v>25.3395</v>
       </c>
       <c r="D16" t="n">
-        <v>59.5355</v>
+        <v>60.0171</v>
       </c>
       <c r="E16" t="n">
-        <v>18.7085</v>
+        <v>18.7016</v>
       </c>
       <c r="F16" t="n">
-        <v>33.7923</v>
+        <v>33.7928</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.445</v>
+        <v>22.1908</v>
       </c>
       <c r="C17" t="n">
-        <v>24.789</v>
+        <v>24.8554</v>
       </c>
       <c r="D17" t="n">
-        <v>58.9085</v>
+        <v>59.5663</v>
       </c>
       <c r="E17" t="n">
-        <v>18.285</v>
+        <v>18.2061</v>
       </c>
       <c r="F17" t="n">
-        <v>33.357</v>
+        <v>33.3709</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>22.3345</v>
+        <v>22.0284</v>
       </c>
       <c r="C18" t="n">
-        <v>24.3301</v>
+        <v>24.3343</v>
       </c>
       <c r="D18" t="n">
-        <v>58.1433</v>
+        <v>58.6319</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7996</v>
+        <v>17.7479</v>
       </c>
       <c r="F18" t="n">
-        <v>32.9549</v>
+        <v>32.9418</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.2592</v>
+        <v>21.5698</v>
       </c>
       <c r="C19" t="n">
-        <v>23.81</v>
+        <v>23.9441</v>
       </c>
       <c r="D19" t="n">
-        <v>57.5989</v>
+        <v>58.062</v>
       </c>
       <c r="E19" t="n">
-        <v>17.428</v>
+        <v>17.3909</v>
       </c>
       <c r="F19" t="n">
-        <v>32.6395</v>
+        <v>32.6119</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>21.2506</v>
+        <v>21.0265</v>
       </c>
       <c r="C20" t="n">
-        <v>23.4437</v>
+        <v>23.4569</v>
       </c>
       <c r="D20" t="n">
-        <v>57.262</v>
+        <v>57.7851</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1412</v>
+        <v>17.1322</v>
       </c>
       <c r="F20" t="n">
-        <v>32.5117</v>
+        <v>32.4764</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.3226</v>
+        <v>20.5059</v>
       </c>
       <c r="C21" t="n">
-        <v>23.2276</v>
+        <v>23.1271</v>
       </c>
       <c r="D21" t="n">
-        <v>74.8485</v>
+        <v>75.2851</v>
       </c>
       <c r="E21" t="n">
-        <v>26.1173</v>
+        <v>25.9676</v>
       </c>
       <c r="F21" t="n">
-        <v>40.6407</v>
+        <v>40.6661</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.4398</v>
+        <v>20.2351</v>
       </c>
       <c r="C22" t="n">
-        <v>31.5361</v>
+        <v>31.5925</v>
       </c>
       <c r="D22" t="n">
-        <v>73.3068</v>
+        <v>73.6262</v>
       </c>
       <c r="E22" t="n">
-        <v>25.0293</v>
+        <v>24.9398</v>
       </c>
       <c r="F22" t="n">
-        <v>39.7287</v>
+        <v>39.8029</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>20.5869</v>
+        <v>20.4079</v>
       </c>
       <c r="C23" t="n">
-        <v>30.8055</v>
+        <v>30.851</v>
       </c>
       <c r="D23" t="n">
-        <v>71.9371</v>
+        <v>72.19589999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>24.147</v>
+        <v>24.1474</v>
       </c>
       <c r="F23" t="n">
-        <v>38.9231</v>
+        <v>38.9593</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>28.6314</v>
+        <v>28.6486</v>
       </c>
       <c r="C24" t="n">
-        <v>30.0204</v>
+        <v>30.0687</v>
       </c>
       <c r="D24" t="n">
-        <v>70.55289999999999</v>
+        <v>70.9414</v>
       </c>
       <c r="E24" t="n">
-        <v>23.4209</v>
+        <v>23.3794</v>
       </c>
       <c r="F24" t="n">
-        <v>38.1336</v>
+        <v>38.186</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>27.5531</v>
+        <v>27.5857</v>
       </c>
       <c r="C25" t="n">
-        <v>29.2816</v>
+        <v>29.3358</v>
       </c>
       <c r="D25" t="n">
-        <v>69.3922</v>
+        <v>69.7119</v>
       </c>
       <c r="E25" t="n">
-        <v>22.6517</v>
+        <v>22.6357</v>
       </c>
       <c r="F25" t="n">
-        <v>37.3404</v>
+        <v>37.4286</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>26.6666</v>
+        <v>26.8288</v>
       </c>
       <c r="C26" t="n">
-        <v>28.5512</v>
+        <v>28.5999</v>
       </c>
       <c r="D26" t="n">
-        <v>68.176</v>
+        <v>68.59220000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>21.9369</v>
+        <v>21.9388</v>
       </c>
       <c r="F26" t="n">
-        <v>36.8916</v>
+        <v>36.8009</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>26.7545</v>
+        <v>25.9343</v>
       </c>
       <c r="C27" t="n">
-        <v>27.8766</v>
+        <v>27.8826</v>
       </c>
       <c r="D27" t="n">
-        <v>67.2779</v>
+        <v>67.6636</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2567</v>
+        <v>21.2482</v>
       </c>
       <c r="F27" t="n">
-        <v>36.1754</v>
+        <v>36.1444</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.1544</v>
+        <v>25.1363</v>
       </c>
       <c r="C28" t="n">
-        <v>27.1816</v>
+        <v>27.2228</v>
       </c>
       <c r="D28" t="n">
-        <v>66.2531</v>
+        <v>66.5459</v>
       </c>
       <c r="E28" t="n">
-        <v>20.545</v>
+        <v>20.6308</v>
       </c>
       <c r="F28" t="n">
-        <v>35.5852</v>
+        <v>35.5795</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>25.1351</v>
+        <v>24.3892</v>
       </c>
       <c r="C29" t="n">
-        <v>26.6113</v>
+        <v>26.609</v>
       </c>
       <c r="D29" t="n">
-        <v>65.598</v>
+        <v>65.84699999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>20.0441</v>
+        <v>20.0093</v>
       </c>
       <c r="F29" t="n">
-        <v>35.0673</v>
+        <v>34.914</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>23.6969</v>
+        <v>24.1749</v>
       </c>
       <c r="C30" t="n">
-        <v>25.9774</v>
+        <v>26.0227</v>
       </c>
       <c r="D30" t="n">
-        <v>64.71210000000001</v>
+        <v>64.9524</v>
       </c>
       <c r="E30" t="n">
-        <v>19.4224</v>
+        <v>19.4875</v>
       </c>
       <c r="F30" t="n">
-        <v>34.5054</v>
+        <v>34.5042</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.0198</v>
+        <v>23.0287</v>
       </c>
       <c r="C31" t="n">
-        <v>25.4201</v>
+        <v>25.4664</v>
       </c>
       <c r="D31" t="n">
-        <v>64.1968</v>
+        <v>64.411</v>
       </c>
       <c r="E31" t="n">
-        <v>18.9366</v>
+        <v>18.9352</v>
       </c>
       <c r="F31" t="n">
-        <v>33.4575</v>
+        <v>33.7013</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>23.5076</v>
+        <v>23.5351</v>
       </c>
       <c r="C32" t="n">
-        <v>24.9702</v>
+        <v>25.1367</v>
       </c>
       <c r="D32" t="n">
-        <v>63.7702</v>
+        <v>63.981</v>
       </c>
       <c r="E32" t="n">
-        <v>18.5058</v>
+        <v>18.4814</v>
       </c>
       <c r="F32" t="n">
-        <v>33.3341</v>
+        <v>33.3404</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>22.6226</v>
+        <v>22.9459</v>
       </c>
       <c r="C33" t="n">
-        <v>24.5439</v>
+        <v>24.6807</v>
       </c>
       <c r="D33" t="n">
-        <v>63.4031</v>
+        <v>63.5857</v>
       </c>
       <c r="E33" t="n">
-        <v>18.1673</v>
+        <v>18.1441</v>
       </c>
       <c r="F33" t="n">
-        <v>32.9385</v>
+        <v>32.9892</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>22.0426</v>
+        <v>21.676</v>
       </c>
       <c r="C34" t="n">
-        <v>24.0999</v>
+        <v>24.2936</v>
       </c>
       <c r="D34" t="n">
-        <v>62.7091</v>
+        <v>62.8305</v>
       </c>
       <c r="E34" t="n">
-        <v>17.8552</v>
+        <v>17.8493</v>
       </c>
       <c r="F34" t="n">
-        <v>32.7567</v>
+        <v>32.7862</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>21.1077</v>
+        <v>21.4585</v>
       </c>
       <c r="C35" t="n">
-        <v>23.7587</v>
+        <v>23.7829</v>
       </c>
       <c r="D35" t="n">
-        <v>80.97709999999999</v>
+        <v>81.27970000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>26.6007</v>
+        <v>26.7336</v>
       </c>
       <c r="F35" t="n">
-        <v>41.4983</v>
+        <v>41.5472</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>21.2048</v>
+        <v>21.4154</v>
       </c>
       <c r="C36" t="n">
-        <v>23.4848</v>
+        <v>23.5392</v>
       </c>
       <c r="D36" t="n">
-        <v>79.3026</v>
+        <v>79.51690000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>25.7688</v>
+        <v>25.8144</v>
       </c>
       <c r="F36" t="n">
-        <v>40.7226</v>
+        <v>40.778</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>20.6637</v>
+        <v>21.0266</v>
       </c>
       <c r="C37" t="n">
-        <v>31.784</v>
+        <v>31.6298</v>
       </c>
       <c r="D37" t="n">
-        <v>77.7668</v>
+        <v>77.9781</v>
       </c>
       <c r="E37" t="n">
-        <v>24.9616</v>
+        <v>25.0416</v>
       </c>
       <c r="F37" t="n">
-        <v>39.9404</v>
+        <v>39.9755</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>29.4554</v>
+        <v>29.7482</v>
       </c>
       <c r="C38" t="n">
-        <v>30.8393</v>
+        <v>30.9607</v>
       </c>
       <c r="D38" t="n">
-        <v>76.2316</v>
+        <v>76.4845</v>
       </c>
       <c r="E38" t="n">
-        <v>24.2023</v>
+        <v>24.1909</v>
       </c>
       <c r="F38" t="n">
-        <v>39.3209</v>
+        <v>39.0015</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>28.5735</v>
+        <v>28.6229</v>
       </c>
       <c r="C39" t="n">
-        <v>30.225</v>
+        <v>30.1046</v>
       </c>
       <c r="D39" t="n">
-        <v>74.9838</v>
+        <v>75.16930000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5269</v>
+        <v>23.473</v>
       </c>
       <c r="F39" t="n">
-        <v>38.3909</v>
+        <v>38.6222</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>27.6938</v>
+        <v>27.3591</v>
       </c>
       <c r="C40" t="n">
-        <v>29.5018</v>
+        <v>29.5103</v>
       </c>
       <c r="D40" t="n">
-        <v>73.78959999999999</v>
+        <v>73.8861</v>
       </c>
       <c r="E40" t="n">
-        <v>22.7724</v>
+        <v>22.7694</v>
       </c>
       <c r="F40" t="n">
-        <v>37.5663</v>
+        <v>37.7968</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.7043</v>
+        <v>26.4309</v>
       </c>
       <c r="C41" t="n">
-        <v>28.7812</v>
+        <v>28.9802</v>
       </c>
       <c r="D41" t="n">
-        <v>72.5397</v>
+        <v>72.67789999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>22.1176</v>
+        <v>22.0872</v>
       </c>
       <c r="F41" t="n">
-        <v>36.994</v>
+        <v>37.151</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>25.6332</v>
+        <v>25.8258</v>
       </c>
       <c r="C42" t="n">
-        <v>28.2673</v>
+        <v>28.1843</v>
       </c>
       <c r="D42" t="n">
-        <v>71.79300000000001</v>
+        <v>71.96120000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>21.5425</v>
+        <v>21.4682</v>
       </c>
       <c r="F42" t="n">
-        <v>36.4268</v>
+        <v>36.6442</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>25.3158</v>
+        <v>25.0505</v>
       </c>
       <c r="C43" t="n">
-        <v>27.5544</v>
+        <v>27.797</v>
       </c>
       <c r="D43" t="n">
-        <v>70.4302</v>
+        <v>70.678</v>
       </c>
       <c r="E43" t="n">
-        <v>20.9435</v>
+        <v>20.9209</v>
       </c>
       <c r="F43" t="n">
-        <v>35.9084</v>
+        <v>36.0937</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.385</v>
+        <v>24.7968</v>
       </c>
       <c r="C44" t="n">
-        <v>26.9849</v>
+        <v>26.9503</v>
       </c>
       <c r="D44" t="n">
-        <v>69.7152</v>
+        <v>69.9598</v>
       </c>
       <c r="E44" t="n">
-        <v>20.5102</v>
+        <v>20.3361</v>
       </c>
       <c r="F44" t="n">
-        <v>35.3897</v>
+        <v>35.6239</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>23.7284</v>
+        <v>23.4628</v>
       </c>
       <c r="C45" t="n">
-        <v>26.67</v>
+        <v>26.5439</v>
       </c>
       <c r="D45" t="n">
-        <v>69.11790000000001</v>
+        <v>69.3074</v>
       </c>
       <c r="E45" t="n">
-        <v>19.9416</v>
+        <v>19.8585</v>
       </c>
       <c r="F45" t="n">
-        <v>34.9247</v>
+        <v>35.1501</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>23.0855</v>
+        <v>23.211</v>
       </c>
       <c r="C46" t="n">
-        <v>26.1393</v>
+        <v>26.183</v>
       </c>
       <c r="D46" t="n">
-        <v>68.4836</v>
+        <v>68.7503</v>
       </c>
       <c r="E46" t="n">
-        <v>19.454</v>
+        <v>19.4352</v>
       </c>
       <c r="F46" t="n">
-        <v>34.5347</v>
+        <v>34.7513</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.3674</v>
+        <v>22.5979</v>
       </c>
       <c r="C47" t="n">
-        <v>25.5549</v>
+        <v>25.728</v>
       </c>
       <c r="D47" t="n">
-        <v>68.0423</v>
+        <v>68.29730000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>19.145</v>
+        <v>19.0018</v>
       </c>
       <c r="F47" t="n">
-        <v>34.1671</v>
+        <v>34.4021</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>21.9338</v>
+        <v>21.9906</v>
       </c>
       <c r="C48" t="n">
-        <v>25.202</v>
+        <v>25.285</v>
       </c>
       <c r="D48" t="n">
-        <v>67.3022</v>
+        <v>67.495</v>
       </c>
       <c r="E48" t="n">
-        <v>18.8746</v>
+        <v>18.7038</v>
       </c>
       <c r="F48" t="n">
-        <v>33.9605</v>
+        <v>34.145</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>21.9172</v>
+        <v>21.4363</v>
       </c>
       <c r="C49" t="n">
-        <v>24.9245</v>
+        <v>24.9376</v>
       </c>
       <c r="D49" t="n">
-        <v>66.94710000000001</v>
+        <v>67.1322</v>
       </c>
       <c r="E49" t="n">
-        <v>18.5346</v>
+        <v>18.5053</v>
       </c>
       <c r="F49" t="n">
-        <v>33.8528</v>
+        <v>34.0834</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.2269</v>
+        <v>21.6408</v>
       </c>
       <c r="C50" t="n">
-        <v>24.5387</v>
+        <v>24.4326</v>
       </c>
       <c r="D50" t="n">
-        <v>84.20050000000001</v>
+        <v>84.34650000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>27.2401</v>
+        <v>27.0044</v>
       </c>
       <c r="F50" t="n">
-        <v>42.3185</v>
+        <v>42.1584</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>21.1522</v>
+        <v>21.1324</v>
       </c>
       <c r="C51" t="n">
-        <v>32.7221</v>
+        <v>32.5653</v>
       </c>
       <c r="D51" t="n">
-        <v>82.4426</v>
+        <v>82.717</v>
       </c>
       <c r="E51" t="n">
-        <v>26.5743</v>
+        <v>26.2147</v>
       </c>
       <c r="F51" t="n">
-        <v>41.4397</v>
+        <v>41.2576</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>21.2064</v>
+        <v>22.1225</v>
       </c>
       <c r="C52" t="n">
-        <v>32.019</v>
+        <v>31.9769</v>
       </c>
       <c r="D52" t="n">
-        <v>80.8591</v>
+        <v>81.0138</v>
       </c>
       <c r="E52" t="n">
-        <v>25.5398</v>
+        <v>25.5623</v>
       </c>
       <c r="F52" t="n">
-        <v>40.4598</v>
+        <v>40.5449</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.4242</v>
+        <v>29.1056</v>
       </c>
       <c r="C53" t="n">
-        <v>31.4286</v>
+        <v>31.2413</v>
       </c>
       <c r="D53" t="n">
-        <v>79.3202</v>
+        <v>79.5104</v>
       </c>
       <c r="E53" t="n">
-        <v>24.9043</v>
+        <v>24.5337</v>
       </c>
       <c r="F53" t="n">
-        <v>39.9431</v>
+        <v>39.9752</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>28.6398</v>
+        <v>28.4388</v>
       </c>
       <c r="C54" t="n">
-        <v>30.827</v>
+        <v>30.5156</v>
       </c>
       <c r="D54" t="n">
-        <v>77.9648</v>
+        <v>78.078</v>
       </c>
       <c r="E54" t="n">
-        <v>24.2389</v>
+        <v>24.0775</v>
       </c>
       <c r="F54" t="n">
-        <v>39.2644</v>
+        <v>39.2183</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>28.005</v>
+        <v>27.4978</v>
       </c>
       <c r="C55" t="n">
-        <v>30.2691</v>
+        <v>30.2436</v>
       </c>
       <c r="D55" t="n">
-        <v>76.7525</v>
+        <v>76.8853</v>
       </c>
       <c r="E55" t="n">
-        <v>23.5031</v>
+        <v>23.2245</v>
       </c>
       <c r="F55" t="n">
-        <v>38.5641</v>
+        <v>38.6736</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>27.4461</v>
+        <v>26.9189</v>
       </c>
       <c r="C56" t="n">
-        <v>29.6066</v>
+        <v>29.7503</v>
       </c>
       <c r="D56" t="n">
-        <v>75.6412</v>
+        <v>75.8104</v>
       </c>
       <c r="E56" t="n">
-        <v>22.8702</v>
+        <v>22.6332</v>
       </c>
       <c r="F56" t="n">
-        <v>37.9039</v>
+        <v>38.0724</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.4455</v>
+        <v>26.5538</v>
       </c>
       <c r="C57" t="n">
-        <v>29.1528</v>
+        <v>28.8268</v>
       </c>
       <c r="D57" t="n">
-        <v>74.50920000000001</v>
+        <v>74.5964</v>
       </c>
       <c r="E57" t="n">
-        <v>22.3774</v>
+        <v>22.2039</v>
       </c>
       <c r="F57" t="n">
-        <v>37.4155</v>
+        <v>37.5918</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>26.0101</v>
+        <v>25.5998</v>
       </c>
       <c r="C58" t="n">
-        <v>28.4267</v>
+        <v>28.2986</v>
       </c>
       <c r="D58" t="n">
-        <v>73.6883</v>
+        <v>73.78</v>
       </c>
       <c r="E58" t="n">
-        <v>21.7868</v>
+        <v>21.5481</v>
       </c>
       <c r="F58" t="n">
-        <v>36.9598</v>
+        <v>37.057</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>25.3231</v>
+        <v>24.5735</v>
       </c>
       <c r="C59" t="n">
-        <v>27.7192</v>
+        <v>27.7935</v>
       </c>
       <c r="D59" t="n">
-        <v>72.7941</v>
+        <v>72.9157</v>
       </c>
       <c r="E59" t="n">
-        <v>21.2503</v>
+        <v>21.0612</v>
       </c>
       <c r="F59" t="n">
-        <v>36.4689</v>
+        <v>36.6138</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>24.2224</v>
+        <v>24.0745</v>
       </c>
       <c r="C60" t="n">
-        <v>27.3294</v>
+        <v>27.5321</v>
       </c>
       <c r="D60" t="n">
-        <v>72.20310000000001</v>
+        <v>72.2882</v>
       </c>
       <c r="E60" t="n">
-        <v>20.8063</v>
+        <v>20.5712</v>
       </c>
       <c r="F60" t="n">
-        <v>36.18</v>
+        <v>36.2219</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>23.7656</v>
+        <v>23.7424</v>
       </c>
       <c r="C61" t="n">
-        <v>27.1922</v>
+        <v>27.2641</v>
       </c>
       <c r="D61" t="n">
-        <v>71.44450000000001</v>
+        <v>71.5177</v>
       </c>
       <c r="E61" t="n">
-        <v>20.4182</v>
+        <v>20.1371</v>
       </c>
       <c r="F61" t="n">
-        <v>35.7579</v>
+        <v>35.9404</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>23.416</v>
+        <v>23.2004</v>
       </c>
       <c r="C62" t="n">
-        <v>26.5103</v>
+        <v>26.8696</v>
       </c>
       <c r="D62" t="n">
-        <v>70.85380000000001</v>
+        <v>70.919</v>
       </c>
       <c r="E62" t="n">
-        <v>20.0701</v>
+        <v>19.9589</v>
       </c>
       <c r="F62" t="n">
-        <v>35.5105</v>
+        <v>35.7233</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>23.1922</v>
+        <v>22.6852</v>
       </c>
       <c r="C63" t="n">
-        <v>26.5806</v>
+        <v>26.2414</v>
       </c>
       <c r="D63" t="n">
-        <v>70.4594</v>
+        <v>70.56059999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>19.8099</v>
+        <v>19.5386</v>
       </c>
       <c r="F63" t="n">
-        <v>35.369</v>
+        <v>35.5622</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>22.7457</v>
+        <v>22.7357</v>
       </c>
       <c r="C64" t="n">
-        <v>26.0198</v>
+        <v>26.2451</v>
       </c>
       <c r="D64" t="n">
-        <v>91.5795</v>
+        <v>91.0294</v>
       </c>
       <c r="E64" t="n">
-        <v>33.1484</v>
+        <v>32.3845</v>
       </c>
       <c r="F64" t="n">
-        <v>45.1853</v>
+        <v>45.7983</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>22.5982</v>
+        <v>22.0103</v>
       </c>
       <c r="C65" t="n">
-        <v>35.4152</v>
+        <v>35.0084</v>
       </c>
       <c r="D65" t="n">
-        <v>89.3963</v>
+        <v>88.9235</v>
       </c>
       <c r="E65" t="n">
-        <v>32.447</v>
+        <v>31.8065</v>
       </c>
       <c r="F65" t="n">
-        <v>44.6922</v>
+        <v>45.1799</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.6007</v>
+        <v>22.5215</v>
       </c>
       <c r="C66" t="n">
-        <v>34.8461</v>
+        <v>34.4468</v>
       </c>
       <c r="D66" t="n">
-        <v>87.5857</v>
+        <v>87.1237</v>
       </c>
       <c r="E66" t="n">
-        <v>31.7201</v>
+        <v>31.1366</v>
       </c>
       <c r="F66" t="n">
-        <v>44.1212</v>
+        <v>44.5695</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>38.4989</v>
+        <v>36.6491</v>
       </c>
       <c r="C67" t="n">
-        <v>34.3178</v>
+        <v>33.9966</v>
       </c>
       <c r="D67" t="n">
-        <v>85.95820000000001</v>
+        <v>85.46559999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>30.8482</v>
+        <v>30.21</v>
       </c>
       <c r="F67" t="n">
-        <v>43.303</v>
+        <v>43.9867</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>37.0806</v>
+        <v>36.8396</v>
       </c>
       <c r="C68" t="n">
-        <v>33.9235</v>
+        <v>33.6819</v>
       </c>
       <c r="D68" t="n">
-        <v>84.47369999999999</v>
+        <v>84.072</v>
       </c>
       <c r="E68" t="n">
-        <v>29.9357</v>
+        <v>29.7785</v>
       </c>
       <c r="F68" t="n">
-        <v>43.0578</v>
+        <v>43.4889</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>36.606</v>
+        <v>36.2301</v>
       </c>
       <c r="C69" t="n">
-        <v>33.694</v>
+        <v>33.3635</v>
       </c>
       <c r="D69" t="n">
-        <v>83.1525</v>
+        <v>82.5643</v>
       </c>
       <c r="E69" t="n">
-        <v>29.6414</v>
+        <v>29.1326</v>
       </c>
       <c r="F69" t="n">
-        <v>42.509</v>
+        <v>42.8584</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>35.9793</v>
+        <v>34.9896</v>
       </c>
       <c r="C70" t="n">
-        <v>33.4179</v>
+        <v>33.0804</v>
       </c>
       <c r="D70" t="n">
-        <v>82.1876</v>
+        <v>81.7521</v>
       </c>
       <c r="E70" t="n">
-        <v>28.7421</v>
+        <v>28.2415</v>
       </c>
       <c r="F70" t="n">
-        <v>41.9115</v>
+        <v>42.266</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>35.2145</v>
+        <v>34.1662</v>
       </c>
       <c r="C71" t="n">
-        <v>32.744</v>
+        <v>32.8718</v>
       </c>
       <c r="D71" t="n">
-        <v>81.4949</v>
+        <v>81.05889999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>28.0449</v>
+        <v>27.8182</v>
       </c>
       <c r="F71" t="n">
-        <v>41.4742</v>
+        <v>41.8571</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>33.3155</v>
+        <v>33.6162</v>
       </c>
       <c r="C72" t="n">
-        <v>32.6514</v>
+        <v>32.4381</v>
       </c>
       <c r="D72" t="n">
-        <v>81.1058</v>
+        <v>80.5301</v>
       </c>
       <c r="E72" t="n">
-        <v>27.4154</v>
+        <v>26.9609</v>
       </c>
       <c r="F72" t="n">
-        <v>41.0953</v>
+        <v>41.4708</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>31.6419</v>
+        <v>33.7501</v>
       </c>
       <c r="C73" t="n">
-        <v>32.1968</v>
+        <v>32.1804</v>
       </c>
       <c r="D73" t="n">
-        <v>80.8027</v>
+        <v>80.2901</v>
       </c>
       <c r="E73" t="n">
-        <v>26.8941</v>
+        <v>26.5272</v>
       </c>
       <c r="F73" t="n">
-        <v>40.7224</v>
+        <v>41.0912</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>32.8813</v>
+        <v>32.699</v>
       </c>
       <c r="C74" t="n">
-        <v>31.684</v>
+        <v>31.8217</v>
       </c>
       <c r="D74" t="n">
-        <v>80.35899999999999</v>
+        <v>79.92</v>
       </c>
       <c r="E74" t="n">
-        <v>26.5563</v>
+        <v>25.9326</v>
       </c>
       <c r="F74" t="n">
-        <v>40.4008</v>
+        <v>40.7505</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>32.1114</v>
+        <v>32.5512</v>
       </c>
       <c r="C75" t="n">
-        <v>31.6625</v>
+        <v>31.4305</v>
       </c>
       <c r="D75" t="n">
-        <v>78.96729999999999</v>
+        <v>79.25109999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>26.0218</v>
+        <v>25.6851</v>
       </c>
       <c r="F75" t="n">
-        <v>40.1572</v>
+        <v>40.3559</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>31.9179</v>
+        <v>31.0972</v>
       </c>
       <c r="C76" t="n">
-        <v>31.2469</v>
+        <v>31.2323</v>
       </c>
       <c r="D76" t="n">
-        <v>78.97369999999999</v>
+        <v>79.22190000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>25.2625</v>
+        <v>25.4095</v>
       </c>
       <c r="F76" t="n">
-        <v>39.9673</v>
+        <v>40.1606</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>32.3128</v>
+        <v>31.2423</v>
       </c>
       <c r="C77" t="n">
-        <v>30.8857</v>
+        <v>30.9384</v>
       </c>
       <c r="D77" t="n">
-        <v>79.3053</v>
+        <v>79.52</v>
       </c>
       <c r="E77" t="n">
-        <v>25.1217</v>
+        <v>24.9204</v>
       </c>
       <c r="F77" t="n">
-        <v>39.963</v>
+        <v>40.1473</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>31.1892</v>
+        <v>30.2074</v>
       </c>
       <c r="C78" t="n">
-        <v>30.8638</v>
+        <v>30.6237</v>
       </c>
       <c r="D78" t="n">
-        <v>129.808</v>
+        <v>130.081</v>
       </c>
       <c r="E78" t="n">
-        <v>42.5405</v>
+        <v>42.3438</v>
       </c>
       <c r="F78" t="n">
-        <v>64.3704</v>
+        <v>66.2375</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>34.3289</v>
+        <v>30.9098</v>
       </c>
       <c r="C79" t="n">
-        <v>40.6761</v>
+        <v>40.4722</v>
       </c>
       <c r="D79" t="n">
-        <v>127.657</v>
+        <v>127.935</v>
       </c>
       <c r="E79" t="n">
-        <v>41.9682</v>
+        <v>41.7695</v>
       </c>
       <c r="F79" t="n">
-        <v>64.5635</v>
+        <v>67.5857</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>32.4596</v>
+        <v>30.6899</v>
       </c>
       <c r="C80" t="n">
-        <v>41.2865</v>
+        <v>41.1323</v>
       </c>
       <c r="D80" t="n">
-        <v>125.645</v>
+        <v>125.953</v>
       </c>
       <c r="E80" t="n">
-        <v>41.2457</v>
+        <v>41.0614</v>
       </c>
       <c r="F80" t="n">
-        <v>64.53789999999999</v>
+        <v>66.62730000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>45.5792</v>
+        <v>46.0342</v>
       </c>
       <c r="C81" t="n">
-        <v>41.7564</v>
+        <v>41.4951</v>
       </c>
       <c r="D81" t="n">
-        <v>124.161</v>
+        <v>124.462</v>
       </c>
       <c r="E81" t="n">
-        <v>40.5971</v>
+        <v>40.2465</v>
       </c>
       <c r="F81" t="n">
-        <v>64.0117</v>
+        <v>65.12779999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>49.9322</v>
+        <v>45.0493</v>
       </c>
       <c r="C82" t="n">
-        <v>41.9557</v>
+        <v>41.8383</v>
       </c>
       <c r="D82" t="n">
-        <v>122.844</v>
+        <v>122.998</v>
       </c>
       <c r="E82" t="n">
-        <v>39.686</v>
+        <v>39.2491</v>
       </c>
       <c r="F82" t="n">
-        <v>63.4076</v>
+        <v>65.5094</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>44.2949</v>
+        <v>47.0648</v>
       </c>
       <c r="C83" t="n">
-        <v>42.1867</v>
+        <v>41.9999</v>
       </c>
       <c r="D83" t="n">
-        <v>122.044</v>
+        <v>122.172</v>
       </c>
       <c r="E83" t="n">
-        <v>38.689</v>
+        <v>38.4723</v>
       </c>
       <c r="F83" t="n">
-        <v>62.5588</v>
+        <v>63.9068</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.4612</v>
+        <v>45.5523</v>
       </c>
       <c r="C84" t="n">
-        <v>42.3608</v>
+        <v>42.2014</v>
       </c>
       <c r="D84" t="n">
-        <v>121.726</v>
+        <v>121.718</v>
       </c>
       <c r="E84" t="n">
-        <v>37.9377</v>
+        <v>37.6388</v>
       </c>
       <c r="F84" t="n">
-        <v>62.4521</v>
+        <v>63.3134</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>43.6533</v>
+        <v>45.6279</v>
       </c>
       <c r="C85" t="n">
-        <v>42.5424</v>
+        <v>42.3668</v>
       </c>
       <c r="D85" t="n">
-        <v>121.269</v>
+        <v>121.427</v>
       </c>
       <c r="E85" t="n">
-        <v>37.1704</v>
+        <v>36.7848</v>
       </c>
       <c r="F85" t="n">
-        <v>60.1118</v>
+        <v>61.8883</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>44.8508</v>
+        <v>45.2006</v>
       </c>
       <c r="C86" t="n">
-        <v>42.5668</v>
+        <v>42.3202</v>
       </c>
       <c r="D86" t="n">
-        <v>121.13</v>
+        <v>121.382</v>
       </c>
       <c r="E86" t="n">
-        <v>36.2378</v>
+        <v>35.8614</v>
       </c>
       <c r="F86" t="n">
-        <v>59.6952</v>
+        <v>61.3365</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>44.3963</v>
+        <v>40.7608</v>
       </c>
       <c r="C87" t="n">
-        <v>42.6145</v>
+        <v>42.255</v>
       </c>
       <c r="D87" t="n">
-        <v>121.348</v>
+        <v>121.651</v>
       </c>
       <c r="E87" t="n">
-        <v>35.3856</v>
+        <v>35.123</v>
       </c>
       <c r="F87" t="n">
-        <v>58.7467</v>
+        <v>60.693</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>43.2017</v>
+        <v>43.4381</v>
       </c>
       <c r="C88" t="n">
-        <v>42.4694</v>
+        <v>42.1772</v>
       </c>
       <c r="D88" t="n">
-        <v>122.016</v>
+        <v>122.456</v>
       </c>
       <c r="E88" t="n">
-        <v>34.6435</v>
+        <v>34.3223</v>
       </c>
       <c r="F88" t="n">
-        <v>57.5131</v>
+        <v>59.6107</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>42.6516</v>
+        <v>43.2329</v>
       </c>
       <c r="C89" t="n">
-        <v>42.3497</v>
+        <v>42.0221</v>
       </c>
       <c r="D89" t="n">
-        <v>122.217</v>
+        <v>122.6</v>
       </c>
       <c r="E89" t="n">
-        <v>33.9358</v>
+        <v>33.6264</v>
       </c>
       <c r="F89" t="n">
-        <v>56.8299</v>
+        <v>58.5729</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>41.3734</v>
+        <v>40.8205</v>
       </c>
       <c r="C90" t="n">
-        <v>42.2929</v>
+        <v>42.0018</v>
       </c>
       <c r="D90" t="n">
-        <v>123.669</v>
+        <v>122.947</v>
       </c>
       <c r="E90" t="n">
-        <v>33.2845</v>
+        <v>32.9816</v>
       </c>
       <c r="F90" t="n">
-        <v>56.0231</v>
+        <v>56.9996</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>38.6674</v>
+        <v>38.3358</v>
       </c>
       <c r="C91" t="n">
-        <v>42.2348</v>
+        <v>41.788</v>
       </c>
       <c r="D91" t="n">
-        <v>125.112</v>
+        <v>124.938</v>
       </c>
       <c r="E91" t="n">
-        <v>32.5015</v>
+        <v>32.3488</v>
       </c>
       <c r="F91" t="n">
-        <v>56.5223</v>
+        <v>56.693</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>41.0918</v>
+        <v>40.1499</v>
       </c>
       <c r="C92" t="n">
-        <v>41.8793</v>
+        <v>41.7176</v>
       </c>
       <c r="D92" t="n">
-        <v>188.643</v>
+        <v>188.512</v>
       </c>
       <c r="E92" t="n">
-        <v>66.66589999999999</v>
+        <v>66.6831</v>
       </c>
       <c r="F92" t="n">
-        <v>86.4931</v>
+        <v>88.974</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>39.6301</v>
+        <v>43.1641</v>
       </c>
       <c r="C93" t="n">
-        <v>41.7387</v>
+        <v>41.2716</v>
       </c>
       <c r="D93" t="n">
-        <v>187.974</v>
+        <v>187.894</v>
       </c>
       <c r="E93" t="n">
-        <v>65.5107</v>
+        <v>65.1016</v>
       </c>
       <c r="F93" t="n">
-        <v>86.361</v>
+        <v>88.4068</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>40.3101</v>
+        <v>38.5752</v>
       </c>
       <c r="C94" t="n">
-        <v>75.1439</v>
+        <v>74.06910000000001</v>
       </c>
       <c r="D94" t="n">
-        <v>186.773</v>
+        <v>186.034</v>
       </c>
       <c r="E94" t="n">
-        <v>63.9477</v>
+        <v>63.4614</v>
       </c>
       <c r="F94" t="n">
-        <v>86.001</v>
+        <v>87.7154</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>68.84699999999999</v>
+        <v>70.5992</v>
       </c>
       <c r="C95" t="n">
-        <v>74.6908</v>
+        <v>73.79259999999999</v>
       </c>
       <c r="D95" t="n">
-        <v>185.074</v>
+        <v>184.605</v>
       </c>
       <c r="E95" t="n">
-        <v>62.3056</v>
+        <v>61.8768</v>
       </c>
       <c r="F95" t="n">
-        <v>86.3874</v>
+        <v>86.5889</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>73.55500000000001</v>
+        <v>69.93129999999999</v>
       </c>
       <c r="C96" t="n">
-        <v>74.0656</v>
+        <v>73.2343</v>
       </c>
       <c r="D96" t="n">
-        <v>183.592</v>
+        <v>183.505</v>
       </c>
       <c r="E96" t="n">
-        <v>60.6393</v>
+        <v>60.2538</v>
       </c>
       <c r="F96" t="n">
-        <v>85.6121</v>
+        <v>85.12439999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>69.4781</v>
+        <v>71.44929999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>73.31610000000001</v>
+        <v>72.3503</v>
       </c>
       <c r="D97" t="n">
-        <v>183.094</v>
+        <v>182.557</v>
       </c>
       <c r="E97" t="n">
-        <v>59.1645</v>
+        <v>58.4843</v>
       </c>
       <c r="F97" t="n">
-        <v>84.7732</v>
+        <v>85.99850000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>69.7003</v>
+        <v>66.45440000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>72.54089999999999</v>
+        <v>72.2081</v>
       </c>
       <c r="D98" t="n">
-        <v>182.904</v>
+        <v>183.473</v>
       </c>
       <c r="E98" t="n">
-        <v>57.4514</v>
+        <v>57.3329</v>
       </c>
       <c r="F98" t="n">
-        <v>83.7509</v>
+        <v>84.31910000000001</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>66.3391</v>
+        <v>67.02719999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>71.8283</v>
+        <v>71.6703</v>
       </c>
       <c r="D99" t="n">
-        <v>182.991</v>
+        <v>183.288</v>
       </c>
       <c r="E99" t="n">
-        <v>56.0634</v>
+        <v>55.7255</v>
       </c>
       <c r="F99" t="n">
-        <v>82.6902</v>
+        <v>83.4697</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>65.38939999999999</v>
+        <v>66.099</v>
       </c>
       <c r="C100" t="n">
-        <v>71.11709999999999</v>
+        <v>71.011</v>
       </c>
       <c r="D100" t="n">
-        <v>183.342</v>
+        <v>184.223</v>
       </c>
       <c r="E100" t="n">
-        <v>54.6705</v>
+        <v>54.4057</v>
       </c>
       <c r="F100" t="n">
-        <v>81.6306</v>
+        <v>82.87730000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>63.903</v>
+        <v>64.8561</v>
       </c>
       <c r="C101" t="n">
-        <v>70.4199</v>
+        <v>70.142</v>
       </c>
       <c r="D101" t="n">
-        <v>183.583</v>
+        <v>183.947</v>
       </c>
       <c r="E101" t="n">
-        <v>53.1029</v>
+        <v>53.0953</v>
       </c>
       <c r="F101" t="n">
-        <v>81.8524</v>
+        <v>81.2546</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>64.4054</v>
+        <v>62.698</v>
       </c>
       <c r="C102" t="n">
-        <v>69.7235</v>
+        <v>69.7148</v>
       </c>
       <c r="D102" t="n">
-        <v>184.948</v>
+        <v>185.434</v>
       </c>
       <c r="E102" t="n">
-        <v>51.9585</v>
+        <v>51.7766</v>
       </c>
       <c r="F102" t="n">
-        <v>83.0304</v>
+        <v>80.4362</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>62.0098</v>
+        <v>62.0792</v>
       </c>
       <c r="C103" t="n">
-        <v>69.1713</v>
+        <v>69.10850000000001</v>
       </c>
       <c r="D103" t="n">
-        <v>185.927</v>
+        <v>186.722</v>
       </c>
       <c r="E103" t="n">
-        <v>50.7776</v>
+        <v>50.5112</v>
       </c>
       <c r="F103" t="n">
-        <v>79.10080000000001</v>
+        <v>81.1045</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>57.3017</v>
+        <v>60.7168</v>
       </c>
       <c r="C104" t="n">
-        <v>68.679</v>
+        <v>68.63809999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>187.329</v>
+        <v>188.096</v>
       </c>
       <c r="E104" t="n">
-        <v>49.5311</v>
+        <v>49.5247</v>
       </c>
       <c r="F104" t="n">
-        <v>79.3681</v>
+        <v>80.3642</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>60.5518</v>
+        <v>59.8452</v>
       </c>
       <c r="C105" t="n">
-        <v>68.02509999999999</v>
+        <v>68.0736</v>
       </c>
       <c r="D105" t="n">
-        <v>188.975</v>
+        <v>189.68</v>
       </c>
       <c r="E105" t="n">
-        <v>48.5636</v>
+        <v>48.442</v>
       </c>
       <c r="F105" t="n">
-        <v>81.83799999999999</v>
+        <v>89.2217</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>58.7272</v>
+        <v>60.7967</v>
       </c>
       <c r="C106" t="n">
-        <v>67.532</v>
+        <v>67.38800000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>190.982</v>
+        <v>191.431</v>
       </c>
       <c r="E106" t="n">
-        <v>47.6281</v>
+        <v>47.5499</v>
       </c>
       <c r="F106" t="n">
-        <v>83.5792</v>
+        <v>89.0868</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>57.3235</v>
+        <v>56.5388</v>
       </c>
       <c r="C107" t="n">
-        <v>67.0565</v>
+        <v>66.8954</v>
       </c>
       <c r="D107" t="n">
-        <v>258.492</v>
+        <v>258.764</v>
       </c>
       <c r="E107" t="n">
-        <v>71.3485</v>
+        <v>82.7371</v>
       </c>
       <c r="F107" t="n">
-        <v>242.525</v>
+        <v>243.055</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>56.7287</v>
+        <v>57.3183</v>
       </c>
       <c r="C108" t="n">
-        <v>101.164</v>
+        <v>101.698</v>
       </c>
       <c r="D108" t="n">
-        <v>255.572</v>
+        <v>255.744</v>
       </c>
       <c r="E108" t="n">
-        <v>80.8869</v>
+        <v>80.8621</v>
       </c>
       <c r="F108" t="n">
-        <v>242.725</v>
+        <v>243.821</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>54.6241</v>
+        <v>46.1552</v>
       </c>
       <c r="C109" t="n">
-        <v>100.272</v>
+        <v>87.0635</v>
       </c>
       <c r="D109" t="n">
-        <v>253.196</v>
+        <v>253.025</v>
       </c>
       <c r="E109" t="n">
-        <v>68.1871</v>
+        <v>78.5615</v>
       </c>
       <c r="F109" t="n">
-        <v>244.458</v>
+        <v>245.048</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>88.5742</v>
+        <v>88.2803</v>
       </c>
       <c r="C110" t="n">
-        <v>99.5183</v>
+        <v>99.586</v>
       </c>
       <c r="D110" t="n">
-        <v>250.745</v>
+        <v>251.229</v>
       </c>
       <c r="E110" t="n">
-        <v>66.70440000000001</v>
+        <v>76.71420000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>245.353</v>
+        <v>243.666</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>85.5184</v>
+        <v>74.9221</v>
       </c>
       <c r="C111" t="n">
-        <v>98.0688</v>
+        <v>85.5855</v>
       </c>
       <c r="D111" t="n">
-        <v>249.368</v>
+        <v>251.903</v>
       </c>
       <c r="E111" t="n">
-        <v>65.0561</v>
+        <v>74.1794</v>
       </c>
       <c r="F111" t="n">
-        <v>245.529</v>
+        <v>244.513</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>78.009</v>
+        <v>83.24890000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>84.8403</v>
+        <v>96.6378</v>
       </c>
       <c r="D112" t="n">
-        <v>248.088</v>
+        <v>248.43</v>
       </c>
       <c r="E112" t="n">
-        <v>63.4093</v>
+        <v>63.4819</v>
       </c>
       <c r="F112" t="n">
-        <v>246.088</v>
+        <v>245.266</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>75.2183</v>
+        <v>82.9525</v>
       </c>
       <c r="C113" t="n">
-        <v>83.9357</v>
+        <v>95.3199</v>
       </c>
       <c r="D113" t="n">
-        <v>249.476</v>
+        <v>249.556</v>
       </c>
       <c r="E113" t="n">
-        <v>70.5029</v>
+        <v>62.0228</v>
       </c>
       <c r="F113" t="n">
-        <v>247.015</v>
+        <v>246.322</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>72.8083</v>
+        <v>78.3471</v>
       </c>
       <c r="C114" t="n">
-        <v>83.2597</v>
+        <v>93.82859999999999</v>
       </c>
       <c r="D114" t="n">
-        <v>260.9</v>
+        <v>248.852</v>
       </c>
       <c r="E114" t="n">
-        <v>68.93470000000001</v>
+        <v>68.7458</v>
       </c>
       <c r="F114" t="n">
-        <v>247.667</v>
+        <v>247.291</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>68.46720000000001</v>
+        <v>78.6936</v>
       </c>
       <c r="C115" t="n">
-        <v>82.455</v>
+        <v>92.64149999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>260.256</v>
+        <v>256.575</v>
       </c>
       <c r="E115" t="n">
-        <v>59.4306</v>
+        <v>67.1521</v>
       </c>
       <c r="F115" t="n">
-        <v>248.028</v>
+        <v>246.658</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>75.33280000000001</v>
+        <v>68.44589999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>91.4726</v>
+        <v>81.69799999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>260.473</v>
+        <v>260.068</v>
       </c>
       <c r="E116" t="n">
-        <v>65.7667</v>
+        <v>65.5919</v>
       </c>
       <c r="F116" t="n">
-        <v>247.641</v>
+        <v>247.61</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>75.0367</v>
+        <v>74.934</v>
       </c>
       <c r="C117" t="n">
-        <v>90.3986</v>
+        <v>90.37139999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>261.109</v>
+        <v>261.5</v>
       </c>
       <c r="E117" t="n">
-        <v>64.23860000000001</v>
+        <v>64.0873</v>
       </c>
       <c r="F117" t="n">
-        <v>248.926</v>
+        <v>248.136</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>73.1713</v>
+        <v>73.13549999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>89.179</v>
+        <v>89.271</v>
       </c>
       <c r="D118" t="n">
-        <v>245.95</v>
+        <v>245.752</v>
       </c>
       <c r="E118" t="n">
-        <v>56.0158</v>
+        <v>55.7424</v>
       </c>
       <c r="F118" t="n">
-        <v>249.237</v>
+        <v>248.729</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>65.943</v>
+        <v>71.6631</v>
       </c>
       <c r="C119" t="n">
-        <v>79.86</v>
+        <v>88.16930000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>247.187</v>
+        <v>247.308</v>
       </c>
       <c r="E119" t="n">
-        <v>55.0717</v>
+        <v>54.9258</v>
       </c>
       <c r="F119" t="n">
-        <v>226.486</v>
+        <v>103.207</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>65.6811</v>
+        <v>69.64060000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>79.47450000000001</v>
+        <v>87.2967</v>
       </c>
       <c r="D120" t="n">
-        <v>248.298</v>
+        <v>248.323</v>
       </c>
       <c r="E120" t="n">
-        <v>54.2927</v>
+        <v>53.9897</v>
       </c>
       <c r="F120" t="n">
-        <v>152.728</v>
+        <v>151.924</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>68.5248</v>
+        <v>69.5698</v>
       </c>
       <c r="C121" t="n">
-        <v>86.4761</v>
+        <v>86.4834</v>
       </c>
       <c r="D121" t="n">
-        <v>327.873</v>
+        <v>327.692</v>
       </c>
       <c r="E121" t="n">
-        <v>89.5879</v>
+        <v>89.4781</v>
       </c>
       <c r="F121" t="n">
-        <v>297</v>
+        <v>297.381</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>63.433</v>
+        <v>61.3945</v>
       </c>
       <c r="C122" t="n">
-        <v>113.842</v>
+        <v>113.765</v>
       </c>
       <c r="D122" t="n">
-        <v>322.329</v>
+        <v>322.642</v>
       </c>
       <c r="E122" t="n">
-        <v>87.7047</v>
+        <v>87.68210000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>296.054</v>
+        <v>296.721</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>61.8563</v>
+        <v>62.3245</v>
       </c>
       <c r="C123" t="n">
-        <v>112.454</v>
+        <v>112.433</v>
       </c>
       <c r="D123" t="n">
-        <v>317.847</v>
+        <v>318.388</v>
       </c>
       <c r="E123" t="n">
-        <v>85.82689999999999</v>
+        <v>85.86499999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>296.208</v>
+        <v>296.413</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>99.15560000000001</v>
+        <v>93.4314</v>
       </c>
       <c r="C124" t="n">
-        <v>118.662</v>
+        <v>112.172</v>
       </c>
       <c r="D124" t="n">
-        <v>314.821</v>
+        <v>314.571</v>
       </c>
       <c r="E124" t="n">
-        <v>84.2867</v>
+        <v>84.2782</v>
       </c>
       <c r="F124" t="n">
-        <v>295.935</v>
+        <v>295.317</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>97.61799999999999</v>
+        <v>96.92310000000001</v>
       </c>
       <c r="C125" t="n">
-        <v>117.307</v>
+        <v>117.171</v>
       </c>
       <c r="D125" t="n">
-        <v>302.023</v>
+        <v>309.173</v>
       </c>
       <c r="E125" t="n">
-        <v>85.5368</v>
+        <v>80.4542</v>
       </c>
       <c r="F125" t="n">
-        <v>287.183</v>
+        <v>285.782</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>92.20350000000001</v>
+        <v>87.60720000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>113.502</v>
+        <v>107.567</v>
       </c>
       <c r="D126" t="n">
-        <v>298.987</v>
+        <v>297.295</v>
       </c>
       <c r="E126" t="n">
-        <v>81.11499999999999</v>
+        <v>83.36320000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>295.207</v>
+        <v>284.904</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>90.23220000000001</v>
+        <v>91.1919</v>
       </c>
       <c r="C127" t="n">
-        <v>108.939</v>
+        <v>112.121</v>
       </c>
       <c r="D127" t="n">
-        <v>305.544</v>
+        <v>294.746</v>
       </c>
       <c r="E127" t="n">
-        <v>83.7457</v>
+        <v>77.27670000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>294.566</v>
+        <v>285.307</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>91.3182</v>
+        <v>84.93389999999999</v>
       </c>
       <c r="C128" t="n">
-        <v>113.39</v>
+        <v>105.583</v>
       </c>
       <c r="D128" t="n">
-        <v>303.114</v>
+        <v>292.48</v>
       </c>
       <c r="E128" t="n">
-        <v>78.1327</v>
+        <v>75.8779</v>
       </c>
       <c r="F128" t="n">
-        <v>294.131</v>
+        <v>284.459</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>83.8685</v>
+        <v>86.84059999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>106.984</v>
+        <v>109.569</v>
       </c>
       <c r="D129" t="n">
-        <v>301.101</v>
+        <v>290.632</v>
       </c>
       <c r="E129" t="n">
-        <v>76.6763</v>
+        <v>74.6061</v>
       </c>
       <c r="F129" t="n">
-        <v>293.528</v>
+        <v>284.872</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>82.80200000000001</v>
+        <v>85.9096</v>
       </c>
       <c r="C130" t="n">
-        <v>106.136</v>
+        <v>108.565</v>
       </c>
       <c r="D130" t="n">
-        <v>299.38</v>
+        <v>289.407</v>
       </c>
       <c r="E130" t="n">
-        <v>75.44329999999999</v>
+        <v>73.22410000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>293.349</v>
+        <v>283.325</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>82.66840000000001</v>
+        <v>79.9866</v>
       </c>
       <c r="C131" t="n">
-        <v>105.338</v>
+        <v>102.755</v>
       </c>
       <c r="D131" t="n">
-        <v>298.356</v>
+        <v>288.051</v>
       </c>
       <c r="E131" t="n">
-        <v>74.1562</v>
+        <v>72.1777</v>
       </c>
       <c r="F131" t="n">
-        <v>293.755</v>
+        <v>283.649</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>81.9049</v>
+        <v>79.9092</v>
       </c>
       <c r="C132" t="n">
-        <v>104.491</v>
+        <v>102.006</v>
       </c>
       <c r="D132" t="n">
-        <v>297.497</v>
+        <v>287.111</v>
       </c>
       <c r="E132" t="n">
-        <v>73.1027</v>
+        <v>74.2076</v>
       </c>
       <c r="F132" t="n">
-        <v>292.97</v>
+        <v>283.95</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>80.41330000000001</v>
+        <v>74.8306</v>
       </c>
       <c r="C133" t="n">
-        <v>103.71</v>
+        <v>92.30240000000001</v>
       </c>
       <c r="D133" t="n">
-        <v>297.007</v>
+        <v>286.926</v>
       </c>
       <c r="E133" t="n">
-        <v>72.04900000000001</v>
+        <v>69.8801</v>
       </c>
       <c r="F133" t="n">
-        <v>293.383</v>
+        <v>284.486</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>80.14619999999999</v>
+        <v>78.1626</v>
       </c>
       <c r="C134" t="n">
-        <v>103.142</v>
+        <v>100.482</v>
       </c>
       <c r="D134" t="n">
-        <v>293.249</v>
+        <v>281.985</v>
       </c>
       <c r="E134" t="n">
-        <v>64.98609999999999</v>
+        <v>62.8232</v>
       </c>
       <c r="F134" t="n">
-        <v>240.181</v>
+        <v>233.744</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>78.42310000000001</v>
+        <v>75.7641</v>
       </c>
       <c r="C135" t="n">
-        <v>102.499</v>
+        <v>99.74590000000001</v>
       </c>
       <c r="D135" t="n">
-        <v>375.021</v>
+        <v>361.436</v>
       </c>
       <c r="E135" t="n">
-        <v>100.67</v>
+        <v>98.25579999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>338.855</v>
+        <v>326.64</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>77.9896</v>
+        <v>74.8656</v>
       </c>
       <c r="C136" t="n">
-        <v>136.466</v>
+        <v>133.605</v>
       </c>
       <c r="D136" t="n">
-        <v>368.38</v>
+        <v>355.404</v>
       </c>
       <c r="E136" t="n">
-        <v>98.75409999999999</v>
+        <v>96.68810000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>335.862</v>
+        <v>326.099</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>77.0624</v>
+        <v>74.4106</v>
       </c>
       <c r="C137" t="n">
-        <v>135.33</v>
+        <v>132.243</v>
       </c>
       <c r="D137" t="n">
-        <v>362.398</v>
+        <v>349.758</v>
       </c>
       <c r="E137" t="n">
-        <v>96.9136</v>
+        <v>94.7608</v>
       </c>
       <c r="F137" t="n">
-        <v>336.236</v>
+        <v>325.051</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>109.415</v>
+        <v>106.621</v>
       </c>
       <c r="C138" t="n">
-        <v>134.908</v>
+        <v>132.337</v>
       </c>
       <c r="D138" t="n">
-        <v>357.926</v>
+        <v>344.45</v>
       </c>
       <c r="E138" t="n">
-        <v>95.11279999999999</v>
+        <v>92.9729</v>
       </c>
       <c r="F138" t="n">
-        <v>333.616</v>
+        <v>324.121</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>107.497</v>
+        <v>99.85809999999999</v>
       </c>
       <c r="C139" t="n">
-        <v>133.623</v>
+        <v>123.941</v>
       </c>
       <c r="D139" t="n">
-        <v>352.298</v>
+        <v>339.908</v>
       </c>
       <c r="E139" t="n">
-        <v>93.58710000000001</v>
+        <v>91.4504</v>
       </c>
       <c r="F139" t="n">
-        <v>334.124</v>
+        <v>323.992</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>102.222</v>
+        <v>103.058</v>
       </c>
       <c r="C140" t="n">
-        <v>124.877</v>
+        <v>129.755</v>
       </c>
       <c r="D140" t="n">
-        <v>337.17</v>
+        <v>335.423</v>
       </c>
       <c r="E140" t="n">
-        <v>94.6936</v>
+        <v>94.354</v>
       </c>
       <c r="F140" t="n">
-        <v>323.713</v>
+        <v>323.338</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>100.879</v>
+        <v>101.21</v>
       </c>
       <c r="C141" t="n">
-        <v>128.837</v>
+        <v>128.581</v>
       </c>
       <c r="D141" t="n">
-        <v>335.189</v>
+        <v>335.151</v>
       </c>
       <c r="E141" t="n">
-        <v>88.7714</v>
+        <v>92.8296</v>
       </c>
       <c r="F141" t="n">
-        <v>321.619</v>
+        <v>323.416</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>95.73690000000001</v>
+        <v>96.2944</v>
       </c>
       <c r="C142" t="n">
-        <v>121.542</v>
+        <v>121.903</v>
       </c>
       <c r="D142" t="n">
-        <v>332.606</v>
+        <v>334.654</v>
       </c>
       <c r="E142" t="n">
-        <v>87.19499999999999</v>
+        <v>91.12090000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>320.15</v>
+        <v>322.212</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>93.99209999999999</v>
+        <v>97.66719999999999</v>
       </c>
       <c r="C143" t="n">
-        <v>120.839</v>
+        <v>126.587</v>
       </c>
       <c r="D143" t="n">
-        <v>329.527</v>
+        <v>332.594</v>
       </c>
       <c r="E143" t="n">
-        <v>85.8742</v>
+        <v>85.81829999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>319.358</v>
+        <v>320.579</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>22.0351</v>
+        <v>22.3191</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6058</v>
+        <v>24.5708</v>
       </c>
       <c r="D2" t="n">
-        <v>56.0545</v>
+        <v>55.6332</v>
       </c>
       <c r="E2" t="n">
-        <v>17.8695</v>
+        <v>17.8294</v>
       </c>
       <c r="F2" t="n">
-        <v>33.3511</v>
+        <v>33.297</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9369</v>
+        <v>21.2335</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1827</v>
+        <v>24.0472</v>
       </c>
       <c r="D3" t="n">
-        <v>55.3951</v>
+        <v>54.9302</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3667</v>
+        <v>17.3219</v>
       </c>
       <c r="F3" t="n">
-        <v>32.9122</v>
+        <v>32.7994</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>20.7245</v>
+        <v>20.3697</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5574</v>
+        <v>23.546</v>
       </c>
       <c r="D4" t="n">
-        <v>54.9393</v>
+        <v>54.5362</v>
       </c>
       <c r="E4" t="n">
-        <v>16.8864</v>
+        <v>16.8296</v>
       </c>
       <c r="F4" t="n">
-        <v>32.5201</v>
+        <v>32.4129</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>20.6427</v>
+        <v>19.8605</v>
       </c>
       <c r="C5" t="n">
-        <v>23.128</v>
+        <v>23.1132</v>
       </c>
       <c r="D5" t="n">
-        <v>54.7189</v>
+        <v>54.2253</v>
       </c>
       <c r="E5" t="n">
-        <v>16.4808</v>
+        <v>16.4632</v>
       </c>
       <c r="F5" t="n">
-        <v>32.2774</v>
+        <v>32.177</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>19.9836</v>
+        <v>20.0021</v>
       </c>
       <c r="C6" t="n">
-        <v>22.8309</v>
+        <v>22.7555</v>
       </c>
       <c r="D6" t="n">
-        <v>54.1771</v>
+        <v>53.7783</v>
       </c>
       <c r="E6" t="n">
-        <v>16.1572</v>
+        <v>16.1254</v>
       </c>
       <c r="F6" t="n">
-        <v>32.2166</v>
+        <v>32.0718</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.5328</v>
+        <v>19.5199</v>
       </c>
       <c r="C7" t="n">
-        <v>22.4742</v>
+        <v>22.4509</v>
       </c>
       <c r="D7" t="n">
-        <v>68.95999999999999</v>
+        <v>68.2129</v>
       </c>
       <c r="E7" t="n">
-        <v>24.8705</v>
+        <v>25.0286</v>
       </c>
       <c r="F7" t="n">
-        <v>40.2158</v>
+        <v>39.952</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>19.4204</v>
+        <v>19.2405</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8984</v>
+        <v>30.8462</v>
       </c>
       <c r="D8" t="n">
-        <v>67.4871</v>
+        <v>66.65309999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>23.8497</v>
+        <v>23.9216</v>
       </c>
       <c r="F8" t="n">
-        <v>39.135</v>
+        <v>39.0451</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>19.3386</v>
+        <v>19.3444</v>
       </c>
       <c r="C9" t="n">
-        <v>30.204</v>
+        <v>30.1202</v>
       </c>
       <c r="D9" t="n">
-        <v>66.18600000000001</v>
+        <v>65.29949999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>23.1555</v>
+        <v>23.2083</v>
       </c>
       <c r="F9" t="n">
-        <v>38.4809</v>
+        <v>38.2524</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.8275</v>
+        <v>28.8149</v>
       </c>
       <c r="C10" t="n">
-        <v>29.3113</v>
+        <v>29.3166</v>
       </c>
       <c r="D10" t="n">
-        <v>65.0448</v>
+        <v>64.13079999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>22.456</v>
+        <v>22.3761</v>
       </c>
       <c r="F10" t="n">
-        <v>37.5369</v>
+        <v>37.4079</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>26.8415</v>
+        <v>27.1421</v>
       </c>
       <c r="C11" t="n">
-        <v>28.5718</v>
+        <v>28.4698</v>
       </c>
       <c r="D11" t="n">
-        <v>63.9498</v>
+        <v>63.0387</v>
       </c>
       <c r="E11" t="n">
-        <v>21.6489</v>
+        <v>21.6993</v>
       </c>
       <c r="F11" t="n">
-        <v>36.7401</v>
+        <v>36.6357</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.5671</v>
+        <v>26.3369</v>
       </c>
       <c r="C12" t="n">
-        <v>27.9195</v>
+        <v>27.8117</v>
       </c>
       <c r="D12" t="n">
-        <v>62.8664</v>
+        <v>62.1468</v>
       </c>
       <c r="E12" t="n">
-        <v>20.9942</v>
+        <v>21.1662</v>
       </c>
       <c r="F12" t="n">
-        <v>36.0316</v>
+        <v>35.9568</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.8246</v>
+        <v>25.3971</v>
       </c>
       <c r="C13" t="n">
-        <v>27.1604</v>
+        <v>27.1554</v>
       </c>
       <c r="D13" t="n">
-        <v>61.936</v>
+        <v>61.0002</v>
       </c>
       <c r="E13" t="n">
-        <v>20.3522</v>
+        <v>20.2468</v>
       </c>
       <c r="F13" t="n">
-        <v>35.4327</v>
+        <v>35.3196</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.8562</v>
+        <v>24.6105</v>
       </c>
       <c r="C14" t="n">
-        <v>26.4963</v>
+        <v>26.5124</v>
       </c>
       <c r="D14" t="n">
-        <v>61.132</v>
+        <v>60.2782</v>
       </c>
       <c r="E14" t="n">
-        <v>19.6879</v>
+        <v>19.703</v>
       </c>
       <c r="F14" t="n">
-        <v>34.8531</v>
+        <v>34.7507</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.9588</v>
+        <v>23.5664</v>
       </c>
       <c r="C15" t="n">
-        <v>25.9205</v>
+        <v>25.8592</v>
       </c>
       <c r="D15" t="n">
-        <v>60.7427</v>
+        <v>59.6025</v>
       </c>
       <c r="E15" t="n">
-        <v>19.1905</v>
+        <v>19.1498</v>
       </c>
       <c r="F15" t="n">
-        <v>34.2805</v>
+        <v>34.2027</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.2494</v>
+        <v>23.5175</v>
       </c>
       <c r="C16" t="n">
-        <v>25.3395</v>
+        <v>25.3375</v>
       </c>
       <c r="D16" t="n">
-        <v>60.0171</v>
+        <v>59.1582</v>
       </c>
       <c r="E16" t="n">
-        <v>18.7016</v>
+        <v>18.5929</v>
       </c>
       <c r="F16" t="n">
-        <v>33.7928</v>
+        <v>33.6574</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.1908</v>
+        <v>22.6857</v>
       </c>
       <c r="C17" t="n">
-        <v>24.8554</v>
+        <v>24.756</v>
       </c>
       <c r="D17" t="n">
-        <v>59.5663</v>
+        <v>58.6173</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2061</v>
+        <v>18.1274</v>
       </c>
       <c r="F17" t="n">
-        <v>33.3709</v>
+        <v>33.2785</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>22.0284</v>
+        <v>21.987</v>
       </c>
       <c r="C18" t="n">
-        <v>24.3343</v>
+        <v>24.2773</v>
       </c>
       <c r="D18" t="n">
-        <v>58.6319</v>
+        <v>57.8241</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7479</v>
+        <v>17.7261</v>
       </c>
       <c r="F18" t="n">
-        <v>32.9418</v>
+        <v>32.8399</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.5698</v>
+        <v>21.8014</v>
       </c>
       <c r="C19" t="n">
-        <v>23.9441</v>
+        <v>23.8137</v>
       </c>
       <c r="D19" t="n">
-        <v>58.062</v>
+        <v>57.3149</v>
       </c>
       <c r="E19" t="n">
-        <v>17.3909</v>
+        <v>17.3592</v>
       </c>
       <c r="F19" t="n">
-        <v>32.6119</v>
+        <v>32.5745</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>21.0265</v>
+        <v>21.0462</v>
       </c>
       <c r="C20" t="n">
-        <v>23.4569</v>
+        <v>23.4521</v>
       </c>
       <c r="D20" t="n">
-        <v>57.7851</v>
+        <v>57.1029</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1322</v>
+        <v>17.1715</v>
       </c>
       <c r="F20" t="n">
-        <v>32.4764</v>
+        <v>32.3804</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.5059</v>
+        <v>20.6034</v>
       </c>
       <c r="C21" t="n">
-        <v>23.1271</v>
+        <v>23.1295</v>
       </c>
       <c r="D21" t="n">
-        <v>75.2851</v>
+        <v>74.6996</v>
       </c>
       <c r="E21" t="n">
-        <v>25.9676</v>
+        <v>25.8893</v>
       </c>
       <c r="F21" t="n">
-        <v>40.6661</v>
+        <v>40.3823</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.2351</v>
+        <v>20.2772</v>
       </c>
       <c r="C22" t="n">
-        <v>31.5925</v>
+        <v>31.669</v>
       </c>
       <c r="D22" t="n">
-        <v>73.6262</v>
+        <v>73.0425</v>
       </c>
       <c r="E22" t="n">
-        <v>24.9398</v>
+        <v>25.1226</v>
       </c>
       <c r="F22" t="n">
-        <v>39.8029</v>
+        <v>39.5601</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>20.4079</v>
+        <v>20.2875</v>
       </c>
       <c r="C23" t="n">
-        <v>30.851</v>
+        <v>30.7871</v>
       </c>
       <c r="D23" t="n">
-        <v>72.19589999999999</v>
+        <v>71.6588</v>
       </c>
       <c r="E23" t="n">
-        <v>24.1474</v>
+        <v>24.1204</v>
       </c>
       <c r="F23" t="n">
-        <v>38.9593</v>
+        <v>38.745</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>28.6486</v>
+        <v>28.5181</v>
       </c>
       <c r="C24" t="n">
-        <v>30.0687</v>
+        <v>30.0286</v>
       </c>
       <c r="D24" t="n">
-        <v>70.9414</v>
+        <v>70.5282</v>
       </c>
       <c r="E24" t="n">
-        <v>23.3794</v>
+        <v>23.3327</v>
       </c>
       <c r="F24" t="n">
-        <v>38.186</v>
+        <v>37.9507</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>27.5857</v>
+        <v>27.957</v>
       </c>
       <c r="C25" t="n">
-        <v>29.3358</v>
+        <v>29.2648</v>
       </c>
       <c r="D25" t="n">
-        <v>69.7119</v>
+        <v>69.27670000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>22.6357</v>
+        <v>22.5625</v>
       </c>
       <c r="F25" t="n">
-        <v>37.4286</v>
+        <v>37.232</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>26.8288</v>
+        <v>27.0585</v>
       </c>
       <c r="C26" t="n">
-        <v>28.5999</v>
+        <v>28.5252</v>
       </c>
       <c r="D26" t="n">
-        <v>68.59220000000001</v>
+        <v>68.0192</v>
       </c>
       <c r="E26" t="n">
-        <v>21.9388</v>
+        <v>21.8984</v>
       </c>
       <c r="F26" t="n">
-        <v>36.8009</v>
+        <v>36.4282</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>25.9343</v>
+        <v>26.0334</v>
       </c>
       <c r="C27" t="n">
-        <v>27.8826</v>
+        <v>27.874</v>
       </c>
       <c r="D27" t="n">
-        <v>67.6636</v>
+        <v>67.1464</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2482</v>
+        <v>21.2222</v>
       </c>
       <c r="F27" t="n">
-        <v>36.1444</v>
+        <v>35.7861</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.1363</v>
+        <v>25.712</v>
       </c>
       <c r="C28" t="n">
-        <v>27.2228</v>
+        <v>27.2239</v>
       </c>
       <c r="D28" t="n">
-        <v>66.5459</v>
+        <v>65.98909999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>20.6308</v>
+        <v>20.5638</v>
       </c>
       <c r="F28" t="n">
-        <v>35.5795</v>
+        <v>35.2299</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>24.3892</v>
+        <v>24.9316</v>
       </c>
       <c r="C29" t="n">
         <v>26.609</v>
       </c>
       <c r="D29" t="n">
-        <v>65.84699999999999</v>
+        <v>65.345</v>
       </c>
       <c r="E29" t="n">
-        <v>20.0093</v>
+        <v>19.9982</v>
       </c>
       <c r="F29" t="n">
-        <v>34.914</v>
+        <v>34.6889</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>24.1749</v>
+        <v>24.21</v>
       </c>
       <c r="C30" t="n">
-        <v>26.0227</v>
+        <v>26.028</v>
       </c>
       <c r="D30" t="n">
-        <v>64.9524</v>
+        <v>64.613</v>
       </c>
       <c r="E30" t="n">
-        <v>19.4875</v>
+        <v>19.4152</v>
       </c>
       <c r="F30" t="n">
-        <v>34.5042</v>
+        <v>34.1986</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.0287</v>
+        <v>23.5422</v>
       </c>
       <c r="C31" t="n">
-        <v>25.4664</v>
+        <v>25.4498</v>
       </c>
       <c r="D31" t="n">
-        <v>64.411</v>
+        <v>64.0878</v>
       </c>
       <c r="E31" t="n">
-        <v>18.9352</v>
+        <v>18.8819</v>
       </c>
       <c r="F31" t="n">
-        <v>33.7013</v>
+        <v>33.5134</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>23.5351</v>
+        <v>23.0931</v>
       </c>
       <c r="C32" t="n">
-        <v>25.1367</v>
+        <v>24.8762</v>
       </c>
       <c r="D32" t="n">
-        <v>63.981</v>
+        <v>63.6867</v>
       </c>
       <c r="E32" t="n">
-        <v>18.4814</v>
+        <v>18.4338</v>
       </c>
       <c r="F32" t="n">
-        <v>33.3404</v>
+        <v>33.1488</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>22.9459</v>
+        <v>22.9828</v>
       </c>
       <c r="C33" t="n">
-        <v>24.6807</v>
+        <v>24.5425</v>
       </c>
       <c r="D33" t="n">
-        <v>63.5857</v>
+        <v>63.2721</v>
       </c>
       <c r="E33" t="n">
-        <v>18.1441</v>
+        <v>18.1364</v>
       </c>
       <c r="F33" t="n">
-        <v>32.9892</v>
+        <v>32.9982</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>21.676</v>
+        <v>21.7648</v>
       </c>
       <c r="C34" t="n">
-        <v>24.2936</v>
+        <v>24.0461</v>
       </c>
       <c r="D34" t="n">
-        <v>62.8305</v>
+        <v>62.6168</v>
       </c>
       <c r="E34" t="n">
-        <v>17.8493</v>
+        <v>17.841</v>
       </c>
       <c r="F34" t="n">
-        <v>32.7862</v>
+        <v>32.7162</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>21.4585</v>
+        <v>21.4568</v>
       </c>
       <c r="C35" t="n">
-        <v>23.7829</v>
+        <v>23.7162</v>
       </c>
       <c r="D35" t="n">
-        <v>81.27970000000001</v>
+        <v>80.8364</v>
       </c>
       <c r="E35" t="n">
-        <v>26.7336</v>
+        <v>26.5717</v>
       </c>
       <c r="F35" t="n">
-        <v>41.5472</v>
+        <v>41.4224</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>21.4154</v>
+        <v>20.8705</v>
       </c>
       <c r="C36" t="n">
-        <v>23.5392</v>
+        <v>23.4329</v>
       </c>
       <c r="D36" t="n">
-        <v>79.51690000000001</v>
+        <v>79.2189</v>
       </c>
       <c r="E36" t="n">
-        <v>25.8144</v>
+        <v>25.7621</v>
       </c>
       <c r="F36" t="n">
-        <v>40.778</v>
+        <v>40.6403</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>21.0266</v>
+        <v>21.5191</v>
       </c>
       <c r="C37" t="n">
-        <v>31.6298</v>
+        <v>31.5609</v>
       </c>
       <c r="D37" t="n">
-        <v>77.9781</v>
+        <v>77.6292</v>
       </c>
       <c r="E37" t="n">
-        <v>25.0416</v>
+        <v>24.9807</v>
       </c>
       <c r="F37" t="n">
-        <v>39.9755</v>
+        <v>39.7604</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>29.7482</v>
+        <v>29.3272</v>
       </c>
       <c r="C38" t="n">
-        <v>30.9607</v>
+        <v>30.8093</v>
       </c>
       <c r="D38" t="n">
-        <v>76.4845</v>
+        <v>76.0984</v>
       </c>
       <c r="E38" t="n">
-        <v>24.1909</v>
+        <v>24.1609</v>
       </c>
       <c r="F38" t="n">
-        <v>39.0015</v>
+        <v>38.961</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>28.6229</v>
+        <v>27.9717</v>
       </c>
       <c r="C39" t="n">
-        <v>30.1046</v>
+        <v>30.1076</v>
       </c>
       <c r="D39" t="n">
-        <v>75.16930000000001</v>
+        <v>74.8138</v>
       </c>
       <c r="E39" t="n">
-        <v>23.473</v>
+        <v>23.4233</v>
       </c>
       <c r="F39" t="n">
-        <v>38.6222</v>
+        <v>38.1952</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>27.3591</v>
+        <v>27.5464</v>
       </c>
       <c r="C40" t="n">
-        <v>29.5103</v>
+        <v>29.3698</v>
       </c>
       <c r="D40" t="n">
-        <v>73.8861</v>
+        <v>73.5522</v>
       </c>
       <c r="E40" t="n">
-        <v>22.7694</v>
+        <v>22.7313</v>
       </c>
       <c r="F40" t="n">
-        <v>37.7968</v>
+        <v>37.5279</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.4309</v>
+        <v>26.3311</v>
       </c>
       <c r="C41" t="n">
-        <v>28.9802</v>
+        <v>28.7487</v>
       </c>
       <c r="D41" t="n">
-        <v>72.67789999999999</v>
+        <v>72.38849999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>22.0872</v>
+        <v>22.0614</v>
       </c>
       <c r="F41" t="n">
-        <v>37.151</v>
+        <v>36.8456</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>25.8258</v>
+        <v>25.7219</v>
       </c>
       <c r="C42" t="n">
-        <v>28.1843</v>
+        <v>28.1222</v>
       </c>
       <c r="D42" t="n">
-        <v>71.96120000000001</v>
+        <v>71.5909</v>
       </c>
       <c r="E42" t="n">
-        <v>21.4682</v>
+        <v>21.3647</v>
       </c>
       <c r="F42" t="n">
-        <v>36.6442</v>
+        <v>36.1919</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>25.0505</v>
+        <v>25.1709</v>
       </c>
       <c r="C43" t="n">
-        <v>27.797</v>
+        <v>27.5094</v>
       </c>
       <c r="D43" t="n">
-        <v>70.678</v>
+        <v>70.31319999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>20.9209</v>
+        <v>20.8791</v>
       </c>
       <c r="F43" t="n">
-        <v>36.0937</v>
+        <v>35.6849</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.7968</v>
+        <v>24.4496</v>
       </c>
       <c r="C44" t="n">
-        <v>26.9503</v>
+        <v>26.9056</v>
       </c>
       <c r="D44" t="n">
-        <v>69.9598</v>
+        <v>69.4704</v>
       </c>
       <c r="E44" t="n">
-        <v>20.3361</v>
+        <v>20.3123</v>
       </c>
       <c r="F44" t="n">
-        <v>35.6239</v>
+        <v>35.1784</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>23.4628</v>
+        <v>23.6571</v>
       </c>
       <c r="C45" t="n">
-        <v>26.5439</v>
+        <v>26.4193</v>
       </c>
       <c r="D45" t="n">
-        <v>69.3074</v>
+        <v>68.8415</v>
       </c>
       <c r="E45" t="n">
-        <v>19.8585</v>
+        <v>19.7937</v>
       </c>
       <c r="F45" t="n">
-        <v>35.1501</v>
+        <v>34.7857</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>23.211</v>
+        <v>23.1392</v>
       </c>
       <c r="C46" t="n">
-        <v>26.183</v>
+        <v>26.0549</v>
       </c>
       <c r="D46" t="n">
-        <v>68.7503</v>
+        <v>68.3223</v>
       </c>
       <c r="E46" t="n">
-        <v>19.4352</v>
+        <v>19.3884</v>
       </c>
       <c r="F46" t="n">
-        <v>34.7513</v>
+        <v>34.3545</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.5979</v>
+        <v>22.8529</v>
       </c>
       <c r="C47" t="n">
-        <v>25.728</v>
+        <v>25.4367</v>
       </c>
       <c r="D47" t="n">
-        <v>68.29730000000001</v>
+        <v>67.8258</v>
       </c>
       <c r="E47" t="n">
-        <v>19.0018</v>
+        <v>19.0477</v>
       </c>
       <c r="F47" t="n">
-        <v>34.4021</v>
+        <v>34.0006</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>21.9906</v>
+        <v>22.0073</v>
       </c>
       <c r="C48" t="n">
-        <v>25.285</v>
+        <v>25.0639</v>
       </c>
       <c r="D48" t="n">
-        <v>67.495</v>
+        <v>67.0138</v>
       </c>
       <c r="E48" t="n">
-        <v>18.7038</v>
+        <v>18.6219</v>
       </c>
       <c r="F48" t="n">
-        <v>34.145</v>
+        <v>33.7429</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>21.4363</v>
+        <v>21.5736</v>
       </c>
       <c r="C49" t="n">
-        <v>24.9376</v>
+        <v>24.731</v>
       </c>
       <c r="D49" t="n">
-        <v>67.1322</v>
+        <v>66.7517</v>
       </c>
       <c r="E49" t="n">
-        <v>18.5053</v>
+        <v>18.4645</v>
       </c>
       <c r="F49" t="n">
-        <v>34.0834</v>
+        <v>33.5937</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.6408</v>
+        <v>21.4399</v>
       </c>
       <c r="C50" t="n">
-        <v>24.4326</v>
+        <v>24.4523</v>
       </c>
       <c r="D50" t="n">
-        <v>84.34650000000001</v>
+        <v>83.82559999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>27.0044</v>
+        <v>27.0009</v>
       </c>
       <c r="F50" t="n">
-        <v>42.1584</v>
+        <v>41.8418</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>21.1324</v>
+        <v>21.467</v>
       </c>
       <c r="C51" t="n">
-        <v>32.5653</v>
+        <v>32.5657</v>
       </c>
       <c r="D51" t="n">
-        <v>82.717</v>
+        <v>82.20050000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>26.2147</v>
+        <v>26.2485</v>
       </c>
       <c r="F51" t="n">
-        <v>41.2576</v>
+        <v>41.1776</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>22.1225</v>
+        <v>21.5312</v>
       </c>
       <c r="C52" t="n">
-        <v>31.9769</v>
+        <v>31.863</v>
       </c>
       <c r="D52" t="n">
-        <v>81.0138</v>
+        <v>80.6454</v>
       </c>
       <c r="E52" t="n">
-        <v>25.5623</v>
+        <v>25.5404</v>
       </c>
       <c r="F52" t="n">
-        <v>40.5449</v>
+        <v>40.3637</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.1056</v>
+        <v>29.3071</v>
       </c>
       <c r="C53" t="n">
-        <v>31.2413</v>
+        <v>31.2595</v>
       </c>
       <c r="D53" t="n">
-        <v>79.5104</v>
+        <v>79.1217</v>
       </c>
       <c r="E53" t="n">
-        <v>24.5337</v>
+        <v>24.7287</v>
       </c>
       <c r="F53" t="n">
-        <v>39.9752</v>
+        <v>39.7238</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>28.4388</v>
+        <v>28.4816</v>
       </c>
       <c r="C54" t="n">
-        <v>30.5156</v>
+        <v>30.5416</v>
       </c>
       <c r="D54" t="n">
-        <v>78.078</v>
+        <v>77.71980000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>24.0775</v>
+        <v>23.9757</v>
       </c>
       <c r="F54" t="n">
-        <v>39.2183</v>
+        <v>39.0637</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>27.4978</v>
+        <v>27.5075</v>
       </c>
       <c r="C55" t="n">
-        <v>30.2436</v>
+        <v>29.9581</v>
       </c>
       <c r="D55" t="n">
-        <v>76.8853</v>
+        <v>76.5129</v>
       </c>
       <c r="E55" t="n">
-        <v>23.2245</v>
+        <v>23.3835</v>
       </c>
       <c r="F55" t="n">
-        <v>38.6736</v>
+        <v>38.4669</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>26.9189</v>
+        <v>26.9856</v>
       </c>
       <c r="C56" t="n">
-        <v>29.7503</v>
+        <v>29.3222</v>
       </c>
       <c r="D56" t="n">
-        <v>75.8104</v>
+        <v>75.47709999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>22.6332</v>
+        <v>22.7189</v>
       </c>
       <c r="F56" t="n">
-        <v>38.0724</v>
+        <v>37.9172</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.5538</v>
+        <v>26.2389</v>
       </c>
       <c r="C57" t="n">
-        <v>28.8268</v>
+        <v>28.9382</v>
       </c>
       <c r="D57" t="n">
-        <v>74.5964</v>
+        <v>74.31319999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>22.2039</v>
+        <v>22.1304</v>
       </c>
       <c r="F57" t="n">
-        <v>37.5918</v>
+        <v>37.3933</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>25.5998</v>
+        <v>25.4611</v>
       </c>
       <c r="C58" t="n">
-        <v>28.2986</v>
+        <v>28.5379</v>
       </c>
       <c r="D58" t="n">
-        <v>73.78</v>
+        <v>73.47880000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>21.5481</v>
+        <v>21.5516</v>
       </c>
       <c r="F58" t="n">
-        <v>37.057</v>
+        <v>36.9006</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>24.5735</v>
+        <v>25.2756</v>
       </c>
       <c r="C59" t="n">
-        <v>27.7935</v>
+        <v>27.9874</v>
       </c>
       <c r="D59" t="n">
-        <v>72.9157</v>
+        <v>72.62520000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>21.0612</v>
+        <v>21.1132</v>
       </c>
       <c r="F59" t="n">
-        <v>36.6138</v>
+        <v>36.5079</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>24.0745</v>
+        <v>24.0267</v>
       </c>
       <c r="C60" t="n">
-        <v>27.5321</v>
+        <v>27.6051</v>
       </c>
       <c r="D60" t="n">
-        <v>72.2882</v>
+        <v>72.0197</v>
       </c>
       <c r="E60" t="n">
-        <v>20.5712</v>
+        <v>20.5941</v>
       </c>
       <c r="F60" t="n">
-        <v>36.2219</v>
+        <v>36.158</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>23.7424</v>
+        <v>24.1523</v>
       </c>
       <c r="C61" t="n">
-        <v>27.2641</v>
+        <v>27.2291</v>
       </c>
       <c r="D61" t="n">
-        <v>71.5177</v>
+        <v>71.29689999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>20.1371</v>
+        <v>20.1927</v>
       </c>
       <c r="F61" t="n">
-        <v>35.9404</v>
+        <v>35.8438</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>23.2004</v>
+        <v>23.7943</v>
       </c>
       <c r="C62" t="n">
-        <v>26.8696</v>
+        <v>26.764</v>
       </c>
       <c r="D62" t="n">
-        <v>70.919</v>
+        <v>70.6922</v>
       </c>
       <c r="E62" t="n">
-        <v>19.9589</v>
+        <v>19.8619</v>
       </c>
       <c r="F62" t="n">
-        <v>35.7233</v>
+        <v>35.6634</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>22.6852</v>
+        <v>22.8605</v>
       </c>
       <c r="C63" t="n">
-        <v>26.2414</v>
+        <v>26.5098</v>
       </c>
       <c r="D63" t="n">
-        <v>70.56059999999999</v>
+        <v>70.3664</v>
       </c>
       <c r="E63" t="n">
-        <v>19.5386</v>
+        <v>19.6262</v>
       </c>
       <c r="F63" t="n">
-        <v>35.5622</v>
+        <v>35.5014</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>22.7357</v>
+        <v>22.8402</v>
       </c>
       <c r="C64" t="n">
-        <v>26.2451</v>
+        <v>26.3326</v>
       </c>
       <c r="D64" t="n">
-        <v>91.0294</v>
+        <v>91.43510000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>32.3845</v>
+        <v>32.4596</v>
       </c>
       <c r="F64" t="n">
-        <v>45.7983</v>
+        <v>45.4838</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>22.0103</v>
+        <v>22.5605</v>
       </c>
       <c r="C65" t="n">
-        <v>35.0084</v>
+        <v>35.0976</v>
       </c>
       <c r="D65" t="n">
-        <v>88.9235</v>
+        <v>89.0996</v>
       </c>
       <c r="E65" t="n">
-        <v>31.8065</v>
+        <v>31.8376</v>
       </c>
       <c r="F65" t="n">
-        <v>45.1799</v>
+        <v>44.9844</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.5215</v>
+        <v>22.3447</v>
       </c>
       <c r="C66" t="n">
-        <v>34.4468</v>
+        <v>34.4663</v>
       </c>
       <c r="D66" t="n">
-        <v>87.1237</v>
+        <v>87.2702</v>
       </c>
       <c r="E66" t="n">
-        <v>31.1366</v>
+        <v>31.1232</v>
       </c>
       <c r="F66" t="n">
-        <v>44.5695</v>
+        <v>44.3273</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>36.6491</v>
+        <v>38.1568</v>
       </c>
       <c r="C67" t="n">
-        <v>33.9966</v>
+        <v>34.1148</v>
       </c>
       <c r="D67" t="n">
-        <v>85.46559999999999</v>
+        <v>85.6144</v>
       </c>
       <c r="E67" t="n">
-        <v>30.21</v>
+        <v>30.4086</v>
       </c>
       <c r="F67" t="n">
-        <v>43.9867</v>
+        <v>43.7852</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>36.8396</v>
+        <v>36.769</v>
       </c>
       <c r="C68" t="n">
-        <v>33.6819</v>
+        <v>33.8709</v>
       </c>
       <c r="D68" t="n">
-        <v>84.072</v>
+        <v>84.1253</v>
       </c>
       <c r="E68" t="n">
-        <v>29.7785</v>
+        <v>29.6276</v>
       </c>
       <c r="F68" t="n">
-        <v>43.4889</v>
+        <v>43.1524</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>36.2301</v>
+        <v>35.076</v>
       </c>
       <c r="C69" t="n">
-        <v>33.3635</v>
+        <v>33.4917</v>
       </c>
       <c r="D69" t="n">
-        <v>82.5643</v>
+        <v>82.84180000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>29.1326</v>
+        <v>29.0701</v>
       </c>
       <c r="F69" t="n">
-        <v>42.8584</v>
+        <v>42.5952</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>34.9896</v>
+        <v>34.9014</v>
       </c>
       <c r="C70" t="n">
-        <v>33.0804</v>
+        <v>33.1427</v>
       </c>
       <c r="D70" t="n">
-        <v>81.7521</v>
+        <v>81.96559999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>28.2415</v>
+        <v>28.2389</v>
       </c>
       <c r="F70" t="n">
-        <v>42.266</v>
+        <v>42.0428</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>34.1662</v>
+        <v>34.3602</v>
       </c>
       <c r="C71" t="n">
-        <v>32.8718</v>
+        <v>32.9557</v>
       </c>
       <c r="D71" t="n">
-        <v>81.05889999999999</v>
+        <v>81.2047</v>
       </c>
       <c r="E71" t="n">
-        <v>27.8182</v>
+        <v>27.5549</v>
       </c>
       <c r="F71" t="n">
-        <v>41.8571</v>
+        <v>41.6093</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>33.6162</v>
+        <v>33.9753</v>
       </c>
       <c r="C72" t="n">
-        <v>32.4381</v>
+        <v>32.6353</v>
       </c>
       <c r="D72" t="n">
-        <v>80.5301</v>
+        <v>80.81789999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>26.9609</v>
+        <v>27.1899</v>
       </c>
       <c r="F72" t="n">
-        <v>41.4708</v>
+        <v>41.3345</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>33.7501</v>
+        <v>33.0648</v>
       </c>
       <c r="C73" t="n">
-        <v>32.1804</v>
+        <v>32.3553</v>
       </c>
       <c r="D73" t="n">
-        <v>80.2901</v>
+        <v>80.5797</v>
       </c>
       <c r="E73" t="n">
-        <v>26.5272</v>
+        <v>26.4899</v>
       </c>
       <c r="F73" t="n">
-        <v>41.0912</v>
+        <v>40.8713</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>32.699</v>
+        <v>33.1506</v>
       </c>
       <c r="C74" t="n">
-        <v>31.8217</v>
+        <v>32.0379</v>
       </c>
       <c r="D74" t="n">
-        <v>79.92</v>
+        <v>80.2804</v>
       </c>
       <c r="E74" t="n">
-        <v>25.9326</v>
+        <v>26.0508</v>
       </c>
       <c r="F74" t="n">
-        <v>40.7505</v>
+        <v>40.6385</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>32.5512</v>
+        <v>31.9422</v>
       </c>
       <c r="C75" t="n">
-        <v>31.4305</v>
+        <v>31.6459</v>
       </c>
       <c r="D75" t="n">
-        <v>79.25109999999999</v>
+        <v>79.251</v>
       </c>
       <c r="E75" t="n">
-        <v>25.6851</v>
+        <v>25.6161</v>
       </c>
       <c r="F75" t="n">
-        <v>40.3559</v>
+        <v>40.3925</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>31.0972</v>
+        <v>31.2724</v>
       </c>
       <c r="C76" t="n">
-        <v>31.2323</v>
+        <v>31.334</v>
       </c>
       <c r="D76" t="n">
-        <v>79.22190000000001</v>
+        <v>79.54989999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>25.4095</v>
+        <v>25.1054</v>
       </c>
       <c r="F76" t="n">
-        <v>40.1606</v>
+        <v>40.1165</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>31.2423</v>
+        <v>30.9997</v>
       </c>
       <c r="C77" t="n">
-        <v>30.9384</v>
+        <v>31.1172</v>
       </c>
       <c r="D77" t="n">
-        <v>79.52</v>
+        <v>79.9421</v>
       </c>
       <c r="E77" t="n">
-        <v>24.9204</v>
+        <v>24.9112</v>
       </c>
       <c r="F77" t="n">
-        <v>40.1473</v>
+        <v>40.117</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>30.2074</v>
+        <v>30.2942</v>
       </c>
       <c r="C78" t="n">
-        <v>30.6237</v>
+        <v>30.9042</v>
       </c>
       <c r="D78" t="n">
-        <v>130.081</v>
+        <v>130.129</v>
       </c>
       <c r="E78" t="n">
-        <v>42.3438</v>
+        <v>42.2357</v>
       </c>
       <c r="F78" t="n">
-        <v>66.2375</v>
+        <v>63.4963</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>30.9098</v>
+        <v>28.8089</v>
       </c>
       <c r="C79" t="n">
-        <v>40.4722</v>
+        <v>40.1506</v>
       </c>
       <c r="D79" t="n">
-        <v>127.935</v>
+        <v>127.786</v>
       </c>
       <c r="E79" t="n">
-        <v>41.7695</v>
+        <v>44.7056</v>
       </c>
       <c r="F79" t="n">
-        <v>67.5857</v>
+        <v>62.7097</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>30.6899</v>
+        <v>32.5635</v>
       </c>
       <c r="C80" t="n">
-        <v>41.1323</v>
+        <v>40.6728</v>
       </c>
       <c r="D80" t="n">
-        <v>125.953</v>
+        <v>124.428</v>
       </c>
       <c r="E80" t="n">
-        <v>41.0614</v>
+        <v>38.9223</v>
       </c>
       <c r="F80" t="n">
-        <v>66.62730000000001</v>
+        <v>62.7781</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>46.0342</v>
+        <v>46.4506</v>
       </c>
       <c r="C81" t="n">
-        <v>41.4951</v>
+        <v>41.0391</v>
       </c>
       <c r="D81" t="n">
-        <v>124.462</v>
+        <v>122.792</v>
       </c>
       <c r="E81" t="n">
-        <v>40.2465</v>
+        <v>38.2757</v>
       </c>
       <c r="F81" t="n">
-        <v>65.12779999999999</v>
+        <v>62.291</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>45.0493</v>
+        <v>46.6309</v>
       </c>
       <c r="C82" t="n">
-        <v>41.8383</v>
+        <v>41.2908</v>
       </c>
       <c r="D82" t="n">
-        <v>122.998</v>
+        <v>121.439</v>
       </c>
       <c r="E82" t="n">
-        <v>39.2491</v>
+        <v>37.55</v>
       </c>
       <c r="F82" t="n">
-        <v>65.5094</v>
+        <v>61.4848</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>47.0648</v>
+        <v>44.4827</v>
       </c>
       <c r="C83" t="n">
-        <v>41.9999</v>
+        <v>41.5812</v>
       </c>
       <c r="D83" t="n">
-        <v>122.172</v>
+        <v>120.486</v>
       </c>
       <c r="E83" t="n">
-        <v>38.4723</v>
+        <v>36.6773</v>
       </c>
       <c r="F83" t="n">
-        <v>63.9068</v>
+        <v>60.9249</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>45.5523</v>
+        <v>43.2934</v>
       </c>
       <c r="C84" t="n">
-        <v>42.2014</v>
+        <v>41.685</v>
       </c>
       <c r="D84" t="n">
-        <v>121.718</v>
+        <v>119.82</v>
       </c>
       <c r="E84" t="n">
-        <v>37.6388</v>
+        <v>35.8044</v>
       </c>
       <c r="F84" t="n">
-        <v>63.3134</v>
+        <v>60.3379</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>45.6279</v>
+        <v>43.741</v>
       </c>
       <c r="C85" t="n">
-        <v>42.3668</v>
+        <v>41.7866</v>
       </c>
       <c r="D85" t="n">
-        <v>121.427</v>
+        <v>119.813</v>
       </c>
       <c r="E85" t="n">
-        <v>36.7848</v>
+        <v>35.1144</v>
       </c>
       <c r="F85" t="n">
-        <v>61.8883</v>
+        <v>59.3849</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>45.2006</v>
+        <v>37.5837</v>
       </c>
       <c r="C86" t="n">
-        <v>42.3202</v>
+        <v>41.8921</v>
       </c>
       <c r="D86" t="n">
-        <v>121.382</v>
+        <v>119.538</v>
       </c>
       <c r="E86" t="n">
-        <v>35.8614</v>
+        <v>34.3873</v>
       </c>
       <c r="F86" t="n">
-        <v>61.3365</v>
+        <v>58.6299</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>40.7608</v>
+        <v>40.2375</v>
       </c>
       <c r="C87" t="n">
-        <v>42.255</v>
+        <v>41.9441</v>
       </c>
       <c r="D87" t="n">
-        <v>121.651</v>
+        <v>119.52</v>
       </c>
       <c r="E87" t="n">
-        <v>35.123</v>
+        <v>33.5965</v>
       </c>
       <c r="F87" t="n">
-        <v>60.693</v>
+        <v>57.4676</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>43.4381</v>
+        <v>41.5858</v>
       </c>
       <c r="C88" t="n">
-        <v>42.1772</v>
+        <v>41.9348</v>
       </c>
       <c r="D88" t="n">
-        <v>122.456</v>
+        <v>120.141</v>
       </c>
       <c r="E88" t="n">
-        <v>34.3223</v>
+        <v>32.9098</v>
       </c>
       <c r="F88" t="n">
-        <v>59.6107</v>
+        <v>56.785</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>43.2329</v>
+        <v>37.886</v>
       </c>
       <c r="C89" t="n">
-        <v>42.0221</v>
+        <v>41.5745</v>
       </c>
       <c r="D89" t="n">
-        <v>122.6</v>
+        <v>120.523</v>
       </c>
       <c r="E89" t="n">
-        <v>33.6264</v>
+        <v>32.2222</v>
       </c>
       <c r="F89" t="n">
-        <v>58.5729</v>
+        <v>55.9896</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>40.8205</v>
+        <v>41.125</v>
       </c>
       <c r="C90" t="n">
-        <v>42.0018</v>
+        <v>41.7134</v>
       </c>
       <c r="D90" t="n">
-        <v>122.947</v>
+        <v>121.742</v>
       </c>
       <c r="E90" t="n">
-        <v>32.9816</v>
+        <v>31.5513</v>
       </c>
       <c r="F90" t="n">
-        <v>56.9996</v>
+        <v>55.4431</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>38.3358</v>
+        <v>40.4031</v>
       </c>
       <c r="C91" t="n">
-        <v>41.788</v>
+        <v>41.3464</v>
       </c>
       <c r="D91" t="n">
-        <v>124.938</v>
+        <v>123.323</v>
       </c>
       <c r="E91" t="n">
-        <v>32.3488</v>
+        <v>31.141</v>
       </c>
       <c r="F91" t="n">
-        <v>56.693</v>
+        <v>55.4291</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>40.1499</v>
+        <v>38.3972</v>
       </c>
       <c r="C92" t="n">
-        <v>41.7176</v>
+        <v>41.2136</v>
       </c>
       <c r="D92" t="n">
-        <v>188.512</v>
+        <v>184.973</v>
       </c>
       <c r="E92" t="n">
-        <v>66.6831</v>
+        <v>64.9716</v>
       </c>
       <c r="F92" t="n">
-        <v>88.974</v>
+        <v>85.7516</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>43.1641</v>
+        <v>41.7178</v>
       </c>
       <c r="C93" t="n">
-        <v>41.2716</v>
+        <v>40.6818</v>
       </c>
       <c r="D93" t="n">
-        <v>187.894</v>
+        <v>184.419</v>
       </c>
       <c r="E93" t="n">
-        <v>65.1016</v>
+        <v>63.671</v>
       </c>
       <c r="F93" t="n">
-        <v>88.4068</v>
+        <v>85.7347</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>38.5752</v>
+        <v>40.9095</v>
       </c>
       <c r="C94" t="n">
-        <v>74.06910000000001</v>
+        <v>73.8425</v>
       </c>
       <c r="D94" t="n">
-        <v>186.034</v>
+        <v>182.396</v>
       </c>
       <c r="E94" t="n">
-        <v>63.4614</v>
+        <v>62.0354</v>
       </c>
       <c r="F94" t="n">
-        <v>87.7154</v>
+        <v>84.43689999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>70.5992</v>
+        <v>70.50360000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>73.79259999999999</v>
+        <v>73.8884</v>
       </c>
       <c r="D95" t="n">
-        <v>184.605</v>
+        <v>181.343</v>
       </c>
       <c r="E95" t="n">
-        <v>61.8768</v>
+        <v>60.2287</v>
       </c>
       <c r="F95" t="n">
-        <v>86.5889</v>
+        <v>84.6148</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>69.93129999999999</v>
+        <v>68.92400000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>73.2343</v>
+        <v>72.89279999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>183.505</v>
+        <v>180.392</v>
       </c>
       <c r="E96" t="n">
-        <v>60.2538</v>
+        <v>58.4533</v>
       </c>
       <c r="F96" t="n">
-        <v>85.12439999999999</v>
+        <v>83.79559999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>71.44929999999999</v>
+        <v>69.2392</v>
       </c>
       <c r="C97" t="n">
-        <v>72.3503</v>
+        <v>72.0681</v>
       </c>
       <c r="D97" t="n">
-        <v>182.557</v>
+        <v>179.045</v>
       </c>
       <c r="E97" t="n">
-        <v>58.4843</v>
+        <v>57.0698</v>
       </c>
       <c r="F97" t="n">
-        <v>85.99850000000001</v>
+        <v>82.6086</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>66.45440000000001</v>
+        <v>68.4486</v>
       </c>
       <c r="C98" t="n">
-        <v>72.2081</v>
+        <v>71.12779999999999</v>
       </c>
       <c r="D98" t="n">
-        <v>183.473</v>
+        <v>178.81</v>
       </c>
       <c r="E98" t="n">
-        <v>57.3329</v>
+        <v>55.4493</v>
       </c>
       <c r="F98" t="n">
-        <v>84.31910000000001</v>
+        <v>80.9034</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>67.02719999999999</v>
+        <v>64.2529</v>
       </c>
       <c r="C99" t="n">
-        <v>71.6703</v>
+        <v>70.61969999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>183.288</v>
+        <v>179.324</v>
       </c>
       <c r="E99" t="n">
-        <v>55.7255</v>
+        <v>54.1986</v>
       </c>
       <c r="F99" t="n">
-        <v>83.4697</v>
+        <v>81.349</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>66.099</v>
+        <v>63.9497</v>
       </c>
       <c r="C100" t="n">
-        <v>71.011</v>
+        <v>70.00020000000001</v>
       </c>
       <c r="D100" t="n">
-        <v>184.223</v>
+        <v>179.484</v>
       </c>
       <c r="E100" t="n">
-        <v>54.4057</v>
+        <v>52.5182</v>
       </c>
       <c r="F100" t="n">
-        <v>82.87730000000001</v>
+        <v>78.45529999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>64.8561</v>
+        <v>63.3016</v>
       </c>
       <c r="C101" t="n">
-        <v>70.142</v>
+        <v>69.3094</v>
       </c>
       <c r="D101" t="n">
-        <v>183.947</v>
+        <v>179.514</v>
       </c>
       <c r="E101" t="n">
-        <v>53.0953</v>
+        <v>51.2874</v>
       </c>
       <c r="F101" t="n">
-        <v>81.2546</v>
+        <v>81.22929999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>62.698</v>
+        <v>58.4636</v>
       </c>
       <c r="C102" t="n">
-        <v>69.7148</v>
+        <v>68.7054</v>
       </c>
       <c r="D102" t="n">
-        <v>185.434</v>
+        <v>180.531</v>
       </c>
       <c r="E102" t="n">
-        <v>51.7766</v>
+        <v>50.0976</v>
       </c>
       <c r="F102" t="n">
-        <v>80.4362</v>
+        <v>78.6472</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>62.0792</v>
+        <v>61.1742</v>
       </c>
       <c r="C103" t="n">
-        <v>69.10850000000001</v>
+        <v>68.0329</v>
       </c>
       <c r="D103" t="n">
-        <v>186.722</v>
+        <v>181.411</v>
       </c>
       <c r="E103" t="n">
-        <v>50.5112</v>
+        <v>48.7874</v>
       </c>
       <c r="F103" t="n">
-        <v>81.1045</v>
+        <v>81.25790000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>60.7168</v>
+        <v>59.338</v>
       </c>
       <c r="C104" t="n">
-        <v>68.63809999999999</v>
+        <v>67.36579999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>188.096</v>
+        <v>182.904</v>
       </c>
       <c r="E104" t="n">
-        <v>49.5247</v>
+        <v>47.9261</v>
       </c>
       <c r="F104" t="n">
-        <v>80.3642</v>
+        <v>76.80329999999999</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>59.8452</v>
+        <v>57.8766</v>
       </c>
       <c r="C105" t="n">
-        <v>68.0736</v>
+        <v>66.81489999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>189.68</v>
+        <v>184.392</v>
       </c>
       <c r="E105" t="n">
-        <v>48.442</v>
+        <v>46.8668</v>
       </c>
       <c r="F105" t="n">
-        <v>89.2217</v>
+        <v>75.6969</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>60.7967</v>
+        <v>55.0773</v>
       </c>
       <c r="C106" t="n">
-        <v>67.38800000000001</v>
+        <v>66.21939999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>191.431</v>
+        <v>185.452</v>
       </c>
       <c r="E106" t="n">
-        <v>47.5499</v>
+        <v>45.9664</v>
       </c>
       <c r="F106" t="n">
-        <v>89.0868</v>
+        <v>87.97110000000001</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>56.5388</v>
+        <v>53.5058</v>
       </c>
       <c r="C107" t="n">
-        <v>66.8954</v>
+        <v>65.7723</v>
       </c>
       <c r="D107" t="n">
-        <v>258.764</v>
+        <v>250.59</v>
       </c>
       <c r="E107" t="n">
-        <v>82.7371</v>
+        <v>80.9755</v>
       </c>
       <c r="F107" t="n">
-        <v>243.055</v>
+        <v>237.07</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>57.3183</v>
+        <v>54.119</v>
       </c>
       <c r="C108" t="n">
-        <v>101.698</v>
+        <v>100.182</v>
       </c>
       <c r="D108" t="n">
-        <v>255.744</v>
+        <v>247.611</v>
       </c>
       <c r="E108" t="n">
-        <v>80.8621</v>
+        <v>78.65649999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>243.821</v>
+        <v>237.265</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>46.1552</v>
+        <v>51.2658</v>
       </c>
       <c r="C109" t="n">
-        <v>87.0635</v>
+        <v>98.9889</v>
       </c>
       <c r="D109" t="n">
-        <v>253.025</v>
+        <v>245.175</v>
       </c>
       <c r="E109" t="n">
-        <v>78.5615</v>
+        <v>76.62860000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>245.048</v>
+        <v>236.994</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>88.2803</v>
+        <v>86.6726</v>
       </c>
       <c r="C110" t="n">
-        <v>99.586</v>
+        <v>97.9906</v>
       </c>
       <c r="D110" t="n">
-        <v>251.229</v>
+        <v>242.665</v>
       </c>
       <c r="E110" t="n">
-        <v>76.71420000000001</v>
+        <v>64.2942</v>
       </c>
       <c r="F110" t="n">
-        <v>243.666</v>
+        <v>239.266</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>74.9221</v>
+        <v>83.1258</v>
       </c>
       <c r="C111" t="n">
-        <v>85.5855</v>
+        <v>96.38679999999999</v>
       </c>
       <c r="D111" t="n">
-        <v>251.903</v>
+        <v>241.199</v>
       </c>
       <c r="E111" t="n">
-        <v>74.1794</v>
+        <v>72.2508</v>
       </c>
       <c r="F111" t="n">
-        <v>244.513</v>
+        <v>237.605</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>83.24890000000001</v>
+        <v>81.9408</v>
       </c>
       <c r="C112" t="n">
-        <v>96.6378</v>
+        <v>94.8982</v>
       </c>
       <c r="D112" t="n">
-        <v>248.43</v>
+        <v>239.373</v>
       </c>
       <c r="E112" t="n">
-        <v>63.4819</v>
+        <v>61.2871</v>
       </c>
       <c r="F112" t="n">
-        <v>245.266</v>
+        <v>238.547</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>82.9525</v>
+        <v>79.73350000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>95.3199</v>
+        <v>93.3394</v>
       </c>
       <c r="D113" t="n">
-        <v>249.556</v>
+        <v>240.846</v>
       </c>
       <c r="E113" t="n">
-        <v>62.0228</v>
+        <v>60.1808</v>
       </c>
       <c r="F113" t="n">
-        <v>246.322</v>
+        <v>239.101</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>78.3471</v>
+        <v>77.1084</v>
       </c>
       <c r="C114" t="n">
-        <v>93.82859999999999</v>
+        <v>92.12220000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>248.852</v>
+        <v>250.855</v>
       </c>
       <c r="E114" t="n">
-        <v>68.7458</v>
+        <v>66.7119</v>
       </c>
       <c r="F114" t="n">
-        <v>247.291</v>
+        <v>240.585</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>78.6936</v>
+        <v>75.59520000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>92.64149999999999</v>
+        <v>90.9692</v>
       </c>
       <c r="D115" t="n">
-        <v>256.575</v>
+        <v>251.035</v>
       </c>
       <c r="E115" t="n">
-        <v>67.1521</v>
+        <v>65.1407</v>
       </c>
       <c r="F115" t="n">
-        <v>246.658</v>
+        <v>239.9</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>68.44589999999999</v>
+        <v>74.83969999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>81.69799999999999</v>
+        <v>89.81699999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>260.068</v>
+        <v>251.215</v>
       </c>
       <c r="E116" t="n">
-        <v>65.5919</v>
+        <v>63.6024</v>
       </c>
       <c r="F116" t="n">
-        <v>247.61</v>
+        <v>241.006</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>74.934</v>
+        <v>72.1801</v>
       </c>
       <c r="C117" t="n">
-        <v>90.37139999999999</v>
+        <v>88.6952</v>
       </c>
       <c r="D117" t="n">
-        <v>261.5</v>
+        <v>251.36</v>
       </c>
       <c r="E117" t="n">
-        <v>64.0873</v>
+        <v>62.2493</v>
       </c>
       <c r="F117" t="n">
-        <v>248.136</v>
+        <v>241.614</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>73.13549999999999</v>
+        <v>63.4065</v>
       </c>
       <c r="C118" t="n">
-        <v>89.271</v>
+        <v>78.9858</v>
       </c>
       <c r="D118" t="n">
-        <v>245.752</v>
+        <v>238.448</v>
       </c>
       <c r="E118" t="n">
-        <v>55.7424</v>
+        <v>60.8498</v>
       </c>
       <c r="F118" t="n">
-        <v>248.729</v>
+        <v>241.148</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>71.6631</v>
+        <v>69.72069999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>88.16930000000001</v>
+        <v>86.491</v>
       </c>
       <c r="D119" t="n">
-        <v>247.308</v>
+        <v>238.554</v>
       </c>
       <c r="E119" t="n">
-        <v>54.9258</v>
+        <v>52.9862</v>
       </c>
       <c r="F119" t="n">
-        <v>103.207</v>
+        <v>242.228</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>69.64060000000001</v>
+        <v>62.098</v>
       </c>
       <c r="C120" t="n">
-        <v>87.2967</v>
+        <v>77.7111</v>
       </c>
       <c r="D120" t="n">
-        <v>248.323</v>
+        <v>239.853</v>
       </c>
       <c r="E120" t="n">
-        <v>53.9897</v>
+        <v>52.2827</v>
       </c>
       <c r="F120" t="n">
-        <v>151.924</v>
+        <v>196.73</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>69.5698</v>
+        <v>62.7811</v>
       </c>
       <c r="C121" t="n">
-        <v>86.4834</v>
+        <v>77.2002</v>
       </c>
       <c r="D121" t="n">
-        <v>327.692</v>
+        <v>316.999</v>
       </c>
       <c r="E121" t="n">
-        <v>89.4781</v>
+        <v>87.6617</v>
       </c>
       <c r="F121" t="n">
-        <v>297.381</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>61.3945</v>
+        <v>60.0973</v>
       </c>
       <c r="C122" t="n">
-        <v>113.765</v>
+        <v>111.725</v>
       </c>
       <c r="D122" t="n">
-        <v>322.642</v>
+        <v>311.984</v>
       </c>
       <c r="E122" t="n">
-        <v>87.68210000000001</v>
+        <v>85.62869999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>296.721</v>
+        <v>287.371</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>62.3245</v>
+        <v>60.0821</v>
       </c>
       <c r="C123" t="n">
-        <v>112.433</v>
+        <v>110.54</v>
       </c>
       <c r="D123" t="n">
-        <v>318.388</v>
+        <v>307.563</v>
       </c>
       <c r="E123" t="n">
-        <v>85.86499999999999</v>
+        <v>83.82550000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>296.413</v>
+        <v>286.555</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>93.4314</v>
+        <v>94.2557</v>
       </c>
       <c r="C124" t="n">
-        <v>112.172</v>
+        <v>110.024</v>
       </c>
       <c r="D124" t="n">
-        <v>314.571</v>
+        <v>303.976</v>
       </c>
       <c r="E124" t="n">
-        <v>84.2782</v>
+        <v>81.8728</v>
       </c>
       <c r="F124" t="n">
-        <v>295.317</v>
+        <v>285.853</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>96.92310000000001</v>
+        <v>90.86369999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>117.171</v>
+        <v>108.675</v>
       </c>
       <c r="D125" t="n">
-        <v>309.173</v>
+        <v>300.507</v>
       </c>
       <c r="E125" t="n">
-        <v>80.4542</v>
+        <v>85.04949999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>285.782</v>
+        <v>285.969</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>87.60720000000001</v>
+        <v>86.82729999999999</v>
       </c>
       <c r="C126" t="n">
-        <v>107.567</v>
+        <v>107.663</v>
       </c>
       <c r="D126" t="n">
-        <v>297.295</v>
+        <v>297.657</v>
       </c>
       <c r="E126" t="n">
-        <v>83.36320000000001</v>
+        <v>83.2179</v>
       </c>
       <c r="F126" t="n">
-        <v>284.904</v>
+        <v>285.672</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>91.1919</v>
+        <v>88.1396</v>
       </c>
       <c r="C127" t="n">
-        <v>112.121</v>
+        <v>106.646</v>
       </c>
       <c r="D127" t="n">
-        <v>294.746</v>
+        <v>295.019</v>
       </c>
       <c r="E127" t="n">
-        <v>77.27670000000001</v>
+        <v>77.25490000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>285.307</v>
+        <v>284.443</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>84.93389999999999</v>
+        <v>82.70399999999999</v>
       </c>
       <c r="C128" t="n">
-        <v>105.583</v>
+        <v>105.535</v>
       </c>
       <c r="D128" t="n">
-        <v>292.48</v>
+        <v>292.838</v>
       </c>
       <c r="E128" t="n">
-        <v>75.8779</v>
+        <v>75.7754</v>
       </c>
       <c r="F128" t="n">
-        <v>284.459</v>
+        <v>284.634</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>86.84059999999999</v>
+        <v>87.15389999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>109.569</v>
+        <v>109.683</v>
       </c>
       <c r="D129" t="n">
-        <v>290.632</v>
+        <v>290.694</v>
       </c>
       <c r="E129" t="n">
-        <v>74.6061</v>
+        <v>74.4156</v>
       </c>
       <c r="F129" t="n">
-        <v>284.872</v>
+        <v>283.744</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>85.9096</v>
+        <v>85.697</v>
       </c>
       <c r="C130" t="n">
-        <v>108.565</v>
+        <v>108.538</v>
       </c>
       <c r="D130" t="n">
-        <v>289.407</v>
+        <v>290.89</v>
       </c>
       <c r="E130" t="n">
-        <v>73.22410000000001</v>
+        <v>73.23309999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>283.325</v>
+        <v>284.537</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>79.9866</v>
+        <v>80.45950000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>102.755</v>
+        <v>102.713</v>
       </c>
       <c r="D131" t="n">
-        <v>288.051</v>
+        <v>287.876</v>
       </c>
       <c r="E131" t="n">
-        <v>72.1777</v>
+        <v>71.8672</v>
       </c>
       <c r="F131" t="n">
-        <v>283.649</v>
+        <v>283.089</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>79.9092</v>
+        <v>79.5112</v>
       </c>
       <c r="C132" t="n">
-        <v>102.006</v>
+        <v>101.941</v>
       </c>
       <c r="D132" t="n">
-        <v>287.111</v>
+        <v>287.429</v>
       </c>
       <c r="E132" t="n">
-        <v>74.2076</v>
+        <v>70.8998</v>
       </c>
       <c r="F132" t="n">
-        <v>283.95</v>
+        <v>283.906</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>74.8306</v>
+        <v>78.66889999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>92.30240000000001</v>
+        <v>101.282</v>
       </c>
       <c r="D133" t="n">
-        <v>286.926</v>
+        <v>287.009</v>
       </c>
       <c r="E133" t="n">
-        <v>69.8801</v>
+        <v>69.82129999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>284.486</v>
+        <v>283.587</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>78.1626</v>
+        <v>77.43049999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>100.482</v>
+        <v>100.548</v>
       </c>
       <c r="D134" t="n">
-        <v>281.985</v>
+        <v>282.288</v>
       </c>
       <c r="E134" t="n">
-        <v>62.8232</v>
+        <v>62.7342</v>
       </c>
       <c r="F134" t="n">
-        <v>233.744</v>
+        <v>257.792</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>75.7641</v>
+        <v>73.80110000000001</v>
       </c>
       <c r="C135" t="n">
-        <v>99.74590000000001</v>
+        <v>92.0856</v>
       </c>
       <c r="D135" t="n">
-        <v>361.436</v>
+        <v>362.065</v>
       </c>
       <c r="E135" t="n">
-        <v>98.25579999999999</v>
+        <v>98.5642</v>
       </c>
       <c r="F135" t="n">
-        <v>326.64</v>
+        <v>326.1</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>74.8656</v>
+        <v>75.7002</v>
       </c>
       <c r="C136" t="n">
-        <v>133.605</v>
+        <v>132.746</v>
       </c>
       <c r="D136" t="n">
-        <v>355.404</v>
+        <v>355.718</v>
       </c>
       <c r="E136" t="n">
-        <v>96.68810000000001</v>
+        <v>96.8125</v>
       </c>
       <c r="F136" t="n">
-        <v>326.099</v>
+        <v>325.714</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>74.4106</v>
+        <v>73.6033</v>
       </c>
       <c r="C137" t="n">
-        <v>132.243</v>
+        <v>132.196</v>
       </c>
       <c r="D137" t="n">
-        <v>349.758</v>
+        <v>350.168</v>
       </c>
       <c r="E137" t="n">
-        <v>94.7608</v>
+        <v>94.46259999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>325.051</v>
+        <v>325.416</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>106.621</v>
+        <v>102.962</v>
       </c>
       <c r="C138" t="n">
-        <v>132.337</v>
+        <v>125.025</v>
       </c>
       <c r="D138" t="n">
-        <v>344.45</v>
+        <v>344.945</v>
       </c>
       <c r="E138" t="n">
-        <v>92.9729</v>
+        <v>92.9941</v>
       </c>
       <c r="F138" t="n">
-        <v>324.121</v>
+        <v>323.536</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>99.85809999999999</v>
+        <v>103.784</v>
       </c>
       <c r="C139" t="n">
-        <v>123.941</v>
+        <v>130.986</v>
       </c>
       <c r="D139" t="n">
-        <v>339.908</v>
+        <v>340.861</v>
       </c>
       <c r="E139" t="n">
-        <v>91.4504</v>
+        <v>96.2373</v>
       </c>
       <c r="F139" t="n">
-        <v>323.992</v>
+        <v>323.678</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>103.058</v>
+        <v>97.6939</v>
       </c>
       <c r="C140" t="n">
-        <v>129.755</v>
+        <v>123.228</v>
       </c>
       <c r="D140" t="n">
-        <v>335.423</v>
+        <v>336.045</v>
       </c>
       <c r="E140" t="n">
-        <v>94.354</v>
+        <v>93.81229999999999</v>
       </c>
       <c r="F140" t="n">
-        <v>323.338</v>
+        <v>322.78</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>101.21</v>
+        <v>96.35380000000001</v>
       </c>
       <c r="C141" t="n">
-        <v>128.581</v>
+        <v>122.344</v>
       </c>
       <c r="D141" t="n">
-        <v>335.151</v>
+        <v>332.783</v>
       </c>
       <c r="E141" t="n">
-        <v>92.8296</v>
+        <v>92.5737</v>
       </c>
       <c r="F141" t="n">
-        <v>323.416</v>
+        <v>321.513</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>96.2944</v>
+        <v>96.09610000000001</v>
       </c>
       <c r="C142" t="n">
-        <v>121.903</v>
+        <v>121.645</v>
       </c>
       <c r="D142" t="n">
-        <v>334.654</v>
+        <v>332.769</v>
       </c>
       <c r="E142" t="n">
-        <v>91.12090000000001</v>
+        <v>90.6447</v>
       </c>
       <c r="F142" t="n">
-        <v>322.212</v>
+        <v>321.095</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>97.66719999999999</v>
+        <v>91.459</v>
       </c>
       <c r="C143" t="n">
-        <v>126.587</v>
+        <v>120.877</v>
       </c>
       <c r="D143" t="n">
-        <v>332.594</v>
+        <v>330.457</v>
       </c>
       <c r="E143" t="n">
-        <v>85.81829999999999</v>
+        <v>89.553</v>
       </c>
       <c r="F143" t="n">
-        <v>320.579</v>
+        <v>320.023</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>22.3191</v>
+        <v>22.0788</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5708</v>
+        <v>24.6364</v>
       </c>
       <c r="D2" t="n">
-        <v>55.6332</v>
+        <v>55.8455</v>
       </c>
       <c r="E2" t="n">
-        <v>17.8294</v>
+        <v>17.8375</v>
       </c>
       <c r="F2" t="n">
-        <v>33.297</v>
+        <v>33.3484</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>21.2335</v>
+        <v>21.7658</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0472</v>
+        <v>24.1034</v>
       </c>
       <c r="D3" t="n">
-        <v>54.9302</v>
+        <v>55.196</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3219</v>
+        <v>17.4261</v>
       </c>
       <c r="F3" t="n">
-        <v>32.7994</v>
+        <v>32.8994</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>20.3697</v>
+        <v>21.1063</v>
       </c>
       <c r="C4" t="n">
-        <v>23.546</v>
+        <v>23.5867</v>
       </c>
       <c r="D4" t="n">
-        <v>54.5362</v>
+        <v>54.7752</v>
       </c>
       <c r="E4" t="n">
-        <v>16.8296</v>
+        <v>16.8839</v>
       </c>
       <c r="F4" t="n">
-        <v>32.4129</v>
+        <v>32.5777</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>19.8605</v>
+        <v>20.4511</v>
       </c>
       <c r="C5" t="n">
-        <v>23.1132</v>
+        <v>23.1415</v>
       </c>
       <c r="D5" t="n">
-        <v>54.2253</v>
+        <v>54.3979</v>
       </c>
       <c r="E5" t="n">
-        <v>16.4632</v>
+        <v>16.6114</v>
       </c>
       <c r="F5" t="n">
-        <v>32.177</v>
+        <v>32.3226</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>20.0021</v>
+        <v>20.4708</v>
       </c>
       <c r="C6" t="n">
-        <v>22.7555</v>
+        <v>22.7784</v>
       </c>
       <c r="D6" t="n">
-        <v>53.7783</v>
+        <v>54.0115</v>
       </c>
       <c r="E6" t="n">
-        <v>16.1254</v>
+        <v>16.1796</v>
       </c>
       <c r="F6" t="n">
-        <v>32.0718</v>
+        <v>32.2199</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.5199</v>
+        <v>19.7723</v>
       </c>
       <c r="C7" t="n">
-        <v>22.4509</v>
+        <v>22.468</v>
       </c>
       <c r="D7" t="n">
-        <v>68.2129</v>
+        <v>69.0442</v>
       </c>
       <c r="E7" t="n">
-        <v>25.0286</v>
+        <v>24.922</v>
       </c>
       <c r="F7" t="n">
-        <v>39.952</v>
+        <v>40.0968</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>19.2405</v>
+        <v>19.8749</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8462</v>
+        <v>30.8671</v>
       </c>
       <c r="D8" t="n">
-        <v>66.65309999999999</v>
+        <v>67.52209999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>23.9216</v>
+        <v>24.0388</v>
       </c>
       <c r="F8" t="n">
-        <v>39.0451</v>
+        <v>39.2494</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>19.3444</v>
+        <v>19.2008</v>
       </c>
       <c r="C9" t="n">
-        <v>30.1202</v>
+        <v>30.0585</v>
       </c>
       <c r="D9" t="n">
-        <v>65.29949999999999</v>
+        <v>66.09780000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>23.2083</v>
+        <v>23.1325</v>
       </c>
       <c r="F9" t="n">
-        <v>38.2524</v>
+        <v>38.3835</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>28.8149</v>
+        <v>27.3654</v>
       </c>
       <c r="C10" t="n">
-        <v>29.3166</v>
+        <v>29.3183</v>
       </c>
       <c r="D10" t="n">
-        <v>64.13079999999999</v>
+        <v>64.8524</v>
       </c>
       <c r="E10" t="n">
-        <v>22.3761</v>
+        <v>22.4638</v>
       </c>
       <c r="F10" t="n">
-        <v>37.4079</v>
+        <v>37.5884</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.1421</v>
+        <v>27.4026</v>
       </c>
       <c r="C11" t="n">
-        <v>28.4698</v>
+        <v>28.7224</v>
       </c>
       <c r="D11" t="n">
-        <v>63.0387</v>
+        <v>63.7549</v>
       </c>
       <c r="E11" t="n">
-        <v>21.6993</v>
+        <v>21.7241</v>
       </c>
       <c r="F11" t="n">
-        <v>36.6357</v>
+        <v>36.7409</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.3369</v>
+        <v>25.9755</v>
       </c>
       <c r="C12" t="n">
-        <v>27.8117</v>
+        <v>27.8235</v>
       </c>
       <c r="D12" t="n">
-        <v>62.1468</v>
+        <v>62.6544</v>
       </c>
       <c r="E12" t="n">
-        <v>21.1662</v>
+        <v>20.9627</v>
       </c>
       <c r="F12" t="n">
-        <v>35.9568</v>
+        <v>36.0891</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.3971</v>
+        <v>25.009</v>
       </c>
       <c r="C13" t="n">
-        <v>27.1554</v>
+        <v>27.2089</v>
       </c>
       <c r="D13" t="n">
-        <v>61.0002</v>
+        <v>61.7694</v>
       </c>
       <c r="E13" t="n">
-        <v>20.2468</v>
+        <v>20.4478</v>
       </c>
       <c r="F13" t="n">
-        <v>35.3196</v>
+        <v>35.506</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.6105</v>
+        <v>24.4661</v>
       </c>
       <c r="C14" t="n">
-        <v>26.5124</v>
+        <v>26.5262</v>
       </c>
       <c r="D14" t="n">
-        <v>60.2782</v>
+        <v>61.0389</v>
       </c>
       <c r="E14" t="n">
-        <v>19.703</v>
+        <v>19.7821</v>
       </c>
       <c r="F14" t="n">
-        <v>34.7507</v>
+        <v>34.8775</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.5664</v>
+        <v>23.8962</v>
       </c>
       <c r="C15" t="n">
-        <v>25.8592</v>
+        <v>25.9141</v>
       </c>
       <c r="D15" t="n">
-        <v>59.6025</v>
+        <v>60.4314</v>
       </c>
       <c r="E15" t="n">
-        <v>19.1498</v>
+        <v>19.1382</v>
       </c>
       <c r="F15" t="n">
-        <v>34.2027</v>
+        <v>34.3432</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.5175</v>
+        <v>23.2244</v>
       </c>
       <c r="C16" t="n">
-        <v>25.3375</v>
+        <v>25.3358</v>
       </c>
       <c r="D16" t="n">
-        <v>59.1582</v>
+        <v>59.8773</v>
       </c>
       <c r="E16" t="n">
-        <v>18.5929</v>
+        <v>18.6775</v>
       </c>
       <c r="F16" t="n">
-        <v>33.6574</v>
+        <v>33.8181</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.6857</v>
+        <v>22.4727</v>
       </c>
       <c r="C17" t="n">
-        <v>24.756</v>
+        <v>24.7945</v>
       </c>
       <c r="D17" t="n">
-        <v>58.6173</v>
+        <v>59.3657</v>
       </c>
       <c r="E17" t="n">
-        <v>18.1274</v>
+        <v>18.2509</v>
       </c>
       <c r="F17" t="n">
-        <v>33.2785</v>
+        <v>33.4146</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>21.987</v>
+        <v>22.3983</v>
       </c>
       <c r="C18" t="n">
-        <v>24.2773</v>
+        <v>24.3021</v>
       </c>
       <c r="D18" t="n">
-        <v>57.8241</v>
+        <v>58.6833</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7261</v>
+        <v>17.7884</v>
       </c>
       <c r="F18" t="n">
-        <v>32.8399</v>
+        <v>33.0197</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.8014</v>
+        <v>21.5677</v>
       </c>
       <c r="C19" t="n">
-        <v>23.8137</v>
+        <v>23.8912</v>
       </c>
       <c r="D19" t="n">
-        <v>57.3149</v>
+        <v>58.0569</v>
       </c>
       <c r="E19" t="n">
-        <v>17.3592</v>
+        <v>17.4745</v>
       </c>
       <c r="F19" t="n">
-        <v>32.5745</v>
+        <v>32.7008</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>21.0462</v>
+        <v>20.9529</v>
       </c>
       <c r="C20" t="n">
-        <v>23.4521</v>
+        <v>23.463</v>
       </c>
       <c r="D20" t="n">
-        <v>57.1029</v>
+        <v>57.7193</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1715</v>
+        <v>17.1728</v>
       </c>
       <c r="F20" t="n">
-        <v>32.3804</v>
+        <v>32.5415</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.6034</v>
+        <v>20.5201</v>
       </c>
       <c r="C21" t="n">
-        <v>23.1295</v>
+        <v>23.1401</v>
       </c>
       <c r="D21" t="n">
-        <v>74.6996</v>
+        <v>75.4198</v>
       </c>
       <c r="E21" t="n">
-        <v>25.8893</v>
+        <v>25.8153</v>
       </c>
       <c r="F21" t="n">
-        <v>40.3823</v>
+        <v>40.626</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.2772</v>
+        <v>20.2741</v>
       </c>
       <c r="C22" t="n">
-        <v>31.669</v>
+        <v>31.6725</v>
       </c>
       <c r="D22" t="n">
-        <v>73.0425</v>
+        <v>73.7375</v>
       </c>
       <c r="E22" t="n">
-        <v>25.1226</v>
+        <v>25.0038</v>
       </c>
       <c r="F22" t="n">
-        <v>39.5601</v>
+        <v>39.7507</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>20.2875</v>
+        <v>20.2597</v>
       </c>
       <c r="C23" t="n">
-        <v>30.7871</v>
+        <v>30.8168</v>
       </c>
       <c r="D23" t="n">
-        <v>71.6588</v>
+        <v>72.2402</v>
       </c>
       <c r="E23" t="n">
-        <v>24.1204</v>
+        <v>24.2201</v>
       </c>
       <c r="F23" t="n">
-        <v>38.745</v>
+        <v>38.9475</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>28.5181</v>
+        <v>29.1399</v>
       </c>
       <c r="C24" t="n">
-        <v>30.0286</v>
+        <v>30.2488</v>
       </c>
       <c r="D24" t="n">
-        <v>70.5282</v>
+        <v>70.958</v>
       </c>
       <c r="E24" t="n">
-        <v>23.3327</v>
+        <v>23.4139</v>
       </c>
       <c r="F24" t="n">
-        <v>37.9507</v>
+        <v>38.2173</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>27.957</v>
+        <v>27.7782</v>
       </c>
       <c r="C25" t="n">
-        <v>29.2648</v>
+        <v>29.3287</v>
       </c>
       <c r="D25" t="n">
-        <v>69.27670000000001</v>
+        <v>69.74639999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>22.5625</v>
+        <v>22.6699</v>
       </c>
       <c r="F25" t="n">
-        <v>37.232</v>
+        <v>37.451</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>27.0585</v>
+        <v>27.0313</v>
       </c>
       <c r="C26" t="n">
-        <v>28.5252</v>
+        <v>28.5998</v>
       </c>
       <c r="D26" t="n">
-        <v>68.0192</v>
+        <v>68.48950000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>21.8984</v>
+        <v>21.9607</v>
       </c>
       <c r="F26" t="n">
-        <v>36.4282</v>
+        <v>37.3754</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>26.0334</v>
+        <v>25.9676</v>
       </c>
       <c r="C27" t="n">
-        <v>27.874</v>
+        <v>27.8858</v>
       </c>
       <c r="D27" t="n">
-        <v>67.1464</v>
+        <v>67.5868</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2222</v>
+        <v>21.1993</v>
       </c>
       <c r="F27" t="n">
-        <v>35.7861</v>
+        <v>36.6645</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.712</v>
+        <v>25.7106</v>
       </c>
       <c r="C28" t="n">
-        <v>27.2239</v>
+        <v>27.2622</v>
       </c>
       <c r="D28" t="n">
-        <v>65.98909999999999</v>
+        <v>66.51739999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>20.5638</v>
+        <v>20.8241</v>
       </c>
       <c r="F28" t="n">
-        <v>35.2299</v>
+        <v>36.1152</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>24.9316</v>
+        <v>25.0071</v>
       </c>
       <c r="C29" t="n">
-        <v>26.609</v>
+        <v>26.66</v>
       </c>
       <c r="D29" t="n">
-        <v>65.345</v>
+        <v>65.94759999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>19.9982</v>
+        <v>20.1067</v>
       </c>
       <c r="F29" t="n">
-        <v>34.6889</v>
+        <v>35.5429</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>24.21</v>
+        <v>23.7134</v>
       </c>
       <c r="C30" t="n">
-        <v>26.028</v>
+        <v>26.0371</v>
       </c>
       <c r="D30" t="n">
-        <v>64.613</v>
+        <v>65.07599999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>19.4152</v>
+        <v>19.5021</v>
       </c>
       <c r="F30" t="n">
-        <v>34.1986</v>
+        <v>34.9236</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.5422</v>
+        <v>23.0626</v>
       </c>
       <c r="C31" t="n">
-        <v>25.4498</v>
+        <v>25.4666</v>
       </c>
       <c r="D31" t="n">
-        <v>64.0878</v>
+        <v>64.5463</v>
       </c>
       <c r="E31" t="n">
-        <v>18.8819</v>
+        <v>19.101</v>
       </c>
       <c r="F31" t="n">
-        <v>33.5134</v>
+        <v>33.5429</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>23.0931</v>
+        <v>23.6183</v>
       </c>
       <c r="C32" t="n">
-        <v>24.8762</v>
+        <v>25.0896</v>
       </c>
       <c r="D32" t="n">
-        <v>63.6867</v>
+        <v>64.1037</v>
       </c>
       <c r="E32" t="n">
-        <v>18.4338</v>
+        <v>18.5686</v>
       </c>
       <c r="F32" t="n">
-        <v>33.1488</v>
+        <v>33.1683</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>22.9828</v>
+        <v>22.5676</v>
       </c>
       <c r="C33" t="n">
-        <v>24.5425</v>
+        <v>24.5283</v>
       </c>
       <c r="D33" t="n">
-        <v>63.2721</v>
+        <v>63.6329</v>
       </c>
       <c r="E33" t="n">
-        <v>18.1364</v>
+        <v>18.2062</v>
       </c>
       <c r="F33" t="n">
-        <v>32.9982</v>
+        <v>33.048</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>21.7648</v>
+        <v>21.6074</v>
       </c>
       <c r="C34" t="n">
-        <v>24.0461</v>
+        <v>24.1267</v>
       </c>
       <c r="D34" t="n">
-        <v>62.6168</v>
+        <v>63.0069</v>
       </c>
       <c r="E34" t="n">
-        <v>17.841</v>
+        <v>17.9999</v>
       </c>
       <c r="F34" t="n">
-        <v>32.7162</v>
+        <v>32.8291</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>21.4568</v>
+        <v>21.7911</v>
       </c>
       <c r="C35" t="n">
-        <v>23.7162</v>
+        <v>23.8088</v>
       </c>
       <c r="D35" t="n">
-        <v>80.8364</v>
+        <v>81.393</v>
       </c>
       <c r="E35" t="n">
-        <v>26.5717</v>
+        <v>26.9048</v>
       </c>
       <c r="F35" t="n">
-        <v>41.4224</v>
+        <v>41.374</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>20.8705</v>
+        <v>21.2527</v>
       </c>
       <c r="C36" t="n">
-        <v>23.4329</v>
+        <v>23.6681</v>
       </c>
       <c r="D36" t="n">
-        <v>79.2189</v>
+        <v>79.68300000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>25.7621</v>
+        <v>25.9235</v>
       </c>
       <c r="F36" t="n">
-        <v>40.6403</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>21.5191</v>
+        <v>21.6973</v>
       </c>
       <c r="C37" t="n">
-        <v>31.5609</v>
+        <v>31.7086</v>
       </c>
       <c r="D37" t="n">
-        <v>77.6292</v>
+        <v>78.04940000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>24.9807</v>
+        <v>25.1179</v>
       </c>
       <c r="F37" t="n">
-        <v>39.7604</v>
+        <v>39.7849</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>29.3272</v>
+        <v>28.9235</v>
       </c>
       <c r="C38" t="n">
-        <v>30.8093</v>
+        <v>31.089</v>
       </c>
       <c r="D38" t="n">
-        <v>76.0984</v>
+        <v>76.53619999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>24.1609</v>
+        <v>24.2576</v>
       </c>
       <c r="F38" t="n">
-        <v>38.961</v>
+        <v>39.0303</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>27.9717</v>
+        <v>28.8069</v>
       </c>
       <c r="C39" t="n">
-        <v>30.1076</v>
+        <v>30.1464</v>
       </c>
       <c r="D39" t="n">
-        <v>74.8138</v>
+        <v>75.2259</v>
       </c>
       <c r="E39" t="n">
-        <v>23.4233</v>
+        <v>23.5317</v>
       </c>
       <c r="F39" t="n">
-        <v>38.1952</v>
+        <v>38.3062</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>27.5464</v>
+        <v>27.3431</v>
       </c>
       <c r="C40" t="n">
-        <v>29.3698</v>
+        <v>29.457</v>
       </c>
       <c r="D40" t="n">
-        <v>73.5522</v>
+        <v>73.91240000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>22.7313</v>
+        <v>22.7921</v>
       </c>
       <c r="F40" t="n">
-        <v>37.5279</v>
+        <v>37.5983</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.3311</v>
+        <v>26.7536</v>
       </c>
       <c r="C41" t="n">
-        <v>28.7487</v>
+        <v>28.7273</v>
       </c>
       <c r="D41" t="n">
-        <v>72.38849999999999</v>
+        <v>72.72150000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>22.0614</v>
+        <v>22.2507</v>
       </c>
       <c r="F41" t="n">
-        <v>36.8456</v>
+        <v>36.9677</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>25.7219</v>
+        <v>26.4442</v>
       </c>
       <c r="C42" t="n">
-        <v>28.1222</v>
+        <v>28.1739</v>
       </c>
       <c r="D42" t="n">
-        <v>71.5909</v>
+        <v>71.8535</v>
       </c>
       <c r="E42" t="n">
-        <v>21.3647</v>
+        <v>21.6214</v>
       </c>
       <c r="F42" t="n">
-        <v>36.1919</v>
+        <v>36.364</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>25.1709</v>
+        <v>24.8134</v>
       </c>
       <c r="C43" t="n">
-        <v>27.5094</v>
+        <v>27.673</v>
       </c>
       <c r="D43" t="n">
-        <v>70.31319999999999</v>
+        <v>70.7756</v>
       </c>
       <c r="E43" t="n">
-        <v>20.8791</v>
+        <v>20.9537</v>
       </c>
       <c r="F43" t="n">
-        <v>35.6849</v>
+        <v>35.8703</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.4496</v>
+        <v>24.6651</v>
       </c>
       <c r="C44" t="n">
-        <v>26.9056</v>
+        <v>27.0531</v>
       </c>
       <c r="D44" t="n">
-        <v>69.4704</v>
+        <v>69.92449999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>20.3123</v>
+        <v>20.4526</v>
       </c>
       <c r="F44" t="n">
-        <v>35.1784</v>
+        <v>35.326</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>23.6571</v>
+        <v>23.6902</v>
       </c>
       <c r="C45" t="n">
-        <v>26.4193</v>
+        <v>26.392</v>
       </c>
       <c r="D45" t="n">
-        <v>68.8415</v>
+        <v>69.2388</v>
       </c>
       <c r="E45" t="n">
-        <v>19.7937</v>
+        <v>19.9347</v>
       </c>
       <c r="F45" t="n">
-        <v>34.7857</v>
+        <v>34.817</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>23.1392</v>
+        <v>23.3474</v>
       </c>
       <c r="C46" t="n">
-        <v>26.0549</v>
+        <v>25.9254</v>
       </c>
       <c r="D46" t="n">
-        <v>68.3223</v>
+        <v>68.6631</v>
       </c>
       <c r="E46" t="n">
-        <v>19.3884</v>
+        <v>19.4327</v>
       </c>
       <c r="F46" t="n">
-        <v>34.3545</v>
+        <v>34.5356</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.8529</v>
+        <v>22.5723</v>
       </c>
       <c r="C47" t="n">
-        <v>25.4367</v>
+        <v>25.3934</v>
       </c>
       <c r="D47" t="n">
-        <v>67.8258</v>
+        <v>68.2287</v>
       </c>
       <c r="E47" t="n">
-        <v>19.0477</v>
+        <v>19.1093</v>
       </c>
       <c r="F47" t="n">
-        <v>34.0006</v>
+        <v>34.2769</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>22.0073</v>
+        <v>22.0844</v>
       </c>
       <c r="C48" t="n">
-        <v>25.0639</v>
+        <v>25.0874</v>
       </c>
       <c r="D48" t="n">
-        <v>67.0138</v>
+        <v>67.49209999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>18.6219</v>
+        <v>18.6823</v>
       </c>
       <c r="F48" t="n">
-        <v>33.7429</v>
+        <v>34.0002</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>21.5736</v>
+        <v>21.7671</v>
       </c>
       <c r="C49" t="n">
-        <v>24.731</v>
+        <v>24.782</v>
       </c>
       <c r="D49" t="n">
-        <v>66.7517</v>
+        <v>67.1373</v>
       </c>
       <c r="E49" t="n">
-        <v>18.4645</v>
+        <v>18.4885</v>
       </c>
       <c r="F49" t="n">
-        <v>33.5937</v>
+        <v>33.8502</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.4399</v>
+        <v>21.5946</v>
       </c>
       <c r="C50" t="n">
-        <v>24.4523</v>
+        <v>24.3375</v>
       </c>
       <c r="D50" t="n">
-        <v>83.82559999999999</v>
+        <v>84.3807</v>
       </c>
       <c r="E50" t="n">
-        <v>27.0009</v>
+        <v>26.7291</v>
       </c>
       <c r="F50" t="n">
-        <v>41.8418</v>
+        <v>42.0874</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>21.467</v>
+        <v>21.3504</v>
       </c>
       <c r="C51" t="n">
-        <v>32.5657</v>
+        <v>32.7016</v>
       </c>
       <c r="D51" t="n">
-        <v>82.20050000000001</v>
+        <v>82.6044</v>
       </c>
       <c r="E51" t="n">
-        <v>26.2485</v>
+        <v>25.9586</v>
       </c>
       <c r="F51" t="n">
-        <v>41.1776</v>
+        <v>41.3439</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>21.5312</v>
+        <v>21.4242</v>
       </c>
       <c r="C52" t="n">
-        <v>31.863</v>
+        <v>32.0823</v>
       </c>
       <c r="D52" t="n">
-        <v>80.6454</v>
+        <v>80.95099999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>25.5404</v>
+        <v>25.3269</v>
       </c>
       <c r="F52" t="n">
-        <v>40.3637</v>
+        <v>40.6647</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.3071</v>
+        <v>29.8397</v>
       </c>
       <c r="C53" t="n">
-        <v>31.2595</v>
+        <v>31.3605</v>
       </c>
       <c r="D53" t="n">
-        <v>79.1217</v>
+        <v>79.4461</v>
       </c>
       <c r="E53" t="n">
-        <v>24.7287</v>
+        <v>24.4531</v>
       </c>
       <c r="F53" t="n">
-        <v>39.7238</v>
+        <v>39.9139</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>28.4816</v>
+        <v>28.1748</v>
       </c>
       <c r="C54" t="n">
-        <v>30.5416</v>
+        <v>30.7701</v>
       </c>
       <c r="D54" t="n">
-        <v>77.71980000000001</v>
+        <v>78.03019999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>23.9757</v>
+        <v>23.7049</v>
       </c>
       <c r="F54" t="n">
-        <v>39.0637</v>
+        <v>39.241</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>27.5075</v>
+        <v>27.3086</v>
       </c>
       <c r="C55" t="n">
-        <v>29.9581</v>
+        <v>30.1465</v>
       </c>
       <c r="D55" t="n">
-        <v>76.5129</v>
+        <v>76.8002</v>
       </c>
       <c r="E55" t="n">
-        <v>23.3835</v>
+        <v>23.1444</v>
       </c>
       <c r="F55" t="n">
-        <v>38.4669</v>
+        <v>38.7355</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>26.9856</v>
+        <v>27.2433</v>
       </c>
       <c r="C56" t="n">
-        <v>29.3222</v>
+        <v>29.3886</v>
       </c>
       <c r="D56" t="n">
-        <v>75.47709999999999</v>
+        <v>75.7807</v>
       </c>
       <c r="E56" t="n">
-        <v>22.7189</v>
+        <v>22.4766</v>
       </c>
       <c r="F56" t="n">
-        <v>37.9172</v>
+        <v>38.1211</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.2389</v>
+        <v>26.1245</v>
       </c>
       <c r="C57" t="n">
-        <v>28.9382</v>
+        <v>29.1288</v>
       </c>
       <c r="D57" t="n">
-        <v>74.31319999999999</v>
+        <v>74.56870000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>22.1304</v>
+        <v>21.9939</v>
       </c>
       <c r="F57" t="n">
-        <v>37.3933</v>
+        <v>37.5902</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>25.4611</v>
+        <v>25.9434</v>
       </c>
       <c r="C58" t="n">
-        <v>28.5379</v>
+        <v>28.5669</v>
       </c>
       <c r="D58" t="n">
-        <v>73.47880000000001</v>
+        <v>73.76739999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>21.5516</v>
+        <v>21.4523</v>
       </c>
       <c r="F58" t="n">
-        <v>36.9006</v>
+        <v>37.1684</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>25.2756</v>
+        <v>24.9734</v>
       </c>
       <c r="C59" t="n">
-        <v>27.9874</v>
+        <v>27.9208</v>
       </c>
       <c r="D59" t="n">
-        <v>72.62520000000001</v>
+        <v>72.8647</v>
       </c>
       <c r="E59" t="n">
-        <v>21.1132</v>
+        <v>20.8704</v>
       </c>
       <c r="F59" t="n">
-        <v>36.5079</v>
+        <v>36.6249</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>24.0267</v>
+        <v>23.9553</v>
       </c>
       <c r="C60" t="n">
-        <v>27.6051</v>
+        <v>27.63</v>
       </c>
       <c r="D60" t="n">
-        <v>72.0197</v>
+        <v>72.2773</v>
       </c>
       <c r="E60" t="n">
-        <v>20.5941</v>
+        <v>20.4666</v>
       </c>
       <c r="F60" t="n">
-        <v>36.158</v>
+        <v>36.2315</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>24.1523</v>
+        <v>23.4584</v>
       </c>
       <c r="C61" t="n">
-        <v>27.2291</v>
+        <v>27.1795</v>
       </c>
       <c r="D61" t="n">
-        <v>71.29689999999999</v>
+        <v>71.5226</v>
       </c>
       <c r="E61" t="n">
-        <v>20.1927</v>
+        <v>20.0184</v>
       </c>
       <c r="F61" t="n">
-        <v>35.8438</v>
+        <v>35.9315</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>23.7943</v>
+        <v>22.9751</v>
       </c>
       <c r="C62" t="n">
-        <v>26.764</v>
+        <v>26.6853</v>
       </c>
       <c r="D62" t="n">
-        <v>70.6922</v>
+        <v>70.8967</v>
       </c>
       <c r="E62" t="n">
-        <v>19.8619</v>
+        <v>19.7551</v>
       </c>
       <c r="F62" t="n">
-        <v>35.6634</v>
+        <v>35.675</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>22.8605</v>
+        <v>23.1218</v>
       </c>
       <c r="C63" t="n">
-        <v>26.5098</v>
+        <v>26.263</v>
       </c>
       <c r="D63" t="n">
-        <v>70.3664</v>
+        <v>70.55110000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>19.6262</v>
+        <v>19.4929</v>
       </c>
       <c r="F63" t="n">
-        <v>35.5014</v>
+        <v>35.4692</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>22.8402</v>
+        <v>22.1544</v>
       </c>
       <c r="C64" t="n">
-        <v>26.3326</v>
+        <v>26.3165</v>
       </c>
       <c r="D64" t="n">
-        <v>91.43510000000001</v>
+        <v>91.4855</v>
       </c>
       <c r="E64" t="n">
-        <v>32.4596</v>
+        <v>31.936</v>
       </c>
       <c r="F64" t="n">
-        <v>45.4838</v>
+        <v>45.3915</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>22.5605</v>
+        <v>22.1325</v>
       </c>
       <c r="C65" t="n">
-        <v>35.0976</v>
+        <v>34.754</v>
       </c>
       <c r="D65" t="n">
-        <v>89.0996</v>
+        <v>89.2591</v>
       </c>
       <c r="E65" t="n">
-        <v>31.8376</v>
+        <v>30.9138</v>
       </c>
       <c r="F65" t="n">
-        <v>44.9844</v>
+        <v>44.8533</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.3447</v>
+        <v>22.1032</v>
       </c>
       <c r="C66" t="n">
-        <v>34.4663</v>
+        <v>34.3216</v>
       </c>
       <c r="D66" t="n">
-        <v>87.2702</v>
+        <v>87.45950000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>31.1232</v>
+        <v>29.547</v>
       </c>
       <c r="F66" t="n">
-        <v>44.3273</v>
+        <v>44.1457</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>38.1568</v>
+        <v>36.4698</v>
       </c>
       <c r="C67" t="n">
-        <v>34.1148</v>
+        <v>33.8541</v>
       </c>
       <c r="D67" t="n">
-        <v>85.6144</v>
+        <v>85.79940000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>30.4086</v>
+        <v>28.7678</v>
       </c>
       <c r="F67" t="n">
-        <v>43.7852</v>
+        <v>43.5876</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>36.769</v>
+        <v>37.0079</v>
       </c>
       <c r="C68" t="n">
-        <v>33.8709</v>
+        <v>33.4547</v>
       </c>
       <c r="D68" t="n">
-        <v>84.1253</v>
+        <v>84.2766</v>
       </c>
       <c r="E68" t="n">
-        <v>29.6276</v>
+        <v>28.1711</v>
       </c>
       <c r="F68" t="n">
-        <v>43.1524</v>
+        <v>43.0127</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>35.076</v>
+        <v>35.179</v>
       </c>
       <c r="C69" t="n">
-        <v>33.4917</v>
+        <v>33.3975</v>
       </c>
       <c r="D69" t="n">
-        <v>82.84180000000001</v>
+        <v>82.9392</v>
       </c>
       <c r="E69" t="n">
-        <v>29.0701</v>
+        <v>27.5301</v>
       </c>
       <c r="F69" t="n">
-        <v>42.5952</v>
+        <v>42.5772</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>34.9014</v>
+        <v>34.4599</v>
       </c>
       <c r="C70" t="n">
-        <v>33.1427</v>
+        <v>32.8072</v>
       </c>
       <c r="D70" t="n">
-        <v>81.96559999999999</v>
+        <v>81.91970000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>28.2389</v>
+        <v>27.5488</v>
       </c>
       <c r="F70" t="n">
-        <v>42.0428</v>
+        <v>41.7496</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>34.3602</v>
+        <v>34.722</v>
       </c>
       <c r="C71" t="n">
-        <v>32.9557</v>
+        <v>32.4341</v>
       </c>
       <c r="D71" t="n">
-        <v>81.2047</v>
+        <v>81.16630000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>27.5549</v>
+        <v>26.482</v>
       </c>
       <c r="F71" t="n">
-        <v>41.6093</v>
+        <v>41.3247</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>33.9753</v>
+        <v>34.0358</v>
       </c>
       <c r="C72" t="n">
-        <v>32.6353</v>
+        <v>32.1005</v>
       </c>
       <c r="D72" t="n">
-        <v>80.81789999999999</v>
+        <v>80.5573</v>
       </c>
       <c r="E72" t="n">
-        <v>27.1899</v>
+        <v>25.9255</v>
       </c>
       <c r="F72" t="n">
-        <v>41.3345</v>
+        <v>40.9606</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>33.0648</v>
+        <v>33.3916</v>
       </c>
       <c r="C73" t="n">
-        <v>32.3553</v>
+        <v>31.8801</v>
       </c>
       <c r="D73" t="n">
-        <v>80.5797</v>
+        <v>80.03360000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>26.4899</v>
+        <v>25.7254</v>
       </c>
       <c r="F73" t="n">
-        <v>40.8713</v>
+        <v>40.6315</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>33.1506</v>
+        <v>32.9668</v>
       </c>
       <c r="C74" t="n">
-        <v>32.0379</v>
+        <v>31.7206</v>
       </c>
       <c r="D74" t="n">
-        <v>80.2804</v>
+        <v>79.62179999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>26.0508</v>
+        <v>24.805</v>
       </c>
       <c r="F74" t="n">
-        <v>40.6385</v>
+        <v>40.2889</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>31.9422</v>
+        <v>32.2183</v>
       </c>
       <c r="C75" t="n">
-        <v>31.6459</v>
+        <v>31.064</v>
       </c>
       <c r="D75" t="n">
-        <v>79.251</v>
+        <v>78.93899999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>25.6161</v>
+        <v>24.8828</v>
       </c>
       <c r="F75" t="n">
-        <v>40.3925</v>
+        <v>39.985</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>31.2724</v>
+        <v>31.5116</v>
       </c>
       <c r="C76" t="n">
-        <v>31.334</v>
+        <v>30.6883</v>
       </c>
       <c r="D76" t="n">
-        <v>79.54989999999999</v>
+        <v>78.88079999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>25.1054</v>
+        <v>23.8089</v>
       </c>
       <c r="F76" t="n">
-        <v>40.1165</v>
+        <v>39.7732</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>30.9997</v>
+        <v>31.1928</v>
       </c>
       <c r="C77" t="n">
-        <v>31.1172</v>
+        <v>30.4735</v>
       </c>
       <c r="D77" t="n">
-        <v>79.9421</v>
+        <v>79.1665</v>
       </c>
       <c r="E77" t="n">
-        <v>24.9112</v>
+        <v>23.9907</v>
       </c>
       <c r="F77" t="n">
-        <v>40.117</v>
+        <v>39.6357</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>30.2942</v>
+        <v>29.4839</v>
       </c>
       <c r="C78" t="n">
-        <v>30.9042</v>
+        <v>30.1972</v>
       </c>
       <c r="D78" t="n">
-        <v>130.129</v>
+        <v>128.814</v>
       </c>
       <c r="E78" t="n">
-        <v>42.2357</v>
+        <v>40.3686</v>
       </c>
       <c r="F78" t="n">
-        <v>63.4963</v>
+        <v>63.5841</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>28.8089</v>
+        <v>34.2609</v>
       </c>
       <c r="C79" t="n">
-        <v>40.1506</v>
+        <v>39.8484</v>
       </c>
       <c r="D79" t="n">
-        <v>127.786</v>
+        <v>126.468</v>
       </c>
       <c r="E79" t="n">
-        <v>44.7056</v>
+        <v>39.6184</v>
       </c>
       <c r="F79" t="n">
-        <v>62.7097</v>
+        <v>64.2955</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>32.5635</v>
+        <v>32.6836</v>
       </c>
       <c r="C80" t="n">
-        <v>40.6728</v>
+        <v>40.535</v>
       </c>
       <c r="D80" t="n">
-        <v>124.428</v>
+        <v>124.603</v>
       </c>
       <c r="E80" t="n">
-        <v>38.9223</v>
+        <v>39.1095</v>
       </c>
       <c r="F80" t="n">
-        <v>62.7781</v>
+        <v>63.8507</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>46.4506</v>
+        <v>48.3478</v>
       </c>
       <c r="C81" t="n">
-        <v>41.0391</v>
+        <v>40.8732</v>
       </c>
       <c r="D81" t="n">
-        <v>122.792</v>
+        <v>122.983</v>
       </c>
       <c r="E81" t="n">
-        <v>38.2757</v>
+        <v>38.3664</v>
       </c>
       <c r="F81" t="n">
-        <v>62.291</v>
+        <v>63.5237</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>46.6309</v>
+        <v>46.8358</v>
       </c>
       <c r="C82" t="n">
-        <v>41.2908</v>
+        <v>41.1338</v>
       </c>
       <c r="D82" t="n">
-        <v>121.439</v>
+        <v>121.628</v>
       </c>
       <c r="E82" t="n">
-        <v>37.55</v>
+        <v>37.516</v>
       </c>
       <c r="F82" t="n">
-        <v>61.4848</v>
+        <v>62.8937</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>44.4827</v>
+        <v>45.2262</v>
       </c>
       <c r="C83" t="n">
-        <v>41.5812</v>
+        <v>41.3886</v>
       </c>
       <c r="D83" t="n">
-        <v>120.486</v>
+        <v>120.6</v>
       </c>
       <c r="E83" t="n">
-        <v>36.6773</v>
+        <v>36.8902</v>
       </c>
       <c r="F83" t="n">
-        <v>60.9249</v>
+        <v>61.8337</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.2934</v>
+        <v>44.9942</v>
       </c>
       <c r="C84" t="n">
-        <v>41.685</v>
+        <v>41.5381</v>
       </c>
       <c r="D84" t="n">
-        <v>119.82</v>
+        <v>120.742</v>
       </c>
       <c r="E84" t="n">
-        <v>35.8044</v>
+        <v>36.1053</v>
       </c>
       <c r="F84" t="n">
-        <v>60.3379</v>
+        <v>60.0641</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>43.741</v>
+        <v>44.77</v>
       </c>
       <c r="C85" t="n">
-        <v>41.7866</v>
+        <v>41.8713</v>
       </c>
       <c r="D85" t="n">
-        <v>119.813</v>
+        <v>121.162</v>
       </c>
       <c r="E85" t="n">
-        <v>35.1144</v>
+        <v>35.2273</v>
       </c>
       <c r="F85" t="n">
-        <v>59.3849</v>
+        <v>60.0909</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>37.5837</v>
+        <v>41.6766</v>
       </c>
       <c r="C86" t="n">
-        <v>41.8921</v>
+        <v>41.9062</v>
       </c>
       <c r="D86" t="n">
-        <v>119.538</v>
+        <v>120.57</v>
       </c>
       <c r="E86" t="n">
-        <v>34.3873</v>
+        <v>34.5114</v>
       </c>
       <c r="F86" t="n">
-        <v>58.6299</v>
+        <v>59.038</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>40.2375</v>
+        <v>39.1166</v>
       </c>
       <c r="C87" t="n">
-        <v>41.9441</v>
+        <v>41.9876</v>
       </c>
       <c r="D87" t="n">
-        <v>119.52</v>
+        <v>120.675</v>
       </c>
       <c r="E87" t="n">
-        <v>33.5965</v>
+        <v>33.7832</v>
       </c>
       <c r="F87" t="n">
-        <v>57.4676</v>
+        <v>58.0135</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>41.5858</v>
+        <v>42.0015</v>
       </c>
       <c r="C88" t="n">
-        <v>41.9348</v>
+        <v>41.8339</v>
       </c>
       <c r="D88" t="n">
-        <v>120.141</v>
+        <v>121.216</v>
       </c>
       <c r="E88" t="n">
-        <v>32.9098</v>
+        <v>33.0335</v>
       </c>
       <c r="F88" t="n">
-        <v>56.785</v>
+        <v>57.4024</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>37.886</v>
+        <v>39.7907</v>
       </c>
       <c r="C89" t="n">
-        <v>41.5745</v>
+        <v>41.7207</v>
       </c>
       <c r="D89" t="n">
-        <v>120.523</v>
+        <v>121.381</v>
       </c>
       <c r="E89" t="n">
-        <v>32.2222</v>
+        <v>32.4134</v>
       </c>
       <c r="F89" t="n">
-        <v>55.9896</v>
+        <v>57.7695</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>41.125</v>
+        <v>37.9189</v>
       </c>
       <c r="C90" t="n">
-        <v>41.7134</v>
+        <v>41.5275</v>
       </c>
       <c r="D90" t="n">
-        <v>121.742</v>
+        <v>122.348</v>
       </c>
       <c r="E90" t="n">
-        <v>31.5513</v>
+        <v>31.8428</v>
       </c>
       <c r="F90" t="n">
-        <v>55.4431</v>
+        <v>56.9211</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>40.4031</v>
+        <v>40.6505</v>
       </c>
       <c r="C91" t="n">
-        <v>41.3464</v>
+        <v>41.3111</v>
       </c>
       <c r="D91" t="n">
-        <v>123.323</v>
+        <v>124.039</v>
       </c>
       <c r="E91" t="n">
-        <v>31.141</v>
+        <v>31.3829</v>
       </c>
       <c r="F91" t="n">
-        <v>55.4291</v>
+        <v>55.4069</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>38.3972</v>
+        <v>38.011</v>
       </c>
       <c r="C92" t="n">
-        <v>41.2136</v>
+        <v>41.2527</v>
       </c>
       <c r="D92" t="n">
-        <v>184.973</v>
+        <v>185.717</v>
       </c>
       <c r="E92" t="n">
-        <v>64.9716</v>
+        <v>65.2715</v>
       </c>
       <c r="F92" t="n">
-        <v>85.7516</v>
+        <v>85.2281</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>41.7178</v>
+        <v>36.6594</v>
       </c>
       <c r="C93" t="n">
-        <v>40.6818</v>
+        <v>41.2285</v>
       </c>
       <c r="D93" t="n">
-        <v>184.419</v>
+        <v>184.515</v>
       </c>
       <c r="E93" t="n">
-        <v>63.671</v>
+        <v>63.6378</v>
       </c>
       <c r="F93" t="n">
-        <v>85.7347</v>
+        <v>86.0943</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>40.9095</v>
+        <v>40.7076</v>
       </c>
       <c r="C94" t="n">
-        <v>73.8425</v>
+        <v>73.533</v>
       </c>
       <c r="D94" t="n">
-        <v>182.396</v>
+        <v>182.952</v>
       </c>
       <c r="E94" t="n">
-        <v>62.0354</v>
+        <v>61.9542</v>
       </c>
       <c r="F94" t="n">
-        <v>84.43689999999999</v>
+        <v>85.3837</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>70.50360000000001</v>
+        <v>73.6237</v>
       </c>
       <c r="C95" t="n">
-        <v>73.8884</v>
+        <v>73.0615</v>
       </c>
       <c r="D95" t="n">
-        <v>181.343</v>
+        <v>181.364</v>
       </c>
       <c r="E95" t="n">
-        <v>60.2287</v>
+        <v>59.9302</v>
       </c>
       <c r="F95" t="n">
-        <v>84.6148</v>
+        <v>84.9996</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>68.92400000000001</v>
+        <v>67.6176</v>
       </c>
       <c r="C96" t="n">
-        <v>72.89279999999999</v>
+        <v>72.3409</v>
       </c>
       <c r="D96" t="n">
-        <v>180.392</v>
+        <v>180.409</v>
       </c>
       <c r="E96" t="n">
-        <v>58.4533</v>
+        <v>58.8862</v>
       </c>
       <c r="F96" t="n">
-        <v>83.79559999999999</v>
+        <v>83.9057</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>69.2392</v>
+        <v>67.80200000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>72.0681</v>
+        <v>72.1772</v>
       </c>
       <c r="D97" t="n">
-        <v>179.045</v>
+        <v>180</v>
       </c>
       <c r="E97" t="n">
-        <v>57.0698</v>
+        <v>57.0801</v>
       </c>
       <c r="F97" t="n">
-        <v>82.6086</v>
+        <v>81.7034</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>68.4486</v>
+        <v>67.0424</v>
       </c>
       <c r="C98" t="n">
-        <v>71.12779999999999</v>
+        <v>71.2993</v>
       </c>
       <c r="D98" t="n">
-        <v>178.81</v>
+        <v>179.594</v>
       </c>
       <c r="E98" t="n">
-        <v>55.4493</v>
+        <v>55.6077</v>
       </c>
       <c r="F98" t="n">
-        <v>80.9034</v>
+        <v>80.8177</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>64.2529</v>
+        <v>63.2216</v>
       </c>
       <c r="C99" t="n">
-        <v>70.61969999999999</v>
+        <v>70.7264</v>
       </c>
       <c r="D99" t="n">
-        <v>179.324</v>
+        <v>179.586</v>
       </c>
       <c r="E99" t="n">
-        <v>54.1986</v>
+        <v>54.1097</v>
       </c>
       <c r="F99" t="n">
-        <v>81.349</v>
+        <v>81.9952</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>63.9497</v>
+        <v>63.3389</v>
       </c>
       <c r="C100" t="n">
-        <v>70.00020000000001</v>
+        <v>70.10899999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>179.484</v>
+        <v>180.106</v>
       </c>
       <c r="E100" t="n">
-        <v>52.5182</v>
+        <v>52.6124</v>
       </c>
       <c r="F100" t="n">
-        <v>78.45529999999999</v>
+        <v>81.0117</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>63.3016</v>
+        <v>59.7006</v>
       </c>
       <c r="C101" t="n">
-        <v>69.3094</v>
+        <v>69.408</v>
       </c>
       <c r="D101" t="n">
-        <v>179.514</v>
+        <v>180.407</v>
       </c>
       <c r="E101" t="n">
-        <v>51.2874</v>
+        <v>51.3098</v>
       </c>
       <c r="F101" t="n">
-        <v>81.22929999999999</v>
+        <v>81.1948</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>58.4636</v>
+        <v>58.9043</v>
       </c>
       <c r="C102" t="n">
-        <v>68.7054</v>
+        <v>68.717</v>
       </c>
       <c r="D102" t="n">
-        <v>180.531</v>
+        <v>181.01</v>
       </c>
       <c r="E102" t="n">
-        <v>50.0976</v>
+        <v>50.2607</v>
       </c>
       <c r="F102" t="n">
-        <v>78.6472</v>
+        <v>78.70650000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>61.1742</v>
+        <v>59.5873</v>
       </c>
       <c r="C103" t="n">
-        <v>68.0329</v>
+        <v>68.1434</v>
       </c>
       <c r="D103" t="n">
-        <v>181.411</v>
+        <v>182.09</v>
       </c>
       <c r="E103" t="n">
-        <v>48.7874</v>
+        <v>49.017</v>
       </c>
       <c r="F103" t="n">
-        <v>81.25790000000001</v>
+        <v>82.0545</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>59.338</v>
+        <v>56.834</v>
       </c>
       <c r="C104" t="n">
-        <v>67.36579999999999</v>
+        <v>67.3267</v>
       </c>
       <c r="D104" t="n">
-        <v>182.904</v>
+        <v>183.466</v>
       </c>
       <c r="E104" t="n">
-        <v>47.9261</v>
+        <v>47.8642</v>
       </c>
       <c r="F104" t="n">
-        <v>76.80329999999999</v>
+        <v>78.4881</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>57.8766</v>
+        <v>57.4125</v>
       </c>
       <c r="C105" t="n">
-        <v>66.81489999999999</v>
+        <v>66.9229</v>
       </c>
       <c r="D105" t="n">
-        <v>184.392</v>
+        <v>184.841</v>
       </c>
       <c r="E105" t="n">
-        <v>46.8668</v>
+        <v>46.9294</v>
       </c>
       <c r="F105" t="n">
-        <v>75.6969</v>
+        <v>76.7075</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>55.0773</v>
+        <v>56.5851</v>
       </c>
       <c r="C106" t="n">
-        <v>66.21939999999999</v>
+        <v>66.4303</v>
       </c>
       <c r="D106" t="n">
-        <v>185.452</v>
+        <v>186.523</v>
       </c>
       <c r="E106" t="n">
-        <v>45.9664</v>
+        <v>46.175</v>
       </c>
       <c r="F106" t="n">
-        <v>87.97110000000001</v>
+        <v>86.96339999999999</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>53.5058</v>
+        <v>55.142</v>
       </c>
       <c r="C107" t="n">
-        <v>65.7723</v>
+        <v>65.7983</v>
       </c>
       <c r="D107" t="n">
-        <v>250.59</v>
+        <v>251.087</v>
       </c>
       <c r="E107" t="n">
-        <v>80.9755</v>
+        <v>69.56319999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>237.07</v>
+        <v>237.785</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>54.119</v>
+        <v>55.3258</v>
       </c>
       <c r="C108" t="n">
-        <v>100.182</v>
+        <v>100.269</v>
       </c>
       <c r="D108" t="n">
-        <v>247.611</v>
+        <v>248.121</v>
       </c>
       <c r="E108" t="n">
-        <v>78.65649999999999</v>
+        <v>78.8609</v>
       </c>
       <c r="F108" t="n">
-        <v>237.265</v>
+        <v>237.423</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>51.2658</v>
+        <v>53.1257</v>
       </c>
       <c r="C109" t="n">
-        <v>98.9889</v>
+        <v>98.7769</v>
       </c>
       <c r="D109" t="n">
-        <v>245.175</v>
+        <v>245.35</v>
       </c>
       <c r="E109" t="n">
-        <v>76.62860000000001</v>
+        <v>66.2826</v>
       </c>
       <c r="F109" t="n">
-        <v>236.994</v>
+        <v>237.35</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>86.6726</v>
+        <v>87.2603</v>
       </c>
       <c r="C110" t="n">
-        <v>97.9906</v>
+        <v>97.90940000000001</v>
       </c>
       <c r="D110" t="n">
-        <v>242.665</v>
+        <v>243.735</v>
       </c>
       <c r="E110" t="n">
-        <v>64.2942</v>
+        <v>74.3926</v>
       </c>
       <c r="F110" t="n">
-        <v>239.266</v>
+        <v>237.991</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>83.1258</v>
+        <v>75.2928</v>
       </c>
       <c r="C111" t="n">
-        <v>96.38679999999999</v>
+        <v>84.33669999999999</v>
       </c>
       <c r="D111" t="n">
-        <v>241.199</v>
+        <v>241.793</v>
       </c>
       <c r="E111" t="n">
-        <v>72.2508</v>
+        <v>72.7058</v>
       </c>
       <c r="F111" t="n">
-        <v>237.605</v>
+        <v>238.008</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>81.9408</v>
+        <v>82.29300000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>94.8982</v>
+        <v>94.9402</v>
       </c>
       <c r="D112" t="n">
-        <v>239.373</v>
+        <v>240.832</v>
       </c>
       <c r="E112" t="n">
-        <v>61.2871</v>
+        <v>61.4246</v>
       </c>
       <c r="F112" t="n">
-        <v>238.547</v>
+        <v>239.306</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>79.73350000000001</v>
+        <v>80.5337</v>
       </c>
       <c r="C113" t="n">
-        <v>93.3394</v>
+        <v>93.5341</v>
       </c>
       <c r="D113" t="n">
-        <v>240.846</v>
+        <v>242.176</v>
       </c>
       <c r="E113" t="n">
-        <v>60.1808</v>
+        <v>60.4173</v>
       </c>
       <c r="F113" t="n">
-        <v>239.101</v>
+        <v>239.268</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>77.1084</v>
+        <v>78.73269999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>92.12220000000001</v>
+        <v>92.2829</v>
       </c>
       <c r="D114" t="n">
-        <v>250.855</v>
+        <v>250.382</v>
       </c>
       <c r="E114" t="n">
-        <v>66.7119</v>
+        <v>66.91630000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>240.585</v>
+        <v>240.937</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>75.59520000000001</v>
+        <v>75.1641</v>
       </c>
       <c r="C115" t="n">
-        <v>90.9692</v>
+        <v>91.02979999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>251.035</v>
+        <v>250.128</v>
       </c>
       <c r="E115" t="n">
-        <v>65.1407</v>
+        <v>65.3329</v>
       </c>
       <c r="F115" t="n">
-        <v>239.9</v>
+        <v>240.763</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>74.83969999999999</v>
+        <v>68.7273</v>
       </c>
       <c r="C116" t="n">
-        <v>89.81699999999999</v>
+        <v>80.36579999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>251.215</v>
+        <v>252.362</v>
       </c>
       <c r="E116" t="n">
-        <v>63.6024</v>
+        <v>63.7444</v>
       </c>
       <c r="F116" t="n">
-        <v>241.006</v>
+        <v>241.339</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>72.1801</v>
+        <v>73.279</v>
       </c>
       <c r="C117" t="n">
-        <v>88.6952</v>
+        <v>88.7958</v>
       </c>
       <c r="D117" t="n">
-        <v>251.36</v>
+        <v>247.963</v>
       </c>
       <c r="E117" t="n">
-        <v>62.2493</v>
+        <v>62.3847</v>
       </c>
       <c r="F117" t="n">
-        <v>241.614</v>
+        <v>241.95</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>63.4065</v>
+        <v>66.8232</v>
       </c>
       <c r="C118" t="n">
-        <v>78.9858</v>
+        <v>79.0478</v>
       </c>
       <c r="D118" t="n">
-        <v>238.448</v>
+        <v>239.188</v>
       </c>
       <c r="E118" t="n">
-        <v>60.8498</v>
+        <v>54.6128</v>
       </c>
       <c r="F118" t="n">
-        <v>241.148</v>
+        <v>242.673</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>69.72069999999999</v>
+        <v>65.7561</v>
       </c>
       <c r="C119" t="n">
-        <v>86.491</v>
+        <v>78.4087</v>
       </c>
       <c r="D119" t="n">
-        <v>238.554</v>
+        <v>240.45</v>
       </c>
       <c r="E119" t="n">
-        <v>52.9862</v>
+        <v>53.3619</v>
       </c>
       <c r="F119" t="n">
-        <v>242.228</v>
+        <v>150.482</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>62.098</v>
+        <v>68.1066</v>
       </c>
       <c r="C120" t="n">
-        <v>77.7111</v>
+        <v>85.80759999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>239.853</v>
+        <v>241.854</v>
       </c>
       <c r="E120" t="n">
-        <v>52.2827</v>
+        <v>52.6106</v>
       </c>
       <c r="F120" t="n">
-        <v>196.73</v>
+        <v>100.419</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>62.7811</v>
+        <v>67.1551</v>
       </c>
       <c r="C121" t="n">
-        <v>77.2002</v>
+        <v>84.87179999999999</v>
       </c>
       <c r="D121" t="n">
-        <v>316.999</v>
+        <v>318.497</v>
       </c>
       <c r="E121" t="n">
-        <v>87.6617</v>
+        <v>93.03440000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>288.03</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>60.0973</v>
+        <v>64.7551</v>
       </c>
       <c r="C122" t="n">
-        <v>111.725</v>
+        <v>118.907</v>
       </c>
       <c r="D122" t="n">
-        <v>311.984</v>
+        <v>313.302</v>
       </c>
       <c r="E122" t="n">
-        <v>85.62869999999999</v>
+        <v>85.77670000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>287.371</v>
+        <v>288.743</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>60.0821</v>
+        <v>60.2542</v>
       </c>
       <c r="C123" t="n">
-        <v>110.54</v>
+        <v>110.793</v>
       </c>
       <c r="D123" t="n">
-        <v>307.563</v>
+        <v>309.219</v>
       </c>
       <c r="E123" t="n">
-        <v>83.82550000000001</v>
+        <v>83.92829999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>286.555</v>
+        <v>287.888</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>94.2557</v>
+        <v>91.1191</v>
       </c>
       <c r="C124" t="n">
-        <v>110.024</v>
+        <v>109.978</v>
       </c>
       <c r="D124" t="n">
-        <v>303.976</v>
+        <v>305.613</v>
       </c>
       <c r="E124" t="n">
-        <v>81.8728</v>
+        <v>81.9436</v>
       </c>
       <c r="F124" t="n">
-        <v>285.853</v>
+        <v>287.663</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>90.86369999999999</v>
+        <v>90.6254</v>
       </c>
       <c r="C125" t="n">
-        <v>108.675</v>
+        <v>108.857</v>
       </c>
       <c r="D125" t="n">
-        <v>300.507</v>
+        <v>302.26</v>
       </c>
       <c r="E125" t="n">
-        <v>85.04949999999999</v>
+        <v>85.1066</v>
       </c>
       <c r="F125" t="n">
-        <v>285.969</v>
+        <v>286.72</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>86.82729999999999</v>
+        <v>88.71720000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>107.663</v>
+        <v>107.744</v>
       </c>
       <c r="D126" t="n">
-        <v>297.657</v>
+        <v>299.36</v>
       </c>
       <c r="E126" t="n">
-        <v>83.2179</v>
+        <v>78.7993</v>
       </c>
       <c r="F126" t="n">
-        <v>285.672</v>
+        <v>286.316</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>88.1396</v>
+        <v>87.0859</v>
       </c>
       <c r="C127" t="n">
-        <v>106.646</v>
+        <v>106.606</v>
       </c>
       <c r="D127" t="n">
-        <v>295.019</v>
+        <v>296.574</v>
       </c>
       <c r="E127" t="n">
-        <v>77.25490000000001</v>
+        <v>81.5712</v>
       </c>
       <c r="F127" t="n">
-        <v>284.443</v>
+        <v>286.732</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>82.70399999999999</v>
+        <v>85.3952</v>
       </c>
       <c r="C128" t="n">
-        <v>105.535</v>
+        <v>105.691</v>
       </c>
       <c r="D128" t="n">
-        <v>292.838</v>
+        <v>294.376</v>
       </c>
       <c r="E128" t="n">
-        <v>75.7754</v>
+        <v>79.97620000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>284.634</v>
+        <v>284.592</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>87.15389999999999</v>
+        <v>84.8644</v>
       </c>
       <c r="C129" t="n">
-        <v>109.683</v>
+        <v>104.556</v>
       </c>
       <c r="D129" t="n">
-        <v>290.694</v>
+        <v>292.166</v>
       </c>
       <c r="E129" t="n">
-        <v>74.4156</v>
+        <v>74.4584</v>
       </c>
       <c r="F129" t="n">
-        <v>283.744</v>
+        <v>284.98</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>85.697</v>
+        <v>86.0341</v>
       </c>
       <c r="C130" t="n">
-        <v>108.538</v>
+        <v>108.554</v>
       </c>
       <c r="D130" t="n">
-        <v>290.89</v>
+        <v>290.704</v>
       </c>
       <c r="E130" t="n">
-        <v>73.23309999999999</v>
+        <v>73.2522</v>
       </c>
       <c r="F130" t="n">
-        <v>284.537</v>
+        <v>284.482</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>80.45950000000001</v>
+        <v>80.88509999999999</v>
       </c>
       <c r="C131" t="n">
-        <v>102.713</v>
+        <v>102.86</v>
       </c>
       <c r="D131" t="n">
-        <v>287.876</v>
+        <v>289.291</v>
       </c>
       <c r="E131" t="n">
-        <v>71.8672</v>
+        <v>72.1613</v>
       </c>
       <c r="F131" t="n">
-        <v>283.089</v>
+        <v>284.707</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>79.5112</v>
+        <v>79.765</v>
       </c>
       <c r="C132" t="n">
-        <v>101.941</v>
+        <v>102.09</v>
       </c>
       <c r="D132" t="n">
-        <v>287.429</v>
+        <v>288.702</v>
       </c>
       <c r="E132" t="n">
-        <v>70.8998</v>
+        <v>74.2659</v>
       </c>
       <c r="F132" t="n">
-        <v>283.906</v>
+        <v>285.275</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>78.66889999999999</v>
+        <v>77.586</v>
       </c>
       <c r="C133" t="n">
-        <v>101.282</v>
+        <v>101.494</v>
       </c>
       <c r="D133" t="n">
-        <v>287.009</v>
+        <v>289.173</v>
       </c>
       <c r="E133" t="n">
-        <v>69.82129999999999</v>
+        <v>69.94799999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>283.587</v>
+        <v>285.595</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>77.43049999999999</v>
+        <v>68.8494</v>
       </c>
       <c r="C134" t="n">
-        <v>100.548</v>
+        <v>92.4164</v>
       </c>
       <c r="D134" t="n">
-        <v>282.288</v>
+        <v>284.341</v>
       </c>
       <c r="E134" t="n">
-        <v>62.7342</v>
+        <v>62.9315</v>
       </c>
       <c r="F134" t="n">
-        <v>257.792</v>
+        <v>179.705</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>73.80110000000001</v>
+        <v>77.00060000000001</v>
       </c>
       <c r="C135" t="n">
-        <v>92.0856</v>
+        <v>100.035</v>
       </c>
       <c r="D135" t="n">
-        <v>362.065</v>
+        <v>365.409</v>
       </c>
       <c r="E135" t="n">
-        <v>98.5642</v>
+        <v>98.7153</v>
       </c>
       <c r="F135" t="n">
-        <v>326.1</v>
+        <v>328.097</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>75.7002</v>
+        <v>76.6049</v>
       </c>
       <c r="C136" t="n">
-        <v>132.746</v>
+        <v>133.312</v>
       </c>
       <c r="D136" t="n">
-        <v>355.718</v>
+        <v>358.215</v>
       </c>
       <c r="E136" t="n">
-        <v>96.8125</v>
+        <v>96.6957</v>
       </c>
       <c r="F136" t="n">
-        <v>325.714</v>
+        <v>325.916</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>73.6033</v>
+        <v>73.3681</v>
       </c>
       <c r="C137" t="n">
-        <v>132.196</v>
+        <v>132.791</v>
       </c>
       <c r="D137" t="n">
-        <v>350.168</v>
+        <v>353.344</v>
       </c>
       <c r="E137" t="n">
-        <v>94.46259999999999</v>
+        <v>94.7881</v>
       </c>
       <c r="F137" t="n">
-        <v>325.416</v>
+        <v>327.009</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>102.962</v>
+        <v>102.041</v>
       </c>
       <c r="C138" t="n">
-        <v>125.025</v>
+        <v>125.289</v>
       </c>
       <c r="D138" t="n">
-        <v>344.945</v>
+        <v>346.878</v>
       </c>
       <c r="E138" t="n">
-        <v>92.9941</v>
+        <v>97.47329999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>323.536</v>
+        <v>325.472</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>103.784</v>
+        <v>104.971</v>
       </c>
       <c r="C139" t="n">
-        <v>130.986</v>
+        <v>130.964</v>
       </c>
       <c r="D139" t="n">
-        <v>340.861</v>
+        <v>341.749</v>
       </c>
       <c r="E139" t="n">
-        <v>96.2373</v>
+        <v>95.9845</v>
       </c>
       <c r="F139" t="n">
-        <v>323.678</v>
+        <v>324.023</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>97.6939</v>
+        <v>98.31100000000001</v>
       </c>
       <c r="C140" t="n">
-        <v>123.228</v>
+        <v>123.295</v>
       </c>
       <c r="D140" t="n">
-        <v>336.045</v>
+        <v>337.165</v>
       </c>
       <c r="E140" t="n">
-        <v>93.81229999999999</v>
+        <v>94.1828</v>
       </c>
       <c r="F140" t="n">
-        <v>322.78</v>
+        <v>324</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>96.35380000000001</v>
+        <v>101.282</v>
       </c>
       <c r="C141" t="n">
-        <v>122.344</v>
+        <v>128.686</v>
       </c>
       <c r="D141" t="n">
-        <v>332.783</v>
+        <v>334.884</v>
       </c>
       <c r="E141" t="n">
-        <v>92.5737</v>
+        <v>88.5557</v>
       </c>
       <c r="F141" t="n">
-        <v>321.513</v>
+        <v>322.203</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>96.09610000000001</v>
+        <v>95.37820000000001</v>
       </c>
       <c r="C142" t="n">
-        <v>121.645</v>
+        <v>121.591</v>
       </c>
       <c r="D142" t="n">
-        <v>332.769</v>
+        <v>335.263</v>
       </c>
       <c r="E142" t="n">
-        <v>90.6447</v>
+        <v>86.9061</v>
       </c>
       <c r="F142" t="n">
-        <v>321.095</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>91.459</v>
+        <v>93.5184</v>
       </c>
       <c r="C143" t="n">
-        <v>120.877</v>
+        <v>121.29</v>
       </c>
       <c r="D143" t="n">
-        <v>330.457</v>
+        <v>332.984</v>
       </c>
       <c r="E143" t="n">
-        <v>89.553</v>
+        <v>89.6888</v>
       </c>
       <c r="F143" t="n">
-        <v>320.023</v>
+        <v>322.669</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>22.0788</v>
+        <v>21.9105</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6364</v>
+        <v>24.5219</v>
       </c>
       <c r="D2" t="n">
-        <v>55.8455</v>
+        <v>55.9237</v>
       </c>
       <c r="E2" t="n">
-        <v>17.8375</v>
+        <v>17.0565</v>
       </c>
       <c r="F2" t="n">
-        <v>33.3484</v>
+        <v>32.1128</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>21.7658</v>
+        <v>21.2342</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1034</v>
+        <v>24.0553</v>
       </c>
       <c r="D3" t="n">
-        <v>55.196</v>
+        <v>55.1773</v>
       </c>
       <c r="E3" t="n">
-        <v>17.4261</v>
+        <v>16.5941</v>
       </c>
       <c r="F3" t="n">
-        <v>32.8994</v>
+        <v>31.7381</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>21.1063</v>
+        <v>20.7982</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5867</v>
+        <v>23.5449</v>
       </c>
       <c r="D4" t="n">
-        <v>54.7752</v>
+        <v>54.6942</v>
       </c>
       <c r="E4" t="n">
-        <v>16.8839</v>
+        <v>16.168</v>
       </c>
       <c r="F4" t="n">
-        <v>32.5777</v>
+        <v>31.4624</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>20.4511</v>
+        <v>19.9265</v>
       </c>
       <c r="C5" t="n">
-        <v>23.1415</v>
+        <v>23.1807</v>
       </c>
       <c r="D5" t="n">
-        <v>54.3979</v>
+        <v>54.3467</v>
       </c>
       <c r="E5" t="n">
-        <v>16.6114</v>
+        <v>25.096</v>
       </c>
       <c r="F5" t="n">
-        <v>32.3226</v>
+        <v>39.5999</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>20.4708</v>
+        <v>20.0829</v>
       </c>
       <c r="C6" t="n">
-        <v>22.7784</v>
+        <v>22.7062</v>
       </c>
       <c r="D6" t="n">
-        <v>54.0115</v>
+        <v>53.948</v>
       </c>
       <c r="E6" t="n">
-        <v>16.1796</v>
+        <v>24.1716</v>
       </c>
       <c r="F6" t="n">
-        <v>32.2199</v>
+        <v>38.7905</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.7723</v>
+        <v>19.4345</v>
       </c>
       <c r="C7" t="n">
-        <v>22.468</v>
+        <v>22.4316</v>
       </c>
       <c r="D7" t="n">
-        <v>69.0442</v>
+        <v>68.4618</v>
       </c>
       <c r="E7" t="n">
-        <v>24.922</v>
+        <v>23.3996</v>
       </c>
       <c r="F7" t="n">
-        <v>40.0968</v>
+        <v>38.0194</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>19.8749</v>
+        <v>19.4033</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8671</v>
+        <v>31.5294</v>
       </c>
       <c r="D8" t="n">
-        <v>67.52209999999999</v>
+        <v>66.98009999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>24.0388</v>
+        <v>22.6148</v>
       </c>
       <c r="F8" t="n">
-        <v>39.2494</v>
+        <v>37.2488</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>19.2008</v>
+        <v>19.6896</v>
       </c>
       <c r="C9" t="n">
-        <v>30.0585</v>
+        <v>30.6587</v>
       </c>
       <c r="D9" t="n">
-        <v>66.09780000000001</v>
+        <v>65.68170000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>23.1325</v>
+        <v>21.8697</v>
       </c>
       <c r="F9" t="n">
-        <v>38.3835</v>
+        <v>36.5107</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.3654</v>
+        <v>27.8594</v>
       </c>
       <c r="C10" t="n">
-        <v>29.3183</v>
+        <v>29.1996</v>
       </c>
       <c r="D10" t="n">
-        <v>64.8524</v>
+        <v>64.5742</v>
       </c>
       <c r="E10" t="n">
-        <v>22.4638</v>
+        <v>21.204</v>
       </c>
       <c r="F10" t="n">
-        <v>37.5884</v>
+        <v>35.788</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.4026</v>
+        <v>26.9779</v>
       </c>
       <c r="C11" t="n">
-        <v>28.7224</v>
+        <v>28.5097</v>
       </c>
       <c r="D11" t="n">
-        <v>63.7549</v>
+        <v>63.4117</v>
       </c>
       <c r="E11" t="n">
-        <v>21.7241</v>
+        <v>20.4683</v>
       </c>
       <c r="F11" t="n">
-        <v>36.7409</v>
+        <v>35.1107</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>25.9755</v>
+        <v>26.0197</v>
       </c>
       <c r="C12" t="n">
-        <v>27.8235</v>
+        <v>28.3016</v>
       </c>
       <c r="D12" t="n">
-        <v>62.6544</v>
+        <v>62.2683</v>
       </c>
       <c r="E12" t="n">
-        <v>20.9627</v>
+        <v>19.7614</v>
       </c>
       <c r="F12" t="n">
-        <v>36.0891</v>
+        <v>34.5452</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.009</v>
+        <v>25.0883</v>
       </c>
       <c r="C13" t="n">
-        <v>27.2089</v>
+        <v>27.055</v>
       </c>
       <c r="D13" t="n">
-        <v>61.7694</v>
+        <v>61.4417</v>
       </c>
       <c r="E13" t="n">
-        <v>20.4478</v>
+        <v>19.2964</v>
       </c>
       <c r="F13" t="n">
-        <v>35.506</v>
+        <v>34.0011</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.4661</v>
+        <v>24.5493</v>
       </c>
       <c r="C14" t="n">
-        <v>26.5262</v>
+        <v>26.4282</v>
       </c>
       <c r="D14" t="n">
-        <v>61.0389</v>
+        <v>60.7289</v>
       </c>
       <c r="E14" t="n">
-        <v>19.7821</v>
+        <v>18.5986</v>
       </c>
       <c r="F14" t="n">
-        <v>34.8775</v>
+        <v>33.4318</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.8962</v>
+        <v>23.8847</v>
       </c>
       <c r="C15" t="n">
-        <v>25.9141</v>
+        <v>26.3005</v>
       </c>
       <c r="D15" t="n">
-        <v>60.4314</v>
+        <v>60.2337</v>
       </c>
       <c r="E15" t="n">
-        <v>19.1382</v>
+        <v>18.068</v>
       </c>
       <c r="F15" t="n">
-        <v>34.3432</v>
+        <v>32.9538</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.2244</v>
+        <v>23.3828</v>
       </c>
       <c r="C16" t="n">
-        <v>25.3358</v>
+        <v>25.2851</v>
       </c>
       <c r="D16" t="n">
-        <v>59.8773</v>
+        <v>59.5531</v>
       </c>
       <c r="E16" t="n">
-        <v>18.6775</v>
+        <v>17.5568</v>
       </c>
       <c r="F16" t="n">
-        <v>33.8181</v>
+        <v>32.5676</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.4727</v>
+        <v>22.3633</v>
       </c>
       <c r="C17" t="n">
-        <v>24.7945</v>
+        <v>25.0992</v>
       </c>
       <c r="D17" t="n">
-        <v>59.3657</v>
+        <v>59.1305</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2509</v>
+        <v>17.1261</v>
       </c>
       <c r="F17" t="n">
-        <v>33.4146</v>
+        <v>32.203</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>22.3983</v>
+        <v>21.9419</v>
       </c>
       <c r="C18" t="n">
-        <v>24.3021</v>
+        <v>24.5227</v>
       </c>
       <c r="D18" t="n">
-        <v>58.6833</v>
+        <v>58.257</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7884</v>
+        <v>16.7594</v>
       </c>
       <c r="F18" t="n">
-        <v>33.0197</v>
+        <v>31.8593</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.5677</v>
+        <v>21.3728</v>
       </c>
       <c r="C19" t="n">
-        <v>23.8912</v>
+        <v>24.0967</v>
       </c>
       <c r="D19" t="n">
-        <v>58.0569</v>
+        <v>57.667</v>
       </c>
       <c r="E19" t="n">
-        <v>17.4745</v>
+        <v>16.3711</v>
       </c>
       <c r="F19" t="n">
-        <v>32.7008</v>
+        <v>31.6078</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>20.9529</v>
+        <v>20.6651</v>
       </c>
       <c r="C20" t="n">
-        <v>23.463</v>
+        <v>23.6405</v>
       </c>
       <c r="D20" t="n">
-        <v>57.7193</v>
+        <v>57.3166</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1728</v>
+        <v>25.0043</v>
       </c>
       <c r="F20" t="n">
-        <v>32.5415</v>
+        <v>39.412</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.5201</v>
+        <v>20.685</v>
       </c>
       <c r="C21" t="n">
-        <v>23.1401</v>
+        <v>23.105</v>
       </c>
       <c r="D21" t="n">
-        <v>75.4198</v>
+        <v>74.4487</v>
       </c>
       <c r="E21" t="n">
-        <v>25.8153</v>
+        <v>24.0509</v>
       </c>
       <c r="F21" t="n">
-        <v>40.626</v>
+        <v>38.562</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.2741</v>
+        <v>20.1458</v>
       </c>
       <c r="C22" t="n">
-        <v>31.6725</v>
+        <v>31.4272</v>
       </c>
       <c r="D22" t="n">
-        <v>73.7375</v>
+        <v>72.8686</v>
       </c>
       <c r="E22" t="n">
-        <v>25.0038</v>
+        <v>23.3085</v>
       </c>
       <c r="F22" t="n">
-        <v>39.7507</v>
+        <v>37.7781</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>20.2597</v>
+        <v>19.9923</v>
       </c>
       <c r="C23" t="n">
-        <v>30.8168</v>
+        <v>30.6513</v>
       </c>
       <c r="D23" t="n">
-        <v>72.2402</v>
+        <v>71.5076</v>
       </c>
       <c r="E23" t="n">
-        <v>24.2201</v>
+        <v>22.5054</v>
       </c>
       <c r="F23" t="n">
-        <v>38.9475</v>
+        <v>37.0593</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>29.1399</v>
+        <v>28.7803</v>
       </c>
       <c r="C24" t="n">
-        <v>30.2488</v>
+        <v>29.9426</v>
       </c>
       <c r="D24" t="n">
-        <v>70.958</v>
+        <v>70.15770000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>23.4139</v>
+        <v>21.8191</v>
       </c>
       <c r="F24" t="n">
-        <v>38.2173</v>
+        <v>36.3416</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>27.7782</v>
+        <v>27.9096</v>
       </c>
       <c r="C25" t="n">
-        <v>29.3287</v>
+        <v>29.1768</v>
       </c>
       <c r="D25" t="n">
-        <v>69.74639999999999</v>
+        <v>68.8994</v>
       </c>
       <c r="E25" t="n">
-        <v>22.6699</v>
+        <v>21.1283</v>
       </c>
       <c r="F25" t="n">
-        <v>37.451</v>
+        <v>35.6649</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>27.0313</v>
+        <v>26.9642</v>
       </c>
       <c r="C26" t="n">
-        <v>28.5998</v>
+        <v>28.4556</v>
       </c>
       <c r="D26" t="n">
-        <v>68.48950000000001</v>
+        <v>67.7435</v>
       </c>
       <c r="E26" t="n">
-        <v>21.9607</v>
+        <v>20.5041</v>
       </c>
       <c r="F26" t="n">
-        <v>37.3754</v>
+        <v>34.9136</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>25.9676</v>
+        <v>26.2684</v>
       </c>
       <c r="C27" t="n">
-        <v>27.8858</v>
+        <v>27.7621</v>
       </c>
       <c r="D27" t="n">
-        <v>67.5868</v>
+        <v>66.81140000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>21.1993</v>
+        <v>19.9268</v>
       </c>
       <c r="F27" t="n">
-        <v>36.6645</v>
+        <v>34.3456</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.7106</v>
+        <v>25.5408</v>
       </c>
       <c r="C28" t="n">
-        <v>27.2622</v>
+        <v>27.1279</v>
       </c>
       <c r="D28" t="n">
-        <v>66.51739999999999</v>
+        <v>65.7253</v>
       </c>
       <c r="E28" t="n">
-        <v>20.8241</v>
+        <v>19.247</v>
       </c>
       <c r="F28" t="n">
-        <v>36.1152</v>
+        <v>33.8229</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>25.0071</v>
+        <v>24.4831</v>
       </c>
       <c r="C29" t="n">
-        <v>26.66</v>
+        <v>26.4752</v>
       </c>
       <c r="D29" t="n">
-        <v>65.94759999999999</v>
+        <v>65.1289</v>
       </c>
       <c r="E29" t="n">
-        <v>20.1067</v>
+        <v>18.7135</v>
       </c>
       <c r="F29" t="n">
-        <v>35.5429</v>
+        <v>33.3323</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>23.7134</v>
+        <v>23.6128</v>
       </c>
       <c r="C30" t="n">
-        <v>26.0371</v>
+        <v>25.856</v>
       </c>
       <c r="D30" t="n">
-        <v>65.07599999999999</v>
+        <v>64.2291</v>
       </c>
       <c r="E30" t="n">
-        <v>19.5021</v>
+        <v>18.1641</v>
       </c>
       <c r="F30" t="n">
-        <v>34.9236</v>
+        <v>32.9015</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.0626</v>
+        <v>23.4974</v>
       </c>
       <c r="C31" t="n">
-        <v>25.4666</v>
+        <v>25.3301</v>
       </c>
       <c r="D31" t="n">
-        <v>64.5463</v>
+        <v>63.8411</v>
       </c>
       <c r="E31" t="n">
-        <v>19.101</v>
+        <v>17.87</v>
       </c>
       <c r="F31" t="n">
-        <v>33.5429</v>
+        <v>32.4487</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>23.6183</v>
+        <v>22.8558</v>
       </c>
       <c r="C32" t="n">
-        <v>25.0896</v>
+        <v>24.787</v>
       </c>
       <c r="D32" t="n">
-        <v>64.1037</v>
+        <v>63.3874</v>
       </c>
       <c r="E32" t="n">
-        <v>18.5686</v>
+        <v>17.4999</v>
       </c>
       <c r="F32" t="n">
-        <v>33.1683</v>
+        <v>32.0936</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>22.5676</v>
+        <v>22.4022</v>
       </c>
       <c r="C33" t="n">
-        <v>24.5283</v>
+        <v>24.3043</v>
       </c>
       <c r="D33" t="n">
-        <v>63.6329</v>
+        <v>62.9517</v>
       </c>
       <c r="E33" t="n">
-        <v>18.2062</v>
+        <v>17.2187</v>
       </c>
       <c r="F33" t="n">
-        <v>33.048</v>
+        <v>31.8565</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>21.6074</v>
+        <v>21.5786</v>
       </c>
       <c r="C34" t="n">
-        <v>24.1267</v>
+        <v>23.9687</v>
       </c>
       <c r="D34" t="n">
-        <v>63.0069</v>
+        <v>62.3138</v>
       </c>
       <c r="E34" t="n">
-        <v>17.9999</v>
+        <v>25.6812</v>
       </c>
       <c r="F34" t="n">
-        <v>32.8291</v>
+        <v>40.2902</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>21.7911</v>
+        <v>20.91</v>
       </c>
       <c r="C35" t="n">
-        <v>23.8088</v>
+        <v>23.6685</v>
       </c>
       <c r="D35" t="n">
-        <v>81.393</v>
+        <v>80.40940000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>26.9048</v>
+        <v>24.9772</v>
       </c>
       <c r="F35" t="n">
-        <v>41.374</v>
+        <v>39.5212</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>21.2527</v>
+        <v>21.513</v>
       </c>
       <c r="C36" t="n">
-        <v>23.6681</v>
+        <v>23.3386</v>
       </c>
       <c r="D36" t="n">
-        <v>79.68300000000001</v>
+        <v>78.65349999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>25.9235</v>
+        <v>24.1822</v>
       </c>
       <c r="F36" t="n">
-        <v>40.58</v>
+        <v>38.8163</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>21.6973</v>
+        <v>21.0795</v>
       </c>
       <c r="C37" t="n">
-        <v>31.7086</v>
+        <v>31.4648</v>
       </c>
       <c r="D37" t="n">
-        <v>78.04940000000001</v>
+        <v>77.0592</v>
       </c>
       <c r="E37" t="n">
-        <v>25.1179</v>
+        <v>23.3481</v>
       </c>
       <c r="F37" t="n">
-        <v>39.7849</v>
+        <v>38.0631</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>28.9235</v>
+        <v>29.1883</v>
       </c>
       <c r="C38" t="n">
-        <v>31.089</v>
+        <v>30.7503</v>
       </c>
       <c r="D38" t="n">
-        <v>76.53619999999999</v>
+        <v>75.652</v>
       </c>
       <c r="E38" t="n">
-        <v>24.2576</v>
+        <v>22.649</v>
       </c>
       <c r="F38" t="n">
-        <v>39.0303</v>
+        <v>37.1739</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>28.8069</v>
+        <v>28.1473</v>
       </c>
       <c r="C39" t="n">
-        <v>30.1464</v>
+        <v>30.1181</v>
       </c>
       <c r="D39" t="n">
-        <v>75.2259</v>
+        <v>74.4148</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5317</v>
+        <v>21.9371</v>
       </c>
       <c r="F39" t="n">
-        <v>38.3062</v>
+        <v>36.7689</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>27.3431</v>
+        <v>26.9105</v>
       </c>
       <c r="C40" t="n">
-        <v>29.457</v>
+        <v>29.3027</v>
       </c>
       <c r="D40" t="n">
-        <v>73.91240000000001</v>
+        <v>73.1288</v>
       </c>
       <c r="E40" t="n">
-        <v>22.7921</v>
+        <v>21.3826</v>
       </c>
       <c r="F40" t="n">
-        <v>37.5983</v>
+        <v>36.1907</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.7536</v>
+        <v>26.4582</v>
       </c>
       <c r="C41" t="n">
-        <v>28.7273</v>
+        <v>28.8146</v>
       </c>
       <c r="D41" t="n">
-        <v>72.72150000000001</v>
+        <v>71.9323</v>
       </c>
       <c r="E41" t="n">
-        <v>22.2507</v>
+        <v>20.7643</v>
       </c>
       <c r="F41" t="n">
-        <v>36.9677</v>
+        <v>35.5043</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>26.4442</v>
+        <v>25.7149</v>
       </c>
       <c r="C42" t="n">
-        <v>28.1739</v>
+        <v>28.0729</v>
       </c>
       <c r="D42" t="n">
-        <v>71.8535</v>
+        <v>71.0826</v>
       </c>
       <c r="E42" t="n">
-        <v>21.6214</v>
+        <v>20.2336</v>
       </c>
       <c r="F42" t="n">
-        <v>36.364</v>
+        <v>34.9138</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>24.8134</v>
+        <v>25.428</v>
       </c>
       <c r="C43" t="n">
-        <v>27.673</v>
+        <v>27.5545</v>
       </c>
       <c r="D43" t="n">
-        <v>70.7756</v>
+        <v>69.9863</v>
       </c>
       <c r="E43" t="n">
-        <v>20.9537</v>
+        <v>19.7603</v>
       </c>
       <c r="F43" t="n">
-        <v>35.8703</v>
+        <v>34.499</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.6651</v>
+        <v>24.1776</v>
       </c>
       <c r="C44" t="n">
-        <v>27.0531</v>
+        <v>26.9556</v>
       </c>
       <c r="D44" t="n">
-        <v>69.92449999999999</v>
+        <v>69.16119999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>20.4526</v>
+        <v>19.2383</v>
       </c>
       <c r="F44" t="n">
-        <v>35.326</v>
+        <v>34.1071</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>23.6902</v>
+        <v>23.4617</v>
       </c>
       <c r="C45" t="n">
-        <v>26.392</v>
+        <v>26.3823</v>
       </c>
       <c r="D45" t="n">
-        <v>69.2388</v>
+        <v>68.5737</v>
       </c>
       <c r="E45" t="n">
-        <v>19.9347</v>
+        <v>18.7575</v>
       </c>
       <c r="F45" t="n">
-        <v>34.817</v>
+        <v>33.6234</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>23.3474</v>
+        <v>22.9131</v>
       </c>
       <c r="C46" t="n">
-        <v>25.9254</v>
+        <v>25.7486</v>
       </c>
       <c r="D46" t="n">
-        <v>68.6631</v>
+        <v>68.05070000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>19.4327</v>
+        <v>18.3893</v>
       </c>
       <c r="F46" t="n">
-        <v>34.5356</v>
+        <v>33.2998</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.5723</v>
+        <v>22.4646</v>
       </c>
       <c r="C47" t="n">
-        <v>25.3934</v>
+        <v>25.535</v>
       </c>
       <c r="D47" t="n">
-        <v>68.2287</v>
+        <v>67.5866</v>
       </c>
       <c r="E47" t="n">
-        <v>19.1093</v>
+        <v>18.0594</v>
       </c>
       <c r="F47" t="n">
-        <v>34.2769</v>
+        <v>33.1226</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>22.0844</v>
+        <v>21.9762</v>
       </c>
       <c r="C48" t="n">
-        <v>25.0874</v>
+        <v>25.1988</v>
       </c>
       <c r="D48" t="n">
-        <v>67.49209999999999</v>
+        <v>66.8831</v>
       </c>
       <c r="E48" t="n">
-        <v>18.6823</v>
+        <v>26.7881</v>
       </c>
       <c r="F48" t="n">
-        <v>34.0002</v>
+        <v>41.6593</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>21.7671</v>
+        <v>22.3083</v>
       </c>
       <c r="C49" t="n">
-        <v>24.782</v>
+        <v>24.6646</v>
       </c>
       <c r="D49" t="n">
-        <v>67.1373</v>
+        <v>66.53619999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>18.4885</v>
+        <v>25.994</v>
       </c>
       <c r="F49" t="n">
-        <v>33.8502</v>
+        <v>40.9641</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.5946</v>
+        <v>21.1209</v>
       </c>
       <c r="C50" t="n">
-        <v>24.3375</v>
+        <v>24.2749</v>
       </c>
       <c r="D50" t="n">
-        <v>84.3807</v>
+        <v>83.7294</v>
       </c>
       <c r="E50" t="n">
-        <v>26.7291</v>
+        <v>25.2015</v>
       </c>
       <c r="F50" t="n">
-        <v>42.0874</v>
+        <v>40.2617</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>21.3504</v>
+        <v>21.4166</v>
       </c>
       <c r="C51" t="n">
-        <v>32.7016</v>
+        <v>32.5461</v>
       </c>
       <c r="D51" t="n">
-        <v>82.6044</v>
+        <v>81.9768</v>
       </c>
       <c r="E51" t="n">
-        <v>25.9586</v>
+        <v>24.4072</v>
       </c>
       <c r="F51" t="n">
-        <v>41.3439</v>
+        <v>39.6047</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>21.4242</v>
+        <v>21.188</v>
       </c>
       <c r="C52" t="n">
-        <v>32.0823</v>
+        <v>32.0221</v>
       </c>
       <c r="D52" t="n">
-        <v>80.95099999999999</v>
+        <v>80.4229</v>
       </c>
       <c r="E52" t="n">
-        <v>25.3269</v>
+        <v>23.7775</v>
       </c>
       <c r="F52" t="n">
-        <v>40.6647</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.8397</v>
+        <v>29.4114</v>
       </c>
       <c r="C53" t="n">
-        <v>31.3605</v>
+        <v>31.2482</v>
       </c>
       <c r="D53" t="n">
-        <v>79.4461</v>
+        <v>78.9106</v>
       </c>
       <c r="E53" t="n">
-        <v>24.4531</v>
+        <v>23.1354</v>
       </c>
       <c r="F53" t="n">
-        <v>39.9139</v>
+        <v>38.3593</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>28.1748</v>
+        <v>27.8762</v>
       </c>
       <c r="C54" t="n">
-        <v>30.7701</v>
+        <v>30.547</v>
       </c>
       <c r="D54" t="n">
-        <v>78.03019999999999</v>
+        <v>77.5652</v>
       </c>
       <c r="E54" t="n">
-        <v>23.7049</v>
+        <v>22.4607</v>
       </c>
       <c r="F54" t="n">
-        <v>39.241</v>
+        <v>37.7849</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>27.3086</v>
+        <v>27.2619</v>
       </c>
       <c r="C55" t="n">
-        <v>30.1465</v>
+        <v>30.0336</v>
       </c>
       <c r="D55" t="n">
-        <v>76.8002</v>
+        <v>76.3871</v>
       </c>
       <c r="E55" t="n">
-        <v>23.1444</v>
+        <v>21.8789</v>
       </c>
       <c r="F55" t="n">
-        <v>38.7355</v>
+        <v>37.1819</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>27.2433</v>
+        <v>26.6209</v>
       </c>
       <c r="C56" t="n">
-        <v>29.3886</v>
+        <v>29.4767</v>
       </c>
       <c r="D56" t="n">
-        <v>75.7807</v>
+        <v>75.42570000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>22.4766</v>
+        <v>21.3323</v>
       </c>
       <c r="F56" t="n">
-        <v>38.1211</v>
+        <v>36.7496</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.1245</v>
+        <v>26.4303</v>
       </c>
       <c r="C57" t="n">
-        <v>29.1288</v>
+        <v>28.9031</v>
       </c>
       <c r="D57" t="n">
-        <v>74.56870000000001</v>
+        <v>74.2453</v>
       </c>
       <c r="E57" t="n">
-        <v>21.9939</v>
+        <v>20.7839</v>
       </c>
       <c r="F57" t="n">
-        <v>37.5902</v>
+        <v>36.2261</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>25.9434</v>
+        <v>25.7147</v>
       </c>
       <c r="C58" t="n">
-        <v>28.5669</v>
+        <v>28.4005</v>
       </c>
       <c r="D58" t="n">
-        <v>73.76739999999999</v>
+        <v>73.422</v>
       </c>
       <c r="E58" t="n">
-        <v>21.4523</v>
+        <v>20.2385</v>
       </c>
       <c r="F58" t="n">
-        <v>37.1684</v>
+        <v>35.8042</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>24.9734</v>
+        <v>25.0589</v>
       </c>
       <c r="C59" t="n">
-        <v>27.9208</v>
+        <v>27.9182</v>
       </c>
       <c r="D59" t="n">
-        <v>72.8647</v>
+        <v>72.56010000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>20.8704</v>
+        <v>19.8167</v>
       </c>
       <c r="F59" t="n">
-        <v>36.6249</v>
+        <v>35.453</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>23.9553</v>
+        <v>24.1206</v>
       </c>
       <c r="C60" t="n">
-        <v>27.63</v>
+        <v>27.4892</v>
       </c>
       <c r="D60" t="n">
-        <v>72.2773</v>
+        <v>71.9003</v>
       </c>
       <c r="E60" t="n">
-        <v>20.4666</v>
+        <v>19.4897</v>
       </c>
       <c r="F60" t="n">
-        <v>36.2315</v>
+        <v>35.1206</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>23.4584</v>
+        <v>23.4048</v>
       </c>
       <c r="C61" t="n">
-        <v>27.1795</v>
+        <v>27.0746</v>
       </c>
       <c r="D61" t="n">
-        <v>71.5226</v>
+        <v>71.22369999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>20.0184</v>
+        <v>19.19</v>
       </c>
       <c r="F61" t="n">
-        <v>35.9315</v>
+        <v>34.838</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>22.9751</v>
+        <v>22.9612</v>
       </c>
       <c r="C62" t="n">
-        <v>26.6853</v>
+        <v>26.6168</v>
       </c>
       <c r="D62" t="n">
-        <v>70.8967</v>
+        <v>70.6118</v>
       </c>
       <c r="E62" t="n">
-        <v>19.7551</v>
+        <v>18.752</v>
       </c>
       <c r="F62" t="n">
-        <v>35.675</v>
+        <v>34.5902</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>23.1218</v>
+        <v>23.0186</v>
       </c>
       <c r="C63" t="n">
-        <v>26.263</v>
+        <v>26.3308</v>
       </c>
       <c r="D63" t="n">
-        <v>70.55110000000001</v>
+        <v>70.2242</v>
       </c>
       <c r="E63" t="n">
-        <v>19.4929</v>
+        <v>31.7219</v>
       </c>
       <c r="F63" t="n">
-        <v>35.4692</v>
+        <v>43.9794</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>22.1544</v>
+        <v>22.5051</v>
       </c>
       <c r="C64" t="n">
-        <v>26.3165</v>
+        <v>25.9958</v>
       </c>
       <c r="D64" t="n">
-        <v>91.4855</v>
+        <v>90.8272</v>
       </c>
       <c r="E64" t="n">
-        <v>31.936</v>
+        <v>31.2298</v>
       </c>
       <c r="F64" t="n">
-        <v>45.3915</v>
+        <v>43.3655</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>22.1325</v>
+        <v>23.0156</v>
       </c>
       <c r="C65" t="n">
-        <v>34.754</v>
+        <v>34.9404</v>
       </c>
       <c r="D65" t="n">
-        <v>89.2591</v>
+        <v>88.8725</v>
       </c>
       <c r="E65" t="n">
-        <v>30.9138</v>
+        <v>30.3723</v>
       </c>
       <c r="F65" t="n">
-        <v>44.8533</v>
+        <v>42.9603</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.1032</v>
+        <v>22.6076</v>
       </c>
       <c r="C66" t="n">
-        <v>34.3216</v>
+        <v>34.3451</v>
       </c>
       <c r="D66" t="n">
-        <v>87.45950000000001</v>
+        <v>87.0121</v>
       </c>
       <c r="E66" t="n">
-        <v>29.547</v>
+        <v>29.1401</v>
       </c>
       <c r="F66" t="n">
-        <v>44.1457</v>
+        <v>42.2819</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>36.4698</v>
+        <v>37.4108</v>
       </c>
       <c r="C67" t="n">
-        <v>33.8541</v>
+        <v>33.9062</v>
       </c>
       <c r="D67" t="n">
-        <v>85.79940000000001</v>
+        <v>85.384</v>
       </c>
       <c r="E67" t="n">
-        <v>28.7678</v>
+        <v>28.8194</v>
       </c>
       <c r="F67" t="n">
-        <v>43.5876</v>
+        <v>41.8155</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>37.0079</v>
+        <v>36.2919</v>
       </c>
       <c r="C68" t="n">
-        <v>33.4547</v>
+        <v>33.4662</v>
       </c>
       <c r="D68" t="n">
-        <v>84.2766</v>
+        <v>83.8781</v>
       </c>
       <c r="E68" t="n">
-        <v>28.1711</v>
+        <v>27.8191</v>
       </c>
       <c r="F68" t="n">
-        <v>43.0127</v>
+        <v>41.1934</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>35.179</v>
+        <v>37.8271</v>
       </c>
       <c r="C69" t="n">
-        <v>33.3975</v>
+        <v>33.3015</v>
       </c>
       <c r="D69" t="n">
-        <v>82.9392</v>
+        <v>82.392</v>
       </c>
       <c r="E69" t="n">
-        <v>27.5301</v>
+        <v>27.7326</v>
       </c>
       <c r="F69" t="n">
-        <v>42.5772</v>
+        <v>40.6948</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>34.4599</v>
+        <v>34.7304</v>
       </c>
       <c r="C70" t="n">
-        <v>32.8072</v>
+        <v>32.7639</v>
       </c>
       <c r="D70" t="n">
-        <v>81.91970000000001</v>
+        <v>81.52630000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>27.5488</v>
+        <v>26.7104</v>
       </c>
       <c r="F70" t="n">
-        <v>41.7496</v>
+        <v>40.3807</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>34.722</v>
+        <v>34.099</v>
       </c>
       <c r="C71" t="n">
-        <v>32.4341</v>
+        <v>32.4923</v>
       </c>
       <c r="D71" t="n">
-        <v>81.16630000000001</v>
+        <v>80.8199</v>
       </c>
       <c r="E71" t="n">
-        <v>26.482</v>
+        <v>26.4138</v>
       </c>
       <c r="F71" t="n">
-        <v>41.3247</v>
+        <v>39.8999</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>34.0358</v>
+        <v>36.4175</v>
       </c>
       <c r="C72" t="n">
-        <v>32.1005</v>
+        <v>32.3119</v>
       </c>
       <c r="D72" t="n">
-        <v>80.5573</v>
+        <v>80.1435</v>
       </c>
       <c r="E72" t="n">
-        <v>25.9255</v>
+        <v>25.3713</v>
       </c>
       <c r="F72" t="n">
-        <v>40.9606</v>
+        <v>39.6491</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>33.3916</v>
+        <v>32.9852</v>
       </c>
       <c r="C73" t="n">
-        <v>31.8801</v>
+        <v>31.895</v>
       </c>
       <c r="D73" t="n">
-        <v>80.03360000000001</v>
+        <v>79.60509999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>25.7254</v>
+        <v>25.0262</v>
       </c>
       <c r="F73" t="n">
-        <v>40.6315</v>
+        <v>39.2079</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>32.9668</v>
+        <v>35.0902</v>
       </c>
       <c r="C74" t="n">
-        <v>31.7206</v>
+        <v>31.6558</v>
       </c>
       <c r="D74" t="n">
-        <v>79.62179999999999</v>
+        <v>79.1484</v>
       </c>
       <c r="E74" t="n">
-        <v>24.805</v>
+        <v>24.6526</v>
       </c>
       <c r="F74" t="n">
-        <v>40.2889</v>
+        <v>39.0657</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>32.2183</v>
+        <v>31.9627</v>
       </c>
       <c r="C75" t="n">
-        <v>31.064</v>
+        <v>31.2258</v>
       </c>
       <c r="D75" t="n">
-        <v>78.93899999999999</v>
+        <v>78.77889999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>24.8828</v>
+        <v>24.5011</v>
       </c>
       <c r="F75" t="n">
-        <v>39.985</v>
+        <v>38.9362</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>31.5116</v>
+        <v>33.9191</v>
       </c>
       <c r="C76" t="n">
-        <v>30.6883</v>
+        <v>31.0312</v>
       </c>
       <c r="D76" t="n">
-        <v>78.88079999999999</v>
+        <v>79.0453</v>
       </c>
       <c r="E76" t="n">
-        <v>23.8089</v>
+        <v>23.7017</v>
       </c>
       <c r="F76" t="n">
-        <v>39.7732</v>
+        <v>38.687</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>31.1928</v>
+        <v>29.5423</v>
       </c>
       <c r="C77" t="n">
-        <v>30.4735</v>
+        <v>30.6231</v>
       </c>
       <c r="D77" t="n">
-        <v>79.1665</v>
+        <v>79.3554</v>
       </c>
       <c r="E77" t="n">
-        <v>23.9907</v>
+        <v>41.9705</v>
       </c>
       <c r="F77" t="n">
-        <v>39.6357</v>
+        <v>62.3423</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>29.4839</v>
+        <v>32.9178</v>
       </c>
       <c r="C78" t="n">
-        <v>30.1972</v>
+        <v>30.3219</v>
       </c>
       <c r="D78" t="n">
-        <v>128.814</v>
+        <v>129.123</v>
       </c>
       <c r="E78" t="n">
-        <v>40.3686</v>
+        <v>41.5719</v>
       </c>
       <c r="F78" t="n">
-        <v>63.5841</v>
+        <v>61.4242</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>34.2609</v>
+        <v>34.0805</v>
       </c>
       <c r="C79" t="n">
-        <v>39.8484</v>
+        <v>40.252</v>
       </c>
       <c r="D79" t="n">
-        <v>126.468</v>
+        <v>125.879</v>
       </c>
       <c r="E79" t="n">
-        <v>39.6184</v>
+        <v>40.2922</v>
       </c>
       <c r="F79" t="n">
-        <v>64.2955</v>
+        <v>61.4122</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>32.6836</v>
+        <v>33.4409</v>
       </c>
       <c r="C80" t="n">
-        <v>40.535</v>
+        <v>40.8401</v>
       </c>
       <c r="D80" t="n">
-        <v>124.603</v>
+        <v>123.901</v>
       </c>
       <c r="E80" t="n">
-        <v>39.1095</v>
+        <v>39.6639</v>
       </c>
       <c r="F80" t="n">
-        <v>63.8507</v>
+        <v>60.8866</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>48.3478</v>
+        <v>44.8217</v>
       </c>
       <c r="C81" t="n">
-        <v>40.8732</v>
+        <v>41.2898</v>
       </c>
       <c r="D81" t="n">
-        <v>122.983</v>
+        <v>122.529</v>
       </c>
       <c r="E81" t="n">
-        <v>38.3664</v>
+        <v>38.6681</v>
       </c>
       <c r="F81" t="n">
-        <v>63.5237</v>
+        <v>60.0525</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>46.8358</v>
+        <v>42.8286</v>
       </c>
       <c r="C82" t="n">
-        <v>41.1338</v>
+        <v>41.3743</v>
       </c>
       <c r="D82" t="n">
-        <v>121.628</v>
+        <v>120.881</v>
       </c>
       <c r="E82" t="n">
-        <v>37.516</v>
+        <v>37.8956</v>
       </c>
       <c r="F82" t="n">
-        <v>62.8937</v>
+        <v>59.4107</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>45.2262</v>
+        <v>43.7916</v>
       </c>
       <c r="C83" t="n">
-        <v>41.3886</v>
+        <v>41.5661</v>
       </c>
       <c r="D83" t="n">
-        <v>120.6</v>
+        <v>120.136</v>
       </c>
       <c r="E83" t="n">
-        <v>36.8902</v>
+        <v>36.9006</v>
       </c>
       <c r="F83" t="n">
-        <v>61.8337</v>
+        <v>59.2752</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>44.9942</v>
+        <v>44.9807</v>
       </c>
       <c r="C84" t="n">
-        <v>41.5381</v>
+        <v>41.9589</v>
       </c>
       <c r="D84" t="n">
-        <v>120.742</v>
+        <v>120.025</v>
       </c>
       <c r="E84" t="n">
-        <v>36.1053</v>
+        <v>36.3737</v>
       </c>
       <c r="F84" t="n">
-        <v>60.0641</v>
+        <v>58.9076</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>44.77</v>
+        <v>42.0856</v>
       </c>
       <c r="C85" t="n">
-        <v>41.8713</v>
+        <v>41.7316</v>
       </c>
       <c r="D85" t="n">
-        <v>121.162</v>
+        <v>119.872</v>
       </c>
       <c r="E85" t="n">
-        <v>35.2273</v>
+        <v>35.5703</v>
       </c>
       <c r="F85" t="n">
-        <v>60.0909</v>
+        <v>57.7345</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>41.6766</v>
+        <v>38.502</v>
       </c>
       <c r="C86" t="n">
-        <v>41.9062</v>
+        <v>42.104</v>
       </c>
       <c r="D86" t="n">
-        <v>120.57</v>
+        <v>119.75</v>
       </c>
       <c r="E86" t="n">
-        <v>34.5114</v>
+        <v>34.6939</v>
       </c>
       <c r="F86" t="n">
-        <v>59.038</v>
+        <v>56.8339</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>39.1166</v>
+        <v>41.8345</v>
       </c>
       <c r="C87" t="n">
-        <v>41.9876</v>
+        <v>41.8607</v>
       </c>
       <c r="D87" t="n">
-        <v>120.675</v>
+        <v>120.113</v>
       </c>
       <c r="E87" t="n">
-        <v>33.7832</v>
+        <v>33.6985</v>
       </c>
       <c r="F87" t="n">
-        <v>58.0135</v>
+        <v>55.9765</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>42.0015</v>
+        <v>38.8702</v>
       </c>
       <c r="C88" t="n">
-        <v>41.8339</v>
+        <v>41.9676</v>
       </c>
       <c r="D88" t="n">
-        <v>121.216</v>
+        <v>120.488</v>
       </c>
       <c r="E88" t="n">
-        <v>33.0335</v>
+        <v>33.3002</v>
       </c>
       <c r="F88" t="n">
-        <v>57.4024</v>
+        <v>55.292</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>39.7907</v>
+        <v>41.3861</v>
       </c>
       <c r="C89" t="n">
-        <v>41.7207</v>
+        <v>41.9045</v>
       </c>
       <c r="D89" t="n">
-        <v>121.381</v>
+        <v>120.932</v>
       </c>
       <c r="E89" t="n">
-        <v>32.4134</v>
+        <v>32.9354</v>
       </c>
       <c r="F89" t="n">
-        <v>57.7695</v>
+        <v>54.7905</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>37.9189</v>
+        <v>40.8192</v>
       </c>
       <c r="C90" t="n">
-        <v>41.5275</v>
+        <v>41.4717</v>
       </c>
       <c r="D90" t="n">
-        <v>122.348</v>
+        <v>122.763</v>
       </c>
       <c r="E90" t="n">
-        <v>31.8428</v>
+        <v>32.2466</v>
       </c>
       <c r="F90" t="n">
-        <v>56.9211</v>
+        <v>54.5857</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>40.6505</v>
+        <v>40.984</v>
       </c>
       <c r="C91" t="n">
-        <v>41.3111</v>
+        <v>41.5944</v>
       </c>
       <c r="D91" t="n">
-        <v>124.039</v>
+        <v>124.023</v>
       </c>
       <c r="E91" t="n">
-        <v>31.3829</v>
+        <v>67.928</v>
       </c>
       <c r="F91" t="n">
-        <v>55.4069</v>
+        <v>85.9663</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>38.011</v>
+        <v>41.1833</v>
       </c>
       <c r="C92" t="n">
-        <v>41.2527</v>
+        <v>41.5829</v>
       </c>
       <c r="D92" t="n">
-        <v>185.717</v>
+        <v>186.394</v>
       </c>
       <c r="E92" t="n">
-        <v>65.2715</v>
+        <v>66.5341</v>
       </c>
       <c r="F92" t="n">
-        <v>85.2281</v>
+        <v>84.819</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>36.6594</v>
+        <v>41.6383</v>
       </c>
       <c r="C93" t="n">
-        <v>41.2285</v>
+        <v>41.6005</v>
       </c>
       <c r="D93" t="n">
-        <v>184.515</v>
+        <v>185.799</v>
       </c>
       <c r="E93" t="n">
-        <v>63.6378</v>
+        <v>64.7487</v>
       </c>
       <c r="F93" t="n">
-        <v>86.0943</v>
+        <v>84.1738</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>40.7076</v>
+        <v>34.219</v>
       </c>
       <c r="C94" t="n">
-        <v>73.533</v>
+        <v>75.4769</v>
       </c>
       <c r="D94" t="n">
-        <v>182.952</v>
+        <v>184.953</v>
       </c>
       <c r="E94" t="n">
-        <v>61.9542</v>
+        <v>62.6936</v>
       </c>
       <c r="F94" t="n">
-        <v>85.3837</v>
+        <v>82.8603</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>73.6237</v>
+        <v>72.866</v>
       </c>
       <c r="C95" t="n">
-        <v>73.0615</v>
+        <v>74.7123</v>
       </c>
       <c r="D95" t="n">
-        <v>181.364</v>
+        <v>183.86</v>
       </c>
       <c r="E95" t="n">
-        <v>59.9302</v>
+        <v>60.7597</v>
       </c>
       <c r="F95" t="n">
-        <v>84.9996</v>
+        <v>83.3569</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>67.6176</v>
+        <v>69.44670000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>72.3409</v>
+        <v>73.91849999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>180.409</v>
+        <v>182.536</v>
       </c>
       <c r="E96" t="n">
-        <v>58.8862</v>
+        <v>59.0053</v>
       </c>
       <c r="F96" t="n">
-        <v>83.9057</v>
+        <v>80.95059999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>67.80200000000001</v>
+        <v>69.2731</v>
       </c>
       <c r="C97" t="n">
-        <v>72.1772</v>
+        <v>73.19759999999999</v>
       </c>
       <c r="D97" t="n">
-        <v>180</v>
+        <v>181.105</v>
       </c>
       <c r="E97" t="n">
-        <v>57.0801</v>
+        <v>57.5207</v>
       </c>
       <c r="F97" t="n">
-        <v>81.7034</v>
+        <v>80.351</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>67.0424</v>
+        <v>69.976</v>
       </c>
       <c r="C98" t="n">
-        <v>71.2993</v>
+        <v>72.47499999999999</v>
       </c>
       <c r="D98" t="n">
-        <v>179.594</v>
+        <v>180.85</v>
       </c>
       <c r="E98" t="n">
-        <v>55.6077</v>
+        <v>56.0997</v>
       </c>
       <c r="F98" t="n">
-        <v>80.8177</v>
+        <v>80.2056</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>63.2216</v>
+        <v>64.3417</v>
       </c>
       <c r="C99" t="n">
-        <v>70.7264</v>
+        <v>71.6429</v>
       </c>
       <c r="D99" t="n">
-        <v>179.586</v>
+        <v>181.257</v>
       </c>
       <c r="E99" t="n">
-        <v>54.1097</v>
+        <v>54.4038</v>
       </c>
       <c r="F99" t="n">
-        <v>81.9952</v>
+        <v>79.5527</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>63.3389</v>
+        <v>62.0707</v>
       </c>
       <c r="C100" t="n">
-        <v>70.10899999999999</v>
+        <v>70.8708</v>
       </c>
       <c r="D100" t="n">
-        <v>180.106</v>
+        <v>181.299</v>
       </c>
       <c r="E100" t="n">
-        <v>52.6124</v>
+        <v>53.1706</v>
       </c>
       <c r="F100" t="n">
-        <v>81.0117</v>
+        <v>81.8839</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>59.7006</v>
+        <v>62.7747</v>
       </c>
       <c r="C101" t="n">
-        <v>69.408</v>
+        <v>70.087</v>
       </c>
       <c r="D101" t="n">
-        <v>180.407</v>
+        <v>181.772</v>
       </c>
       <c r="E101" t="n">
-        <v>51.3098</v>
+        <v>51.7033</v>
       </c>
       <c r="F101" t="n">
-        <v>81.1948</v>
+        <v>79.3665</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>58.9043</v>
+        <v>62.5259</v>
       </c>
       <c r="C102" t="n">
-        <v>68.717</v>
+        <v>69.38679999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>181.01</v>
+        <v>181.971</v>
       </c>
       <c r="E102" t="n">
-        <v>50.2607</v>
+        <v>50.3624</v>
       </c>
       <c r="F102" t="n">
-        <v>78.70650000000001</v>
+        <v>77.1765</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>59.5873</v>
+        <v>61.0102</v>
       </c>
       <c r="C103" t="n">
-        <v>68.1434</v>
+        <v>68.7424</v>
       </c>
       <c r="D103" t="n">
-        <v>182.09</v>
+        <v>183.663</v>
       </c>
       <c r="E103" t="n">
-        <v>49.017</v>
+        <v>49.059</v>
       </c>
       <c r="F103" t="n">
-        <v>82.0545</v>
+        <v>78.5299</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>56.834</v>
+        <v>60.1298</v>
       </c>
       <c r="C104" t="n">
-        <v>67.3267</v>
+        <v>68.0574</v>
       </c>
       <c r="D104" t="n">
-        <v>183.466</v>
+        <v>184.703</v>
       </c>
       <c r="E104" t="n">
-        <v>47.8642</v>
+        <v>48.1792</v>
       </c>
       <c r="F104" t="n">
-        <v>78.4881</v>
+        <v>77.4246</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>57.4125</v>
+        <v>56.3739</v>
       </c>
       <c r="C105" t="n">
-        <v>66.9229</v>
+        <v>67.4532</v>
       </c>
       <c r="D105" t="n">
-        <v>184.841</v>
+        <v>186.325</v>
       </c>
       <c r="E105" t="n">
-        <v>46.9294</v>
+        <v>85.6871</v>
       </c>
       <c r="F105" t="n">
-        <v>76.7075</v>
+        <v>236.685</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>56.5851</v>
+        <v>57.981</v>
       </c>
       <c r="C106" t="n">
-        <v>66.4303</v>
+        <v>66.7907</v>
       </c>
       <c r="D106" t="n">
-        <v>186.523</v>
+        <v>187.562</v>
       </c>
       <c r="E106" t="n">
-        <v>46.175</v>
+        <v>83.9123</v>
       </c>
       <c r="F106" t="n">
-        <v>86.96339999999999</v>
+        <v>237.704</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>55.142</v>
+        <v>56.0794</v>
       </c>
       <c r="C107" t="n">
-        <v>65.7983</v>
+        <v>66.1812</v>
       </c>
       <c r="D107" t="n">
-        <v>251.087</v>
+        <v>252.624</v>
       </c>
       <c r="E107" t="n">
-        <v>69.56319999999999</v>
+        <v>81.7569</v>
       </c>
       <c r="F107" t="n">
-        <v>237.785</v>
+        <v>238.538</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>55.3258</v>
+        <v>56.1123</v>
       </c>
       <c r="C108" t="n">
-        <v>100.269</v>
+        <v>101.436</v>
       </c>
       <c r="D108" t="n">
-        <v>248.121</v>
+        <v>249.584</v>
       </c>
       <c r="E108" t="n">
-        <v>78.8609</v>
+        <v>78.94929999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>237.423</v>
+        <v>238.078</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>53.1257</v>
+        <v>55.1196</v>
       </c>
       <c r="C109" t="n">
-        <v>98.7769</v>
+        <v>99.8652</v>
       </c>
       <c r="D109" t="n">
-        <v>245.35</v>
+        <v>247.031</v>
       </c>
       <c r="E109" t="n">
-        <v>66.2826</v>
+        <v>76.7821</v>
       </c>
       <c r="F109" t="n">
-        <v>237.35</v>
+        <v>237.974</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>87.2603</v>
+        <v>77.64619999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>97.90940000000001</v>
+        <v>84.9152</v>
       </c>
       <c r="D110" t="n">
-        <v>243.735</v>
+        <v>245.353</v>
       </c>
       <c r="E110" t="n">
-        <v>74.3926</v>
+        <v>74.7197</v>
       </c>
       <c r="F110" t="n">
-        <v>237.991</v>
+        <v>239.894</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>75.2928</v>
+        <v>85.1588</v>
       </c>
       <c r="C111" t="n">
-        <v>84.33669999999999</v>
+        <v>97.3349</v>
       </c>
       <c r="D111" t="n">
-        <v>241.793</v>
+        <v>244.175</v>
       </c>
       <c r="E111" t="n">
-        <v>72.7058</v>
+        <v>63.0004</v>
       </c>
       <c r="F111" t="n">
-        <v>238.008</v>
+        <v>239.113</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>82.29300000000001</v>
+        <v>82.4337</v>
       </c>
       <c r="C112" t="n">
-        <v>94.9402</v>
+        <v>95.9332</v>
       </c>
       <c r="D112" t="n">
-        <v>240.832</v>
+        <v>242.144</v>
       </c>
       <c r="E112" t="n">
-        <v>61.4246</v>
+        <v>61.8236</v>
       </c>
       <c r="F112" t="n">
-        <v>239.306</v>
+        <v>238.869</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>80.5337</v>
+        <v>73.6866</v>
       </c>
       <c r="C113" t="n">
-        <v>93.5341</v>
+        <v>82.3935</v>
       </c>
       <c r="D113" t="n">
-        <v>242.176</v>
+        <v>241.011</v>
       </c>
       <c r="E113" t="n">
-        <v>60.4173</v>
+        <v>60.1557</v>
       </c>
       <c r="F113" t="n">
-        <v>239.268</v>
+        <v>239.742</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>78.73269999999999</v>
+        <v>72.02209999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>92.2829</v>
+        <v>81.616</v>
       </c>
       <c r="D114" t="n">
-        <v>250.382</v>
+        <v>254.624</v>
       </c>
       <c r="E114" t="n">
-        <v>66.91630000000001</v>
+        <v>67.1538</v>
       </c>
       <c r="F114" t="n">
-        <v>240.937</v>
+        <v>240.114</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>75.1641</v>
+        <v>76.5776</v>
       </c>
       <c r="C115" t="n">
-        <v>91.02979999999999</v>
+        <v>91.90009999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>250.128</v>
+        <v>251.583</v>
       </c>
       <c r="E115" t="n">
-        <v>65.3329</v>
+        <v>65.5467</v>
       </c>
       <c r="F115" t="n">
-        <v>240.763</v>
+        <v>240.775</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>68.7273</v>
+        <v>73.9104</v>
       </c>
       <c r="C116" t="n">
-        <v>80.36579999999999</v>
+        <v>90.7105</v>
       </c>
       <c r="D116" t="n">
-        <v>252.362</v>
+        <v>251.817</v>
       </c>
       <c r="E116" t="n">
-        <v>63.7444</v>
+        <v>63.8379</v>
       </c>
       <c r="F116" t="n">
-        <v>241.339</v>
+        <v>241.468</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>73.279</v>
+        <v>66.8394</v>
       </c>
       <c r="C117" t="n">
-        <v>88.7958</v>
+        <v>79.3797</v>
       </c>
       <c r="D117" t="n">
-        <v>247.963</v>
+        <v>255.51</v>
       </c>
       <c r="E117" t="n">
-        <v>62.3847</v>
+        <v>62.455</v>
       </c>
       <c r="F117" t="n">
-        <v>241.95</v>
+        <v>241.543</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>66.8232</v>
+        <v>71.42870000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>79.0478</v>
+        <v>88.3434</v>
       </c>
       <c r="D118" t="n">
-        <v>239.188</v>
+        <v>240.336</v>
       </c>
       <c r="E118" t="n">
-        <v>54.6128</v>
+        <v>54.3892</v>
       </c>
       <c r="F118" t="n">
-        <v>242.673</v>
+        <v>241.238</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>65.7561</v>
+        <v>65.0505</v>
       </c>
       <c r="C119" t="n">
-        <v>78.4087</v>
+        <v>78.32250000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>240.45</v>
+        <v>241.253</v>
       </c>
       <c r="E119" t="n">
-        <v>53.3619</v>
+        <v>92.68899999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>150.482</v>
+        <v>289.133</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>68.1066</v>
+        <v>67.91119999999999</v>
       </c>
       <c r="C120" t="n">
-        <v>85.80759999999999</v>
+        <v>86.2961</v>
       </c>
       <c r="D120" t="n">
-        <v>241.854</v>
+        <v>242.431</v>
       </c>
       <c r="E120" t="n">
-        <v>52.6106</v>
+        <v>90.75839999999999</v>
       </c>
       <c r="F120" t="n">
-        <v>100.419</v>
+        <v>288.154</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>67.1551</v>
+        <v>61.1314</v>
       </c>
       <c r="C121" t="n">
-        <v>84.87179999999999</v>
+        <v>77.35299999999999</v>
       </c>
       <c r="D121" t="n">
-        <v>318.497</v>
+        <v>319.786</v>
       </c>
       <c r="E121" t="n">
-        <v>93.03440000000001</v>
+        <v>88.5214</v>
       </c>
       <c r="F121" t="n">
-        <v>290.14</v>
+        <v>288.543</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>64.7551</v>
+        <v>62.3229</v>
       </c>
       <c r="C122" t="n">
-        <v>118.907</v>
+        <v>112.501</v>
       </c>
       <c r="D122" t="n">
-        <v>313.302</v>
+        <v>314.935</v>
       </c>
       <c r="E122" t="n">
-        <v>85.77670000000001</v>
+        <v>86.803</v>
       </c>
       <c r="F122" t="n">
-        <v>288.743</v>
+        <v>288.59</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>60.2542</v>
+        <v>59.5972</v>
       </c>
       <c r="C123" t="n">
-        <v>110.793</v>
+        <v>111.34</v>
       </c>
       <c r="D123" t="n">
-        <v>309.219</v>
+        <v>310.753</v>
       </c>
       <c r="E123" t="n">
-        <v>83.92829999999999</v>
+        <v>84.7997</v>
       </c>
       <c r="F123" t="n">
-        <v>287.888</v>
+        <v>286.962</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>91.1191</v>
+        <v>94.22629999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>109.978</v>
+        <v>110.57</v>
       </c>
       <c r="D124" t="n">
-        <v>305.613</v>
+        <v>307.158</v>
       </c>
       <c r="E124" t="n">
-        <v>81.9436</v>
+        <v>82.8813</v>
       </c>
       <c r="F124" t="n">
-        <v>287.663</v>
+        <v>285.827</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>90.6254</v>
+        <v>90.56870000000001</v>
       </c>
       <c r="C125" t="n">
-        <v>108.857</v>
+        <v>109.482</v>
       </c>
       <c r="D125" t="n">
-        <v>302.26</v>
+        <v>303.602</v>
       </c>
       <c r="E125" t="n">
-        <v>85.1066</v>
+        <v>81.3441</v>
       </c>
       <c r="F125" t="n">
-        <v>286.72</v>
+        <v>286.164</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>88.71720000000001</v>
+        <v>89.8605</v>
       </c>
       <c r="C126" t="n">
-        <v>107.744</v>
+        <v>108.464</v>
       </c>
       <c r="D126" t="n">
-        <v>299.36</v>
+        <v>300.821</v>
       </c>
       <c r="E126" t="n">
-        <v>78.7993</v>
+        <v>79.6588</v>
       </c>
       <c r="F126" t="n">
-        <v>286.316</v>
+        <v>286.896</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>87.0859</v>
+        <v>88.6087</v>
       </c>
       <c r="C127" t="n">
-        <v>106.606</v>
+        <v>107.278</v>
       </c>
       <c r="D127" t="n">
-        <v>296.574</v>
+        <v>297.681</v>
       </c>
       <c r="E127" t="n">
-        <v>81.5712</v>
+        <v>78.1123</v>
       </c>
       <c r="F127" t="n">
-        <v>286.732</v>
+        <v>285.721</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>85.3952</v>
+        <v>86.2389</v>
       </c>
       <c r="C128" t="n">
-        <v>105.691</v>
+        <v>106.366</v>
       </c>
       <c r="D128" t="n">
-        <v>294.376</v>
+        <v>295.936</v>
       </c>
       <c r="E128" t="n">
-        <v>79.97620000000001</v>
+        <v>76.67619999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>284.592</v>
+        <v>284.776</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>84.8644</v>
+        <v>83.45229999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>104.556</v>
+        <v>105.216</v>
       </c>
       <c r="D129" t="n">
-        <v>292.166</v>
+        <v>293.438</v>
       </c>
       <c r="E129" t="n">
-        <v>74.4584</v>
+        <v>75.2235</v>
       </c>
       <c r="F129" t="n">
-        <v>284.98</v>
+        <v>285.536</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>86.0341</v>
+        <v>82.04940000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>108.554</v>
+        <v>104.306</v>
       </c>
       <c r="D130" t="n">
-        <v>290.704</v>
+        <v>292.524</v>
       </c>
       <c r="E130" t="n">
-        <v>73.2522</v>
+        <v>74.1563</v>
       </c>
       <c r="F130" t="n">
-        <v>284.482</v>
+        <v>285.592</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>80.88509999999999</v>
+        <v>80.4898</v>
       </c>
       <c r="C131" t="n">
-        <v>102.86</v>
+        <v>103.535</v>
       </c>
       <c r="D131" t="n">
-        <v>289.291</v>
+        <v>291.273</v>
       </c>
       <c r="E131" t="n">
-        <v>72.1613</v>
+        <v>72.7771</v>
       </c>
       <c r="F131" t="n">
-        <v>284.707</v>
+        <v>284.694</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>79.765</v>
+        <v>79.4421</v>
       </c>
       <c r="C132" t="n">
-        <v>102.09</v>
+        <v>102.734</v>
       </c>
       <c r="D132" t="n">
-        <v>288.702</v>
+        <v>290.624</v>
       </c>
       <c r="E132" t="n">
-        <v>74.2659</v>
+        <v>71.69670000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>285.275</v>
+        <v>284.825</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>77.586</v>
+        <v>70.2046</v>
       </c>
       <c r="C133" t="n">
-        <v>101.494</v>
+        <v>93.19799999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>289.173</v>
+        <v>290.463</v>
       </c>
       <c r="E133" t="n">
-        <v>69.94799999999999</v>
+        <v>70.5433</v>
       </c>
       <c r="F133" t="n">
-        <v>285.595</v>
+        <v>284.052</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>68.8494</v>
+        <v>78.2497</v>
       </c>
       <c r="C134" t="n">
-        <v>92.4164</v>
+        <v>101.132</v>
       </c>
       <c r="D134" t="n">
-        <v>284.341</v>
+        <v>285.272</v>
       </c>
       <c r="E134" t="n">
-        <v>62.9315</v>
+        <v>101.891</v>
       </c>
       <c r="F134" t="n">
-        <v>179.705</v>
+        <v>328.73</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>77.00060000000001</v>
+        <v>76.5956</v>
       </c>
       <c r="C135" t="n">
-        <v>100.035</v>
+        <v>100.541</v>
       </c>
       <c r="D135" t="n">
-        <v>365.409</v>
+        <v>366.086</v>
       </c>
       <c r="E135" t="n">
-        <v>98.7153</v>
+        <v>100.004</v>
       </c>
       <c r="F135" t="n">
-        <v>328.097</v>
+        <v>326.554</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>76.6049</v>
+        <v>74.79130000000001</v>
       </c>
       <c r="C136" t="n">
-        <v>133.312</v>
+        <v>134.721</v>
       </c>
       <c r="D136" t="n">
-        <v>358.215</v>
+        <v>359.401</v>
       </c>
       <c r="E136" t="n">
-        <v>96.6957</v>
+        <v>97.6953</v>
       </c>
       <c r="F136" t="n">
-        <v>325.916</v>
+        <v>325.614</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>73.3681</v>
+        <v>75.46429999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>132.791</v>
+        <v>133.553</v>
       </c>
       <c r="D137" t="n">
-        <v>353.344</v>
+        <v>354.04</v>
       </c>
       <c r="E137" t="n">
-        <v>94.7881</v>
+        <v>96.0778</v>
       </c>
       <c r="F137" t="n">
-        <v>327.009</v>
+        <v>325.363</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>102.041</v>
+        <v>108.468</v>
       </c>
       <c r="C138" t="n">
-        <v>125.289</v>
+        <v>133.477</v>
       </c>
       <c r="D138" t="n">
-        <v>346.878</v>
+        <v>351.06</v>
       </c>
       <c r="E138" t="n">
-        <v>97.47329999999999</v>
+        <v>94.34099999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>325.472</v>
+        <v>324.32</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>104.971</v>
+        <v>99.6923</v>
       </c>
       <c r="C139" t="n">
-        <v>130.964</v>
+        <v>125.586</v>
       </c>
       <c r="D139" t="n">
-        <v>341.749</v>
+        <v>343.79</v>
       </c>
       <c r="E139" t="n">
-        <v>95.9845</v>
+        <v>92.6555</v>
       </c>
       <c r="F139" t="n">
-        <v>324.023</v>
+        <v>323.871</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>98.31100000000001</v>
+        <v>104.091</v>
       </c>
       <c r="C140" t="n">
-        <v>123.295</v>
+        <v>130.793</v>
       </c>
       <c r="D140" t="n">
-        <v>337.165</v>
+        <v>339.502</v>
       </c>
       <c r="E140" t="n">
-        <v>94.1828</v>
+        <v>91.2345</v>
       </c>
       <c r="F140" t="n">
-        <v>324</v>
+        <v>323.237</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>101.282</v>
+        <v>95.82899999999999</v>
       </c>
       <c r="C141" t="n">
-        <v>128.686</v>
+        <v>123.845</v>
       </c>
       <c r="D141" t="n">
-        <v>334.884</v>
+        <v>335.384</v>
       </c>
       <c r="E141" t="n">
-        <v>88.5557</v>
+        <v>89.2835</v>
       </c>
       <c r="F141" t="n">
-        <v>322.203</v>
+        <v>321.456</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>95.37820000000001</v>
+        <v>100.139</v>
       </c>
       <c r="C142" t="n">
-        <v>121.591</v>
+        <v>128.492</v>
       </c>
       <c r="D142" t="n">
-        <v>335.263</v>
+        <v>336.965</v>
       </c>
       <c r="E142" t="n">
-        <v>86.9061</v>
+        <v>87.80800000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>321.24</v>
+        <v>321.21</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>93.5184</v>
+        <v>98.0027</v>
       </c>
       <c r="C143" t="n">
-        <v>121.29</v>
+        <v>127.707</v>
       </c>
       <c r="D143" t="n">
-        <v>332.984</v>
+        <v>335.109</v>
       </c>
       <c r="E143" t="n">
-        <v>89.6888</v>
+        <v>86.7916</v>
       </c>
       <c r="F143" t="n">
-        <v>322.669</v>
+        <v>319.962</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>21.9105</v>
+        <v>22.5387</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5219</v>
+        <v>24.5591</v>
       </c>
       <c r="D2" t="n">
-        <v>55.9237</v>
+        <v>55.4721</v>
       </c>
       <c r="E2" t="n">
-        <v>17.0565</v>
+        <v>17.1046</v>
       </c>
       <c r="F2" t="n">
-        <v>32.1128</v>
+        <v>32.0676</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>21.2342</v>
+        <v>21.3771</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0553</v>
+        <v>24.0398</v>
       </c>
       <c r="D3" t="n">
-        <v>55.1773</v>
+        <v>54.8547</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5941</v>
+        <v>16.6129</v>
       </c>
       <c r="F3" t="n">
-        <v>31.7381</v>
+        <v>31.7175</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>20.7982</v>
+        <v>20.9021</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5449</v>
+        <v>23.5595</v>
       </c>
       <c r="D4" t="n">
-        <v>54.6942</v>
+        <v>54.4826</v>
       </c>
       <c r="E4" t="n">
-        <v>16.168</v>
+        <v>16.1996</v>
       </c>
       <c r="F4" t="n">
-        <v>31.4624</v>
+        <v>31.4174</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>19.9265</v>
+        <v>20.3805</v>
       </c>
       <c r="C5" t="n">
-        <v>23.1807</v>
+        <v>23.1284</v>
       </c>
       <c r="D5" t="n">
-        <v>54.3467</v>
+        <v>53.9579</v>
       </c>
       <c r="E5" t="n">
-        <v>25.096</v>
+        <v>25.1297</v>
       </c>
       <c r="F5" t="n">
-        <v>39.5999</v>
+        <v>39.7381</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>20.0829</v>
+        <v>20.5678</v>
       </c>
       <c r="C6" t="n">
-        <v>22.7062</v>
+        <v>22.7866</v>
       </c>
       <c r="D6" t="n">
-        <v>53.948</v>
+        <v>53.579</v>
       </c>
       <c r="E6" t="n">
-        <v>24.1716</v>
+        <v>24.3826</v>
       </c>
       <c r="F6" t="n">
-        <v>38.7905</v>
+        <v>38.9602</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>19.4345</v>
+        <v>19.3896</v>
       </c>
       <c r="C7" t="n">
-        <v>22.4316</v>
+        <v>22.4292</v>
       </c>
       <c r="D7" t="n">
-        <v>68.4618</v>
+        <v>68.3098</v>
       </c>
       <c r="E7" t="n">
-        <v>23.3996</v>
+        <v>23.5186</v>
       </c>
       <c r="F7" t="n">
-        <v>38.0194</v>
+        <v>38.0899</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>19.4033</v>
+        <v>19.5211</v>
       </c>
       <c r="C8" t="n">
-        <v>31.5294</v>
+        <v>30.8264</v>
       </c>
       <c r="D8" t="n">
-        <v>66.98009999999999</v>
+        <v>66.6001</v>
       </c>
       <c r="E8" t="n">
-        <v>22.6148</v>
+        <v>22.7737</v>
       </c>
       <c r="F8" t="n">
-        <v>37.2488</v>
+        <v>37.2968</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>19.6896</v>
+        <v>19.0514</v>
       </c>
       <c r="C9" t="n">
-        <v>30.6587</v>
+        <v>30.0906</v>
       </c>
       <c r="D9" t="n">
-        <v>65.68170000000001</v>
+        <v>65.431</v>
       </c>
       <c r="E9" t="n">
-        <v>21.8697</v>
+        <v>22.046</v>
       </c>
       <c r="F9" t="n">
-        <v>36.5107</v>
+        <v>36.5467</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.8594</v>
+        <v>27.9265</v>
       </c>
       <c r="C10" t="n">
-        <v>29.1996</v>
+        <v>29.3745</v>
       </c>
       <c r="D10" t="n">
-        <v>64.5742</v>
+        <v>64.24550000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>21.204</v>
+        <v>21.3656</v>
       </c>
       <c r="F10" t="n">
-        <v>35.788</v>
+        <v>35.8343</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>26.9779</v>
+        <v>26.9056</v>
       </c>
       <c r="C11" t="n">
-        <v>28.5097</v>
+        <v>28.534</v>
       </c>
       <c r="D11" t="n">
-        <v>63.4117</v>
+        <v>63.1352</v>
       </c>
       <c r="E11" t="n">
-        <v>20.4683</v>
+        <v>20.6836</v>
       </c>
       <c r="F11" t="n">
-        <v>35.1107</v>
+        <v>35.1731</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.0197</v>
+        <v>26.854</v>
       </c>
       <c r="C12" t="n">
-        <v>28.3016</v>
+        <v>27.8222</v>
       </c>
       <c r="D12" t="n">
-        <v>62.2683</v>
+        <v>62.163</v>
       </c>
       <c r="E12" t="n">
-        <v>19.7614</v>
+        <v>19.9267</v>
       </c>
       <c r="F12" t="n">
-        <v>34.5452</v>
+        <v>34.5221</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.0883</v>
+        <v>24.9368</v>
       </c>
       <c r="C13" t="n">
-        <v>27.055</v>
+        <v>27.178</v>
       </c>
       <c r="D13" t="n">
-        <v>61.4417</v>
+        <v>61.19</v>
       </c>
       <c r="E13" t="n">
-        <v>19.2964</v>
+        <v>19.3506</v>
       </c>
       <c r="F13" t="n">
-        <v>34.0011</v>
+        <v>33.9633</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>24.5493</v>
+        <v>24.5575</v>
       </c>
       <c r="C14" t="n">
-        <v>26.4282</v>
+        <v>26.5243</v>
       </c>
       <c r="D14" t="n">
-        <v>60.7289</v>
+        <v>60.3995</v>
       </c>
       <c r="E14" t="n">
-        <v>18.5986</v>
+        <v>18.8538</v>
       </c>
       <c r="F14" t="n">
-        <v>33.4318</v>
+        <v>33.441</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>23.8847</v>
+        <v>23.8629</v>
       </c>
       <c r="C15" t="n">
-        <v>26.3005</v>
+        <v>25.9347</v>
       </c>
       <c r="D15" t="n">
-        <v>60.2337</v>
+        <v>59.7481</v>
       </c>
       <c r="E15" t="n">
-        <v>18.068</v>
+        <v>18.3613</v>
       </c>
       <c r="F15" t="n">
-        <v>32.9538</v>
+        <v>32.9651</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>23.3828</v>
+        <v>23.4568</v>
       </c>
       <c r="C16" t="n">
-        <v>25.2851</v>
+        <v>25.3534</v>
       </c>
       <c r="D16" t="n">
-        <v>59.5531</v>
+        <v>59.2364</v>
       </c>
       <c r="E16" t="n">
-        <v>17.5568</v>
+        <v>17.7401</v>
       </c>
       <c r="F16" t="n">
-        <v>32.5676</v>
+        <v>32.5254</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>22.3633</v>
+        <v>23.0096</v>
       </c>
       <c r="C17" t="n">
-        <v>25.0992</v>
+        <v>24.774</v>
       </c>
       <c r="D17" t="n">
-        <v>59.1305</v>
+        <v>58.7471</v>
       </c>
       <c r="E17" t="n">
-        <v>17.1261</v>
+        <v>17.2899</v>
       </c>
       <c r="F17" t="n">
-        <v>32.203</v>
+        <v>32.1244</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>21.9419</v>
+        <v>22.5776</v>
       </c>
       <c r="C18" t="n">
-        <v>24.5227</v>
+        <v>24.276</v>
       </c>
       <c r="D18" t="n">
-        <v>58.257</v>
+        <v>58.1175</v>
       </c>
       <c r="E18" t="n">
-        <v>16.7594</v>
+        <v>16.9024</v>
       </c>
       <c r="F18" t="n">
-        <v>31.8593</v>
+        <v>31.881</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>21.3728</v>
+        <v>21.7385</v>
       </c>
       <c r="C19" t="n">
-        <v>24.0967</v>
+        <v>23.8481</v>
       </c>
       <c r="D19" t="n">
-        <v>57.667</v>
+        <v>57.3397</v>
       </c>
       <c r="E19" t="n">
-        <v>16.3711</v>
+        <v>16.5065</v>
       </c>
       <c r="F19" t="n">
-        <v>31.6078</v>
+        <v>31.5441</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>20.6651</v>
+        <v>21.0152</v>
       </c>
       <c r="C20" t="n">
-        <v>23.6405</v>
+        <v>23.4393</v>
       </c>
       <c r="D20" t="n">
-        <v>57.3166</v>
+        <v>57.0453</v>
       </c>
       <c r="E20" t="n">
-        <v>25.0043</v>
+        <v>25.0738</v>
       </c>
       <c r="F20" t="n">
-        <v>39.412</v>
+        <v>39.6207</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>20.685</v>
+        <v>21.2423</v>
       </c>
       <c r="C21" t="n">
-        <v>23.105</v>
+        <v>23.1594</v>
       </c>
       <c r="D21" t="n">
-        <v>74.4487</v>
+        <v>74.90300000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>24.0509</v>
+        <v>24.1732</v>
       </c>
       <c r="F21" t="n">
-        <v>38.562</v>
+        <v>38.8042</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>20.1458</v>
+        <v>20.5625</v>
       </c>
       <c r="C22" t="n">
-        <v>31.4272</v>
+        <v>31.6194</v>
       </c>
       <c r="D22" t="n">
-        <v>72.8686</v>
+        <v>73.1533</v>
       </c>
       <c r="E22" t="n">
-        <v>23.3085</v>
+        <v>23.4936</v>
       </c>
       <c r="F22" t="n">
-        <v>37.7781</v>
+        <v>38.016</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>19.9923</v>
+        <v>20.2889</v>
       </c>
       <c r="C23" t="n">
-        <v>30.6513</v>
+        <v>30.8454</v>
       </c>
       <c r="D23" t="n">
-        <v>71.5076</v>
+        <v>71.66800000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>22.5054</v>
+        <v>22.6841</v>
       </c>
       <c r="F23" t="n">
-        <v>37.0593</v>
+        <v>37.2619</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>28.7803</v>
+        <v>28.4375</v>
       </c>
       <c r="C24" t="n">
-        <v>29.9426</v>
+        <v>30.0143</v>
       </c>
       <c r="D24" t="n">
-        <v>70.15770000000001</v>
+        <v>70.3143</v>
       </c>
       <c r="E24" t="n">
-        <v>21.8191</v>
+        <v>21.9333</v>
       </c>
       <c r="F24" t="n">
-        <v>36.3416</v>
+        <v>36.5246</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>27.9096</v>
+        <v>27.9168</v>
       </c>
       <c r="C25" t="n">
-        <v>29.1768</v>
+        <v>29.417</v>
       </c>
       <c r="D25" t="n">
-        <v>68.8994</v>
+        <v>69.2098</v>
       </c>
       <c r="E25" t="n">
-        <v>21.1283</v>
+        <v>21.2404</v>
       </c>
       <c r="F25" t="n">
-        <v>35.6649</v>
+        <v>35.8322</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>26.9642</v>
+        <v>26.7384</v>
       </c>
       <c r="C26" t="n">
-        <v>28.4556</v>
+        <v>28.5576</v>
       </c>
       <c r="D26" t="n">
-        <v>67.7435</v>
+        <v>67.9931</v>
       </c>
       <c r="E26" t="n">
-        <v>20.5041</v>
+        <v>20.4862</v>
       </c>
       <c r="F26" t="n">
-        <v>34.9136</v>
+        <v>35.0068</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>26.2684</v>
+        <v>26.674</v>
       </c>
       <c r="C27" t="n">
-        <v>27.7621</v>
+        <v>27.9121</v>
       </c>
       <c r="D27" t="n">
-        <v>66.81140000000001</v>
+        <v>67.176</v>
       </c>
       <c r="E27" t="n">
-        <v>19.9268</v>
+        <v>19.8712</v>
       </c>
       <c r="F27" t="n">
-        <v>34.3456</v>
+        <v>34.4002</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>25.5408</v>
+        <v>25.8673</v>
       </c>
       <c r="C28" t="n">
-        <v>27.1279</v>
+        <v>27.2459</v>
       </c>
       <c r="D28" t="n">
-        <v>65.7253</v>
+        <v>65.965</v>
       </c>
       <c r="E28" t="n">
-        <v>19.247</v>
+        <v>19.3585</v>
       </c>
       <c r="F28" t="n">
-        <v>33.8229</v>
+        <v>33.9034</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>24.4831</v>
+        <v>24.977</v>
       </c>
       <c r="C29" t="n">
-        <v>26.4752</v>
+        <v>26.5347</v>
       </c>
       <c r="D29" t="n">
-        <v>65.1289</v>
+        <v>65.4499</v>
       </c>
       <c r="E29" t="n">
-        <v>18.7135</v>
+        <v>18.7872</v>
       </c>
       <c r="F29" t="n">
-        <v>33.3323</v>
+        <v>33.4346</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>23.6128</v>
+        <v>24.3596</v>
       </c>
       <c r="C30" t="n">
-        <v>25.856</v>
+        <v>26.0385</v>
       </c>
       <c r="D30" t="n">
-        <v>64.2291</v>
+        <v>64.5234</v>
       </c>
       <c r="E30" t="n">
-        <v>18.1641</v>
+        <v>18.4287</v>
       </c>
       <c r="F30" t="n">
-        <v>32.9015</v>
+        <v>33.0037</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>23.4974</v>
+        <v>23.4847</v>
       </c>
       <c r="C31" t="n">
-        <v>25.3301</v>
+        <v>25.4344</v>
       </c>
       <c r="D31" t="n">
-        <v>63.8411</v>
+        <v>64.06399999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>17.87</v>
+        <v>17.8863</v>
       </c>
       <c r="F31" t="n">
-        <v>32.4487</v>
+        <v>32.4353</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>22.8558</v>
+        <v>22.9088</v>
       </c>
       <c r="C32" t="n">
-        <v>24.787</v>
+        <v>24.9722</v>
       </c>
       <c r="D32" t="n">
-        <v>63.3874</v>
+        <v>63.5554</v>
       </c>
       <c r="E32" t="n">
-        <v>17.4999</v>
+        <v>17.4806</v>
       </c>
       <c r="F32" t="n">
-        <v>32.0936</v>
+        <v>32.084</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>22.4022</v>
+        <v>22.7779</v>
       </c>
       <c r="C33" t="n">
-        <v>24.3043</v>
+        <v>24.4996</v>
       </c>
       <c r="D33" t="n">
-        <v>62.9517</v>
+        <v>63.1638</v>
       </c>
       <c r="E33" t="n">
-        <v>17.2187</v>
+        <v>17.1721</v>
       </c>
       <c r="F33" t="n">
-        <v>31.8565</v>
+        <v>32.0362</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>21.5786</v>
+        <v>21.3849</v>
       </c>
       <c r="C34" t="n">
-        <v>23.9687</v>
+        <v>24.1894</v>
       </c>
       <c r="D34" t="n">
-        <v>62.3138</v>
+        <v>62.3891</v>
       </c>
       <c r="E34" t="n">
-        <v>25.6812</v>
+        <v>25.8819</v>
       </c>
       <c r="F34" t="n">
-        <v>40.2902</v>
+        <v>40.3875</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>20.91</v>
+        <v>21.7596</v>
       </c>
       <c r="C35" t="n">
-        <v>23.6685</v>
+        <v>23.7776</v>
       </c>
       <c r="D35" t="n">
-        <v>80.40940000000001</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>24.9772</v>
+        <v>25.0305</v>
       </c>
       <c r="F35" t="n">
-        <v>39.5212</v>
+        <v>39.726</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>21.513</v>
+        <v>20.9366</v>
       </c>
       <c r="C36" t="n">
-        <v>23.3386</v>
+        <v>23.5312</v>
       </c>
       <c r="D36" t="n">
-        <v>78.65349999999999</v>
+        <v>79.02979999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>24.1822</v>
+        <v>24.1978</v>
       </c>
       <c r="F36" t="n">
-        <v>38.8163</v>
+        <v>38.9085</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>21.0795</v>
+        <v>21.3874</v>
       </c>
       <c r="C37" t="n">
-        <v>31.4648</v>
+        <v>31.5182</v>
       </c>
       <c r="D37" t="n">
-        <v>77.0592</v>
+        <v>77.4594</v>
       </c>
       <c r="E37" t="n">
-        <v>23.3481</v>
+        <v>23.4782</v>
       </c>
       <c r="F37" t="n">
-        <v>38.0631</v>
+        <v>38.2258</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>29.1883</v>
+        <v>29.6162</v>
       </c>
       <c r="C38" t="n">
-        <v>30.7503</v>
+        <v>30.865</v>
       </c>
       <c r="D38" t="n">
-        <v>75.652</v>
+        <v>76.0013</v>
       </c>
       <c r="E38" t="n">
-        <v>22.649</v>
+        <v>22.76</v>
       </c>
       <c r="F38" t="n">
-        <v>37.1739</v>
+        <v>37.5859</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>28.1473</v>
+        <v>28.1892</v>
       </c>
       <c r="C39" t="n">
-        <v>30.1181</v>
+        <v>30.1847</v>
       </c>
       <c r="D39" t="n">
-        <v>74.4148</v>
+        <v>74.6772</v>
       </c>
       <c r="E39" t="n">
-        <v>21.9371</v>
+        <v>22.0961</v>
       </c>
       <c r="F39" t="n">
-        <v>36.7689</v>
+        <v>36.7045</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>26.9105</v>
+        <v>27.3685</v>
       </c>
       <c r="C40" t="n">
-        <v>29.3027</v>
+        <v>29.3045</v>
       </c>
       <c r="D40" t="n">
-        <v>73.1288</v>
+        <v>73.5077</v>
       </c>
       <c r="E40" t="n">
-        <v>21.3826</v>
+        <v>21.5199</v>
       </c>
       <c r="F40" t="n">
-        <v>36.1907</v>
+        <v>36.119</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>26.4582</v>
+        <v>26.5543</v>
       </c>
       <c r="C41" t="n">
-        <v>28.8146</v>
+        <v>28.7468</v>
       </c>
       <c r="D41" t="n">
-        <v>71.9323</v>
+        <v>72.4242</v>
       </c>
       <c r="E41" t="n">
-        <v>20.7643</v>
+        <v>20.7665</v>
       </c>
       <c r="F41" t="n">
-        <v>35.5043</v>
+        <v>35.6028</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>25.7149</v>
+        <v>25.4958</v>
       </c>
       <c r="C42" t="n">
-        <v>28.0729</v>
+        <v>28.1241</v>
       </c>
       <c r="D42" t="n">
-        <v>71.0826</v>
+        <v>71.3981</v>
       </c>
       <c r="E42" t="n">
-        <v>20.2336</v>
+        <v>20.2152</v>
       </c>
       <c r="F42" t="n">
-        <v>34.9138</v>
+        <v>35.0662</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>25.428</v>
+        <v>25.5528</v>
       </c>
       <c r="C43" t="n">
-        <v>27.5545</v>
+        <v>27.6273</v>
       </c>
       <c r="D43" t="n">
-        <v>69.9863</v>
+        <v>70.3193</v>
       </c>
       <c r="E43" t="n">
-        <v>19.7603</v>
+        <v>19.7383</v>
       </c>
       <c r="F43" t="n">
-        <v>34.499</v>
+        <v>34.622</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>24.1776</v>
+        <v>24.5035</v>
       </c>
       <c r="C44" t="n">
-        <v>26.9556</v>
+        <v>27.0123</v>
       </c>
       <c r="D44" t="n">
-        <v>69.16119999999999</v>
+        <v>69.5172</v>
       </c>
       <c r="E44" t="n">
-        <v>19.2383</v>
+        <v>19.1975</v>
       </c>
       <c r="F44" t="n">
-        <v>34.1071</v>
+        <v>34.1265</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>23.4617</v>
+        <v>23.5098</v>
       </c>
       <c r="C45" t="n">
-        <v>26.3823</v>
+        <v>26.4304</v>
       </c>
       <c r="D45" t="n">
-        <v>68.5737</v>
+        <v>68.8933</v>
       </c>
       <c r="E45" t="n">
-        <v>18.7575</v>
+        <v>18.7955</v>
       </c>
       <c r="F45" t="n">
-        <v>33.6234</v>
+        <v>33.7252</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>22.9131</v>
+        <v>23.1762</v>
       </c>
       <c r="C46" t="n">
-        <v>25.7486</v>
+        <v>25.9117</v>
       </c>
       <c r="D46" t="n">
-        <v>68.05070000000001</v>
+        <v>68.3567</v>
       </c>
       <c r="E46" t="n">
-        <v>18.3893</v>
+        <v>18.4172</v>
       </c>
       <c r="F46" t="n">
-        <v>33.2998</v>
+        <v>33.3831</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>22.4646</v>
+        <v>22.5538</v>
       </c>
       <c r="C47" t="n">
-        <v>25.535</v>
+        <v>25.6449</v>
       </c>
       <c r="D47" t="n">
-        <v>67.5866</v>
+        <v>67.8904</v>
       </c>
       <c r="E47" t="n">
-        <v>18.0594</v>
+        <v>17.9831</v>
       </c>
       <c r="F47" t="n">
-        <v>33.1226</v>
+        <v>33.149</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>21.9762</v>
+        <v>22.0416</v>
       </c>
       <c r="C48" t="n">
-        <v>25.1988</v>
+        <v>25.1508</v>
       </c>
       <c r="D48" t="n">
-        <v>66.8831</v>
+        <v>67.11920000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>26.7881</v>
+        <v>26.9158</v>
       </c>
       <c r="F48" t="n">
-        <v>41.6593</v>
+        <v>42.4629</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>22.3083</v>
+        <v>22.0218</v>
       </c>
       <c r="C49" t="n">
-        <v>24.6646</v>
+        <v>24.6618</v>
       </c>
       <c r="D49" t="n">
-        <v>66.53619999999999</v>
+        <v>66.7961</v>
       </c>
       <c r="E49" t="n">
-        <v>25.994</v>
+        <v>26.069</v>
       </c>
       <c r="F49" t="n">
-        <v>40.9641</v>
+        <v>41.7303</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>21.1209</v>
+        <v>21.9949</v>
       </c>
       <c r="C50" t="n">
-        <v>24.2749</v>
+        <v>24.2116</v>
       </c>
       <c r="D50" t="n">
-        <v>83.7294</v>
+        <v>83.9299</v>
       </c>
       <c r="E50" t="n">
-        <v>25.2015</v>
+        <v>25.2632</v>
       </c>
       <c r="F50" t="n">
-        <v>40.2617</v>
+        <v>40.9313</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>21.4166</v>
+        <v>21.0288</v>
       </c>
       <c r="C51" t="n">
-        <v>32.5461</v>
+        <v>32.645</v>
       </c>
       <c r="D51" t="n">
-        <v>81.9768</v>
+        <v>82.2362</v>
       </c>
       <c r="E51" t="n">
-        <v>24.4072</v>
+        <v>24.4892</v>
       </c>
       <c r="F51" t="n">
-        <v>39.6047</v>
+        <v>39.683</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>21.188</v>
+        <v>21.8318</v>
       </c>
       <c r="C52" t="n">
-        <v>32.0221</v>
+        <v>31.6799</v>
       </c>
       <c r="D52" t="n">
-        <v>80.4229</v>
+        <v>80.59480000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>23.7775</v>
+        <v>23.7497</v>
       </c>
       <c r="F52" t="n">
-        <v>38.98</v>
+        <v>39.0792</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>29.4114</v>
+        <v>28.9625</v>
       </c>
       <c r="C53" t="n">
-        <v>31.2482</v>
+        <v>31.2384</v>
       </c>
       <c r="D53" t="n">
-        <v>78.9106</v>
+        <v>79.12739999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>23.1354</v>
+        <v>23.0981</v>
       </c>
       <c r="F53" t="n">
-        <v>38.3593</v>
+        <v>38.4168</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>27.8762</v>
+        <v>28.7298</v>
       </c>
       <c r="C54" t="n">
-        <v>30.547</v>
+        <v>30.386</v>
       </c>
       <c r="D54" t="n">
-        <v>77.5652</v>
+        <v>77.67010000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>22.4607</v>
+        <v>22.532</v>
       </c>
       <c r="F54" t="n">
-        <v>37.7849</v>
+        <v>37.5446</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>27.2619</v>
+        <v>28.1163</v>
       </c>
       <c r="C55" t="n">
-        <v>30.0336</v>
+        <v>29.8298</v>
       </c>
       <c r="D55" t="n">
-        <v>76.3871</v>
+        <v>76.5013</v>
       </c>
       <c r="E55" t="n">
-        <v>21.8789</v>
+        <v>22.0257</v>
       </c>
       <c r="F55" t="n">
-        <v>37.1819</v>
+        <v>37.3266</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>26.6209</v>
+        <v>26.5104</v>
       </c>
       <c r="C56" t="n">
-        <v>29.4767</v>
+        <v>29.3493</v>
       </c>
       <c r="D56" t="n">
-        <v>75.42570000000001</v>
+        <v>75.41200000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>21.3323</v>
+        <v>21.365</v>
       </c>
       <c r="F56" t="n">
-        <v>36.7496</v>
+        <v>36.8138</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>26.4303</v>
+        <v>25.7418</v>
       </c>
       <c r="C57" t="n">
-        <v>28.9031</v>
+        <v>28.7161</v>
       </c>
       <c r="D57" t="n">
-        <v>74.2453</v>
+        <v>74.2273</v>
       </c>
       <c r="E57" t="n">
-        <v>20.7839</v>
+        <v>20.6941</v>
       </c>
       <c r="F57" t="n">
-        <v>36.2261</v>
+        <v>36.314</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>25.7147</v>
+        <v>25.6666</v>
       </c>
       <c r="C58" t="n">
-        <v>28.4005</v>
+        <v>28.1782</v>
       </c>
       <c r="D58" t="n">
-        <v>73.422</v>
+        <v>73.3824</v>
       </c>
       <c r="E58" t="n">
-        <v>20.2385</v>
+        <v>20.2532</v>
       </c>
       <c r="F58" t="n">
-        <v>35.8042</v>
+        <v>35.7897</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>25.0589</v>
+        <v>24.9547</v>
       </c>
       <c r="C59" t="n">
-        <v>27.9182</v>
+        <v>27.8448</v>
       </c>
       <c r="D59" t="n">
-        <v>72.56010000000001</v>
+        <v>72.6006</v>
       </c>
       <c r="E59" t="n">
-        <v>19.8167</v>
+        <v>19.9732</v>
       </c>
       <c r="F59" t="n">
-        <v>35.453</v>
+        <v>35.388</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>24.1206</v>
+        <v>24.052</v>
       </c>
       <c r="C60" t="n">
-        <v>27.4892</v>
+        <v>27.2681</v>
       </c>
       <c r="D60" t="n">
-        <v>71.9003</v>
+        <v>71.94710000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>19.4897</v>
+        <v>19.5935</v>
       </c>
       <c r="F60" t="n">
-        <v>35.1206</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>23.4048</v>
+        <v>23.521</v>
       </c>
       <c r="C61" t="n">
-        <v>27.0746</v>
+        <v>26.9437</v>
       </c>
       <c r="D61" t="n">
-        <v>71.22369999999999</v>
+        <v>71.1955</v>
       </c>
       <c r="E61" t="n">
-        <v>19.19</v>
+        <v>19.2018</v>
       </c>
       <c r="F61" t="n">
-        <v>34.838</v>
+        <v>34.7969</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>22.9612</v>
+        <v>22.9683</v>
       </c>
       <c r="C62" t="n">
-        <v>26.6168</v>
+        <v>26.5138</v>
       </c>
       <c r="D62" t="n">
-        <v>70.6118</v>
+        <v>70.54040000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>18.752</v>
+        <v>18.7311</v>
       </c>
       <c r="F62" t="n">
-        <v>34.5902</v>
+        <v>34.5474</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>23.0186</v>
+        <v>22.819</v>
       </c>
       <c r="C63" t="n">
-        <v>26.3308</v>
+        <v>26.1148</v>
       </c>
       <c r="D63" t="n">
-        <v>70.2242</v>
+        <v>70.1641</v>
       </c>
       <c r="E63" t="n">
-        <v>31.7219</v>
+        <v>31.5078</v>
       </c>
       <c r="F63" t="n">
-        <v>43.9794</v>
+        <v>43.4773</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>22.5051</v>
+        <v>23.319</v>
       </c>
       <c r="C64" t="n">
-        <v>25.9958</v>
+        <v>25.9918</v>
       </c>
       <c r="D64" t="n">
-        <v>90.8272</v>
+        <v>90.75920000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>31.2298</v>
+        <v>30.8752</v>
       </c>
       <c r="F64" t="n">
-        <v>43.3655</v>
+        <v>42.7929</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>23.0156</v>
+        <v>22.9602</v>
       </c>
       <c r="C65" t="n">
-        <v>34.9404</v>
+        <v>34.766</v>
       </c>
       <c r="D65" t="n">
-        <v>88.8725</v>
+        <v>88.6435</v>
       </c>
       <c r="E65" t="n">
-        <v>30.3723</v>
+        <v>30.2416</v>
       </c>
       <c r="F65" t="n">
-        <v>42.9603</v>
+        <v>42.3608</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.6076</v>
+        <v>22.4829</v>
       </c>
       <c r="C66" t="n">
-        <v>34.3451</v>
+        <v>34.3071</v>
       </c>
       <c r="D66" t="n">
-        <v>87.0121</v>
+        <v>86.81019999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>29.1401</v>
+        <v>29.8317</v>
       </c>
       <c r="F66" t="n">
-        <v>42.2819</v>
+        <v>41.7945</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>37.4108</v>
+        <v>35.9958</v>
       </c>
       <c r="C67" t="n">
-        <v>33.9062</v>
+        <v>33.8479</v>
       </c>
       <c r="D67" t="n">
-        <v>85.384</v>
+        <v>85.2544</v>
       </c>
       <c r="E67" t="n">
-        <v>28.8194</v>
+        <v>29.0222</v>
       </c>
       <c r="F67" t="n">
-        <v>41.8155</v>
+        <v>41.2512</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>36.2919</v>
+        <v>36.5496</v>
       </c>
       <c r="C68" t="n">
-        <v>33.4662</v>
+        <v>33.4485</v>
       </c>
       <c r="D68" t="n">
-        <v>83.8781</v>
+        <v>83.6756</v>
       </c>
       <c r="E68" t="n">
-        <v>27.8191</v>
+        <v>27.9775</v>
       </c>
       <c r="F68" t="n">
-        <v>41.1934</v>
+        <v>40.5515</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>37.8271</v>
+        <v>35.9719</v>
       </c>
       <c r="C69" t="n">
-        <v>33.3015</v>
+        <v>33.1463</v>
       </c>
       <c r="D69" t="n">
-        <v>82.392</v>
+        <v>82.2238</v>
       </c>
       <c r="E69" t="n">
-        <v>27.7326</v>
+        <v>27.6871</v>
       </c>
       <c r="F69" t="n">
-        <v>40.6948</v>
+        <v>40.1985</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>34.7304</v>
+        <v>35.6128</v>
       </c>
       <c r="C70" t="n">
-        <v>32.7639</v>
+        <v>32.9707</v>
       </c>
       <c r="D70" t="n">
-        <v>81.52630000000001</v>
+        <v>81.1915</v>
       </c>
       <c r="E70" t="n">
-        <v>26.7104</v>
+        <v>27.1841</v>
       </c>
       <c r="F70" t="n">
-        <v>40.3807</v>
+        <v>39.7296</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>34.099</v>
+        <v>34.9336</v>
       </c>
       <c r="C71" t="n">
-        <v>32.4923</v>
+        <v>32.5825</v>
       </c>
       <c r="D71" t="n">
-        <v>80.8199</v>
+        <v>80.43089999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>26.4138</v>
+        <v>26.206</v>
       </c>
       <c r="F71" t="n">
-        <v>39.8999</v>
+        <v>39.4085</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.4175</v>
+        <v>34.0804</v>
       </c>
       <c r="C72" t="n">
-        <v>32.3119</v>
+        <v>32.2264</v>
       </c>
       <c r="D72" t="n">
-        <v>80.1435</v>
+        <v>79.79510000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>25.3713</v>
+        <v>25.5828</v>
       </c>
       <c r="F72" t="n">
-        <v>39.6491</v>
+        <v>39.0245</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>32.9852</v>
+        <v>32.1503</v>
       </c>
       <c r="C73" t="n">
-        <v>31.895</v>
+        <v>31.7179</v>
       </c>
       <c r="D73" t="n">
-        <v>79.60509999999999</v>
+        <v>79.34439999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>25.0262</v>
+        <v>25.5524</v>
       </c>
       <c r="F73" t="n">
-        <v>39.2079</v>
+        <v>38.7768</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>35.0902</v>
+        <v>31.8051</v>
       </c>
       <c r="C74" t="n">
-        <v>31.6558</v>
+        <v>31.6509</v>
       </c>
       <c r="D74" t="n">
-        <v>79.1484</v>
+        <v>78.8541</v>
       </c>
       <c r="E74" t="n">
-        <v>24.6526</v>
+        <v>24.9034</v>
       </c>
       <c r="F74" t="n">
-        <v>39.0657</v>
+        <v>38.531</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>31.9627</v>
+        <v>34.7527</v>
       </c>
       <c r="C75" t="n">
-        <v>31.2258</v>
+        <v>31.3021</v>
       </c>
       <c r="D75" t="n">
-        <v>78.77889999999999</v>
+        <v>78.2302</v>
       </c>
       <c r="E75" t="n">
-        <v>24.5011</v>
+        <v>24.3413</v>
       </c>
       <c r="F75" t="n">
-        <v>38.9362</v>
+        <v>38.3403</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>33.9191</v>
+        <v>31.4673</v>
       </c>
       <c r="C76" t="n">
-        <v>31.0312</v>
+        <v>30.8564</v>
       </c>
       <c r="D76" t="n">
-        <v>79.0453</v>
+        <v>78.4329</v>
       </c>
       <c r="E76" t="n">
-        <v>23.7017</v>
+        <v>23.8981</v>
       </c>
       <c r="F76" t="n">
-        <v>38.687</v>
+        <v>38.2453</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>29.5423</v>
+        <v>30.6425</v>
       </c>
       <c r="C77" t="n">
-        <v>30.6231</v>
+        <v>30.5584</v>
       </c>
       <c r="D77" t="n">
-        <v>79.3554</v>
+        <v>78.4823</v>
       </c>
       <c r="E77" t="n">
-        <v>41.9705</v>
+        <v>41.7794</v>
       </c>
       <c r="F77" t="n">
-        <v>62.3423</v>
+        <v>61.7363</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>32.9178</v>
+        <v>28.0512</v>
       </c>
       <c r="C78" t="n">
-        <v>30.3219</v>
+        <v>29.7889</v>
       </c>
       <c r="D78" t="n">
-        <v>129.123</v>
+        <v>126.283</v>
       </c>
       <c r="E78" t="n">
-        <v>41.5719</v>
+        <v>40.8869</v>
       </c>
       <c r="F78" t="n">
-        <v>61.4242</v>
+        <v>60.812</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>34.0805</v>
+        <v>32.0036</v>
       </c>
       <c r="C79" t="n">
-        <v>40.252</v>
+        <v>39.6637</v>
       </c>
       <c r="D79" t="n">
-        <v>125.879</v>
+        <v>123.954</v>
       </c>
       <c r="E79" t="n">
-        <v>40.2922</v>
+        <v>40.0074</v>
       </c>
       <c r="F79" t="n">
-        <v>61.4122</v>
+        <v>60.4648</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>33.4409</v>
+        <v>31.2511</v>
       </c>
       <c r="C80" t="n">
-        <v>40.8401</v>
+        <v>40.308</v>
       </c>
       <c r="D80" t="n">
-        <v>123.901</v>
+        <v>121.931</v>
       </c>
       <c r="E80" t="n">
-        <v>39.6639</v>
+        <v>39.5572</v>
       </c>
       <c r="F80" t="n">
-        <v>60.8866</v>
+        <v>60.5988</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>44.8217</v>
+        <v>44.9514</v>
       </c>
       <c r="C81" t="n">
-        <v>41.2898</v>
+        <v>40.8838</v>
       </c>
       <c r="D81" t="n">
-        <v>122.529</v>
+        <v>121.866</v>
       </c>
       <c r="E81" t="n">
-        <v>38.6681</v>
+        <v>38.7512</v>
       </c>
       <c r="F81" t="n">
-        <v>60.0525</v>
+        <v>60.8504</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>42.8286</v>
+        <v>42.0753</v>
       </c>
       <c r="C82" t="n">
-        <v>41.3743</v>
+        <v>41.2277</v>
       </c>
       <c r="D82" t="n">
-        <v>120.881</v>
+        <v>120.562</v>
       </c>
       <c r="E82" t="n">
-        <v>37.8956</v>
+        <v>37.845</v>
       </c>
       <c r="F82" t="n">
-        <v>59.4107</v>
+        <v>60.7668</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>43.7916</v>
+        <v>42.8894</v>
       </c>
       <c r="C83" t="n">
-        <v>41.5661</v>
+        <v>41.6424</v>
       </c>
       <c r="D83" t="n">
-        <v>120.136</v>
+        <v>119.12</v>
       </c>
       <c r="E83" t="n">
-        <v>36.9006</v>
+        <v>37.0046</v>
       </c>
       <c r="F83" t="n">
-        <v>59.2752</v>
+        <v>59.7141</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>44.9807</v>
+        <v>39.8921</v>
       </c>
       <c r="C84" t="n">
-        <v>41.9589</v>
+        <v>41.5857</v>
       </c>
       <c r="D84" t="n">
-        <v>120.025</v>
+        <v>118.684</v>
       </c>
       <c r="E84" t="n">
-        <v>36.3737</v>
+        <v>36.1946</v>
       </c>
       <c r="F84" t="n">
-        <v>58.9076</v>
+        <v>57.4341</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>42.0856</v>
+        <v>43.2829</v>
       </c>
       <c r="C85" t="n">
-        <v>41.7316</v>
+        <v>41.8378</v>
       </c>
       <c r="D85" t="n">
-        <v>119.872</v>
+        <v>119.229</v>
       </c>
       <c r="E85" t="n">
-        <v>35.5703</v>
+        <v>35.388</v>
       </c>
       <c r="F85" t="n">
-        <v>57.7345</v>
+        <v>56.5094</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>38.502</v>
+        <v>43.1562</v>
       </c>
       <c r="C86" t="n">
-        <v>42.104</v>
+        <v>41.8868</v>
       </c>
       <c r="D86" t="n">
-        <v>119.75</v>
+        <v>119.374</v>
       </c>
       <c r="E86" t="n">
-        <v>34.6939</v>
+        <v>34.6041</v>
       </c>
       <c r="F86" t="n">
-        <v>56.8339</v>
+        <v>56.3586</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>41.8345</v>
+        <v>41.5107</v>
       </c>
       <c r="C87" t="n">
-        <v>41.8607</v>
+        <v>41.8371</v>
       </c>
       <c r="D87" t="n">
-        <v>120.113</v>
+        <v>119.287</v>
       </c>
       <c r="E87" t="n">
-        <v>33.6985</v>
+        <v>33.9569</v>
       </c>
       <c r="F87" t="n">
-        <v>55.9765</v>
+        <v>55.0668</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>38.8702</v>
+        <v>42.9837</v>
       </c>
       <c r="C88" t="n">
-        <v>41.9676</v>
+        <v>41.7524</v>
       </c>
       <c r="D88" t="n">
-        <v>120.488</v>
+        <v>120.315</v>
       </c>
       <c r="E88" t="n">
-        <v>33.3002</v>
+        <v>33.0491</v>
       </c>
       <c r="F88" t="n">
-        <v>55.292</v>
+        <v>55.2484</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>41.3861</v>
+        <v>41.4242</v>
       </c>
       <c r="C89" t="n">
-        <v>41.9045</v>
+        <v>41.5594</v>
       </c>
       <c r="D89" t="n">
-        <v>120.932</v>
+        <v>120.705</v>
       </c>
       <c r="E89" t="n">
-        <v>32.9354</v>
+        <v>32.4672</v>
       </c>
       <c r="F89" t="n">
-        <v>54.7905</v>
+        <v>54.6011</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>40.8192</v>
+        <v>40.1445</v>
       </c>
       <c r="C90" t="n">
-        <v>41.4717</v>
+        <v>41.5951</v>
       </c>
       <c r="D90" t="n">
-        <v>122.763</v>
+        <v>121.905</v>
       </c>
       <c r="E90" t="n">
-        <v>32.2466</v>
+        <v>31.7832</v>
       </c>
       <c r="F90" t="n">
-        <v>54.5857</v>
+        <v>54.0509</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>40.984</v>
+        <v>40.7079</v>
       </c>
       <c r="C91" t="n">
-        <v>41.5944</v>
+        <v>41.4946</v>
       </c>
       <c r="D91" t="n">
-        <v>124.023</v>
+        <v>122.994</v>
       </c>
       <c r="E91" t="n">
-        <v>67.928</v>
+        <v>67.6746</v>
       </c>
       <c r="F91" t="n">
-        <v>85.9663</v>
+        <v>85.8656</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>41.1833</v>
+        <v>38.6598</v>
       </c>
       <c r="C92" t="n">
-        <v>41.5829</v>
+        <v>41.0212</v>
       </c>
       <c r="D92" t="n">
-        <v>186.394</v>
+        <v>184.999</v>
       </c>
       <c r="E92" t="n">
-        <v>66.5341</v>
+        <v>66.274</v>
       </c>
       <c r="F92" t="n">
-        <v>84.819</v>
+        <v>84.9568</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>41.6383</v>
+        <v>42.1341</v>
       </c>
       <c r="C93" t="n">
-        <v>41.6005</v>
+        <v>41.1919</v>
       </c>
       <c r="D93" t="n">
-        <v>185.799</v>
+        <v>184.257</v>
       </c>
       <c r="E93" t="n">
-        <v>64.7487</v>
+        <v>64.59739999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>84.1738</v>
+        <v>84.7166</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>34.219</v>
+        <v>38.3593</v>
       </c>
       <c r="C94" t="n">
-        <v>75.4769</v>
+        <v>74.9134</v>
       </c>
       <c r="D94" t="n">
-        <v>184.953</v>
+        <v>182.86</v>
       </c>
       <c r="E94" t="n">
-        <v>62.6936</v>
+        <v>62.7481</v>
       </c>
       <c r="F94" t="n">
-        <v>82.8603</v>
+        <v>83.63500000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>72.866</v>
+        <v>70.46980000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>74.7123</v>
+        <v>74.1345</v>
       </c>
       <c r="D95" t="n">
-        <v>183.86</v>
+        <v>181.787</v>
       </c>
       <c r="E95" t="n">
-        <v>60.7597</v>
+        <v>60.8804</v>
       </c>
       <c r="F95" t="n">
-        <v>83.3569</v>
+        <v>84.21120000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>69.44670000000001</v>
+        <v>72.3104</v>
       </c>
       <c r="C96" t="n">
-        <v>73.91849999999999</v>
+        <v>73.2993</v>
       </c>
       <c r="D96" t="n">
-        <v>182.536</v>
+        <v>180.735</v>
       </c>
       <c r="E96" t="n">
-        <v>59.0053</v>
+        <v>58.947</v>
       </c>
       <c r="F96" t="n">
-        <v>80.95059999999999</v>
+        <v>82.7114</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>69.2731</v>
+        <v>69.5942</v>
       </c>
       <c r="C97" t="n">
-        <v>73.19759999999999</v>
+        <v>72.5706</v>
       </c>
       <c r="D97" t="n">
-        <v>181.105</v>
+        <v>179.849</v>
       </c>
       <c r="E97" t="n">
-        <v>57.5207</v>
+        <v>57.2539</v>
       </c>
       <c r="F97" t="n">
-        <v>80.351</v>
+        <v>81.5326</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>69.976</v>
+        <v>67.67449999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>72.47499999999999</v>
+        <v>71.9405</v>
       </c>
       <c r="D98" t="n">
-        <v>180.85</v>
+        <v>179.35</v>
       </c>
       <c r="E98" t="n">
-        <v>56.0997</v>
+        <v>55.7782</v>
       </c>
       <c r="F98" t="n">
-        <v>80.2056</v>
+        <v>80.9849</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>64.3417</v>
+        <v>66.3638</v>
       </c>
       <c r="C99" t="n">
-        <v>71.6429</v>
+        <v>71.23869999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>181.257</v>
+        <v>179.084</v>
       </c>
       <c r="E99" t="n">
-        <v>54.4038</v>
+        <v>54.1977</v>
       </c>
       <c r="F99" t="n">
-        <v>79.5527</v>
+        <v>80.07980000000001</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>62.0707</v>
+        <v>64.83929999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>70.8708</v>
+        <v>70.65730000000001</v>
       </c>
       <c r="D100" t="n">
-        <v>181.299</v>
+        <v>179.553</v>
       </c>
       <c r="E100" t="n">
-        <v>53.1706</v>
+        <v>52.7432</v>
       </c>
       <c r="F100" t="n">
-        <v>81.8839</v>
+        <v>79.5928</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>62.7747</v>
+        <v>64.9478</v>
       </c>
       <c r="C101" t="n">
-        <v>70.087</v>
+        <v>69.89919999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>181.772</v>
+        <v>179.509</v>
       </c>
       <c r="E101" t="n">
-        <v>51.7033</v>
+        <v>51.5675</v>
       </c>
       <c r="F101" t="n">
-        <v>79.3665</v>
+        <v>77.6262</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>62.5259</v>
+        <v>61.1685</v>
       </c>
       <c r="C102" t="n">
-        <v>69.38679999999999</v>
+        <v>69.25239999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>181.971</v>
+        <v>180.284</v>
       </c>
       <c r="E102" t="n">
-        <v>50.3624</v>
+        <v>50.3192</v>
       </c>
       <c r="F102" t="n">
-        <v>77.1765</v>
+        <v>77.43380000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>61.0102</v>
+        <v>59.8904</v>
       </c>
       <c r="C103" t="n">
-        <v>68.7424</v>
+        <v>68.4329</v>
       </c>
       <c r="D103" t="n">
-        <v>183.663</v>
+        <v>181.403</v>
       </c>
       <c r="E103" t="n">
-        <v>49.059</v>
+        <v>49.1298</v>
       </c>
       <c r="F103" t="n">
-        <v>78.5299</v>
+        <v>76.41679999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>60.1298</v>
+        <v>56.2898</v>
       </c>
       <c r="C104" t="n">
-        <v>68.0574</v>
+        <v>67.72969999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>184.703</v>
+        <v>182.808</v>
       </c>
       <c r="E104" t="n">
-        <v>48.1792</v>
+        <v>48.0657</v>
       </c>
       <c r="F104" t="n">
-        <v>77.4246</v>
+        <v>77.208</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>56.3739</v>
+        <v>58.0274</v>
       </c>
       <c r="C105" t="n">
-        <v>67.4532</v>
+        <v>67.30840000000001</v>
       </c>
       <c r="D105" t="n">
-        <v>186.325</v>
+        <v>184.152</v>
       </c>
       <c r="E105" t="n">
-        <v>85.6871</v>
+        <v>86.089</v>
       </c>
       <c r="F105" t="n">
-        <v>236.685</v>
+        <v>234.815</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>57.981</v>
+        <v>58.0605</v>
       </c>
       <c r="C106" t="n">
-        <v>66.7907</v>
+        <v>66.6681</v>
       </c>
       <c r="D106" t="n">
-        <v>187.562</v>
+        <v>186.154</v>
       </c>
       <c r="E106" t="n">
-        <v>83.9123</v>
+        <v>84.2032</v>
       </c>
       <c r="F106" t="n">
-        <v>237.704</v>
+        <v>236.472</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>56.0794</v>
+        <v>55.5719</v>
       </c>
       <c r="C107" t="n">
-        <v>66.1812</v>
+        <v>66.23779999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>252.624</v>
+        <v>251.618</v>
       </c>
       <c r="E107" t="n">
-        <v>81.7569</v>
+        <v>82.2747</v>
       </c>
       <c r="F107" t="n">
-        <v>238.538</v>
+        <v>237.137</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>56.1123</v>
+        <v>55.2673</v>
       </c>
       <c r="C108" t="n">
-        <v>101.436</v>
+        <v>101.242</v>
       </c>
       <c r="D108" t="n">
-        <v>249.584</v>
+        <v>248.614</v>
       </c>
       <c r="E108" t="n">
-        <v>78.94929999999999</v>
+        <v>79.5299</v>
       </c>
       <c r="F108" t="n">
-        <v>238.078</v>
+        <v>237.341</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>55.1196</v>
+        <v>53.8475</v>
       </c>
       <c r="C109" t="n">
-        <v>99.8652</v>
+        <v>99.9568</v>
       </c>
       <c r="D109" t="n">
-        <v>247.031</v>
+        <v>246.162</v>
       </c>
       <c r="E109" t="n">
-        <v>76.7821</v>
+        <v>77.3546</v>
       </c>
       <c r="F109" t="n">
-        <v>237.974</v>
+        <v>237.138</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>77.64619999999999</v>
+        <v>87.2308</v>
       </c>
       <c r="C110" t="n">
-        <v>84.9152</v>
+        <v>98.8449</v>
       </c>
       <c r="D110" t="n">
-        <v>245.353</v>
+        <v>243.942</v>
       </c>
       <c r="E110" t="n">
-        <v>74.7197</v>
+        <v>74.95610000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>239.894</v>
+        <v>237.513</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>85.1588</v>
+        <v>84.02379999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>97.3349</v>
+        <v>97.337</v>
       </c>
       <c r="D111" t="n">
-        <v>244.175</v>
+        <v>242.617</v>
       </c>
       <c r="E111" t="n">
-        <v>63.0004</v>
+        <v>72.9915</v>
       </c>
       <c r="F111" t="n">
-        <v>239.113</v>
+        <v>237.959</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>82.4337</v>
+        <v>83.7097</v>
       </c>
       <c r="C112" t="n">
-        <v>95.9332</v>
+        <v>95.7992</v>
       </c>
       <c r="D112" t="n">
-        <v>242.144</v>
+        <v>241.734</v>
       </c>
       <c r="E112" t="n">
-        <v>61.8236</v>
+        <v>70.9143</v>
       </c>
       <c r="F112" t="n">
-        <v>238.869</v>
+        <v>239.433</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>73.6866</v>
+        <v>81.7287</v>
       </c>
       <c r="C113" t="n">
-        <v>82.3935</v>
+        <v>94.3541</v>
       </c>
       <c r="D113" t="n">
-        <v>241.011</v>
+        <v>240.841</v>
       </c>
       <c r="E113" t="n">
-        <v>60.1557</v>
+        <v>60.8117</v>
       </c>
       <c r="F113" t="n">
-        <v>239.742</v>
+        <v>239.506</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>72.02209999999999</v>
+        <v>79.2319</v>
       </c>
       <c r="C114" t="n">
-        <v>81.616</v>
+        <v>93.15560000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>254.624</v>
+        <v>250.982</v>
       </c>
       <c r="E114" t="n">
-        <v>67.1538</v>
+        <v>67.43729999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>240.114</v>
+        <v>240.136</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>76.5776</v>
+        <v>75.7774</v>
       </c>
       <c r="C115" t="n">
-        <v>91.90009999999999</v>
+        <v>91.85599999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>251.583</v>
+        <v>248.783</v>
       </c>
       <c r="E115" t="n">
-        <v>65.5467</v>
+        <v>65.9289</v>
       </c>
       <c r="F115" t="n">
-        <v>240.775</v>
+        <v>240.459</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>73.9104</v>
+        <v>66.1673</v>
       </c>
       <c r="C116" t="n">
-        <v>90.7105</v>
+        <v>80.88800000000001</v>
       </c>
       <c r="D116" t="n">
-        <v>251.817</v>
+        <v>251.445</v>
       </c>
       <c r="E116" t="n">
-        <v>63.8379</v>
+        <v>64.18300000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>241.468</v>
+        <v>242.497</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>66.8394</v>
+        <v>74.11799999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>79.3797</v>
+        <v>89.43210000000001</v>
       </c>
       <c r="D117" t="n">
-        <v>255.51</v>
+        <v>248.676</v>
       </c>
       <c r="E117" t="n">
-        <v>62.455</v>
+        <v>62.7755</v>
       </c>
       <c r="F117" t="n">
-        <v>241.543</v>
+        <v>241.947</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>71.42870000000001</v>
+        <v>67.9907</v>
       </c>
       <c r="C118" t="n">
-        <v>88.3434</v>
+        <v>79.6711</v>
       </c>
       <c r="D118" t="n">
-        <v>240.336</v>
+        <v>239.637</v>
       </c>
       <c r="E118" t="n">
-        <v>54.3892</v>
+        <v>54.9023</v>
       </c>
       <c r="F118" t="n">
-        <v>241.238</v>
+        <v>241.816</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>65.0505</v>
+        <v>66.0568</v>
       </c>
       <c r="C119" t="n">
-        <v>78.32250000000001</v>
+        <v>78.84910000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>241.253</v>
+        <v>240.532</v>
       </c>
       <c r="E119" t="n">
-        <v>92.68899999999999</v>
+        <v>93.1729</v>
       </c>
       <c r="F119" t="n">
-        <v>289.133</v>
+        <v>289.744</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>67.91119999999999</v>
+        <v>61.6853</v>
       </c>
       <c r="C120" t="n">
-        <v>86.2961</v>
+        <v>78.1973</v>
       </c>
       <c r="D120" t="n">
-        <v>242.431</v>
+        <v>241.303</v>
       </c>
       <c r="E120" t="n">
-        <v>90.75839999999999</v>
+        <v>91.1408</v>
       </c>
       <c r="F120" t="n">
-        <v>288.154</v>
+        <v>289.02</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>61.1314</v>
+        <v>63.0792</v>
       </c>
       <c r="C121" t="n">
-        <v>77.35299999999999</v>
+        <v>77.69589999999999</v>
       </c>
       <c r="D121" t="n">
-        <v>319.786</v>
+        <v>319.005</v>
       </c>
       <c r="E121" t="n">
-        <v>88.5214</v>
+        <v>88.91670000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>288.543</v>
+        <v>288.704</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>62.3229</v>
+        <v>66.94540000000001</v>
       </c>
       <c r="C122" t="n">
-        <v>112.501</v>
+        <v>120.256</v>
       </c>
       <c r="D122" t="n">
-        <v>314.935</v>
+        <v>313.827</v>
       </c>
       <c r="E122" t="n">
-        <v>86.803</v>
+        <v>86.9945</v>
       </c>
       <c r="F122" t="n">
-        <v>288.59</v>
+        <v>288.436</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>59.5972</v>
+        <v>61.0931</v>
       </c>
       <c r="C123" t="n">
-        <v>111.34</v>
+        <v>112.054</v>
       </c>
       <c r="D123" t="n">
-        <v>310.753</v>
+        <v>309.473</v>
       </c>
       <c r="E123" t="n">
-        <v>84.7997</v>
+        <v>84.9357</v>
       </c>
       <c r="F123" t="n">
-        <v>286.962</v>
+        <v>287.787</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>94.22629999999999</v>
+        <v>92.38420000000001</v>
       </c>
       <c r="C124" t="n">
-        <v>110.57</v>
+        <v>111.055</v>
       </c>
       <c r="D124" t="n">
-        <v>307.158</v>
+        <v>305.757</v>
       </c>
       <c r="E124" t="n">
-        <v>82.8813</v>
+        <v>83.376</v>
       </c>
       <c r="F124" t="n">
-        <v>285.827</v>
+        <v>286.905</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>90.56870000000001</v>
+        <v>92.5033</v>
       </c>
       <c r="C125" t="n">
-        <v>109.482</v>
+        <v>109.708</v>
       </c>
       <c r="D125" t="n">
-        <v>303.602</v>
+        <v>302.478</v>
       </c>
       <c r="E125" t="n">
-        <v>81.3441</v>
+        <v>81.535</v>
       </c>
       <c r="F125" t="n">
-        <v>286.164</v>
+        <v>285.508</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>89.8605</v>
+        <v>94.0887</v>
       </c>
       <c r="C126" t="n">
-        <v>108.464</v>
+        <v>114.644</v>
       </c>
       <c r="D126" t="n">
-        <v>300.821</v>
+        <v>300.279</v>
       </c>
       <c r="E126" t="n">
-        <v>79.6588</v>
+        <v>79.8292</v>
       </c>
       <c r="F126" t="n">
-        <v>286.896</v>
+        <v>287.346</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>88.6087</v>
+        <v>88.84869999999999</v>
       </c>
       <c r="C127" t="n">
-        <v>107.278</v>
+        <v>107.571</v>
       </c>
       <c r="D127" t="n">
-        <v>297.681</v>
+        <v>297.326</v>
       </c>
       <c r="E127" t="n">
-        <v>78.1123</v>
+        <v>78.3583</v>
       </c>
       <c r="F127" t="n">
-        <v>285.721</v>
+        <v>285.747</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>86.2389</v>
+        <v>89.8257</v>
       </c>
       <c r="C128" t="n">
-        <v>106.366</v>
+        <v>111.955</v>
       </c>
       <c r="D128" t="n">
-        <v>295.936</v>
+        <v>295.393</v>
       </c>
       <c r="E128" t="n">
-        <v>76.67619999999999</v>
+        <v>76.8916</v>
       </c>
       <c r="F128" t="n">
-        <v>284.776</v>
+        <v>285.324</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>83.45229999999999</v>
+        <v>88.416</v>
       </c>
       <c r="C129" t="n">
-        <v>105.216</v>
+        <v>110.745</v>
       </c>
       <c r="D129" t="n">
-        <v>293.438</v>
+        <v>293.188</v>
       </c>
       <c r="E129" t="n">
-        <v>75.2235</v>
+        <v>75.6437</v>
       </c>
       <c r="F129" t="n">
-        <v>285.536</v>
+        <v>285.461</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>82.04940000000001</v>
+        <v>82.4875</v>
       </c>
       <c r="C130" t="n">
-        <v>104.306</v>
+        <v>104.569</v>
       </c>
       <c r="D130" t="n">
-        <v>292.524</v>
+        <v>291.614</v>
       </c>
       <c r="E130" t="n">
-        <v>74.1563</v>
+        <v>77.797</v>
       </c>
       <c r="F130" t="n">
-        <v>285.592</v>
+        <v>285.067</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>80.4898</v>
+        <v>81.7741</v>
       </c>
       <c r="C131" t="n">
-        <v>103.535</v>
+        <v>103.804</v>
       </c>
       <c r="D131" t="n">
-        <v>291.273</v>
+        <v>290.25</v>
       </c>
       <c r="E131" t="n">
-        <v>72.7771</v>
+        <v>72.8699</v>
       </c>
       <c r="F131" t="n">
-        <v>284.694</v>
+        <v>285.135</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>79.4421</v>
+        <v>80.8443</v>
       </c>
       <c r="C132" t="n">
-        <v>102.734</v>
+        <v>102.842</v>
       </c>
       <c r="D132" t="n">
-        <v>290.624</v>
+        <v>289.219</v>
       </c>
       <c r="E132" t="n">
-        <v>71.69670000000001</v>
+        <v>71.893</v>
       </c>
       <c r="F132" t="n">
-        <v>284.825</v>
+        <v>285.424</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>70.2046</v>
+        <v>81.8197</v>
       </c>
       <c r="C133" t="n">
-        <v>93.19799999999999</v>
+        <v>106.447</v>
       </c>
       <c r="D133" t="n">
-        <v>290.463</v>
+        <v>289.376</v>
       </c>
       <c r="E133" t="n">
-        <v>70.5433</v>
+        <v>70.57810000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>284.052</v>
+        <v>285.121</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>78.2497</v>
+        <v>71.79730000000001</v>
       </c>
       <c r="C134" t="n">
-        <v>101.132</v>
+        <v>92.8292</v>
       </c>
       <c r="D134" t="n">
-        <v>285.272</v>
+        <v>284.38</v>
       </c>
       <c r="E134" t="n">
-        <v>101.891</v>
+        <v>102.052</v>
       </c>
       <c r="F134" t="n">
-        <v>328.73</v>
+        <v>328.489</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>76.5956</v>
+        <v>77.2671</v>
       </c>
       <c r="C135" t="n">
-        <v>100.541</v>
+        <v>100.698</v>
       </c>
       <c r="D135" t="n">
-        <v>366.086</v>
+        <v>365.058</v>
       </c>
       <c r="E135" t="n">
-        <v>100.004</v>
+        <v>100.031</v>
       </c>
       <c r="F135" t="n">
-        <v>326.554</v>
+        <v>327.987</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>74.79130000000001</v>
+        <v>70.98439999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>134.721</v>
+        <v>127.938</v>
       </c>
       <c r="D136" t="n">
-        <v>359.401</v>
+        <v>358.512</v>
       </c>
       <c r="E136" t="n">
-        <v>97.6953</v>
+        <v>97.98739999999999</v>
       </c>
       <c r="F136" t="n">
-        <v>325.614</v>
+        <v>328.4</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>75.46429999999999</v>
+        <v>70.89360000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>133.553</v>
+        <v>127.055</v>
       </c>
       <c r="D137" t="n">
-        <v>354.04</v>
+        <v>353.567</v>
       </c>
       <c r="E137" t="n">
-        <v>96.0778</v>
+        <v>96.05500000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>325.363</v>
+        <v>324.404</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>108.468</v>
+        <v>104.308</v>
       </c>
       <c r="C138" t="n">
-        <v>133.477</v>
+        <v>126.502</v>
       </c>
       <c r="D138" t="n">
-        <v>351.06</v>
+        <v>347.778</v>
       </c>
       <c r="E138" t="n">
-        <v>94.34099999999999</v>
+        <v>94.31610000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>324.32</v>
+        <v>324.398</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>99.6923</v>
+        <v>106.23</v>
       </c>
       <c r="C139" t="n">
-        <v>125.586</v>
+        <v>132.445</v>
       </c>
       <c r="D139" t="n">
-        <v>343.79</v>
+        <v>343.176</v>
       </c>
       <c r="E139" t="n">
-        <v>92.6555</v>
+        <v>92.8236</v>
       </c>
       <c r="F139" t="n">
-        <v>323.871</v>
+        <v>324.77</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>104.091</v>
+        <v>104.054</v>
       </c>
       <c r="C140" t="n">
-        <v>130.793</v>
+        <v>131.351</v>
       </c>
       <c r="D140" t="n">
-        <v>339.502</v>
+        <v>339.981</v>
       </c>
       <c r="E140" t="n">
-        <v>91.2345</v>
+        <v>90.7328</v>
       </c>
       <c r="F140" t="n">
-        <v>323.237</v>
+        <v>323.584</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>95.82899999999999</v>
+        <v>102.155</v>
       </c>
       <c r="C141" t="n">
-        <v>123.845</v>
+        <v>129.902</v>
       </c>
       <c r="D141" t="n">
-        <v>335.384</v>
+        <v>335.705</v>
       </c>
       <c r="E141" t="n">
-        <v>89.2835</v>
+        <v>89.24850000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>321.456</v>
+        <v>323.199</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>100.139</v>
+        <v>97.07129999999999</v>
       </c>
       <c r="C142" t="n">
-        <v>128.492</v>
+        <v>122.906</v>
       </c>
       <c r="D142" t="n">
-        <v>336.965</v>
+        <v>336.552</v>
       </c>
       <c r="E142" t="n">
-        <v>87.80800000000001</v>
+        <v>88.2109</v>
       </c>
       <c r="F142" t="n">
-        <v>321.21</v>
+        <v>321.74</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>98.0027</v>
+        <v>93.69110000000001</v>
       </c>
       <c r="C143" t="n">
-        <v>127.707</v>
+        <v>122.092</v>
       </c>
       <c r="D143" t="n">
-        <v>335.109</v>
+        <v>334.146</v>
       </c>
       <c r="E143" t="n">
-        <v>86.7916</v>
+        <v>86.4315</v>
       </c>
       <c r="F143" t="n">
-        <v>319.962</v>
+        <v>319.914</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>25.1572</v>
+        <v>55.1383</v>
       </c>
       <c r="C2" t="n">
-        <v>42.2318</v>
+        <v>82.4915</v>
       </c>
       <c r="D2" t="n">
-        <v>57.3346</v>
+        <v>130.527</v>
       </c>
       <c r="E2" t="n">
-        <v>20.7887</v>
+        <v>55.4733</v>
       </c>
       <c r="F2" t="n">
-        <v>39.5651</v>
+        <v>78.1561</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0192</v>
+        <v>53.7072</v>
       </c>
       <c r="C3" t="n">
-        <v>41.6799</v>
+        <v>80.42400000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>56.2625</v>
+        <v>127.979</v>
       </c>
       <c r="E3" t="n">
-        <v>20.2727</v>
+        <v>53.7792</v>
       </c>
       <c r="F3" t="n">
-        <v>39.2357</v>
+        <v>76.6262</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>24.1894</v>
+        <v>52.439</v>
       </c>
       <c r="C4" t="n">
-        <v>40.9992</v>
+        <v>79.0403</v>
       </c>
       <c r="D4" t="n">
-        <v>55.8829</v>
+        <v>126.135</v>
       </c>
       <c r="E4" t="n">
-        <v>19.7495</v>
+        <v>52.4705</v>
       </c>
       <c r="F4" t="n">
-        <v>38.6216</v>
+        <v>75.0168</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>23.0382</v>
+        <v>51.2965</v>
       </c>
       <c r="C5" t="n">
-        <v>40.5649</v>
+        <v>77.3528</v>
       </c>
       <c r="D5" t="n">
-        <v>55.3956</v>
+        <v>124.504</v>
       </c>
       <c r="E5" t="n">
-        <v>19.7071</v>
+        <v>51.2227</v>
       </c>
       <c r="F5" t="n">
-        <v>38.4077</v>
+        <v>73.59869999999999</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.9887</v>
+        <v>50.133</v>
       </c>
       <c r="C6" t="n">
-        <v>39.9929</v>
+        <v>75.61360000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>54.752</v>
+        <v>122.567</v>
       </c>
       <c r="E6" t="n">
-        <v>18.9307</v>
+        <v>50.2262</v>
       </c>
       <c r="F6" t="n">
-        <v>38.1155</v>
+        <v>72.1353</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>23.3609</v>
+        <v>49.2857</v>
       </c>
       <c r="C7" t="n">
-        <v>39.7766</v>
+        <v>74.6084</v>
       </c>
       <c r="D7" t="n">
-        <v>70.16630000000001</v>
+        <v>169.268</v>
       </c>
       <c r="E7" t="n">
-        <v>18.7042</v>
+        <v>49.2674</v>
       </c>
       <c r="F7" t="n">
-        <v>38.0618</v>
+        <v>70.69929999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>22.6363</v>
+        <v>48.4795</v>
       </c>
       <c r="C8" t="n">
-        <v>39.3238</v>
+        <v>73.16800000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>68.8539</v>
+        <v>166.691</v>
       </c>
       <c r="E8" t="n">
-        <v>18.7594</v>
+        <v>48.6218</v>
       </c>
       <c r="F8" t="n">
-        <v>38.4305</v>
+        <v>69.71899999999999</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>22.508</v>
+        <v>47.7655</v>
       </c>
       <c r="C9" t="n">
-        <v>39.5349</v>
+        <v>72.4066</v>
       </c>
       <c r="D9" t="n">
-        <v>67.6134</v>
+        <v>163.464</v>
       </c>
       <c r="E9" t="n">
-        <v>27.998</v>
+        <v>67.8074</v>
       </c>
       <c r="F9" t="n">
-        <v>46.2522</v>
+        <v>99.4658</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>32.0603</v>
+        <v>64.6015</v>
       </c>
       <c r="C10" t="n">
-        <v>48.4857</v>
+        <v>103.934</v>
       </c>
       <c r="D10" t="n">
-        <v>66.2804</v>
+        <v>158.673</v>
       </c>
       <c r="E10" t="n">
-        <v>27.1248</v>
+        <v>65.7534</v>
       </c>
       <c r="F10" t="n">
-        <v>45.3637</v>
+        <v>97.1159</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>30.7034</v>
+        <v>62.8491</v>
       </c>
       <c r="C11" t="n">
-        <v>47.4394</v>
+        <v>101.394</v>
       </c>
       <c r="D11" t="n">
-        <v>65.1211</v>
+        <v>154.296</v>
       </c>
       <c r="E11" t="n">
-        <v>26.0965</v>
+        <v>63.7977</v>
       </c>
       <c r="F11" t="n">
-        <v>43.8307</v>
+        <v>93.9199</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>29.2139</v>
+        <v>61.0911</v>
       </c>
       <c r="C12" t="n">
-        <v>46.717</v>
+        <v>97.82810000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>64.0153</v>
+        <v>151.057</v>
       </c>
       <c r="E12" t="n">
-        <v>25.2661</v>
+        <v>61.8948</v>
       </c>
       <c r="F12" t="n">
-        <v>42.9505</v>
+        <v>90.9973</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>28.9149</v>
+        <v>59.541</v>
       </c>
       <c r="C13" t="n">
-        <v>45.6568</v>
+        <v>95.8544</v>
       </c>
       <c r="D13" t="n">
-        <v>63.1462</v>
+        <v>149.52</v>
       </c>
       <c r="E13" t="n">
-        <v>24.3217</v>
+        <v>60.1324</v>
       </c>
       <c r="F13" t="n">
-        <v>42.0843</v>
+        <v>89.44970000000001</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>27.5528</v>
+        <v>58.828</v>
       </c>
       <c r="C14" t="n">
-        <v>44.7286</v>
+        <v>93.3314</v>
       </c>
       <c r="D14" t="n">
-        <v>62.1723</v>
+        <v>146.137</v>
       </c>
       <c r="E14" t="n">
-        <v>23.532</v>
+        <v>58.4297</v>
       </c>
       <c r="F14" t="n">
-        <v>41.2695</v>
+        <v>86.6949</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>27.1804</v>
+        <v>56.6283</v>
       </c>
       <c r="C15" t="n">
-        <v>44.5709</v>
+        <v>91.4971</v>
       </c>
       <c r="D15" t="n">
-        <v>61.6618</v>
+        <v>142.997</v>
       </c>
       <c r="E15" t="n">
-        <v>22.9939</v>
+        <v>56.8842</v>
       </c>
       <c r="F15" t="n">
-        <v>40.5517</v>
+        <v>84.8531</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>26.3905</v>
+        <v>55.2237</v>
       </c>
       <c r="C16" t="n">
-        <v>43.9653</v>
+        <v>89.1825</v>
       </c>
       <c r="D16" t="n">
-        <v>61.078</v>
+        <v>141.495</v>
       </c>
       <c r="E16" t="n">
-        <v>22.4133</v>
+        <v>55.3661</v>
       </c>
       <c r="F16" t="n">
-        <v>40.0287</v>
+        <v>82.19799999999999</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>25.6809</v>
+        <v>53.8627</v>
       </c>
       <c r="C17" t="n">
-        <v>43.6887</v>
+        <v>87.1271</v>
       </c>
       <c r="D17" t="n">
-        <v>60.5039</v>
+        <v>138.874</v>
       </c>
       <c r="E17" t="n">
-        <v>21.8042</v>
+        <v>53.9538</v>
       </c>
       <c r="F17" t="n">
-        <v>39.7854</v>
+        <v>80.0771</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.6154</v>
+        <v>52.6349</v>
       </c>
       <c r="C18" t="n">
-        <v>42.3566</v>
+        <v>85.44759999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>60.1315</v>
+        <v>137.064</v>
       </c>
       <c r="E18" t="n">
-        <v>21.2547</v>
+        <v>52.6372</v>
       </c>
       <c r="F18" t="n">
-        <v>39.3909</v>
+        <v>78.39319999999999</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>24.3601</v>
+        <v>51.5238</v>
       </c>
       <c r="C19" t="n">
-        <v>41.7633</v>
+        <v>83.1741</v>
       </c>
       <c r="D19" t="n">
-        <v>59.41</v>
+        <v>135.141</v>
       </c>
       <c r="E19" t="n">
-        <v>20.8112</v>
+        <v>51.4885</v>
       </c>
       <c r="F19" t="n">
-        <v>38.0803</v>
+        <v>76.748</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.8545</v>
+        <v>50.674</v>
       </c>
       <c r="C20" t="n">
-        <v>40.8281</v>
+        <v>81.03740000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>59.0357</v>
+        <v>133.729</v>
       </c>
       <c r="E20" t="n">
-        <v>20.4738</v>
+        <v>50.3725</v>
       </c>
       <c r="F20" t="n">
-        <v>37.91</v>
+        <v>75.7311</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>23.0922</v>
+        <v>49.6572</v>
       </c>
       <c r="C21" t="n">
-        <v>40.3686</v>
+        <v>79.0809</v>
       </c>
       <c r="D21" t="n">
-        <v>76.41419999999999</v>
+        <v>185.142</v>
       </c>
       <c r="E21" t="n">
-        <v>20.4611</v>
+        <v>49.5549</v>
       </c>
       <c r="F21" t="n">
-        <v>37.9169</v>
+        <v>74.1785</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>23.0714</v>
+        <v>48.9094</v>
       </c>
       <c r="C22" t="n">
-        <v>40.1262</v>
+        <v>78.12350000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>74.89870000000001</v>
+        <v>181.303</v>
       </c>
       <c r="E22" t="n">
-        <v>20.4199</v>
+        <v>48.8775</v>
       </c>
       <c r="F22" t="n">
-        <v>37.9326</v>
+        <v>73.548</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>23.8027</v>
+        <v>48.4045</v>
       </c>
       <c r="C23" t="n">
-        <v>40.6808</v>
+        <v>77.1139</v>
       </c>
       <c r="D23" t="n">
-        <v>73.59</v>
+        <v>176.736</v>
       </c>
       <c r="E23" t="n">
-        <v>29.4441</v>
+        <v>68.7102</v>
       </c>
       <c r="F23" t="n">
-        <v>46.3324</v>
+        <v>105.502</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>31.6232</v>
+        <v>65.774</v>
       </c>
       <c r="C24" t="n">
-        <v>50.244</v>
+        <v>111.449</v>
       </c>
       <c r="D24" t="n">
-        <v>72.384</v>
+        <v>172.514</v>
       </c>
       <c r="E24" t="n">
-        <v>28.4455</v>
+        <v>66.5809</v>
       </c>
       <c r="F24" t="n">
-        <v>45.3113</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>31.6026</v>
+        <v>64.026</v>
       </c>
       <c r="C25" t="n">
-        <v>49.7243</v>
+        <v>108.048</v>
       </c>
       <c r="D25" t="n">
-        <v>71.0802</v>
+        <v>169.311</v>
       </c>
       <c r="E25" t="n">
-        <v>27.476</v>
+        <v>64.6528</v>
       </c>
       <c r="F25" t="n">
-        <v>44.4009</v>
+        <v>99.3562</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>30.5636</v>
+        <v>62.454</v>
       </c>
       <c r="C26" t="n">
-        <v>48.2071</v>
+        <v>105.936</v>
       </c>
       <c r="D26" t="n">
-        <v>69.9436</v>
+        <v>165.301</v>
       </c>
       <c r="E26" t="n">
-        <v>26.6729</v>
+        <v>62.8097</v>
       </c>
       <c r="F26" t="n">
-        <v>43.5326</v>
+        <v>96.3754</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>29.3422</v>
+        <v>60.7838</v>
       </c>
       <c r="C27" t="n">
-        <v>47.2231</v>
+        <v>101.375</v>
       </c>
       <c r="D27" t="n">
-        <v>68.9449</v>
+        <v>161.882</v>
       </c>
       <c r="E27" t="n">
-        <v>25.9269</v>
+        <v>61.0283</v>
       </c>
       <c r="F27" t="n">
-        <v>42.6114</v>
+        <v>95.1991</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>28.3717</v>
+        <v>59.2583</v>
       </c>
       <c r="C28" t="n">
-        <v>46.2542</v>
+        <v>99.6634</v>
       </c>
       <c r="D28" t="n">
-        <v>67.94929999999999</v>
+        <v>157.557</v>
       </c>
       <c r="E28" t="n">
-        <v>25.1118</v>
+        <v>59.3888</v>
       </c>
       <c r="F28" t="n">
-        <v>41.8227</v>
+        <v>91.42570000000001</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>28.3026</v>
+        <v>57.9737</v>
       </c>
       <c r="C29" t="n">
-        <v>45.5909</v>
+        <v>96.3629</v>
       </c>
       <c r="D29" t="n">
-        <v>67.23779999999999</v>
+        <v>156.805</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2116</v>
+        <v>57.864</v>
       </c>
       <c r="F29" t="n">
-        <v>41.3369</v>
+        <v>90.05110000000001</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>27.3852</v>
+        <v>56.4702</v>
       </c>
       <c r="C30" t="n">
-        <v>44.65</v>
+        <v>96.1058</v>
       </c>
       <c r="D30" t="n">
-        <v>66.3289</v>
+        <v>154.286</v>
       </c>
       <c r="E30" t="n">
-        <v>23.5148</v>
+        <v>56.2924</v>
       </c>
       <c r="F30" t="n">
-        <v>40.8158</v>
+        <v>85.8344</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>26.0195</v>
+        <v>55.2149</v>
       </c>
       <c r="C31" t="n">
-        <v>43.9441</v>
+        <v>93.07680000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>65.7471</v>
+        <v>152.621</v>
       </c>
       <c r="E31" t="n">
-        <v>22.8742</v>
+        <v>54.8725</v>
       </c>
       <c r="F31" t="n">
-        <v>40.1959</v>
+        <v>86.2636</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.3843</v>
+        <v>53.9513</v>
       </c>
       <c r="C32" t="n">
-        <v>43.4102</v>
+        <v>90.5628</v>
       </c>
       <c r="D32" t="n">
-        <v>65.5063</v>
+        <v>147.884</v>
       </c>
       <c r="E32" t="n">
-        <v>22.3127</v>
+        <v>53.6049</v>
       </c>
       <c r="F32" t="n">
-        <v>39.6669</v>
+        <v>83.3224</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.6577</v>
+        <v>52.8113</v>
       </c>
       <c r="C33" t="n">
-        <v>42.7759</v>
+        <v>87.97790000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>64.79049999999999</v>
+        <v>146.288</v>
       </c>
       <c r="E33" t="n">
-        <v>21.8229</v>
+        <v>52.3629</v>
       </c>
       <c r="F33" t="n">
-        <v>39.6183</v>
+        <v>82.0903</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.6854</v>
+        <v>51.7061</v>
       </c>
       <c r="C34" t="n">
-        <v>42.3548</v>
+        <v>87.017</v>
       </c>
       <c r="D34" t="n">
-        <v>64.19889999999999</v>
+        <v>146.034</v>
       </c>
       <c r="E34" t="n">
-        <v>21.4329</v>
+        <v>51.3825</v>
       </c>
       <c r="F34" t="n">
-        <v>39.0607</v>
+        <v>79.4299</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.8746</v>
+        <v>50.9019</v>
       </c>
       <c r="C35" t="n">
-        <v>42.3207</v>
+        <v>85.0635</v>
       </c>
       <c r="D35" t="n">
-        <v>82.6816</v>
+        <v>205.862</v>
       </c>
       <c r="E35" t="n">
-        <v>21.1731</v>
+        <v>50.4774</v>
       </c>
       <c r="F35" t="n">
-        <v>38.9119</v>
+        <v>78.7029</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.4551</v>
+        <v>50.0691</v>
       </c>
       <c r="C36" t="n">
-        <v>41.4888</v>
+        <v>83.5423</v>
       </c>
       <c r="D36" t="n">
-        <v>80.9297</v>
+        <v>201.679</v>
       </c>
       <c r="E36" t="n">
-        <v>21.2399</v>
+        <v>49.803</v>
       </c>
       <c r="F36" t="n">
-        <v>38.8989</v>
+        <v>77.1003</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.4835</v>
+        <v>49.4376</v>
       </c>
       <c r="C37" t="n">
-        <v>41.3417</v>
+        <v>81.7795</v>
       </c>
       <c r="D37" t="n">
-        <v>79.29340000000001</v>
+        <v>195.538</v>
       </c>
       <c r="E37" t="n">
-        <v>30.4967</v>
+        <v>70.1217</v>
       </c>
       <c r="F37" t="n">
-        <v>47.7575</v>
+        <v>110.625</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>32.4391</v>
+        <v>67.63079999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>51.2495</v>
+        <v>120.875</v>
       </c>
       <c r="D38" t="n">
-        <v>77.90940000000001</v>
+        <v>190.153</v>
       </c>
       <c r="E38" t="n">
-        <v>29.5006</v>
+        <v>68.0955</v>
       </c>
       <c r="F38" t="n">
-        <v>46.8662</v>
+        <v>107.847</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>31.778</v>
+        <v>66.03019999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>50.167</v>
+        <v>115.719</v>
       </c>
       <c r="D39" t="n">
-        <v>76.4084</v>
+        <v>183.73</v>
       </c>
       <c r="E39" t="n">
-        <v>28.6515</v>
+        <v>66.1473</v>
       </c>
       <c r="F39" t="n">
-        <v>45.8871</v>
+        <v>106.629</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>30.9971</v>
+        <v>64.1444</v>
       </c>
       <c r="C40" t="n">
-        <v>49.3471</v>
+        <v>113.477</v>
       </c>
       <c r="D40" t="n">
-        <v>75.1478</v>
+        <v>181.863</v>
       </c>
       <c r="E40" t="n">
-        <v>27.6826</v>
+        <v>64.29519999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>44.8166</v>
+        <v>103.318</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>29.9723</v>
+        <v>62.4504</v>
       </c>
       <c r="C41" t="n">
-        <v>48.2695</v>
+        <v>111.185</v>
       </c>
       <c r="D41" t="n">
-        <v>73.86579999999999</v>
+        <v>179.195</v>
       </c>
       <c r="E41" t="n">
-        <v>26.7791</v>
+        <v>62.5909</v>
       </c>
       <c r="F41" t="n">
-        <v>43.952</v>
+        <v>103.328</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>29.424</v>
+        <v>61.0018</v>
       </c>
       <c r="C42" t="n">
-        <v>47.807</v>
+        <v>109.092</v>
       </c>
       <c r="D42" t="n">
-        <v>72.9477</v>
+        <v>174.346</v>
       </c>
       <c r="E42" t="n">
-        <v>26.0056</v>
+        <v>60.9032</v>
       </c>
       <c r="F42" t="n">
-        <v>43.0007</v>
+        <v>98.3265</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>28.59</v>
+        <v>59.5345</v>
       </c>
       <c r="C43" t="n">
-        <v>47.0449</v>
+        <v>105.917</v>
       </c>
       <c r="D43" t="n">
-        <v>71.9226</v>
+        <v>170.473</v>
       </c>
       <c r="E43" t="n">
-        <v>25.2565</v>
+        <v>59.311</v>
       </c>
       <c r="F43" t="n">
-        <v>42.1553</v>
+        <v>97.05719999999999</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>28.1655</v>
+        <v>58.2298</v>
       </c>
       <c r="C44" t="n">
-        <v>46.2968</v>
+        <v>102.357</v>
       </c>
       <c r="D44" t="n">
-        <v>71.0671</v>
+        <v>168.635</v>
       </c>
       <c r="E44" t="n">
-        <v>24.561</v>
+        <v>57.767</v>
       </c>
       <c r="F44" t="n">
-        <v>41.4517</v>
+        <v>94.2135</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>27.2817</v>
+        <v>56.7356</v>
       </c>
       <c r="C45" t="n">
-        <v>45.4653</v>
+        <v>100.84</v>
       </c>
       <c r="D45" t="n">
-        <v>70.3212</v>
+        <v>166.02</v>
       </c>
       <c r="E45" t="n">
-        <v>23.9202</v>
+        <v>56.3259</v>
       </c>
       <c r="F45" t="n">
-        <v>40.8285</v>
+        <v>89.4666</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>27.2595</v>
+        <v>55.6132</v>
       </c>
       <c r="C46" t="n">
-        <v>44.7184</v>
+        <v>99.62179999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>69.6658</v>
+        <v>163.608</v>
       </c>
       <c r="E46" t="n">
-        <v>23.3226</v>
+        <v>55.0147</v>
       </c>
       <c r="F46" t="n">
-        <v>40.3664</v>
+        <v>88.75960000000001</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>25.6294</v>
+        <v>54.37</v>
       </c>
       <c r="C47" t="n">
-        <v>44.2619</v>
+        <v>96.9773</v>
       </c>
       <c r="D47" t="n">
-        <v>69.1289</v>
+        <v>162.796</v>
       </c>
       <c r="E47" t="n">
-        <v>22.7868</v>
+        <v>53.7596</v>
       </c>
       <c r="F47" t="n">
-        <v>39.9171</v>
+        <v>89.08450000000001</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>25.5338</v>
+        <v>53.2765</v>
       </c>
       <c r="C48" t="n">
-        <v>43.6192</v>
+        <v>93.8887</v>
       </c>
       <c r="D48" t="n">
-        <v>68.60890000000001</v>
+        <v>158.662</v>
       </c>
       <c r="E48" t="n">
-        <v>22.3338</v>
+        <v>52.6605</v>
       </c>
       <c r="F48" t="n">
-        <v>39.6295</v>
+        <v>86.529</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>24.3155</v>
+        <v>52.3981</v>
       </c>
       <c r="C49" t="n">
-        <v>43.1849</v>
+        <v>92.5702</v>
       </c>
       <c r="D49" t="n">
-        <v>68.2616</v>
+        <v>154.731</v>
       </c>
       <c r="E49" t="n">
-        <v>22.0784</v>
+        <v>51.7336</v>
       </c>
       <c r="F49" t="n">
-        <v>39.4354</v>
+        <v>85.1699</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>24.747</v>
+        <v>51.4927</v>
       </c>
       <c r="C50" t="n">
-        <v>42.848</v>
+        <v>91.0603</v>
       </c>
       <c r="D50" t="n">
-        <v>85.6953</v>
+        <v>234.709</v>
       </c>
       <c r="E50" t="n">
-        <v>21.9125</v>
+        <v>50.9877</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4139</v>
+        <v>83.4359</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>24.0854</v>
+        <v>50.9358</v>
       </c>
       <c r="C51" t="n">
-        <v>42.7201</v>
+        <v>88.85339999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>83.9622</v>
+        <v>229.337</v>
       </c>
       <c r="E51" t="n">
-        <v>31.7112</v>
+        <v>72.4819</v>
       </c>
       <c r="F51" t="n">
-        <v>48.7533</v>
+        <v>128.14</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>24.7438</v>
+        <v>50.5683</v>
       </c>
       <c r="C52" t="n">
-        <v>42.6018</v>
+        <v>89.3152</v>
       </c>
       <c r="D52" t="n">
-        <v>82.3749</v>
+        <v>225.137</v>
       </c>
       <c r="E52" t="n">
-        <v>30.7706</v>
+        <v>70.3828</v>
       </c>
       <c r="F52" t="n">
-        <v>47.8528</v>
+        <v>124.356</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>33.4921</v>
+        <v>68.2034</v>
       </c>
       <c r="C53" t="n">
-        <v>52.7188</v>
+        <v>132.248</v>
       </c>
       <c r="D53" t="n">
-        <v>80.7726</v>
+        <v>219.342</v>
       </c>
       <c r="E53" t="n">
-        <v>29.8216</v>
+        <v>68.4308</v>
       </c>
       <c r="F53" t="n">
-        <v>46.9044</v>
+        <v>119.896</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>32.4814</v>
+        <v>66.4164</v>
       </c>
       <c r="C54" t="n">
-        <v>51.883</v>
+        <v>127.524</v>
       </c>
       <c r="D54" t="n">
-        <v>79.43859999999999</v>
+        <v>217.527</v>
       </c>
       <c r="E54" t="n">
-        <v>29.0609</v>
+        <v>66.45180000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>46.0277</v>
+        <v>115.794</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>31.2558</v>
+        <v>64.70659999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>50.9596</v>
+        <v>124.425</v>
       </c>
       <c r="D55" t="n">
-        <v>78.2073</v>
+        <v>210.024</v>
       </c>
       <c r="E55" t="n">
-        <v>28.1718</v>
+        <v>64.7032</v>
       </c>
       <c r="F55" t="n">
-        <v>45.1148</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>30.3511</v>
+        <v>63.1359</v>
       </c>
       <c r="C56" t="n">
-        <v>50.2692</v>
+        <v>121.702</v>
       </c>
       <c r="D56" t="n">
-        <v>77.0476</v>
+        <v>203.743</v>
       </c>
       <c r="E56" t="n">
-        <v>27.3487</v>
+        <v>63.0294</v>
       </c>
       <c r="F56" t="n">
-        <v>44.4719</v>
+        <v>108.66</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>29.8691</v>
+        <v>61.6274</v>
       </c>
       <c r="C57" t="n">
-        <v>49.3509</v>
+        <v>120.812</v>
       </c>
       <c r="D57" t="n">
-        <v>75.8967</v>
+        <v>206.934</v>
       </c>
       <c r="E57" t="n">
-        <v>26.6247</v>
+        <v>61.4576</v>
       </c>
       <c r="F57" t="n">
-        <v>43.5627</v>
+        <v>104.296</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.9213</v>
+        <v>60.2099</v>
       </c>
       <c r="C58" t="n">
-        <v>48.4058</v>
+        <v>116.576</v>
       </c>
       <c r="D58" t="n">
-        <v>74.9405</v>
+        <v>203.389</v>
       </c>
       <c r="E58" t="n">
-        <v>25.9673</v>
+        <v>59.8713</v>
       </c>
       <c r="F58" t="n">
-        <v>42.9518</v>
+        <v>102.355</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.8605</v>
+        <v>58.902</v>
       </c>
       <c r="C59" t="n">
-        <v>47.7399</v>
+        <v>113.74</v>
       </c>
       <c r="D59" t="n">
-        <v>74.1263</v>
+        <v>200.075</v>
       </c>
       <c r="E59" t="n">
-        <v>25.232</v>
+        <v>58.3615</v>
       </c>
       <c r="F59" t="n">
-        <v>42.2698</v>
+        <v>99.1152</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>27.0413</v>
+        <v>57.5401</v>
       </c>
       <c r="C60" t="n">
-        <v>47.1785</v>
+        <v>109.421</v>
       </c>
       <c r="D60" t="n">
-        <v>73.4654</v>
+        <v>200.116</v>
       </c>
       <c r="E60" t="n">
-        <v>24.7379</v>
+        <v>57.124</v>
       </c>
       <c r="F60" t="n">
-        <v>41.7305</v>
+        <v>101.072</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.6164</v>
+        <v>56.2835</v>
       </c>
       <c r="C61" t="n">
-        <v>46.6129</v>
+        <v>107.496</v>
       </c>
       <c r="D61" t="n">
-        <v>72.6348</v>
+        <v>196.738</v>
       </c>
       <c r="E61" t="n">
-        <v>24.0682</v>
+        <v>55.8648</v>
       </c>
       <c r="F61" t="n">
-        <v>41.3269</v>
+        <v>97.7179</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.4174</v>
+        <v>55.2093</v>
       </c>
       <c r="C62" t="n">
-        <v>46.0561</v>
+        <v>106.043</v>
       </c>
       <c r="D62" t="n">
-        <v>72.053</v>
+        <v>196.078</v>
       </c>
       <c r="E62" t="n">
-        <v>23.7687</v>
+        <v>54.6945</v>
       </c>
       <c r="F62" t="n">
-        <v>40.9107</v>
+        <v>92.798</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>26.0025</v>
+        <v>54.2912</v>
       </c>
       <c r="C63" t="n">
-        <v>45.5291</v>
+        <v>103.848</v>
       </c>
       <c r="D63" t="n">
-        <v>71.45189999999999</v>
+        <v>197.203</v>
       </c>
       <c r="E63" t="n">
-        <v>23.3927</v>
+        <v>53.7748</v>
       </c>
       <c r="F63" t="n">
-        <v>40.6288</v>
+        <v>88.8154</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.4005</v>
+        <v>53.4369</v>
       </c>
       <c r="C64" t="n">
-        <v>45.1824</v>
+        <v>98.98</v>
       </c>
       <c r="D64" t="n">
-        <v>92.30419999999999</v>
+        <v>390.672</v>
       </c>
       <c r="E64" t="n">
-        <v>23.1511</v>
+        <v>53.0334</v>
       </c>
       <c r="F64" t="n">
-        <v>40.5925</v>
+        <v>90.1554</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.1058</v>
+        <v>52.6164</v>
       </c>
       <c r="C65" t="n">
-        <v>45.1557</v>
+        <v>101.324</v>
       </c>
       <c r="D65" t="n">
-        <v>90.4376</v>
+        <v>384.453</v>
       </c>
       <c r="E65" t="n">
-        <v>23.2597</v>
+        <v>52.2552</v>
       </c>
       <c r="F65" t="n">
-        <v>40.8185</v>
+        <v>88.9002</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.3653</v>
+        <v>52.2043</v>
       </c>
       <c r="C66" t="n">
-        <v>45.3325</v>
+        <v>99.44499999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>88.67959999999999</v>
+        <v>375.86</v>
       </c>
       <c r="E66" t="n">
-        <v>35.5814</v>
+        <v>73.96339999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>51.7682</v>
+        <v>157.084</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>40.9538</v>
+        <v>70.0055</v>
       </c>
       <c r="C67" t="n">
-        <v>61.4325</v>
+        <v>172.868</v>
       </c>
       <c r="D67" t="n">
-        <v>87.18519999999999</v>
+        <v>360.515</v>
       </c>
       <c r="E67" t="n">
-        <v>34.325</v>
+        <v>71.1759</v>
       </c>
       <c r="F67" t="n">
-        <v>51.2002</v>
+        <v>154.298</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.1023</v>
+        <v>68.47150000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>60.7015</v>
+        <v>167.947</v>
       </c>
       <c r="D68" t="n">
-        <v>85.49250000000001</v>
+        <v>347.575</v>
       </c>
       <c r="E68" t="n">
-        <v>33.6202</v>
+        <v>69.5685</v>
       </c>
       <c r="F68" t="n">
-        <v>50.6211</v>
+        <v>152.263</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>38.0945</v>
+        <v>66.9329</v>
       </c>
       <c r="C69" t="n">
-        <v>59.7455</v>
+        <v>165.966</v>
       </c>
       <c r="D69" t="n">
-        <v>84.3809</v>
+        <v>355.887</v>
       </c>
       <c r="E69" t="n">
-        <v>32.5891</v>
+        <v>67.82299999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>49.9472</v>
+        <v>147.702</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>38.8467</v>
+        <v>65.5932</v>
       </c>
       <c r="C70" t="n">
-        <v>59.1388</v>
+        <v>163.593</v>
       </c>
       <c r="D70" t="n">
-        <v>83.2788</v>
+        <v>347.226</v>
       </c>
       <c r="E70" t="n">
-        <v>31.9186</v>
+        <v>66.13120000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>49.1811</v>
+        <v>148.174</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>37.1091</v>
+        <v>64.1404</v>
       </c>
       <c r="C71" t="n">
-        <v>58.4558</v>
+        <v>154.352</v>
       </c>
       <c r="D71" t="n">
-        <v>82.4577</v>
+        <v>346.049</v>
       </c>
       <c r="E71" t="n">
-        <v>31.0039</v>
+        <v>64.0603</v>
       </c>
       <c r="F71" t="n">
-        <v>48.4413</v>
+        <v>141.18</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.2916</v>
+        <v>62.969</v>
       </c>
       <c r="C72" t="n">
-        <v>57.4812</v>
+        <v>156.622</v>
       </c>
       <c r="D72" t="n">
-        <v>81.875</v>
+        <v>347.171</v>
       </c>
       <c r="E72" t="n">
-        <v>30.1208</v>
+        <v>62.4787</v>
       </c>
       <c r="F72" t="n">
-        <v>47.8906</v>
+        <v>136.101</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>34.3132</v>
+        <v>61.8258</v>
       </c>
       <c r="C73" t="n">
-        <v>56.8107</v>
+        <v>154.574</v>
       </c>
       <c r="D73" t="n">
-        <v>81.8317</v>
+        <v>336.991</v>
       </c>
       <c r="E73" t="n">
-        <v>29.7005</v>
+        <v>61.3765</v>
       </c>
       <c r="F73" t="n">
-        <v>47.3093</v>
+        <v>130.699</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>34.2879</v>
+        <v>60.7052</v>
       </c>
       <c r="C74" t="n">
-        <v>56.3192</v>
+        <v>150.518</v>
       </c>
       <c r="D74" t="n">
-        <v>81.3386</v>
+        <v>332.146</v>
       </c>
       <c r="E74" t="n">
-        <v>28.8857</v>
+        <v>59.9009</v>
       </c>
       <c r="F74" t="n">
-        <v>46.7514</v>
+        <v>130.817</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>36.1179</v>
+        <v>59.2726</v>
       </c>
       <c r="C75" t="n">
-        <v>55.6696</v>
+        <v>144.004</v>
       </c>
       <c r="D75" t="n">
-        <v>80.8323</v>
+        <v>329.535</v>
       </c>
       <c r="E75" t="n">
-        <v>28.5797</v>
+        <v>58.7886</v>
       </c>
       <c r="F75" t="n">
-        <v>46.2518</v>
+        <v>127.019</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>35.4353</v>
+        <v>58.1065</v>
       </c>
       <c r="C76" t="n">
-        <v>55.1569</v>
+        <v>142.687</v>
       </c>
       <c r="D76" t="n">
-        <v>80.7967</v>
+        <v>328.138</v>
       </c>
       <c r="E76" t="n">
-        <v>27.8944</v>
+        <v>57.722</v>
       </c>
       <c r="F76" t="n">
-        <v>45.9044</v>
+        <v>122.289</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.242</v>
+        <v>57.32</v>
       </c>
       <c r="C77" t="n">
-        <v>54.9788</v>
+        <v>138.729</v>
       </c>
       <c r="D77" t="n">
-        <v>81.0899</v>
+        <v>323.612</v>
       </c>
       <c r="E77" t="n">
-        <v>27.6512</v>
+        <v>56.4677</v>
       </c>
       <c r="F77" t="n">
-        <v>45.6749</v>
+        <v>120.368</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.4697</v>
+        <v>56.2852</v>
       </c>
       <c r="C78" t="n">
-        <v>54.6275</v>
+        <v>134.653</v>
       </c>
       <c r="D78" t="n">
-        <v>130.598</v>
+        <v>597.553</v>
       </c>
       <c r="E78" t="n">
-        <v>27.1586</v>
+        <v>55.8678</v>
       </c>
       <c r="F78" t="n">
-        <v>45.5745</v>
+        <v>118.267</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>32.7365</v>
+        <v>55.7535</v>
       </c>
       <c r="C79" t="n">
-        <v>54.7109</v>
+        <v>133.277</v>
       </c>
       <c r="D79" t="n">
-        <v>128.437</v>
+        <v>584.508</v>
       </c>
       <c r="E79" t="n">
-        <v>27.2633</v>
+        <v>55.5176</v>
       </c>
       <c r="F79" t="n">
-        <v>45.6865</v>
+        <v>116.451</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>33.5617</v>
+        <v>55.0512</v>
       </c>
       <c r="C80" t="n">
-        <v>54.4357</v>
+        <v>130.36</v>
       </c>
       <c r="D80" t="n">
-        <v>126.654</v>
+        <v>582.595</v>
       </c>
       <c r="E80" t="n">
-        <v>42.8842</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>75.1378</v>
+        <v>215.522</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>46.6824</v>
+        <v>74.3197</v>
       </c>
       <c r="C81" t="n">
-        <v>90.2311</v>
+        <v>253.668</v>
       </c>
       <c r="D81" t="n">
-        <v>124.844</v>
+        <v>604.254</v>
       </c>
       <c r="E81" t="n">
-        <v>42.3972</v>
+        <v>77.0689</v>
       </c>
       <c r="F81" t="n">
-        <v>76.72490000000001</v>
+        <v>223.361</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>46.7125</v>
+        <v>74.6562</v>
       </c>
       <c r="C82" t="n">
-        <v>92.1811</v>
+        <v>247.573</v>
       </c>
       <c r="D82" t="n">
-        <v>123.467</v>
+        <v>537.16</v>
       </c>
       <c r="E82" t="n">
-        <v>41.6646</v>
+        <v>76.66370000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>76.5956</v>
+        <v>211.685</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>43.7176</v>
+        <v>75.0201</v>
       </c>
       <c r="C83" t="n">
-        <v>90.83459999999999</v>
+        <v>235.271</v>
       </c>
       <c r="D83" t="n">
-        <v>122.359</v>
+        <v>572.09</v>
       </c>
       <c r="E83" t="n">
-        <v>40.5787</v>
+        <v>75.8244</v>
       </c>
       <c r="F83" t="n">
-        <v>75.685</v>
+        <v>218.426</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>45.0354</v>
+        <v>75.69199999999999</v>
       </c>
       <c r="C84" t="n">
-        <v>90.70869999999999</v>
+        <v>236.03</v>
       </c>
       <c r="D84" t="n">
-        <v>121.853</v>
+        <v>489.465</v>
       </c>
       <c r="E84" t="n">
-        <v>39.8746</v>
+        <v>73.9815</v>
       </c>
       <c r="F84" t="n">
-        <v>74.1157</v>
+        <v>202.557</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>43.8591</v>
+        <v>74.6604</v>
       </c>
       <c r="C85" t="n">
-        <v>89.13120000000001</v>
+        <v>217.64</v>
       </c>
       <c r="D85" t="n">
-        <v>121.181</v>
+        <v>538.8</v>
       </c>
       <c r="E85" t="n">
-        <v>38.9207</v>
+        <v>73.35809999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>72.82810000000001</v>
+        <v>205.232</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>44.7823</v>
+        <v>75.4248</v>
       </c>
       <c r="C86" t="n">
-        <v>87.64490000000001</v>
+        <v>227.306</v>
       </c>
       <c r="D86" t="n">
-        <v>121.091</v>
+        <v>507.086</v>
       </c>
       <c r="E86" t="n">
-        <v>38.0336</v>
+        <v>71.7753</v>
       </c>
       <c r="F86" t="n">
-        <v>71.36360000000001</v>
+        <v>197.43</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>46.0224</v>
+        <v>74.69750000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>86.43899999999999</v>
+        <v>216.565</v>
       </c>
       <c r="D87" t="n">
-        <v>121.747</v>
+        <v>532.668</v>
       </c>
       <c r="E87" t="n">
-        <v>37.2117</v>
+        <v>70.47790000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>70.0658</v>
+        <v>183.686</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>41.5491</v>
+        <v>74.2675</v>
       </c>
       <c r="C88" t="n">
-        <v>85.31359999999999</v>
+        <v>214.74</v>
       </c>
       <c r="D88" t="n">
-        <v>121.663</v>
+        <v>518.5890000000001</v>
       </c>
       <c r="E88" t="n">
-        <v>36.4375</v>
+        <v>68.65560000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>68.8398</v>
+        <v>166.657</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>42.9138</v>
+        <v>73.3258</v>
       </c>
       <c r="C89" t="n">
-        <v>83.8656</v>
+        <v>209.637</v>
       </c>
       <c r="D89" t="n">
-        <v>122.751</v>
+        <v>504.703</v>
       </c>
       <c r="E89" t="n">
-        <v>35.6909</v>
+        <v>67.90219999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>67.7586</v>
+        <v>178.24</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>43.3241</v>
+        <v>72.3698</v>
       </c>
       <c r="C90" t="n">
-        <v>82.6375</v>
+        <v>207.571</v>
       </c>
       <c r="D90" t="n">
-        <v>123.989</v>
+        <v>512.824</v>
       </c>
       <c r="E90" t="n">
-        <v>34.9046</v>
+        <v>66.74420000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>66.4276</v>
+        <v>180.113</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>40.1084</v>
+        <v>72.6241</v>
       </c>
       <c r="C91" t="n">
-        <v>81.9859</v>
+        <v>203.869</v>
       </c>
       <c r="D91" t="n">
-        <v>125.384</v>
+        <v>497.191</v>
       </c>
       <c r="E91" t="n">
-        <v>34.309</v>
+        <v>65.73739999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>65.5201</v>
+        <v>176.1</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>40.1601</v>
+        <v>72.54819999999999</v>
       </c>
       <c r="C92" t="n">
-        <v>80.8947</v>
+        <v>194.787</v>
       </c>
       <c r="D92" t="n">
-        <v>186.345</v>
+        <v>800.949</v>
       </c>
       <c r="E92" t="n">
-        <v>33.8049</v>
+        <v>64.6031</v>
       </c>
       <c r="F92" t="n">
-        <v>64.57380000000001</v>
+        <v>176.381</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>39.4582</v>
+        <v>70.99979999999999</v>
       </c>
       <c r="C93" t="n">
-        <v>80.2002</v>
+        <v>187.61</v>
       </c>
       <c r="D93" t="n">
-        <v>185.902</v>
+        <v>817.938</v>
       </c>
       <c r="E93" t="n">
-        <v>33.4024</v>
+        <v>65.49420000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>64.75369999999999</v>
+        <v>170.919</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>38.4131</v>
+        <v>71.3498</v>
       </c>
       <c r="C94" t="n">
-        <v>79.6285</v>
+        <v>192.244</v>
       </c>
       <c r="D94" t="n">
-        <v>184.877</v>
+        <v>773.154</v>
       </c>
       <c r="E94" t="n">
-        <v>54.799</v>
+        <v>92.8344</v>
       </c>
       <c r="F94" t="n">
-        <v>118.875</v>
+        <v>309.839</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>59.8165</v>
+        <v>93.9853</v>
       </c>
       <c r="C95" t="n">
-        <v>129.153</v>
+        <v>351.662</v>
       </c>
       <c r="D95" t="n">
-        <v>183.592</v>
+        <v>780.604</v>
       </c>
       <c r="E95" t="n">
-        <v>54.2785</v>
+        <v>88.7932</v>
       </c>
       <c r="F95" t="n">
-        <v>118.712</v>
+        <v>297.862</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>61.1444</v>
+        <v>91.4091</v>
       </c>
       <c r="C96" t="n">
-        <v>127.891</v>
+        <v>302.146</v>
       </c>
       <c r="D96" t="n">
-        <v>183.241</v>
+        <v>729.956</v>
       </c>
       <c r="E96" t="n">
-        <v>52.9125</v>
+        <v>90.7996</v>
       </c>
       <c r="F96" t="n">
-        <v>117.434</v>
+        <v>290.352</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>60.2784</v>
+        <v>94.68470000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>127.661</v>
+        <v>335.562</v>
       </c>
       <c r="D97" t="n">
-        <v>182.047</v>
+        <v>725.548</v>
       </c>
       <c r="E97" t="n">
-        <v>51.9756</v>
+        <v>89.71040000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>115.795</v>
+        <v>292.025</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>57.9241</v>
+        <v>96.298</v>
       </c>
       <c r="C98" t="n">
-        <v>125.024</v>
+        <v>330.842</v>
       </c>
       <c r="D98" t="n">
-        <v>181.3</v>
+        <v>719.635</v>
       </c>
       <c r="E98" t="n">
-        <v>50.5038</v>
+        <v>90.6789</v>
       </c>
       <c r="F98" t="n">
-        <v>113.883</v>
+        <v>285.006</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>55.8888</v>
+        <v>94.735</v>
       </c>
       <c r="C99" t="n">
-        <v>122.481</v>
+        <v>317.472</v>
       </c>
       <c r="D99" t="n">
-        <v>180.97</v>
+        <v>699.494</v>
       </c>
       <c r="E99" t="n">
-        <v>49.3891</v>
+        <v>89.3873</v>
       </c>
       <c r="F99" t="n">
-        <v>111.939</v>
+        <v>275.472</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>55.8178</v>
+        <v>94.3349</v>
       </c>
       <c r="C100" t="n">
-        <v>120.826</v>
+        <v>310.994</v>
       </c>
       <c r="D100" t="n">
-        <v>180.893</v>
+        <v>689.455</v>
       </c>
       <c r="E100" t="n">
-        <v>48.3737</v>
+        <v>88.364</v>
       </c>
       <c r="F100" t="n">
-        <v>110.501</v>
+        <v>280.837</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>55.042</v>
+        <v>96.9221</v>
       </c>
       <c r="C101" t="n">
-        <v>119.461</v>
+        <v>301.281</v>
       </c>
       <c r="D101" t="n">
-        <v>181.616</v>
+        <v>668.374</v>
       </c>
       <c r="E101" t="n">
-        <v>47.2207</v>
+        <v>86.2287</v>
       </c>
       <c r="F101" t="n">
-        <v>108.638</v>
+        <v>282.606</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>55.0762</v>
+        <v>98.05</v>
       </c>
       <c r="C102" t="n">
-        <v>119.619</v>
+        <v>312.741</v>
       </c>
       <c r="D102" t="n">
-        <v>182.209</v>
+        <v>663.866</v>
       </c>
       <c r="E102" t="n">
-        <v>46.3183</v>
+        <v>85.9115</v>
       </c>
       <c r="F102" t="n">
-        <v>107.107</v>
+        <v>279.677</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>51.8503</v>
+        <v>99.65649999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>115.956</v>
+        <v>304.653</v>
       </c>
       <c r="D103" t="n">
-        <v>183.499</v>
+        <v>651.1660000000001</v>
       </c>
       <c r="E103" t="n">
-        <v>45.3979</v>
+        <v>88.2739</v>
       </c>
       <c r="F103" t="n">
-        <v>105.781</v>
+        <v>265.606</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>50.8827</v>
+        <v>99.7406</v>
       </c>
       <c r="C104" t="n">
-        <v>114.904</v>
+        <v>298.244</v>
       </c>
       <c r="D104" t="n">
-        <v>184.723</v>
+        <v>647.098</v>
       </c>
       <c r="E104" t="n">
-        <v>44.5701</v>
+        <v>85.1866</v>
       </c>
       <c r="F104" t="n">
-        <v>102.649</v>
+        <v>261.956</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>52.5057</v>
+        <v>101.098</v>
       </c>
       <c r="C105" t="n">
-        <v>115.009</v>
+        <v>297.999</v>
       </c>
       <c r="D105" t="n">
-        <v>186.338</v>
+        <v>644.287</v>
       </c>
       <c r="E105" t="n">
-        <v>43.8262</v>
+        <v>86.0849</v>
       </c>
       <c r="F105" t="n">
-        <v>102.875</v>
+        <v>262.967</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>50.6933</v>
+        <v>102.55</v>
       </c>
       <c r="C106" t="n">
-        <v>114.264</v>
+        <v>287.258</v>
       </c>
       <c r="D106" t="n">
-        <v>188.073</v>
+        <v>619.498</v>
       </c>
       <c r="E106" t="n">
-        <v>43.0906</v>
+        <v>85.6382</v>
       </c>
       <c r="F106" t="n">
-        <v>100.472</v>
+        <v>239.73</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>50.1437</v>
+        <v>98.9438</v>
       </c>
       <c r="C107" t="n">
-        <v>112.914</v>
+        <v>279.965</v>
       </c>
       <c r="D107" t="n">
-        <v>252.685</v>
+        <v>918.6559999999999</v>
       </c>
       <c r="E107" t="n">
-        <v>42.5652</v>
+        <v>86.6735</v>
       </c>
       <c r="F107" t="n">
-        <v>98.4423</v>
+        <v>249.657</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>49.6432</v>
+        <v>100.723</v>
       </c>
       <c r="C108" t="n">
-        <v>112.276</v>
+        <v>258.312</v>
       </c>
       <c r="D108" t="n">
-        <v>250.116</v>
+        <v>890.027</v>
       </c>
       <c r="E108" t="n">
-        <v>64.92910000000001</v>
+        <v>114.395</v>
       </c>
       <c r="F108" t="n">
-        <v>264.75</v>
+        <v>411.167</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>49.2711</v>
+        <v>101.038</v>
       </c>
       <c r="C109" t="n">
-        <v>111.597</v>
+        <v>250.293</v>
       </c>
       <c r="D109" t="n">
-        <v>247.706</v>
+        <v>883.425</v>
       </c>
       <c r="E109" t="n">
-        <v>64.2546</v>
+        <v>113.143</v>
       </c>
       <c r="F109" t="n">
-        <v>266.384</v>
+        <v>400.174</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>73.785</v>
+        <v>145.012</v>
       </c>
       <c r="C110" t="n">
-        <v>290.058</v>
+        <v>426.011</v>
       </c>
       <c r="D110" t="n">
-        <v>245.886</v>
+        <v>860.663</v>
       </c>
       <c r="E110" t="n">
-        <v>62.8088</v>
+        <v>133.724</v>
       </c>
       <c r="F110" t="n">
-        <v>266.701</v>
+        <v>397.762</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>70.9776</v>
+        <v>144.435</v>
       </c>
       <c r="C111" t="n">
-        <v>290.647</v>
+        <v>413.127</v>
       </c>
       <c r="D111" t="n">
-        <v>244.371</v>
+        <v>840.841</v>
       </c>
       <c r="E111" t="n">
-        <v>57.436</v>
+        <v>125.745</v>
       </c>
       <c r="F111" t="n">
-        <v>267.289</v>
+        <v>385.433</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>69.931</v>
+        <v>132.152</v>
       </c>
       <c r="C112" t="n">
-        <v>290.057</v>
+        <v>412.286</v>
       </c>
       <c r="D112" t="n">
-        <v>242.869</v>
+        <v>812.746</v>
       </c>
       <c r="E112" t="n">
-        <v>56.2648</v>
+        <v>108.052</v>
       </c>
       <c r="F112" t="n">
-        <v>268.449</v>
+        <v>382.887</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>69.49720000000001</v>
+        <v>116.827</v>
       </c>
       <c r="C113" t="n">
-        <v>290.376</v>
+        <v>400.33</v>
       </c>
       <c r="D113" t="n">
-        <v>243.755</v>
+        <v>808.441</v>
       </c>
       <c r="E113" t="n">
-        <v>58.9213</v>
+        <v>110.574</v>
       </c>
       <c r="F113" t="n">
-        <v>268.731</v>
+        <v>386.683</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>62.2672</v>
+        <v>120.569</v>
       </c>
       <c r="C114" t="n">
-        <v>289.85</v>
+        <v>410.74</v>
       </c>
       <c r="D114" t="n">
-        <v>245.627</v>
+        <v>810.0940000000001</v>
       </c>
       <c r="E114" t="n">
-        <v>57.7278</v>
+        <v>110.742</v>
       </c>
       <c r="F114" t="n">
-        <v>267.197</v>
+        <v>374.801</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>62.0897</v>
+        <v>123.079</v>
       </c>
       <c r="C115" t="n">
-        <v>288.931</v>
+        <v>395.423</v>
       </c>
       <c r="D115" t="n">
-        <v>248.681</v>
+        <v>788.792</v>
       </c>
       <c r="E115" t="n">
-        <v>56.8058</v>
+        <v>109.392</v>
       </c>
       <c r="F115" t="n">
-        <v>269.558</v>
+        <v>357.255</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>62.9389</v>
+        <v>131.364</v>
       </c>
       <c r="C116" t="n">
-        <v>290.481</v>
+        <v>386.478</v>
       </c>
       <c r="D116" t="n">
-        <v>246.77</v>
+        <v>783.484</v>
       </c>
       <c r="E116" t="n">
-        <v>55.6349</v>
+        <v>112.583</v>
       </c>
       <c r="F116" t="n">
-        <v>268.855</v>
+        <v>359.637</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>64.0973</v>
+        <v>133.698</v>
       </c>
       <c r="C117" t="n">
-        <v>290.701</v>
+        <v>379.602</v>
       </c>
       <c r="D117" t="n">
-        <v>248.929</v>
+        <v>766.033</v>
       </c>
       <c r="E117" t="n">
-        <v>54.6976</v>
+        <v>114.389</v>
       </c>
       <c r="F117" t="n">
-        <v>270.059</v>
+        <v>340.977</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>62.9089</v>
+        <v>133.027</v>
       </c>
       <c r="C118" t="n">
-        <v>290.46</v>
+        <v>357.92</v>
       </c>
       <c r="D118" t="n">
-        <v>242.352</v>
+        <v>746.981</v>
       </c>
       <c r="E118" t="n">
-        <v>50.6006</v>
+        <v>109.408</v>
       </c>
       <c r="F118" t="n">
-        <v>224.593</v>
+        <v>328.029</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>59.1125</v>
+        <v>133.232</v>
       </c>
       <c r="C119" t="n">
-        <v>147.009</v>
+        <v>342.482</v>
       </c>
       <c r="D119" t="n">
-        <v>242.597</v>
+        <v>736.636</v>
       </c>
       <c r="E119" t="n">
-        <v>49.8972</v>
+        <v>118.871</v>
       </c>
       <c r="F119" t="n">
-        <v>225.388</v>
+        <v>318.984</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>61.3222</v>
+        <v>137.415</v>
       </c>
       <c r="C120" t="n">
-        <v>290.362</v>
+        <v>338.358</v>
       </c>
       <c r="D120" t="n">
-        <v>244.096</v>
+        <v>726.056</v>
       </c>
       <c r="E120" t="n">
-        <v>49.1461</v>
+        <v>122.306</v>
       </c>
       <c r="F120" t="n">
-        <v>247.959</v>
+        <v>311.989</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>58.7155</v>
+        <v>139.031</v>
       </c>
       <c r="C121" t="n">
-        <v>290.548</v>
+        <v>335.591</v>
       </c>
       <c r="D121" t="n">
-        <v>316.061</v>
+        <v>1033.14</v>
       </c>
       <c r="E121" t="n">
-        <v>48.7583</v>
+        <v>127.157</v>
       </c>
       <c r="F121" t="n">
-        <v>224.349</v>
+        <v>307.818</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>57.3635</v>
+        <v>137.488</v>
       </c>
       <c r="C122" t="n">
-        <v>291.56</v>
+        <v>330.643</v>
       </c>
       <c r="D122" t="n">
-        <v>312.122</v>
+        <v>1035.88</v>
       </c>
       <c r="E122" t="n">
-        <v>48.2664</v>
+        <v>124.535</v>
       </c>
       <c r="F122" t="n">
-        <v>273.299</v>
+        <v>303.281</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>57.6881</v>
+        <v>141.13</v>
       </c>
       <c r="C123" t="n">
-        <v>292.25</v>
+        <v>328.009</v>
       </c>
       <c r="D123" t="n">
-        <v>307.665</v>
+        <v>1026.15</v>
       </c>
       <c r="E123" t="n">
-        <v>70.0082</v>
+        <v>166.047</v>
       </c>
       <c r="F123" t="n">
-        <v>327.589</v>
+        <v>481.049</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>79.261</v>
+        <v>174.138</v>
       </c>
       <c r="C124" t="n">
-        <v>356.844</v>
+        <v>504.111</v>
       </c>
       <c r="D124" t="n">
-        <v>304.319</v>
+        <v>993.772</v>
       </c>
       <c r="E124" t="n">
-        <v>68.9726</v>
+        <v>167.112</v>
       </c>
       <c r="F124" t="n">
-        <v>326.973</v>
+        <v>465.749</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>80.0364</v>
+        <v>181.553</v>
       </c>
       <c r="C125" t="n">
-        <v>353.079</v>
+        <v>478.29</v>
       </c>
       <c r="D125" t="n">
-        <v>301.094</v>
+        <v>965.374</v>
       </c>
       <c r="E125" t="n">
-        <v>68.087</v>
+        <v>164.115</v>
       </c>
       <c r="F125" t="n">
-        <v>326.272</v>
+        <v>454.195</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>79.26600000000001</v>
+        <v>173.511</v>
       </c>
       <c r="C126" t="n">
-        <v>353.671</v>
+        <v>476.653</v>
       </c>
       <c r="D126" t="n">
-        <v>298.32</v>
+        <v>941.0890000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>66.77800000000001</v>
+        <v>162.039</v>
       </c>
       <c r="F126" t="n">
-        <v>325.662</v>
+        <v>439.236</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>77.07940000000001</v>
+        <v>175.192</v>
       </c>
       <c r="C127" t="n">
-        <v>352.258</v>
+        <v>463.503</v>
       </c>
       <c r="D127" t="n">
-        <v>295.974</v>
+        <v>919.527</v>
       </c>
       <c r="E127" t="n">
-        <v>65.9375</v>
+        <v>166.411</v>
       </c>
       <c r="F127" t="n">
-        <v>324.943</v>
+        <v>430.857</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>73.83969999999999</v>
+        <v>180.637</v>
       </c>
       <c r="C128" t="n">
-        <v>350.517</v>
+        <v>478.637</v>
       </c>
       <c r="D128" t="n">
-        <v>294.082</v>
+        <v>917.562</v>
       </c>
       <c r="E128" t="n">
-        <v>65.8961</v>
+        <v>167.199</v>
       </c>
       <c r="F128" t="n">
-        <v>324.51</v>
+        <v>430.819</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>72.1682</v>
+        <v>176.085</v>
       </c>
       <c r="C129" t="n">
-        <v>349.304</v>
+        <v>455.945</v>
       </c>
       <c r="D129" t="n">
-        <v>292.389</v>
+        <v>874.1130000000001</v>
       </c>
       <c r="E129" t="n">
-        <v>65.1504</v>
+        <v>164.067</v>
       </c>
       <c r="F129" t="n">
-        <v>323.396</v>
+        <v>426.609</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>74.0534</v>
+        <v>174.626</v>
       </c>
       <c r="C130" t="n">
-        <v>348.802</v>
+        <v>447.788</v>
       </c>
       <c r="D130" t="n">
-        <v>291.206</v>
+        <v>848.617</v>
       </c>
       <c r="E130" t="n">
-        <v>66.25620000000001</v>
+        <v>163.804</v>
       </c>
       <c r="F130" t="n">
-        <v>323.171</v>
+        <v>417.458</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>73.173</v>
+        <v>171.983</v>
       </c>
       <c r="C131" t="n">
-        <v>346.442</v>
+        <v>436.761</v>
       </c>
       <c r="D131" t="n">
-        <v>290.534</v>
+        <v>830.679</v>
       </c>
       <c r="E131" t="n">
-        <v>63.7877</v>
+        <v>162.729</v>
       </c>
       <c r="F131" t="n">
-        <v>323.123</v>
+        <v>400.163</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>71.5853</v>
+        <v>171.894</v>
       </c>
       <c r="C132" t="n">
-        <v>343.368</v>
+        <v>423.862</v>
       </c>
       <c r="D132" t="n">
-        <v>289.963</v>
+        <v>835.524</v>
       </c>
       <c r="E132" t="n">
-        <v>62.1984</v>
+        <v>162.375</v>
       </c>
       <c r="F132" t="n">
-        <v>322.842</v>
+        <v>394.121</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>70.748</v>
+        <v>171.772</v>
       </c>
       <c r="C133" t="n">
-        <v>346.198</v>
+        <v>410.523</v>
       </c>
       <c r="D133" t="n">
-        <v>289.814</v>
+        <v>835.813</v>
       </c>
       <c r="E133" t="n">
-        <v>62.0086</v>
+        <v>163.21</v>
       </c>
       <c r="F133" t="n">
-        <v>323.258</v>
+        <v>388.557</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>69.99550000000001</v>
+        <v>172.324</v>
       </c>
       <c r="C134" t="n">
-        <v>344.201</v>
+        <v>414.153</v>
       </c>
       <c r="D134" t="n">
-        <v>287.571</v>
+        <v>811.837</v>
       </c>
       <c r="E134" t="n">
-        <v>59.5929</v>
+        <v>160.811</v>
       </c>
       <c r="F134" t="n">
-        <v>297.815</v>
+        <v>376.498</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>69.6782</v>
+        <v>168.676</v>
       </c>
       <c r="C135" t="n">
-        <v>344.019</v>
+        <v>401.189</v>
       </c>
       <c r="D135" t="n">
-        <v>362.524</v>
+        <v>1134.35</v>
       </c>
       <c r="E135" t="n">
-        <v>59.1027</v>
+        <v>163.942</v>
       </c>
       <c r="F135" t="n">
-        <v>296.703</v>
+        <v>381.154</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>69.0198</v>
+        <v>174.893</v>
       </c>
       <c r="C136" t="n">
-        <v>343.1</v>
+        <v>401.909</v>
       </c>
       <c r="D136" t="n">
-        <v>356.395</v>
+        <v>1126.25</v>
       </c>
       <c r="E136" t="n">
-        <v>58.8049</v>
+        <v>163.402</v>
       </c>
       <c r="F136" t="n">
-        <v>322.376</v>
+        <v>376.62</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>68.03279999999999</v>
+        <v>174.2</v>
       </c>
       <c r="C137" t="n">
-        <v>341.3</v>
+        <v>393.98</v>
       </c>
       <c r="D137" t="n">
-        <v>350.969</v>
+        <v>1070.56</v>
       </c>
       <c r="E137" t="n">
-        <v>79.8981</v>
+        <v>203.066</v>
       </c>
       <c r="F137" t="n">
-        <v>376.071</v>
+        <v>561.698</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>90.67310000000001</v>
+        <v>203.456</v>
       </c>
       <c r="C138" t="n">
-        <v>402.821</v>
+        <v>577.678</v>
       </c>
       <c r="D138" t="n">
-        <v>346.279</v>
+        <v>1039.21</v>
       </c>
       <c r="E138" t="n">
-        <v>79.2881</v>
+        <v>205.223</v>
       </c>
       <c r="F138" t="n">
-        <v>374.533</v>
+        <v>531.029</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>89.02979999999999</v>
+        <v>204.205</v>
       </c>
       <c r="C139" t="n">
-        <v>398.264</v>
+        <v>565.9690000000001</v>
       </c>
       <c r="D139" t="n">
-        <v>341.294</v>
+        <v>1021.78</v>
       </c>
       <c r="E139" t="n">
-        <v>78.65770000000001</v>
+        <v>200.602</v>
       </c>
       <c r="F139" t="n">
-        <v>373.555</v>
+        <v>528.895</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>85.40009999999999</v>
+        <v>207.403</v>
       </c>
       <c r="C140" t="n">
-        <v>394.567</v>
+        <v>555.845</v>
       </c>
       <c r="D140" t="n">
-        <v>337.309</v>
+        <v>1013.94</v>
       </c>
       <c r="E140" t="n">
-        <v>77.82680000000001</v>
+        <v>199.568</v>
       </c>
       <c r="F140" t="n">
-        <v>371.518</v>
+        <v>507.37</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>86.57680000000001</v>
+        <v>207.377</v>
       </c>
       <c r="C141" t="n">
-        <v>394.022</v>
+        <v>538.641</v>
       </c>
       <c r="D141" t="n">
-        <v>333.751</v>
+        <v>995.489</v>
       </c>
       <c r="E141" t="n">
-        <v>77.13630000000001</v>
+        <v>198.392</v>
       </c>
       <c r="F141" t="n">
-        <v>369.981</v>
+        <v>493.698</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>85.1566</v>
+        <v>199.528</v>
       </c>
       <c r="C142" t="n">
-        <v>391.054</v>
+        <v>527.558</v>
       </c>
       <c r="D142" t="n">
-        <v>332.86</v>
+        <v>958.72</v>
       </c>
       <c r="E142" t="n">
-        <v>78.4967</v>
+        <v>194.467</v>
       </c>
       <c r="F142" t="n">
-        <v>367.482</v>
+        <v>482.132</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>81.3877</v>
+        <v>204.498</v>
       </c>
       <c r="C143" t="n">
-        <v>390.058</v>
+        <v>518.226</v>
       </c>
       <c r="D143" t="n">
-        <v>330.407</v>
+        <v>945.903</v>
       </c>
       <c r="E143" t="n">
-        <v>77.8546</v>
+        <v>190.199</v>
       </c>
       <c r="F143" t="n">
-        <v>366.332</v>
+        <v>466.91</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>55.1383</v>
+        <v>55.2328</v>
       </c>
       <c r="C2" t="n">
-        <v>82.4915</v>
+        <v>82.6602</v>
       </c>
       <c r="D2" t="n">
-        <v>130.527</v>
+        <v>130.496</v>
       </c>
       <c r="E2" t="n">
-        <v>55.4733</v>
+        <v>55.686</v>
       </c>
       <c r="F2" t="n">
-        <v>78.1561</v>
+        <v>78.1617</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>53.7072</v>
+        <v>53.9874</v>
       </c>
       <c r="C3" t="n">
-        <v>80.42400000000001</v>
+        <v>81.239</v>
       </c>
       <c r="D3" t="n">
-        <v>127.979</v>
+        <v>129.359</v>
       </c>
       <c r="E3" t="n">
-        <v>53.7792</v>
+        <v>53.952</v>
       </c>
       <c r="F3" t="n">
-        <v>76.6262</v>
+        <v>76.809</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>52.439</v>
+        <v>52.726</v>
       </c>
       <c r="C4" t="n">
-        <v>79.0403</v>
+        <v>79.1452</v>
       </c>
       <c r="D4" t="n">
-        <v>126.135</v>
+        <v>126.714</v>
       </c>
       <c r="E4" t="n">
-        <v>52.4705</v>
+        <v>52.5822</v>
       </c>
       <c r="F4" t="n">
-        <v>75.0168</v>
+        <v>74.8133</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>51.2965</v>
+        <v>51.4458</v>
       </c>
       <c r="C5" t="n">
-        <v>77.3528</v>
+        <v>77.4756</v>
       </c>
       <c r="D5" t="n">
-        <v>124.504</v>
+        <v>124.614</v>
       </c>
       <c r="E5" t="n">
-        <v>51.2227</v>
+        <v>51.3794</v>
       </c>
       <c r="F5" t="n">
-        <v>73.59869999999999</v>
+        <v>73.8064</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>50.133</v>
+        <v>50.2337</v>
       </c>
       <c r="C6" t="n">
-        <v>75.61360000000001</v>
+        <v>75.7337</v>
       </c>
       <c r="D6" t="n">
-        <v>122.567</v>
+        <v>123.224</v>
       </c>
       <c r="E6" t="n">
-        <v>50.2262</v>
+        <v>50.3318</v>
       </c>
       <c r="F6" t="n">
-        <v>72.1353</v>
+        <v>72.1788</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>49.2857</v>
+        <v>49.4058</v>
       </c>
       <c r="C7" t="n">
-        <v>74.6084</v>
+        <v>74.92700000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>169.268</v>
+        <v>170.654</v>
       </c>
       <c r="E7" t="n">
-        <v>49.2674</v>
+        <v>49.4335</v>
       </c>
       <c r="F7" t="n">
-        <v>70.69929999999999</v>
+        <v>71.0074</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>48.4795</v>
+        <v>48.5986</v>
       </c>
       <c r="C8" t="n">
-        <v>73.16800000000001</v>
+        <v>73.4558</v>
       </c>
       <c r="D8" t="n">
-        <v>166.691</v>
+        <v>167.958</v>
       </c>
       <c r="E8" t="n">
-        <v>48.6218</v>
+        <v>48.8038</v>
       </c>
       <c r="F8" t="n">
-        <v>69.71899999999999</v>
+        <v>69.8989</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>47.7655</v>
+        <v>47.9651</v>
       </c>
       <c r="C9" t="n">
-        <v>72.4066</v>
+        <v>72.6005</v>
       </c>
       <c r="D9" t="n">
-        <v>163.464</v>
+        <v>162.526</v>
       </c>
       <c r="E9" t="n">
-        <v>67.8074</v>
+        <v>68.1212</v>
       </c>
       <c r="F9" t="n">
-        <v>99.4658</v>
+        <v>100.206</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>64.6015</v>
+        <v>64.9058</v>
       </c>
       <c r="C10" t="n">
-        <v>103.934</v>
+        <v>104.669</v>
       </c>
       <c r="D10" t="n">
-        <v>158.673</v>
+        <v>159.898</v>
       </c>
       <c r="E10" t="n">
-        <v>65.7534</v>
+        <v>65.97920000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>97.1159</v>
+        <v>97.8549</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>62.8491</v>
+        <v>63.0563</v>
       </c>
       <c r="C11" t="n">
-        <v>101.394</v>
+        <v>101.381</v>
       </c>
       <c r="D11" t="n">
-        <v>154.296</v>
+        <v>154.949</v>
       </c>
       <c r="E11" t="n">
-        <v>63.7977</v>
+        <v>63.9303</v>
       </c>
       <c r="F11" t="n">
-        <v>93.9199</v>
+        <v>94.1096</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>61.0911</v>
+        <v>61.3648</v>
       </c>
       <c r="C12" t="n">
-        <v>97.82810000000001</v>
+        <v>98.35639999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>151.057</v>
+        <v>153.26</v>
       </c>
       <c r="E12" t="n">
-        <v>61.8948</v>
+        <v>62.0944</v>
       </c>
       <c r="F12" t="n">
-        <v>90.9973</v>
+        <v>91.9734</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>59.541</v>
+        <v>59.8143</v>
       </c>
       <c r="C13" t="n">
-        <v>95.8544</v>
+        <v>96.1023</v>
       </c>
       <c r="D13" t="n">
-        <v>149.52</v>
+        <v>149.345</v>
       </c>
       <c r="E13" t="n">
-        <v>60.1324</v>
+        <v>60.3647</v>
       </c>
       <c r="F13" t="n">
-        <v>89.44970000000001</v>
+        <v>89.51860000000001</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>58.828</v>
+        <v>58.2646</v>
       </c>
       <c r="C14" t="n">
-        <v>93.3314</v>
+        <v>93.3296</v>
       </c>
       <c r="D14" t="n">
-        <v>146.137</v>
+        <v>146.906</v>
       </c>
       <c r="E14" t="n">
-        <v>58.4297</v>
+        <v>58.5835</v>
       </c>
       <c r="F14" t="n">
-        <v>86.6949</v>
+        <v>87.1934</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>56.6283</v>
+        <v>56.6619</v>
       </c>
       <c r="C15" t="n">
-        <v>91.4971</v>
+        <v>91.77500000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>142.997</v>
+        <v>144.141</v>
       </c>
       <c r="E15" t="n">
-        <v>56.8842</v>
+        <v>57.0208</v>
       </c>
       <c r="F15" t="n">
-        <v>84.8531</v>
+        <v>84.87009999999999</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>55.2237</v>
+        <v>55.3385</v>
       </c>
       <c r="C16" t="n">
-        <v>89.1825</v>
+        <v>89.3068</v>
       </c>
       <c r="D16" t="n">
-        <v>141.495</v>
+        <v>141.868</v>
       </c>
       <c r="E16" t="n">
-        <v>55.3661</v>
+        <v>55.5789</v>
       </c>
       <c r="F16" t="n">
-        <v>82.19799999999999</v>
+        <v>82.5896</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>53.8627</v>
+        <v>54.0565</v>
       </c>
       <c r="C17" t="n">
-        <v>87.1271</v>
+        <v>86.8934</v>
       </c>
       <c r="D17" t="n">
-        <v>138.874</v>
+        <v>139.225</v>
       </c>
       <c r="E17" t="n">
-        <v>53.9538</v>
+        <v>54.1698</v>
       </c>
       <c r="F17" t="n">
-        <v>80.0771</v>
+        <v>81.1579</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>52.6349</v>
+        <v>52.837</v>
       </c>
       <c r="C18" t="n">
-        <v>85.44759999999999</v>
+        <v>85.17570000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>137.064</v>
+        <v>136.259</v>
       </c>
       <c r="E18" t="n">
-        <v>52.6372</v>
+        <v>52.906</v>
       </c>
       <c r="F18" t="n">
-        <v>78.39319999999999</v>
+        <v>79.7714</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>51.5238</v>
+        <v>51.7148</v>
       </c>
       <c r="C19" t="n">
-        <v>83.1741</v>
+        <v>82.5823</v>
       </c>
       <c r="D19" t="n">
-        <v>135.141</v>
+        <v>136.099</v>
       </c>
       <c r="E19" t="n">
-        <v>51.4885</v>
+        <v>51.5953</v>
       </c>
       <c r="F19" t="n">
-        <v>76.748</v>
+        <v>77.3276</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>50.674</v>
+        <v>50.6453</v>
       </c>
       <c r="C20" t="n">
-        <v>81.03740000000001</v>
+        <v>81.04040000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>133.729</v>
+        <v>133.886</v>
       </c>
       <c r="E20" t="n">
-        <v>50.3725</v>
+        <v>50.5828</v>
       </c>
       <c r="F20" t="n">
-        <v>75.7311</v>
+        <v>75.4021</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>49.6572</v>
+        <v>49.7695</v>
       </c>
       <c r="C21" t="n">
-        <v>79.0809</v>
+        <v>79.3425</v>
       </c>
       <c r="D21" t="n">
-        <v>185.142</v>
+        <v>185.836</v>
       </c>
       <c r="E21" t="n">
-        <v>49.5549</v>
+        <v>49.665</v>
       </c>
       <c r="F21" t="n">
-        <v>74.1785</v>
+        <v>74.0822</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>48.9094</v>
+        <v>48.9944</v>
       </c>
       <c r="C22" t="n">
-        <v>78.12350000000001</v>
+        <v>78.087</v>
       </c>
       <c r="D22" t="n">
-        <v>181.303</v>
+        <v>181.632</v>
       </c>
       <c r="E22" t="n">
-        <v>48.8775</v>
+        <v>49.0211</v>
       </c>
       <c r="F22" t="n">
-        <v>73.548</v>
+        <v>73.0806</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>48.4045</v>
+        <v>48.4681</v>
       </c>
       <c r="C23" t="n">
-        <v>77.1139</v>
+        <v>77.03270000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>176.736</v>
+        <v>176.727</v>
       </c>
       <c r="E23" t="n">
-        <v>68.7102</v>
+        <v>68.8959</v>
       </c>
       <c r="F23" t="n">
-        <v>105.502</v>
+        <v>106.316</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>65.774</v>
+        <v>65.991</v>
       </c>
       <c r="C24" t="n">
-        <v>111.449</v>
+        <v>111.454</v>
       </c>
       <c r="D24" t="n">
-        <v>172.514</v>
+        <v>173.632</v>
       </c>
       <c r="E24" t="n">
-        <v>66.5809</v>
+        <v>66.8249</v>
       </c>
       <c r="F24" t="n">
-        <v>102.04</v>
+        <v>102.661</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>64.026</v>
+        <v>64.2831</v>
       </c>
       <c r="C25" t="n">
-        <v>108.048</v>
+        <v>108.249</v>
       </c>
       <c r="D25" t="n">
-        <v>169.311</v>
+        <v>169.224</v>
       </c>
       <c r="E25" t="n">
-        <v>64.6528</v>
+        <v>64.8425</v>
       </c>
       <c r="F25" t="n">
-        <v>99.3562</v>
+        <v>99.9328</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>62.454</v>
+        <v>62.6652</v>
       </c>
       <c r="C26" t="n">
-        <v>105.936</v>
+        <v>105.962</v>
       </c>
       <c r="D26" t="n">
-        <v>165.301</v>
+        <v>166.692</v>
       </c>
       <c r="E26" t="n">
-        <v>62.8097</v>
+        <v>63.0518</v>
       </c>
       <c r="F26" t="n">
-        <v>96.3754</v>
+        <v>96.6708</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>60.7838</v>
+        <v>61.0321</v>
       </c>
       <c r="C27" t="n">
-        <v>101.375</v>
+        <v>102.459</v>
       </c>
       <c r="D27" t="n">
-        <v>161.882</v>
+        <v>162.846</v>
       </c>
       <c r="E27" t="n">
-        <v>61.0283</v>
+        <v>61.3019</v>
       </c>
       <c r="F27" t="n">
-        <v>95.1991</v>
+        <v>95.29600000000001</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>59.2583</v>
+        <v>59.6245</v>
       </c>
       <c r="C28" t="n">
-        <v>99.6634</v>
+        <v>100.043</v>
       </c>
       <c r="D28" t="n">
-        <v>157.557</v>
+        <v>159.358</v>
       </c>
       <c r="E28" t="n">
-        <v>59.3888</v>
+        <v>59.6002</v>
       </c>
       <c r="F28" t="n">
-        <v>91.42570000000001</v>
+        <v>92.02760000000001</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>57.9737</v>
+        <v>58.0653</v>
       </c>
       <c r="C29" t="n">
-        <v>96.3629</v>
+        <v>97.3201</v>
       </c>
       <c r="D29" t="n">
-        <v>156.805</v>
+        <v>157.348</v>
       </c>
       <c r="E29" t="n">
-        <v>57.864</v>
+        <v>57.9727</v>
       </c>
       <c r="F29" t="n">
-        <v>90.05110000000001</v>
+        <v>89.6177</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>56.4702</v>
+        <v>57.2509</v>
       </c>
       <c r="C30" t="n">
-        <v>96.1058</v>
+        <v>95.7517</v>
       </c>
       <c r="D30" t="n">
-        <v>154.286</v>
+        <v>154.223</v>
       </c>
       <c r="E30" t="n">
-        <v>56.2924</v>
+        <v>56.5918</v>
       </c>
       <c r="F30" t="n">
-        <v>85.8344</v>
+        <v>86.4961</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>55.2149</v>
+        <v>55.4095</v>
       </c>
       <c r="C31" t="n">
-        <v>93.07680000000001</v>
+        <v>93.4791</v>
       </c>
       <c r="D31" t="n">
-        <v>152.621</v>
+        <v>153.33</v>
       </c>
       <c r="E31" t="n">
-        <v>54.8725</v>
+        <v>55.0724</v>
       </c>
       <c r="F31" t="n">
-        <v>86.2636</v>
+        <v>86.76139999999999</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>53.9513</v>
+        <v>54.1309</v>
       </c>
       <c r="C32" t="n">
-        <v>90.5628</v>
+        <v>91.1862</v>
       </c>
       <c r="D32" t="n">
-        <v>147.884</v>
+        <v>149.565</v>
       </c>
       <c r="E32" t="n">
-        <v>53.6049</v>
+        <v>53.8079</v>
       </c>
       <c r="F32" t="n">
-        <v>83.3224</v>
+        <v>83.2529</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>52.8113</v>
+        <v>53.0812</v>
       </c>
       <c r="C33" t="n">
-        <v>87.97790000000001</v>
+        <v>88.6767</v>
       </c>
       <c r="D33" t="n">
-        <v>146.288</v>
+        <v>146.407</v>
       </c>
       <c r="E33" t="n">
-        <v>52.3629</v>
+        <v>52.6492</v>
       </c>
       <c r="F33" t="n">
-        <v>82.0903</v>
+        <v>82.43470000000001</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>51.7061</v>
+        <v>51.9687</v>
       </c>
       <c r="C34" t="n">
-        <v>87.017</v>
+        <v>87.26990000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>146.034</v>
+        <v>146.761</v>
       </c>
       <c r="E34" t="n">
-        <v>51.3825</v>
+        <v>51.5074</v>
       </c>
       <c r="F34" t="n">
-        <v>79.4299</v>
+        <v>79.73779999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>50.9019</v>
+        <v>50.9017</v>
       </c>
       <c r="C35" t="n">
-        <v>85.0635</v>
+        <v>85.1855</v>
       </c>
       <c r="D35" t="n">
-        <v>205.862</v>
+        <v>205.077</v>
       </c>
       <c r="E35" t="n">
-        <v>50.4774</v>
+        <v>50.5783</v>
       </c>
       <c r="F35" t="n">
-        <v>78.7029</v>
+        <v>79.6711</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>50.0691</v>
+        <v>50.2048</v>
       </c>
       <c r="C36" t="n">
-        <v>83.5423</v>
+        <v>84.2253</v>
       </c>
       <c r="D36" t="n">
-        <v>201.679</v>
+        <v>203.833</v>
       </c>
       <c r="E36" t="n">
-        <v>49.803</v>
+        <v>49.8716</v>
       </c>
       <c r="F36" t="n">
-        <v>77.1003</v>
+        <v>77.0035</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>49.4376</v>
+        <v>49.4777</v>
       </c>
       <c r="C37" t="n">
-        <v>81.7795</v>
+        <v>82.0415</v>
       </c>
       <c r="D37" t="n">
-        <v>195.538</v>
+        <v>195.938</v>
       </c>
       <c r="E37" t="n">
-        <v>70.1217</v>
+        <v>70.4659</v>
       </c>
       <c r="F37" t="n">
-        <v>110.625</v>
+        <v>114.035</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>67.63079999999999</v>
+        <v>67.9825</v>
       </c>
       <c r="C38" t="n">
-        <v>120.875</v>
+        <v>119.946</v>
       </c>
       <c r="D38" t="n">
-        <v>190.153</v>
+        <v>189.955</v>
       </c>
       <c r="E38" t="n">
-        <v>68.0955</v>
+        <v>68.42959999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>107.847</v>
+        <v>108.941</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>66.03019999999999</v>
+        <v>66.151</v>
       </c>
       <c r="C39" t="n">
-        <v>115.719</v>
+        <v>118.662</v>
       </c>
       <c r="D39" t="n">
-        <v>183.73</v>
+        <v>185.877</v>
       </c>
       <c r="E39" t="n">
-        <v>66.1473</v>
+        <v>66.4278</v>
       </c>
       <c r="F39" t="n">
-        <v>106.629</v>
+        <v>107.17</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>64.1444</v>
+        <v>64.49469999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>113.477</v>
+        <v>113.684</v>
       </c>
       <c r="D40" t="n">
-        <v>181.863</v>
+        <v>183.4</v>
       </c>
       <c r="E40" t="n">
-        <v>64.29519999999999</v>
+        <v>64.491</v>
       </c>
       <c r="F40" t="n">
-        <v>103.318</v>
+        <v>106.078</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>62.4504</v>
+        <v>62.8333</v>
       </c>
       <c r="C41" t="n">
-        <v>111.185</v>
+        <v>111.611</v>
       </c>
       <c r="D41" t="n">
-        <v>179.195</v>
+        <v>181.877</v>
       </c>
       <c r="E41" t="n">
-        <v>62.5909</v>
+        <v>62.6402</v>
       </c>
       <c r="F41" t="n">
-        <v>103.328</v>
+        <v>103.211</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>61.0018</v>
+        <v>61.0416</v>
       </c>
       <c r="C42" t="n">
-        <v>109.092</v>
+        <v>109.268</v>
       </c>
       <c r="D42" t="n">
-        <v>174.346</v>
+        <v>173.646</v>
       </c>
       <c r="E42" t="n">
-        <v>60.9032</v>
+        <v>60.94</v>
       </c>
       <c r="F42" t="n">
-        <v>98.3265</v>
+        <v>98.8265</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>59.5345</v>
+        <v>59.6251</v>
       </c>
       <c r="C43" t="n">
-        <v>105.917</v>
+        <v>105.631</v>
       </c>
       <c r="D43" t="n">
-        <v>170.473</v>
+        <v>170.44</v>
       </c>
       <c r="E43" t="n">
-        <v>59.311</v>
+        <v>59.2901</v>
       </c>
       <c r="F43" t="n">
-        <v>97.05719999999999</v>
+        <v>98.1277</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>58.2298</v>
+        <v>58.204</v>
       </c>
       <c r="C44" t="n">
-        <v>102.357</v>
+        <v>102.408</v>
       </c>
       <c r="D44" t="n">
-        <v>168.635</v>
+        <v>166.085</v>
       </c>
       <c r="E44" t="n">
-        <v>57.767</v>
+        <v>57.7249</v>
       </c>
       <c r="F44" t="n">
-        <v>94.2135</v>
+        <v>94.7166</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>56.7356</v>
+        <v>56.8477</v>
       </c>
       <c r="C45" t="n">
-        <v>100.84</v>
+        <v>101.319</v>
       </c>
       <c r="D45" t="n">
-        <v>166.02</v>
+        <v>166.771</v>
       </c>
       <c r="E45" t="n">
-        <v>56.3259</v>
+        <v>56.2827</v>
       </c>
       <c r="F45" t="n">
-        <v>89.4666</v>
+        <v>91.77379999999999</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>55.6132</v>
+        <v>55.6338</v>
       </c>
       <c r="C46" t="n">
-        <v>99.62179999999999</v>
+        <v>99.4345</v>
       </c>
       <c r="D46" t="n">
-        <v>163.608</v>
+        <v>163.225</v>
       </c>
       <c r="E46" t="n">
-        <v>55.0147</v>
+        <v>55.0734</v>
       </c>
       <c r="F46" t="n">
-        <v>88.75960000000001</v>
+        <v>88.2647</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>54.37</v>
+        <v>54.5439</v>
       </c>
       <c r="C47" t="n">
-        <v>96.9773</v>
+        <v>96.929</v>
       </c>
       <c r="D47" t="n">
-        <v>162.796</v>
+        <v>163.925</v>
       </c>
       <c r="E47" t="n">
-        <v>53.7596</v>
+        <v>53.7593</v>
       </c>
       <c r="F47" t="n">
-        <v>89.08450000000001</v>
+        <v>89.3014</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>53.2765</v>
+        <v>53.3845</v>
       </c>
       <c r="C48" t="n">
-        <v>93.8887</v>
+        <v>94.7016</v>
       </c>
       <c r="D48" t="n">
-        <v>158.662</v>
+        <v>159.361</v>
       </c>
       <c r="E48" t="n">
-        <v>52.6605</v>
+        <v>52.705</v>
       </c>
       <c r="F48" t="n">
-        <v>86.529</v>
+        <v>86.73699999999999</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>52.3981</v>
+        <v>52.4305</v>
       </c>
       <c r="C49" t="n">
-        <v>92.5702</v>
+        <v>93.02800000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>154.731</v>
+        <v>156.089</v>
       </c>
       <c r="E49" t="n">
-        <v>51.7336</v>
+        <v>51.8222</v>
       </c>
       <c r="F49" t="n">
-        <v>85.1699</v>
+        <v>83.6238</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>51.4927</v>
+        <v>51.6752</v>
       </c>
       <c r="C50" t="n">
-        <v>91.0603</v>
+        <v>89.76439999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>234.709</v>
+        <v>236.438</v>
       </c>
       <c r="E50" t="n">
-        <v>50.9877</v>
+        <v>51.058</v>
       </c>
       <c r="F50" t="n">
-        <v>83.4359</v>
+        <v>83.1666</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>50.9358</v>
+        <v>50.9318</v>
       </c>
       <c r="C51" t="n">
-        <v>88.85339999999999</v>
+        <v>89.10429999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>229.337</v>
+        <v>233.239</v>
       </c>
       <c r="E51" t="n">
-        <v>72.4819</v>
+        <v>72.5198</v>
       </c>
       <c r="F51" t="n">
-        <v>128.14</v>
+        <v>129.345</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>50.5683</v>
+        <v>50.5684</v>
       </c>
       <c r="C52" t="n">
-        <v>89.3152</v>
+        <v>89.1752</v>
       </c>
       <c r="D52" t="n">
-        <v>225.137</v>
+        <v>227.456</v>
       </c>
       <c r="E52" t="n">
-        <v>70.3828</v>
+        <v>70.44</v>
       </c>
       <c r="F52" t="n">
-        <v>124.356</v>
+        <v>124.258</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>68.2034</v>
+        <v>68.0279</v>
       </c>
       <c r="C53" t="n">
-        <v>132.248</v>
+        <v>133.074</v>
       </c>
       <c r="D53" t="n">
-        <v>219.342</v>
+        <v>220.214</v>
       </c>
       <c r="E53" t="n">
-        <v>68.4308</v>
+        <v>68.4978</v>
       </c>
       <c r="F53" t="n">
-        <v>119.896</v>
+        <v>121.543</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>66.4164</v>
+        <v>66.2702</v>
       </c>
       <c r="C54" t="n">
-        <v>127.524</v>
+        <v>127.206</v>
       </c>
       <c r="D54" t="n">
-        <v>217.527</v>
+        <v>214.585</v>
       </c>
       <c r="E54" t="n">
-        <v>66.45180000000001</v>
+        <v>66.6465</v>
       </c>
       <c r="F54" t="n">
-        <v>115.794</v>
+        <v>115.558</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>64.70659999999999</v>
+        <v>64.58629999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>124.425</v>
+        <v>125.038</v>
       </c>
       <c r="D55" t="n">
-        <v>210.024</v>
+        <v>206.282</v>
       </c>
       <c r="E55" t="n">
-        <v>64.7032</v>
+        <v>64.8241</v>
       </c>
       <c r="F55" t="n">
-        <v>111.9</v>
+        <v>111.756</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>63.1359</v>
+        <v>62.9627</v>
       </c>
       <c r="C56" t="n">
-        <v>121.702</v>
+        <v>121.996</v>
       </c>
       <c r="D56" t="n">
-        <v>203.743</v>
+        <v>205.997</v>
       </c>
       <c r="E56" t="n">
-        <v>63.0294</v>
+        <v>63.1119</v>
       </c>
       <c r="F56" t="n">
-        <v>108.66</v>
+        <v>108.724</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>61.6274</v>
+        <v>61.4763</v>
       </c>
       <c r="C57" t="n">
-        <v>120.812</v>
+        <v>120.366</v>
       </c>
       <c r="D57" t="n">
-        <v>206.934</v>
+        <v>209.114</v>
       </c>
       <c r="E57" t="n">
-        <v>61.4576</v>
+        <v>61.5404</v>
       </c>
       <c r="F57" t="n">
-        <v>104.296</v>
+        <v>104.789</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>60.2099</v>
+        <v>60.0829</v>
       </c>
       <c r="C58" t="n">
-        <v>116.576</v>
+        <v>117.714</v>
       </c>
       <c r="D58" t="n">
-        <v>203.389</v>
+        <v>201.09</v>
       </c>
       <c r="E58" t="n">
-        <v>59.8713</v>
+        <v>59.9816</v>
       </c>
       <c r="F58" t="n">
-        <v>102.355</v>
+        <v>98.94970000000001</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>58.902</v>
+        <v>58.782</v>
       </c>
       <c r="C59" t="n">
-        <v>113.74</v>
+        <v>113.426</v>
       </c>
       <c r="D59" t="n">
-        <v>200.075</v>
+        <v>200.063</v>
       </c>
       <c r="E59" t="n">
-        <v>58.3615</v>
+        <v>58.487</v>
       </c>
       <c r="F59" t="n">
-        <v>99.1152</v>
+        <v>97.4131</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>57.5401</v>
+        <v>57.5904</v>
       </c>
       <c r="C60" t="n">
-        <v>109.421</v>
+        <v>110.074</v>
       </c>
       <c r="D60" t="n">
-        <v>200.116</v>
+        <v>199.705</v>
       </c>
       <c r="E60" t="n">
-        <v>57.124</v>
+        <v>57.1301</v>
       </c>
       <c r="F60" t="n">
-        <v>101.072</v>
+        <v>100.575</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>56.2835</v>
+        <v>56.3742</v>
       </c>
       <c r="C61" t="n">
-        <v>107.496</v>
+        <v>107.782</v>
       </c>
       <c r="D61" t="n">
-        <v>196.738</v>
+        <v>195.745</v>
       </c>
       <c r="E61" t="n">
-        <v>55.8648</v>
+        <v>55.9705</v>
       </c>
       <c r="F61" t="n">
-        <v>97.7179</v>
+        <v>98.1661</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>55.2093</v>
+        <v>55.2818</v>
       </c>
       <c r="C62" t="n">
-        <v>106.043</v>
+        <v>105.037</v>
       </c>
       <c r="D62" t="n">
-        <v>196.078</v>
+        <v>196.097</v>
       </c>
       <c r="E62" t="n">
-        <v>54.6945</v>
+        <v>54.7732</v>
       </c>
       <c r="F62" t="n">
-        <v>92.798</v>
+        <v>92.96169999999999</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>54.2912</v>
+        <v>54.2319</v>
       </c>
       <c r="C63" t="n">
-        <v>103.848</v>
+        <v>100.953</v>
       </c>
       <c r="D63" t="n">
-        <v>197.203</v>
+        <v>191.235</v>
       </c>
       <c r="E63" t="n">
-        <v>53.7748</v>
+        <v>53.9405</v>
       </c>
       <c r="F63" t="n">
-        <v>88.8154</v>
+        <v>90.73050000000001</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>53.4369</v>
+        <v>53.3852</v>
       </c>
       <c r="C64" t="n">
-        <v>98.98</v>
+        <v>101.358</v>
       </c>
       <c r="D64" t="n">
-        <v>390.672</v>
+        <v>385.938</v>
       </c>
       <c r="E64" t="n">
-        <v>53.0334</v>
+        <v>52.8022</v>
       </c>
       <c r="F64" t="n">
-        <v>90.1554</v>
+        <v>87.68170000000001</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>52.6164</v>
+        <v>52.6437</v>
       </c>
       <c r="C65" t="n">
-        <v>101.324</v>
+        <v>100.434</v>
       </c>
       <c r="D65" t="n">
-        <v>384.453</v>
+        <v>379.735</v>
       </c>
       <c r="E65" t="n">
-        <v>52.2552</v>
+        <v>52.3836</v>
       </c>
       <c r="F65" t="n">
-        <v>88.9002</v>
+        <v>88.9389</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>52.2043</v>
+        <v>52.2247</v>
       </c>
       <c r="C66" t="n">
-        <v>99.44499999999999</v>
+        <v>98.7355</v>
       </c>
       <c r="D66" t="n">
-        <v>375.86</v>
+        <v>377.345</v>
       </c>
       <c r="E66" t="n">
-        <v>73.96339999999999</v>
+        <v>73.595</v>
       </c>
       <c r="F66" t="n">
-        <v>157.084</v>
+        <v>158.039</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>70.0055</v>
+        <v>70.7547</v>
       </c>
       <c r="C67" t="n">
-        <v>172.868</v>
+        <v>174.405</v>
       </c>
       <c r="D67" t="n">
-        <v>360.515</v>
+        <v>360.257</v>
       </c>
       <c r="E67" t="n">
-        <v>71.1759</v>
+        <v>71.3562</v>
       </c>
       <c r="F67" t="n">
-        <v>154.298</v>
+        <v>153.431</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>68.47150000000001</v>
+        <v>68.6759</v>
       </c>
       <c r="C68" t="n">
-        <v>167.947</v>
+        <v>167.007</v>
       </c>
       <c r="D68" t="n">
-        <v>347.575</v>
+        <v>358.62</v>
       </c>
       <c r="E68" t="n">
-        <v>69.5685</v>
+        <v>69.46259999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>152.263</v>
+        <v>150.391</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>66.9329</v>
+        <v>67.3639</v>
       </c>
       <c r="C69" t="n">
-        <v>165.966</v>
+        <v>166.632</v>
       </c>
       <c r="D69" t="n">
-        <v>355.887</v>
+        <v>342.485</v>
       </c>
       <c r="E69" t="n">
-        <v>67.82299999999999</v>
+        <v>67.4648</v>
       </c>
       <c r="F69" t="n">
-        <v>147.702</v>
+        <v>146.905</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>65.5932</v>
+        <v>65.4083</v>
       </c>
       <c r="C70" t="n">
-        <v>163.593</v>
+        <v>157.107</v>
       </c>
       <c r="D70" t="n">
-        <v>347.226</v>
+        <v>335.061</v>
       </c>
       <c r="E70" t="n">
-        <v>66.13120000000001</v>
+        <v>66.08929999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>148.174</v>
+        <v>144.543</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>64.1404</v>
+        <v>64.4834</v>
       </c>
       <c r="C71" t="n">
-        <v>154.352</v>
+        <v>156.03</v>
       </c>
       <c r="D71" t="n">
-        <v>346.049</v>
+        <v>336.178</v>
       </c>
       <c r="E71" t="n">
-        <v>64.0603</v>
+        <v>64.71299999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>141.18</v>
+        <v>140.374</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>62.969</v>
+        <v>63.1747</v>
       </c>
       <c r="C72" t="n">
-        <v>156.622</v>
+        <v>154.347</v>
       </c>
       <c r="D72" t="n">
-        <v>347.171</v>
+        <v>336.683</v>
       </c>
       <c r="E72" t="n">
-        <v>62.4787</v>
+        <v>63.1207</v>
       </c>
       <c r="F72" t="n">
-        <v>136.101</v>
+        <v>136.083</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>61.8258</v>
+        <v>61.9683</v>
       </c>
       <c r="C73" t="n">
-        <v>154.574</v>
+        <v>152.995</v>
       </c>
       <c r="D73" t="n">
-        <v>336.991</v>
+        <v>335.651</v>
       </c>
       <c r="E73" t="n">
-        <v>61.3765</v>
+        <v>61.6425</v>
       </c>
       <c r="F73" t="n">
-        <v>130.699</v>
+        <v>125.299</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>60.7052</v>
+        <v>60.7928</v>
       </c>
       <c r="C74" t="n">
-        <v>150.518</v>
+        <v>142.747</v>
       </c>
       <c r="D74" t="n">
-        <v>332.146</v>
+        <v>334.224</v>
       </c>
       <c r="E74" t="n">
-        <v>59.9009</v>
+        <v>60.2557</v>
       </c>
       <c r="F74" t="n">
-        <v>130.817</v>
+        <v>129.227</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>59.2726</v>
+        <v>59.6687</v>
       </c>
       <c r="C75" t="n">
-        <v>144.004</v>
+        <v>147.112</v>
       </c>
       <c r="D75" t="n">
-        <v>329.535</v>
+        <v>336.522</v>
       </c>
       <c r="E75" t="n">
-        <v>58.7886</v>
+        <v>58.9167</v>
       </c>
       <c r="F75" t="n">
-        <v>127.019</v>
+        <v>129.01</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>58.1065</v>
+        <v>58.3184</v>
       </c>
       <c r="C76" t="n">
-        <v>142.687</v>
+        <v>143.129</v>
       </c>
       <c r="D76" t="n">
-        <v>328.138</v>
+        <v>332.271</v>
       </c>
       <c r="E76" t="n">
-        <v>57.722</v>
+        <v>57.8554</v>
       </c>
       <c r="F76" t="n">
-        <v>122.289</v>
+        <v>119.075</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>57.32</v>
+        <v>57.5685</v>
       </c>
       <c r="C77" t="n">
-        <v>138.729</v>
+        <v>134.81</v>
       </c>
       <c r="D77" t="n">
-        <v>323.612</v>
+        <v>322.089</v>
       </c>
       <c r="E77" t="n">
-        <v>56.4677</v>
+        <v>56.7986</v>
       </c>
       <c r="F77" t="n">
-        <v>120.368</v>
+        <v>121.785</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>56.2852</v>
+        <v>56.7273</v>
       </c>
       <c r="C78" t="n">
-        <v>134.653</v>
+        <v>137.17</v>
       </c>
       <c r="D78" t="n">
-        <v>597.553</v>
+        <v>633.129</v>
       </c>
       <c r="E78" t="n">
-        <v>55.8678</v>
+        <v>56.4411</v>
       </c>
       <c r="F78" t="n">
-        <v>118.267</v>
+        <v>118.946</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>55.7535</v>
+        <v>56.0905</v>
       </c>
       <c r="C79" t="n">
-        <v>133.277</v>
+        <v>133.491</v>
       </c>
       <c r="D79" t="n">
-        <v>584.508</v>
+        <v>604.97</v>
       </c>
       <c r="E79" t="n">
-        <v>55.5176</v>
+        <v>55.8135</v>
       </c>
       <c r="F79" t="n">
-        <v>116.451</v>
+        <v>118.113</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>55.0512</v>
+        <v>55.4518</v>
       </c>
       <c r="C80" t="n">
-        <v>130.36</v>
+        <v>132.855</v>
       </c>
       <c r="D80" t="n">
-        <v>582.595</v>
+        <v>579.758</v>
       </c>
       <c r="E80" t="n">
-        <v>78.01000000000001</v>
+        <v>79.4815</v>
       </c>
       <c r="F80" t="n">
-        <v>215.522</v>
+        <v>211.988</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>74.3197</v>
+        <v>75.3049</v>
       </c>
       <c r="C81" t="n">
-        <v>253.668</v>
+        <v>244.479</v>
       </c>
       <c r="D81" t="n">
-        <v>604.254</v>
+        <v>585.996</v>
       </c>
       <c r="E81" t="n">
-        <v>77.0689</v>
+        <v>77.28270000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>223.361</v>
+        <v>223.939</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>74.6562</v>
+        <v>74.5517</v>
       </c>
       <c r="C82" t="n">
-        <v>247.573</v>
+        <v>246.521</v>
       </c>
       <c r="D82" t="n">
-        <v>537.16</v>
+        <v>555.494</v>
       </c>
       <c r="E82" t="n">
-        <v>76.66370000000001</v>
+        <v>77.4246</v>
       </c>
       <c r="F82" t="n">
-        <v>211.685</v>
+        <v>226.587</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>75.0201</v>
+        <v>76.7456</v>
       </c>
       <c r="C83" t="n">
-        <v>235.271</v>
+        <v>243.981</v>
       </c>
       <c r="D83" t="n">
-        <v>572.09</v>
+        <v>537.081</v>
       </c>
       <c r="E83" t="n">
-        <v>75.8244</v>
+        <v>75.8417</v>
       </c>
       <c r="F83" t="n">
-        <v>218.426</v>
+        <v>201.273</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>75.69199999999999</v>
+        <v>75.8163</v>
       </c>
       <c r="C84" t="n">
-        <v>236.03</v>
+        <v>238.938</v>
       </c>
       <c r="D84" t="n">
-        <v>489.465</v>
+        <v>544.976</v>
       </c>
       <c r="E84" t="n">
-        <v>73.9815</v>
+        <v>75.131</v>
       </c>
       <c r="F84" t="n">
-        <v>202.557</v>
+        <v>213.742</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>74.6604</v>
+        <v>75.5716</v>
       </c>
       <c r="C85" t="n">
-        <v>217.64</v>
+        <v>233.641</v>
       </c>
       <c r="D85" t="n">
-        <v>538.8</v>
+        <v>544.448</v>
       </c>
       <c r="E85" t="n">
-        <v>73.35809999999999</v>
+        <v>73.70910000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>205.232</v>
+        <v>198.34</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>75.4248</v>
+        <v>75.78740000000001</v>
       </c>
       <c r="C86" t="n">
-        <v>227.306</v>
+        <v>227.524</v>
       </c>
       <c r="D86" t="n">
-        <v>507.086</v>
+        <v>510.983</v>
       </c>
       <c r="E86" t="n">
-        <v>71.7753</v>
+        <v>72.65819999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>197.43</v>
+        <v>200.152</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>74.69750000000001</v>
+        <v>75.19629999999999</v>
       </c>
       <c r="C87" t="n">
-        <v>216.565</v>
+        <v>218.841</v>
       </c>
       <c r="D87" t="n">
-        <v>532.668</v>
+        <v>524.422</v>
       </c>
       <c r="E87" t="n">
-        <v>70.47790000000001</v>
+        <v>71.3991</v>
       </c>
       <c r="F87" t="n">
-        <v>183.686</v>
+        <v>176.79</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>74.2675</v>
+        <v>74.4149</v>
       </c>
       <c r="C88" t="n">
-        <v>214.74</v>
+        <v>215.862</v>
       </c>
       <c r="D88" t="n">
-        <v>518.5890000000001</v>
+        <v>511.942</v>
       </c>
       <c r="E88" t="n">
-        <v>68.65560000000001</v>
+        <v>69.6906</v>
       </c>
       <c r="F88" t="n">
-        <v>166.657</v>
+        <v>186.629</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>73.3258</v>
+        <v>73.38630000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>209.637</v>
+        <v>211.229</v>
       </c>
       <c r="D89" t="n">
-        <v>504.703</v>
+        <v>521.006</v>
       </c>
       <c r="E89" t="n">
-        <v>67.90219999999999</v>
+        <v>67.9559</v>
       </c>
       <c r="F89" t="n">
-        <v>178.24</v>
+        <v>186.935</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>72.3698</v>
+        <v>73.0932</v>
       </c>
       <c r="C90" t="n">
-        <v>207.571</v>
+        <v>207.985</v>
       </c>
       <c r="D90" t="n">
-        <v>512.824</v>
+        <v>499.213</v>
       </c>
       <c r="E90" t="n">
-        <v>66.74420000000001</v>
+        <v>67.2058</v>
       </c>
       <c r="F90" t="n">
-        <v>180.113</v>
+        <v>185.017</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>72.6241</v>
+        <v>73.2059</v>
       </c>
       <c r="C91" t="n">
-        <v>203.869</v>
+        <v>204.668</v>
       </c>
       <c r="D91" t="n">
-        <v>497.191</v>
+        <v>493.446</v>
       </c>
       <c r="E91" t="n">
-        <v>65.73739999999999</v>
+        <v>66.675</v>
       </c>
       <c r="F91" t="n">
-        <v>176.1</v>
+        <v>174.609</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>72.54819999999999</v>
+        <v>72.7462</v>
       </c>
       <c r="C92" t="n">
-        <v>194.787</v>
+        <v>198.251</v>
       </c>
       <c r="D92" t="n">
-        <v>800.949</v>
+        <v>822.404</v>
       </c>
       <c r="E92" t="n">
-        <v>64.6031</v>
+        <v>64.95780000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>176.381</v>
+        <v>179.141</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>70.99979999999999</v>
+        <v>72.73860000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>187.61</v>
+        <v>194.96</v>
       </c>
       <c r="D93" t="n">
-        <v>817.938</v>
+        <v>827.191</v>
       </c>
       <c r="E93" t="n">
-        <v>65.49420000000001</v>
+        <v>63.7704</v>
       </c>
       <c r="F93" t="n">
-        <v>170.919</v>
+        <v>170.897</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>71.3498</v>
+        <v>71.75</v>
       </c>
       <c r="C94" t="n">
-        <v>192.244</v>
+        <v>192.506</v>
       </c>
       <c r="D94" t="n">
-        <v>773.154</v>
+        <v>773.228</v>
       </c>
       <c r="E94" t="n">
-        <v>92.8344</v>
+        <v>96.7128</v>
       </c>
       <c r="F94" t="n">
-        <v>309.839</v>
+        <v>326.623</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>93.9853</v>
+        <v>91.3036</v>
       </c>
       <c r="C95" t="n">
-        <v>351.662</v>
+        <v>362.776</v>
       </c>
       <c r="D95" t="n">
-        <v>780.604</v>
+        <v>784.832</v>
       </c>
       <c r="E95" t="n">
-        <v>88.7932</v>
+        <v>95.3356</v>
       </c>
       <c r="F95" t="n">
-        <v>297.862</v>
+        <v>305.15</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>91.4091</v>
+        <v>91.2704</v>
       </c>
       <c r="C96" t="n">
-        <v>302.146</v>
+        <v>345.153</v>
       </c>
       <c r="D96" t="n">
-        <v>729.956</v>
+        <v>733.706</v>
       </c>
       <c r="E96" t="n">
-        <v>90.7996</v>
+        <v>90.7</v>
       </c>
       <c r="F96" t="n">
-        <v>290.352</v>
+        <v>290.849</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>94.68470000000001</v>
+        <v>92.82940000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>335.562</v>
+        <v>329.718</v>
       </c>
       <c r="D97" t="n">
-        <v>725.548</v>
+        <v>741.968</v>
       </c>
       <c r="E97" t="n">
-        <v>89.71040000000001</v>
+        <v>90.06619999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>292.025</v>
+        <v>293.722</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>96.298</v>
+        <v>94.9481</v>
       </c>
       <c r="C98" t="n">
-        <v>330.842</v>
+        <v>337.069</v>
       </c>
       <c r="D98" t="n">
-        <v>719.635</v>
+        <v>723.9400000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>90.6789</v>
+        <v>90.6375</v>
       </c>
       <c r="F98" t="n">
-        <v>285.006</v>
+        <v>283.488</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>94.735</v>
+        <v>94.40779999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>317.472</v>
+        <v>314.933</v>
       </c>
       <c r="D99" t="n">
-        <v>699.494</v>
+        <v>706.4349999999999</v>
       </c>
       <c r="E99" t="n">
-        <v>89.3873</v>
+        <v>88.6242</v>
       </c>
       <c r="F99" t="n">
-        <v>275.472</v>
+        <v>263.007</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>94.3349</v>
+        <v>93.535</v>
       </c>
       <c r="C100" t="n">
-        <v>310.994</v>
+        <v>314.283</v>
       </c>
       <c r="D100" t="n">
-        <v>689.455</v>
+        <v>690.802</v>
       </c>
       <c r="E100" t="n">
-        <v>88.364</v>
+        <v>91.63760000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>280.837</v>
+        <v>283.029</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>96.9221</v>
+        <v>96.301</v>
       </c>
       <c r="C101" t="n">
-        <v>301.281</v>
+        <v>321.945</v>
       </c>
       <c r="D101" t="n">
-        <v>668.374</v>
+        <v>677.6319999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>86.2287</v>
+        <v>87.98480000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>282.606</v>
+        <v>283.73</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>98.05</v>
+        <v>97.26139999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>312.741</v>
+        <v>315.033</v>
       </c>
       <c r="D102" t="n">
-        <v>663.866</v>
+        <v>666.763</v>
       </c>
       <c r="E102" t="n">
-        <v>85.9115</v>
+        <v>88.5433</v>
       </c>
       <c r="F102" t="n">
-        <v>279.677</v>
+        <v>280.64</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>99.65649999999999</v>
+        <v>97.4953</v>
       </c>
       <c r="C103" t="n">
-        <v>304.653</v>
+        <v>312.435</v>
       </c>
       <c r="D103" t="n">
-        <v>651.1660000000001</v>
+        <v>655.678</v>
       </c>
       <c r="E103" t="n">
-        <v>88.2739</v>
+        <v>89.357</v>
       </c>
       <c r="F103" t="n">
-        <v>265.606</v>
+        <v>276.845</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>99.7406</v>
+        <v>97.5234</v>
       </c>
       <c r="C104" t="n">
-        <v>298.244</v>
+        <v>308.086</v>
       </c>
       <c r="D104" t="n">
-        <v>647.098</v>
+        <v>648.772</v>
       </c>
       <c r="E104" t="n">
-        <v>85.1866</v>
+        <v>86.795</v>
       </c>
       <c r="F104" t="n">
-        <v>261.956</v>
+        <v>266.888</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>101.098</v>
+        <v>98.011</v>
       </c>
       <c r="C105" t="n">
-        <v>297.999</v>
+        <v>305.817</v>
       </c>
       <c r="D105" t="n">
-        <v>644.287</v>
+        <v>648.957</v>
       </c>
       <c r="E105" t="n">
-        <v>86.0849</v>
+        <v>86.3278</v>
       </c>
       <c r="F105" t="n">
-        <v>262.967</v>
+        <v>251.425</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>102.55</v>
+        <v>97.8621</v>
       </c>
       <c r="C106" t="n">
-        <v>287.258</v>
+        <v>294.415</v>
       </c>
       <c r="D106" t="n">
-        <v>619.498</v>
+        <v>640.051</v>
       </c>
       <c r="E106" t="n">
-        <v>85.6382</v>
+        <v>84.4992</v>
       </c>
       <c r="F106" t="n">
-        <v>239.73</v>
+        <v>243.257</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>98.9438</v>
+        <v>99.07510000000001</v>
       </c>
       <c r="C107" t="n">
-        <v>279.965</v>
+        <v>284.368</v>
       </c>
       <c r="D107" t="n">
-        <v>918.6559999999999</v>
+        <v>948.856</v>
       </c>
       <c r="E107" t="n">
-        <v>86.6735</v>
+        <v>86.2368</v>
       </c>
       <c r="F107" t="n">
-        <v>249.657</v>
+        <v>252.955</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>100.723</v>
+        <v>99.2903</v>
       </c>
       <c r="C108" t="n">
-        <v>258.312</v>
+        <v>279.09</v>
       </c>
       <c r="D108" t="n">
-        <v>890.027</v>
+        <v>920.2569999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>114.395</v>
+        <v>131.644</v>
       </c>
       <c r="F108" t="n">
-        <v>411.167</v>
+        <v>405.79</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>101.038</v>
+        <v>104.534</v>
       </c>
       <c r="C109" t="n">
-        <v>250.293</v>
+        <v>259.289</v>
       </c>
       <c r="D109" t="n">
-        <v>883.425</v>
+        <v>883.199</v>
       </c>
       <c r="E109" t="n">
-        <v>113.143</v>
+        <v>110.784</v>
       </c>
       <c r="F109" t="n">
-        <v>400.174</v>
+        <v>414.829</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>145.012</v>
+        <v>145.822</v>
       </c>
       <c r="C110" t="n">
-        <v>426.011</v>
+        <v>429.874</v>
       </c>
       <c r="D110" t="n">
-        <v>860.663</v>
+        <v>874.326</v>
       </c>
       <c r="E110" t="n">
-        <v>133.724</v>
+        <v>135.912</v>
       </c>
       <c r="F110" t="n">
-        <v>397.762</v>
+        <v>403.514</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>144.435</v>
+        <v>145.53</v>
       </c>
       <c r="C111" t="n">
-        <v>413.127</v>
+        <v>419.983</v>
       </c>
       <c r="D111" t="n">
-        <v>840.841</v>
+        <v>849.875</v>
       </c>
       <c r="E111" t="n">
-        <v>125.745</v>
+        <v>126.193</v>
       </c>
       <c r="F111" t="n">
-        <v>385.433</v>
+        <v>387.856</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>132.152</v>
+        <v>132.42</v>
       </c>
       <c r="C112" t="n">
-        <v>412.286</v>
+        <v>413.462</v>
       </c>
       <c r="D112" t="n">
-        <v>812.746</v>
+        <v>824.83</v>
       </c>
       <c r="E112" t="n">
-        <v>108.052</v>
+        <v>109.463</v>
       </c>
       <c r="F112" t="n">
-        <v>382.887</v>
+        <v>394.453</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>116.827</v>
+        <v>120.873</v>
       </c>
       <c r="C113" t="n">
-        <v>400.33</v>
+        <v>420.324</v>
       </c>
       <c r="D113" t="n">
-        <v>808.441</v>
+        <v>829.837</v>
       </c>
       <c r="E113" t="n">
-        <v>110.574</v>
+        <v>111.575</v>
       </c>
       <c r="F113" t="n">
-        <v>386.683</v>
+        <v>394.391</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>120.569</v>
+        <v>120.933</v>
       </c>
       <c r="C114" t="n">
-        <v>410.74</v>
+        <v>416.752</v>
       </c>
       <c r="D114" t="n">
-        <v>810.0940000000001</v>
+        <v>820.755</v>
       </c>
       <c r="E114" t="n">
-        <v>110.742</v>
+        <v>111.521</v>
       </c>
       <c r="F114" t="n">
-        <v>374.801</v>
+        <v>374.478</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>123.079</v>
+        <v>123.756</v>
       </c>
       <c r="C115" t="n">
-        <v>395.423</v>
+        <v>401.304</v>
       </c>
       <c r="D115" t="n">
-        <v>788.792</v>
+        <v>801.424</v>
       </c>
       <c r="E115" t="n">
-        <v>109.392</v>
+        <v>111.627</v>
       </c>
       <c r="F115" t="n">
-        <v>357.255</v>
+        <v>368.021</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>131.364</v>
+        <v>130.23</v>
       </c>
       <c r="C116" t="n">
-        <v>386.478</v>
+        <v>397.092</v>
       </c>
       <c r="D116" t="n">
-        <v>783.484</v>
+        <v>773.022</v>
       </c>
       <c r="E116" t="n">
-        <v>112.583</v>
+        <v>110.943</v>
       </c>
       <c r="F116" t="n">
-        <v>359.637</v>
+        <v>356.363</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>133.698</v>
+        <v>133.389</v>
       </c>
       <c r="C117" t="n">
-        <v>379.602</v>
+        <v>368.515</v>
       </c>
       <c r="D117" t="n">
-        <v>766.033</v>
+        <v>770.924</v>
       </c>
       <c r="E117" t="n">
-        <v>114.389</v>
+        <v>114.693</v>
       </c>
       <c r="F117" t="n">
-        <v>340.977</v>
+        <v>340.631</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>133.027</v>
+        <v>127.757</v>
       </c>
       <c r="C118" t="n">
-        <v>357.92</v>
+        <v>358.36</v>
       </c>
       <c r="D118" t="n">
-        <v>746.981</v>
+        <v>750.99</v>
       </c>
       <c r="E118" t="n">
-        <v>109.408</v>
+        <v>110.636</v>
       </c>
       <c r="F118" t="n">
-        <v>328.029</v>
+        <v>326.256</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>133.232</v>
+        <v>134.174</v>
       </c>
       <c r="C119" t="n">
-        <v>342.482</v>
+        <v>344.272</v>
       </c>
       <c r="D119" t="n">
-        <v>736.636</v>
+        <v>740.463</v>
       </c>
       <c r="E119" t="n">
-        <v>118.871</v>
+        <v>116.989</v>
       </c>
       <c r="F119" t="n">
-        <v>318.984</v>
+        <v>320.304</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>137.415</v>
+        <v>135.889</v>
       </c>
       <c r="C120" t="n">
-        <v>338.358</v>
+        <v>344.316</v>
       </c>
       <c r="D120" t="n">
-        <v>726.056</v>
+        <v>739.275</v>
       </c>
       <c r="E120" t="n">
-        <v>122.306</v>
+        <v>124.199</v>
       </c>
       <c r="F120" t="n">
-        <v>311.989</v>
+        <v>319.712</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>139.031</v>
+        <v>141.302</v>
       </c>
       <c r="C121" t="n">
-        <v>335.591</v>
+        <v>352.078</v>
       </c>
       <c r="D121" t="n">
-        <v>1033.14</v>
+        <v>1067.42</v>
       </c>
       <c r="E121" t="n">
-        <v>127.157</v>
+        <v>128.323</v>
       </c>
       <c r="F121" t="n">
-        <v>307.818</v>
+        <v>315.438</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>137.488</v>
+        <v>141.669</v>
       </c>
       <c r="C122" t="n">
-        <v>330.643</v>
+        <v>338.743</v>
       </c>
       <c r="D122" t="n">
-        <v>1035.88</v>
+        <v>1061.1</v>
       </c>
       <c r="E122" t="n">
-        <v>124.535</v>
+        <v>128.388</v>
       </c>
       <c r="F122" t="n">
-        <v>303.281</v>
+        <v>306.418</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>141.13</v>
+        <v>138.927</v>
       </c>
       <c r="C123" t="n">
-        <v>328.009</v>
+        <v>334.528</v>
       </c>
       <c r="D123" t="n">
-        <v>1026.15</v>
+        <v>1037.01</v>
       </c>
       <c r="E123" t="n">
-        <v>166.047</v>
+        <v>167.16</v>
       </c>
       <c r="F123" t="n">
-        <v>481.049</v>
+        <v>468.798</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>174.138</v>
+        <v>171.939</v>
       </c>
       <c r="C124" t="n">
-        <v>504.111</v>
+        <v>491.391</v>
       </c>
       <c r="D124" t="n">
-        <v>993.772</v>
+        <v>980.327</v>
       </c>
       <c r="E124" t="n">
-        <v>167.112</v>
+        <v>165.507</v>
       </c>
       <c r="F124" t="n">
-        <v>465.749</v>
+        <v>449.206</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>181.553</v>
+        <v>169.487</v>
       </c>
       <c r="C125" t="n">
-        <v>478.29</v>
+        <v>478.184</v>
       </c>
       <c r="D125" t="n">
-        <v>965.374</v>
+        <v>957.977</v>
       </c>
       <c r="E125" t="n">
-        <v>164.115</v>
+        <v>162.921</v>
       </c>
       <c r="F125" t="n">
-        <v>454.195</v>
+        <v>444.175</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>173.511</v>
+        <v>175.318</v>
       </c>
       <c r="C126" t="n">
-        <v>476.653</v>
+        <v>464.567</v>
       </c>
       <c r="D126" t="n">
-        <v>941.0890000000001</v>
+        <v>925.3099999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>162.039</v>
+        <v>163.987</v>
       </c>
       <c r="F126" t="n">
-        <v>439.236</v>
+        <v>436.013</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>175.192</v>
+        <v>176.667</v>
       </c>
       <c r="C127" t="n">
-        <v>463.503</v>
+        <v>460.878</v>
       </c>
       <c r="D127" t="n">
-        <v>919.527</v>
+        <v>909.2809999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>166.411</v>
+        <v>166.578</v>
       </c>
       <c r="F127" t="n">
-        <v>430.857</v>
+        <v>425.225</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>180.637</v>
+        <v>176.46</v>
       </c>
       <c r="C128" t="n">
-        <v>478.637</v>
+        <v>468.211</v>
       </c>
       <c r="D128" t="n">
-        <v>917.562</v>
+        <v>905.457</v>
       </c>
       <c r="E128" t="n">
-        <v>167.199</v>
+        <v>167.627</v>
       </c>
       <c r="F128" t="n">
-        <v>430.819</v>
+        <v>435.862</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>176.085</v>
+        <v>175.435</v>
       </c>
       <c r="C129" t="n">
-        <v>455.945</v>
+        <v>457.03</v>
       </c>
       <c r="D129" t="n">
-        <v>874.1130000000001</v>
+        <v>880.011</v>
       </c>
       <c r="E129" t="n">
-        <v>164.067</v>
+        <v>164.842</v>
       </c>
       <c r="F129" t="n">
-        <v>426.609</v>
+        <v>424.26</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>174.626</v>
+        <v>175.582</v>
       </c>
       <c r="C130" t="n">
-        <v>447.788</v>
+        <v>446.557</v>
       </c>
       <c r="D130" t="n">
-        <v>848.617</v>
+        <v>856.965</v>
       </c>
       <c r="E130" t="n">
-        <v>163.804</v>
+        <v>170.25</v>
       </c>
       <c r="F130" t="n">
-        <v>417.458</v>
+        <v>430.134</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>171.983</v>
+        <v>178.958</v>
       </c>
       <c r="C131" t="n">
-        <v>436.761</v>
+        <v>451.95</v>
       </c>
       <c r="D131" t="n">
-        <v>830.679</v>
+        <v>857.982</v>
       </c>
       <c r="E131" t="n">
-        <v>162.729</v>
+        <v>168.982</v>
       </c>
       <c r="F131" t="n">
-        <v>400.163</v>
+        <v>416.894</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>171.894</v>
+        <v>179.107</v>
       </c>
       <c r="C132" t="n">
-        <v>423.862</v>
+        <v>434.46</v>
       </c>
       <c r="D132" t="n">
-        <v>835.524</v>
+        <v>841.148</v>
       </c>
       <c r="E132" t="n">
-        <v>162.375</v>
+        <v>163.615</v>
       </c>
       <c r="F132" t="n">
-        <v>394.121</v>
+        <v>394.396</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>171.772</v>
+        <v>173.191</v>
       </c>
       <c r="C133" t="n">
-        <v>410.523</v>
+        <v>419.144</v>
       </c>
       <c r="D133" t="n">
-        <v>835.813</v>
+        <v>825.29</v>
       </c>
       <c r="E133" t="n">
-        <v>163.21</v>
+        <v>162.347</v>
       </c>
       <c r="F133" t="n">
-        <v>388.557</v>
+        <v>390.766</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>172.324</v>
+        <v>170.748</v>
       </c>
       <c r="C134" t="n">
-        <v>414.153</v>
+        <v>412.389</v>
       </c>
       <c r="D134" t="n">
-        <v>811.837</v>
+        <v>810.617</v>
       </c>
       <c r="E134" t="n">
-        <v>160.811</v>
+        <v>161.505</v>
       </c>
       <c r="F134" t="n">
-        <v>376.498</v>
+        <v>385.752</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>168.676</v>
+        <v>175.479</v>
       </c>
       <c r="C135" t="n">
-        <v>401.189</v>
+        <v>404.261</v>
       </c>
       <c r="D135" t="n">
-        <v>1134.35</v>
+        <v>1119.27</v>
       </c>
       <c r="E135" t="n">
-        <v>163.942</v>
+        <v>160.508</v>
       </c>
       <c r="F135" t="n">
-        <v>381.154</v>
+        <v>376.678</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>174.893</v>
+        <v>170.937</v>
       </c>
       <c r="C136" t="n">
-        <v>401.909</v>
+        <v>400.538</v>
       </c>
       <c r="D136" t="n">
-        <v>1126.25</v>
+        <v>1137.43</v>
       </c>
       <c r="E136" t="n">
-        <v>163.402</v>
+        <v>165.869</v>
       </c>
       <c r="F136" t="n">
-        <v>376.62</v>
+        <v>381.517</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>174.2</v>
+        <v>175.901</v>
       </c>
       <c r="C137" t="n">
-        <v>393.98</v>
+        <v>400.236</v>
       </c>
       <c r="D137" t="n">
-        <v>1070.56</v>
+        <v>1082.51</v>
       </c>
       <c r="E137" t="n">
-        <v>203.066</v>
+        <v>207.93</v>
       </c>
       <c r="F137" t="n">
-        <v>561.698</v>
+        <v>562.572</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>203.456</v>
+        <v>212.645</v>
       </c>
       <c r="C138" t="n">
-        <v>577.678</v>
+        <v>597.152</v>
       </c>
       <c r="D138" t="n">
-        <v>1039.21</v>
+        <v>1078.42</v>
       </c>
       <c r="E138" t="n">
-        <v>205.223</v>
+        <v>207.483</v>
       </c>
       <c r="F138" t="n">
-        <v>531.029</v>
+        <v>546.388</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>204.205</v>
+        <v>212.604</v>
       </c>
       <c r="C139" t="n">
-        <v>565.9690000000001</v>
+        <v>578.093</v>
       </c>
       <c r="D139" t="n">
-        <v>1021.78</v>
+        <v>1062.04</v>
       </c>
       <c r="E139" t="n">
-        <v>200.602</v>
+        <v>203.311</v>
       </c>
       <c r="F139" t="n">
-        <v>528.895</v>
+        <v>532.018</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>207.403</v>
+        <v>210.126</v>
       </c>
       <c r="C140" t="n">
-        <v>555.845</v>
+        <v>557.028</v>
       </c>
       <c r="D140" t="n">
-        <v>1013.94</v>
+        <v>1004.22</v>
       </c>
       <c r="E140" t="n">
-        <v>199.568</v>
+        <v>197.567</v>
       </c>
       <c r="F140" t="n">
-        <v>507.37</v>
+        <v>508.972</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>207.377</v>
+        <v>203.218</v>
       </c>
       <c r="C141" t="n">
-        <v>538.641</v>
+        <v>535.157</v>
       </c>
       <c r="D141" t="n">
-        <v>995.489</v>
+        <v>988.449</v>
       </c>
       <c r="E141" t="n">
-        <v>198.392</v>
+        <v>195.675</v>
       </c>
       <c r="F141" t="n">
-        <v>493.698</v>
+        <v>496.584</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>199.528</v>
+        <v>201.344</v>
       </c>
       <c r="C142" t="n">
-        <v>527.558</v>
+        <v>527.324</v>
       </c>
       <c r="D142" t="n">
-        <v>958.72</v>
+        <v>965.428</v>
       </c>
       <c r="E142" t="n">
-        <v>194.467</v>
+        <v>193.797</v>
       </c>
       <c r="F142" t="n">
-        <v>482.132</v>
+        <v>489.215</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>204.498</v>
+        <v>204.369</v>
       </c>
       <c r="C143" t="n">
-        <v>518.226</v>
+        <v>518.773</v>
       </c>
       <c r="D143" t="n">
-        <v>945.903</v>
+        <v>959.448</v>
       </c>
       <c r="E143" t="n">
-        <v>190.199</v>
+        <v>196.474</v>
       </c>
       <c r="F143" t="n">
-        <v>466.91</v>
+        <v>477.305</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running insertion.xlsx
+++ b/clang-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>55.2328</v>
+        <v>22.5284</v>
       </c>
       <c r="C2" t="n">
-        <v>82.6602</v>
+        <v>39.0044</v>
       </c>
       <c r="D2" t="n">
-        <v>130.496</v>
+        <v>56.4033</v>
       </c>
       <c r="E2" t="n">
-        <v>55.686</v>
+        <v>19.4667</v>
       </c>
       <c r="F2" t="n">
-        <v>78.1617</v>
+        <v>36.2782</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>53.9874</v>
+        <v>21.6981</v>
       </c>
       <c r="C3" t="n">
-        <v>81.239</v>
+        <v>38.352</v>
       </c>
       <c r="D3" t="n">
-        <v>129.359</v>
+        <v>55.7774</v>
       </c>
       <c r="E3" t="n">
-        <v>53.952</v>
+        <v>18.9945</v>
       </c>
       <c r="F3" t="n">
-        <v>76.809</v>
+        <v>35.7703</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>52.726</v>
+        <v>20.9204</v>
       </c>
       <c r="C4" t="n">
-        <v>79.1452</v>
+        <v>37.8303</v>
       </c>
       <c r="D4" t="n">
-        <v>126.714</v>
+        <v>55.2047</v>
       </c>
       <c r="E4" t="n">
-        <v>52.5822</v>
+        <v>18.5071</v>
       </c>
       <c r="F4" t="n">
-        <v>74.8133</v>
+        <v>35.3632</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>51.4458</v>
+        <v>21.2931</v>
       </c>
       <c r="C5" t="n">
-        <v>77.4756</v>
+        <v>37.4518</v>
       </c>
       <c r="D5" t="n">
-        <v>124.614</v>
+        <v>54.7022</v>
       </c>
       <c r="E5" t="n">
-        <v>51.3794</v>
+        <v>18.1492</v>
       </c>
       <c r="F5" t="n">
-        <v>73.8064</v>
+        <v>34.9974</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>50.2337</v>
+        <v>20.5935</v>
       </c>
       <c r="C6" t="n">
-        <v>75.7337</v>
+        <v>37.1684</v>
       </c>
       <c r="D6" t="n">
-        <v>123.224</v>
+        <v>54.2934</v>
       </c>
       <c r="E6" t="n">
-        <v>50.3318</v>
+        <v>17.8466</v>
       </c>
       <c r="F6" t="n">
-        <v>72.1788</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>49.4058</v>
+        <v>20.7536</v>
       </c>
       <c r="C7" t="n">
-        <v>74.92700000000001</v>
+        <v>36.9137</v>
       </c>
       <c r="D7" t="n">
-        <v>170.654</v>
+        <v>69.5963</v>
       </c>
       <c r="E7" t="n">
-        <v>49.4335</v>
+        <v>17.6572</v>
       </c>
       <c r="F7" t="n">
-        <v>71.0074</v>
+        <v>34.598</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>48.5986</v>
+        <v>20.1052</v>
       </c>
       <c r="C8" t="n">
-        <v>73.4558</v>
+        <v>36.7081</v>
       </c>
       <c r="D8" t="n">
-        <v>167.958</v>
+        <v>68.0257</v>
       </c>
       <c r="E8" t="n">
-        <v>48.8038</v>
+        <v>17.6209</v>
       </c>
       <c r="F8" t="n">
-        <v>69.8989</v>
+        <v>34.7494</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>47.9651</v>
+        <v>20.0654</v>
       </c>
       <c r="C9" t="n">
-        <v>72.6005</v>
+        <v>36.7785</v>
       </c>
       <c r="D9" t="n">
-        <v>162.526</v>
+        <v>66.6262</v>
       </c>
       <c r="E9" t="n">
-        <v>68.1212</v>
+        <v>26.0857</v>
       </c>
       <c r="F9" t="n">
-        <v>100.206</v>
+        <v>41.9982</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>64.9058</v>
+        <v>29.1361</v>
       </c>
       <c r="C10" t="n">
-        <v>104.669</v>
+        <v>46.4083</v>
       </c>
       <c r="D10" t="n">
-        <v>159.898</v>
+        <v>65.3262</v>
       </c>
       <c r="E10" t="n">
-        <v>65.97920000000001</v>
+        <v>25.1673</v>
       </c>
       <c r="F10" t="n">
-        <v>97.8549</v>
+        <v>41.9191</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>63.0563</v>
+        <v>28.2742</v>
       </c>
       <c r="C11" t="n">
-        <v>101.381</v>
+        <v>44.9883</v>
       </c>
       <c r="D11" t="n">
-        <v>154.949</v>
+        <v>64.14530000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>63.9303</v>
+        <v>24.3456</v>
       </c>
       <c r="F11" t="n">
-        <v>94.1096</v>
+        <v>40.6001</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>61.3648</v>
+        <v>27.0471</v>
       </c>
       <c r="C12" t="n">
-        <v>98.35639999999999</v>
+        <v>44.0221</v>
       </c>
       <c r="D12" t="n">
-        <v>153.26</v>
+        <v>62.9965</v>
       </c>
       <c r="E12" t="n">
-        <v>62.0944</v>
+        <v>23.6178</v>
       </c>
       <c r="F12" t="n">
-        <v>91.9734</v>
+        <v>39.8112</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>59.8143</v>
+        <v>26.3968</v>
       </c>
       <c r="C13" t="n">
-        <v>96.1023</v>
+        <v>42.5891</v>
       </c>
       <c r="D13" t="n">
-        <v>149.345</v>
+        <v>62.0774</v>
       </c>
       <c r="E13" t="n">
-        <v>60.3647</v>
+        <v>22.8257</v>
       </c>
       <c r="F13" t="n">
-        <v>89.51860000000001</v>
+        <v>38.9557</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>58.2646</v>
+        <v>25.74</v>
       </c>
       <c r="C14" t="n">
-        <v>93.3296</v>
+        <v>41.7263</v>
       </c>
       <c r="D14" t="n">
-        <v>146.906</v>
+        <v>61.407</v>
       </c>
       <c r="E14" t="n">
-        <v>58.5835</v>
+        <v>22.1333</v>
       </c>
       <c r="F14" t="n">
-        <v>87.1934</v>
+        <v>38.093</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>56.6619</v>
+        <v>24.7433</v>
       </c>
       <c r="C15" t="n">
-        <v>91.77500000000001</v>
+        <v>40.7254</v>
       </c>
       <c r="D15" t="n">
-        <v>144.141</v>
+        <v>60.6744</v>
       </c>
       <c r="E15" t="n">
-        <v>57.0208</v>
+        <v>21.6062</v>
       </c>
       <c r="F15" t="n">
-        <v>84.87009999999999</v>
+        <v>37.5234</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>55.3385</v>
+        <v>24.3889</v>
       </c>
       <c r="C16" t="n">
-        <v>89.3068</v>
+        <v>39.7687</v>
       </c>
       <c r="D16" t="n">
-        <v>141.868</v>
+        <v>60.2063</v>
       </c>
       <c r="E16" t="n">
-        <v>55.5789</v>
+        <v>20.9182</v>
       </c>
       <c r="F16" t="n">
-        <v>82.5896</v>
+        <v>36.8918</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>54.0565</v>
+        <v>23.7255</v>
       </c>
       <c r="C17" t="n">
-        <v>86.8934</v>
+        <v>39.1398</v>
       </c>
       <c r="D17" t="n">
-        <v>139.225</v>
+        <v>59.7227</v>
       </c>
       <c r="E17" t="n">
-        <v>54.1698</v>
+        <v>20.3522</v>
       </c>
       <c r="F17" t="n">
-        <v>81.1579</v>
+        <v>36.3644</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>52.837</v>
+        <v>24.1704</v>
       </c>
       <c r="C18" t="n">
-        <v>85.17570000000001</v>
+        <v>39.1854</v>
       </c>
       <c r="D18" t="n">
-        <v>136.259</v>
+        <v>58.7869</v>
       </c>
       <c r="E18" t="n">
-        <v>52.906</v>
+        <v>19.9155</v>
       </c>
       <c r="F18" t="n">
-        <v>79.7714</v>
+        <v>35.8955</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>51.7148</v>
+        <v>22.0801</v>
       </c>
       <c r="C19" t="n">
-        <v>82.5823</v>
+        <v>38.5793</v>
       </c>
       <c r="D19" t="n">
-        <v>136.099</v>
+        <v>58.2516</v>
       </c>
       <c r="E19" t="n">
-        <v>51.5953</v>
+        <v>19.5249</v>
       </c>
       <c r="F19" t="n">
-        <v>77.3276</v>
+        <v>35.2473</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>50.6453</v>
+        <v>21.5854</v>
       </c>
       <c r="C20" t="n">
-        <v>81.04040000000001</v>
+        <v>38.4072</v>
       </c>
       <c r="D20" t="n">
-        <v>133.886</v>
+        <v>57.7182</v>
       </c>
       <c r="E20" t="n">
-        <v>50.5828</v>
+        <v>19.2211</v>
       </c>
       <c r="F20" t="n">
-        <v>75.4021</v>
+        <v>34.8993</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>49.7695</v>
+        <v>21.3951</v>
       </c>
       <c r="C21" t="n">
-        <v>79.3425</v>
+        <v>37.7488</v>
       </c>
       <c r="D21" t="n">
-        <v>185.836</v>
+        <v>75.4609</v>
       </c>
       <c r="E21" t="n">
-        <v>49.665</v>
+        <v>19.1356</v>
       </c>
       <c r="F21" t="n">
-        <v>74.0822</v>
+        <v>34.8386</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>48.9944</v>
+        <v>21.1463</v>
       </c>
       <c r="C22" t="n">
-        <v>78.087</v>
+        <v>37.6303</v>
       </c>
       <c r="D22" t="n">
-        <v>181.632</v>
+        <v>73.6306</v>
       </c>
       <c r="E22" t="n">
-        <v>49.0211</v>
+        <v>19.1057</v>
       </c>
       <c r="F22" t="n">
-        <v>73.0806</v>
+        <v>34.8792</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>48.4681</v>
+        <v>21.4217</v>
       </c>
       <c r="C23" t="n">
-        <v>77.03270000000001</v>
+        <v>37.5505</v>
       </c>
       <c r="D23" t="n">
-        <v>176.727</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>68.8959</v>
+        <v>27.6119</v>
       </c>
       <c r="F23" t="n">
-        <v>106.316</v>
+        <v>43.0897</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>65.991</v>
+        <v>30.0262</v>
       </c>
       <c r="C24" t="n">
-        <v>111.454</v>
+        <v>47.543</v>
       </c>
       <c r="D24" t="n">
-        <v>173.632</v>
+        <v>70.9965</v>
       </c>
       <c r="E24" t="n">
-        <v>66.8249</v>
+        <v>26.7202</v>
       </c>
       <c r="F24" t="n">
-        <v>102.661</v>
+        <v>42.1683</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>64.2831</v>
+        <v>28.9117</v>
       </c>
       <c r="C25" t="n">
-        <v>108.249</v>
+        <v>46.6634</v>
       </c>
       <c r="D25" t="n">
-        <v>169.224</v>
+        <v>69.646</v>
       </c>
       <c r="E25" t="n">
-        <v>64.8425</v>
+        <v>25.7077</v>
       </c>
       <c r="F25" t="n">
-        <v>99.9328</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>62.6652</v>
+        <v>27.9033</v>
       </c>
       <c r="C26" t="n">
-        <v>105.962</v>
+        <v>45.591</v>
       </c>
       <c r="D26" t="n">
-        <v>166.692</v>
+        <v>68.3809</v>
       </c>
       <c r="E26" t="n">
-        <v>63.0518</v>
+        <v>24.9696</v>
       </c>
       <c r="F26" t="n">
-        <v>96.6708</v>
+        <v>40.1018</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>61.0321</v>
+        <v>26.9481</v>
       </c>
       <c r="C27" t="n">
-        <v>102.459</v>
+        <v>44.4766</v>
       </c>
       <c r="D27" t="n">
-        <v>162.846</v>
+        <v>67.6387</v>
       </c>
       <c r="E27" t="n">
-        <v>61.3019</v>
+        <v>24.2369</v>
       </c>
       <c r="F27" t="n">
-        <v>95.29600000000001</v>
+        <v>39.6663</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>59.6245</v>
+        <v>26.1656</v>
       </c>
       <c r="C28" t="n">
-        <v>100.043</v>
+        <v>43.2818</v>
       </c>
       <c r="D28" t="n">
-        <v>159.358</v>
+        <v>66.44970000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>59.6002</v>
+        <v>23.4795</v>
       </c>
       <c r="F28" t="n">
-        <v>92.02760000000001</v>
+        <v>38.6579</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>58.0653</v>
+        <v>25.2576</v>
       </c>
       <c r="C29" t="n">
-        <v>97.3201</v>
+        <v>42.5037</v>
       </c>
       <c r="D29" t="n">
-        <v>157.348</v>
+        <v>65.745</v>
       </c>
       <c r="E29" t="n">
-        <v>57.9727</v>
+        <v>22.5892</v>
       </c>
       <c r="F29" t="n">
-        <v>89.6177</v>
+        <v>38.0376</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>57.2509</v>
+        <v>24.743</v>
       </c>
       <c r="C30" t="n">
-        <v>95.7517</v>
+        <v>41.7408</v>
       </c>
       <c r="D30" t="n">
-        <v>154.223</v>
+        <v>64.92700000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>56.5918</v>
+        <v>22.3809</v>
       </c>
       <c r="F30" t="n">
-        <v>86.4961</v>
+        <v>37.3619</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>55.4095</v>
+        <v>23.9958</v>
       </c>
       <c r="C31" t="n">
-        <v>93.4791</v>
+        <v>41.1954</v>
       </c>
       <c r="D31" t="n">
-        <v>153.33</v>
+        <v>64.36320000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>55.0724</v>
+        <v>21.6012</v>
       </c>
       <c r="F31" t="n">
-        <v>86.76139999999999</v>
+        <v>36.8255</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>54.1309</v>
+        <v>23.5658</v>
       </c>
       <c r="C32" t="n">
-        <v>91.1862</v>
+        <v>40.569</v>
       </c>
       <c r="D32" t="n">
-        <v>149.565</v>
+        <v>63.8971</v>
       </c>
       <c r="E32" t="n">
-        <v>53.8079</v>
+        <v>21.0532</v>
       </c>
       <c r="F32" t="n">
-        <v>83.2529</v>
+        <v>36.3183</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>53.0812</v>
+        <v>22.8697</v>
       </c>
       <c r="C33" t="n">
-        <v>88.6767</v>
+        <v>39.9559</v>
       </c>
       <c r="D33" t="n">
-        <v>146.407</v>
+        <v>63.4223</v>
       </c>
       <c r="E33" t="n">
-        <v>52.6492</v>
+        <v>20.6213</v>
       </c>
       <c r="F33" t="n">
-        <v>82.43470000000001</v>
+        <v>35.9129</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>51.9687</v>
+        <v>22.6144</v>
       </c>
       <c r="C34" t="n">
-        <v>87.26990000000001</v>
+        <v>39.3035</v>
       </c>
       <c r="D34" t="n">
-        <v>146.761</v>
+        <v>62.5967</v>
       </c>
       <c r="E34" t="n">
-        <v>51.5074</v>
+        <v>20.2184</v>
       </c>
       <c r="F34" t="n">
-        <v>79.73779999999999</v>
+        <v>35.6214</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>50.9017</v>
+        <v>21.8138</v>
       </c>
       <c r="C35" t="n">
-        <v>85.1855</v>
+        <v>38.8703</v>
       </c>
       <c r="D35" t="n">
-        <v>205.077</v>
+        <v>80.92010000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>50.5783</v>
+        <v>19.8865</v>
       </c>
       <c r="F35" t="n">
-        <v>79.6711</v>
+        <v>35.4602</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>50.2048</v>
+        <v>21.6987</v>
       </c>
       <c r="C36" t="n">
-        <v>84.2253</v>
+        <v>38.4667</v>
       </c>
       <c r="D36" t="n">
-        <v>203.833</v>
+        <v>79.28400000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>49.8716</v>
+        <v>19.9347</v>
       </c>
       <c r="F36" t="n">
-        <v>77.0035</v>
+        <v>35.5011</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>49.4777</v>
+        <v>21.7308</v>
       </c>
       <c r="C37" t="n">
-        <v>82.0415</v>
+        <v>38.5809</v>
       </c>
       <c r="D37" t="n">
-        <v>195.938</v>
+        <v>77.6327</v>
       </c>
       <c r="E37" t="n">
-        <v>70.4659</v>
+        <v>28.5819</v>
       </c>
       <c r="F37" t="n">
-        <v>114.035</v>
+        <v>44.0813</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>67.9825</v>
+        <v>29.7328</v>
       </c>
       <c r="C38" t="n">
-        <v>119.946</v>
+        <v>47.9488</v>
       </c>
       <c r="D38" t="n">
-        <v>189.955</v>
+        <v>76.07429999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>68.42959999999999</v>
+        <v>27.658</v>
       </c>
       <c r="F38" t="n">
-        <v>108.941</v>
+        <v>43.0935</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>66.151</v>
+        <v>29.0345</v>
       </c>
       <c r="C39" t="n">
-        <v>118.662</v>
+        <v>46.9412</v>
       </c>
       <c r="D39" t="n">
-        <v>185.877</v>
+        <v>74.6763</v>
       </c>
       <c r="E39" t="n">
-        <v>66.4278</v>
+        <v>26.8682</v>
       </c>
       <c r="F39" t="n">
-        <v>107.17</v>
+        <v>42.2957</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>64.49469999999999</v>
+        <v>28.1302</v>
       </c>
       <c r="C40" t="n">
-        <v>113.684</v>
+        <v>46.057</v>
       </c>
       <c r="D40" t="n">
-        <v>183.4</v>
+        <v>73.5771</v>
       </c>
       <c r="E40" t="n">
-        <v>64.491</v>
+        <v>25.8927</v>
       </c>
       <c r="F40" t="n">
-        <v>106.078</v>
+        <v>41.499</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>62.8333</v>
+        <v>27.1611</v>
       </c>
       <c r="C41" t="n">
-        <v>111.611</v>
+        <v>45.0507</v>
       </c>
       <c r="D41" t="n">
-        <v>181.877</v>
+        <v>72.1583</v>
       </c>
       <c r="E41" t="n">
-        <v>62.6402</v>
+        <v>25.344</v>
       </c>
       <c r="F41" t="n">
-        <v>103.211</v>
+        <v>40.6417</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>61.0416</v>
+        <v>26.4578</v>
       </c>
       <c r="C42" t="n">
-        <v>109.268</v>
+        <v>44.2472</v>
       </c>
       <c r="D42" t="n">
-        <v>173.646</v>
+        <v>71.21510000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>60.94</v>
+        <v>24.4352</v>
       </c>
       <c r="F42" t="n">
-        <v>98.8265</v>
+        <v>39.8645</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>59.6251</v>
+        <v>26.294</v>
       </c>
       <c r="C43" t="n">
-        <v>105.631</v>
+        <v>43.4142</v>
       </c>
       <c r="D43" t="n">
-        <v>170.44</v>
+        <v>70.15219999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>59.2901</v>
+        <v>23.8133</v>
       </c>
       <c r="F43" t="n">
-        <v>98.1277</v>
+        <v>39.0352</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>58.204</v>
+        <v>25.7818</v>
       </c>
       <c r="C44" t="n">
-        <v>102.408</v>
+        <v>42.6592</v>
       </c>
       <c r="D44" t="n">
-        <v>166.085</v>
+        <v>69.172</v>
       </c>
       <c r="E44" t="n">
-        <v>57.7249</v>
+        <v>23.1682</v>
       </c>
       <c r="F44" t="n">
-        <v>94.7166</v>
+        <v>38.3952</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>56.8477</v>
+        <v>26.2066</v>
       </c>
       <c r="C45" t="n">
-        <v>101.319</v>
+        <v>42.0816</v>
       </c>
       <c r="D45" t="n">
-        <v>166.771</v>
+        <v>68.46599999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>56.2827</v>
+        <v>22.6835</v>
       </c>
       <c r="F45" t="n">
-        <v>91.77379999999999</v>
+        <v>38.0914</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>55.6338</v>
+        <v>24.0554</v>
       </c>
       <c r="C46" t="n">
-        <v>99.4345</v>
+        <v>41.5565</v>
       </c>
       <c r="D46" t="n">
-        <v>163.225</v>
+        <v>67.8282</v>
       </c>
       <c r="E46" t="n">
-        <v>55.0734</v>
+        <v>22.2799</v>
       </c>
       <c r="F46" t="n">
-        <v>88.2647</v>
+        <v>37.5155</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>54.5439</v>
+        <v>23.7075</v>
       </c>
       <c r="C47" t="n">
-        <v>96.929</v>
+        <v>41.0283</v>
       </c>
       <c r="D47" t="n">
-        <v>163.925</v>
+        <v>67.3766</v>
       </c>
       <c r="E47" t="n">
-        <v>53.7593</v>
+        <v>21.6685</v>
       </c>
       <c r="F47" t="n">
-        <v>89.3014</v>
+        <v>37.4994</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>53.3845</v>
+        <v>23.3698</v>
       </c>
       <c r="C48" t="n">
-        <v>94.7016</v>
+        <v>40.4478</v>
       </c>
       <c r="D48" t="n">
-        <v>159.361</v>
+        <v>66.6096</v>
       </c>
       <c r="E48" t="n">
-        <v>52.705</v>
+        <v>21.2424</v>
       </c>
       <c r="F48" t="n">
-        <v>86.73699999999999</v>
+        <v>37.0772</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>52.4305</v>
+        <v>23.1136</v>
       </c>
       <c r="C49" t="n">
-        <v>93.02800000000001</v>
+        <v>40.2203</v>
       </c>
       <c r="D49" t="n">
-        <v>156.089</v>
+        <v>66.2658</v>
       </c>
       <c r="E49" t="n">
-        <v>51.8222</v>
+        <v>21.0388</v>
       </c>
       <c r="F49" t="n">
-        <v>83.6238</v>
+        <v>36.7693</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>51.6752</v>
+        <v>22.1087</v>
       </c>
       <c r="C50" t="n">
-        <v>89.76439999999999</v>
+        <v>39.9966</v>
       </c>
       <c r="D50" t="n">
-        <v>236.438</v>
+        <v>83.77079999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>51.058</v>
+        <v>20.8265</v>
       </c>
       <c r="F50" t="n">
-        <v>83.1666</v>
+        <v>36.5181</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>50.9318</v>
+        <v>21.9417</v>
       </c>
       <c r="C51" t="n">
-        <v>89.10429999999999</v>
+        <v>39.9009</v>
       </c>
       <c r="D51" t="n">
-        <v>233.239</v>
+        <v>81.9991</v>
       </c>
       <c r="E51" t="n">
-        <v>72.5198</v>
+        <v>29.6956</v>
       </c>
       <c r="F51" t="n">
-        <v>129.345</v>
+        <v>45.4035</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>50.5684</v>
+        <v>23.2521</v>
       </c>
       <c r="C52" t="n">
-        <v>89.1752</v>
+        <v>39.8491</v>
       </c>
       <c r="D52" t="n">
-        <v>227.456</v>
+        <v>80.3909</v>
       </c>
       <c r="E52" t="n">
-        <v>70.44</v>
+        <v>28.7422</v>
       </c>
       <c r="F52" t="n">
-        <v>124.258</v>
+        <v>44.5238</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>68.0279</v>
+        <v>30.3739</v>
       </c>
       <c r="C53" t="n">
-        <v>133.074</v>
+        <v>49.7713</v>
       </c>
       <c r="D53" t="n">
-        <v>220.214</v>
+        <v>78.8109</v>
       </c>
       <c r="E53" t="n">
-        <v>68.4978</v>
+        <v>28.0519</v>
       </c>
       <c r="F53" t="n">
-        <v>121.543</v>
+        <v>43.7155</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>66.2702</v>
+        <v>29.1386</v>
       </c>
       <c r="C54" t="n">
-        <v>127.206</v>
+        <v>48.7159</v>
       </c>
       <c r="D54" t="n">
-        <v>214.585</v>
+        <v>77.4183</v>
       </c>
       <c r="E54" t="n">
-        <v>66.6465</v>
+        <v>27.0675</v>
       </c>
       <c r="F54" t="n">
-        <v>115.558</v>
+        <v>42.9422</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>64.58629999999999</v>
+        <v>28.3489</v>
       </c>
       <c r="C55" t="n">
-        <v>125.038</v>
+        <v>47.6061</v>
       </c>
       <c r="D55" t="n">
-        <v>206.282</v>
+        <v>76.2594</v>
       </c>
       <c r="E55" t="n">
-        <v>64.8241</v>
+        <v>26.2684</v>
       </c>
       <c r="F55" t="n">
-        <v>111.756</v>
+        <v>42.1596</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>62.9627</v>
+        <v>27.2529</v>
       </c>
       <c r="C56" t="n">
-        <v>121.996</v>
+        <v>47.1209</v>
       </c>
       <c r="D56" t="n">
-        <v>205.997</v>
+        <v>75.182</v>
       </c>
       <c r="E56" t="n">
-        <v>63.1119</v>
+        <v>25.6014</v>
       </c>
       <c r="F56" t="n">
-        <v>108.724</v>
+        <v>41.5648</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>61.4763</v>
+        <v>27.391</v>
       </c>
       <c r="C57" t="n">
-        <v>120.366</v>
+        <v>46.282</v>
       </c>
       <c r="D57" t="n">
-        <v>209.114</v>
+        <v>74.0127</v>
       </c>
       <c r="E57" t="n">
-        <v>61.5404</v>
+        <v>24.9008</v>
       </c>
       <c r="F57" t="n">
-        <v>104.789</v>
+        <v>40.9026</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>60.0829</v>
+        <v>26.4177</v>
       </c>
       <c r="C58" t="n">
-        <v>117.714</v>
+        <v>45.6996</v>
       </c>
       <c r="D58" t="n">
-        <v>201.09</v>
+        <v>73.1662</v>
       </c>
       <c r="E58" t="n">
-        <v>59.9816</v>
+        <v>24.2662</v>
       </c>
       <c r="F58" t="n">
-        <v>98.94970000000001</v>
+        <v>40.3408</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>58.782</v>
+        <v>25.4311</v>
       </c>
       <c r="C59" t="n">
-        <v>113.426</v>
+        <v>45.1288</v>
       </c>
       <c r="D59" t="n">
-        <v>200.063</v>
+        <v>72.288</v>
       </c>
       <c r="E59" t="n">
-        <v>58.487</v>
+        <v>23.6981</v>
       </c>
       <c r="F59" t="n">
-        <v>97.4131</v>
+        <v>39.7668</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>57.5904</v>
+        <v>25.0277</v>
       </c>
       <c r="C60" t="n">
-        <v>110.074</v>
+        <v>44.5751</v>
       </c>
       <c r="D60" t="n">
-        <v>199.705</v>
+        <v>71.63379999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>57.1301</v>
+        <v>23.0683</v>
       </c>
       <c r="F60" t="n">
-        <v>100.575</v>
+        <v>39.2154</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>56.3742</v>
+        <v>24.6642</v>
       </c>
       <c r="C61" t="n">
-        <v>107.782</v>
+        <v>43.9676</v>
       </c>
       <c r="D61" t="n">
-        <v>195.745</v>
+        <v>70.8421</v>
       </c>
       <c r="E61" t="n">
-        <v>55.9705</v>
+        <v>22.6826</v>
       </c>
       <c r="F61" t="n">
-        <v>98.1661</v>
+        <v>38.8215</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>55.2818</v>
+        <v>23.9893</v>
       </c>
       <c r="C62" t="n">
-        <v>105.037</v>
+        <v>43.467</v>
       </c>
       <c r="D62" t="n">
-        <v>196.097</v>
+        <v>70.20650000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>54.7732</v>
+        <v>22.2079</v>
       </c>
       <c r="F62" t="n">
-        <v>92.96169999999999</v>
+        <v>38.513</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>54.2319</v>
+        <v>24.2907</v>
       </c>
       <c r="C63" t="n">
-        <v>100.953</v>
+        <v>42.7696</v>
       </c>
       <c r="D63" t="n">
-        <v>191.235</v>
+        <v>69.75369999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>53.9405</v>
+        <v>21.9629</v>
       </c>
       <c r="F63" t="n">
-        <v>90.73050000000001</v>
+        <v>38.1824</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>53.3852</v>
+        <v>23.292</v>
       </c>
       <c r="C64" t="n">
-        <v>101.358</v>
+        <v>42.5558</v>
       </c>
       <c r="D64" t="n">
-        <v>385.938</v>
+        <v>90.6687</v>
       </c>
       <c r="E64" t="n">
-        <v>52.8022</v>
+        <v>21.9381</v>
       </c>
       <c r="F64" t="n">
-        <v>87.68170000000001</v>
+        <v>38.1893</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>52.6437</v>
+        <v>23.055</v>
       </c>
       <c r="C65" t="n">
-        <v>100.434</v>
+        <v>42.5495</v>
       </c>
       <c r="D65" t="n">
-        <v>379.735</v>
+        <v>88.6922</v>
       </c>
       <c r="E65" t="n">
-        <v>52.3836</v>
+        <v>21.8842</v>
       </c>
       <c r="F65" t="n">
-        <v>88.9389</v>
+        <v>38.3279</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>52.2247</v>
+        <v>23.0663</v>
       </c>
       <c r="C66" t="n">
-        <v>98.7355</v>
+        <v>42.4823</v>
       </c>
       <c r="D66" t="n">
-        <v>377.345</v>
+        <v>86.7988</v>
       </c>
       <c r="E66" t="n">
-        <v>73.595</v>
+        <v>33.6074</v>
       </c>
       <c r="F66" t="n">
-        <v>158.039</v>
+        <v>48.6492</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>70.7547</v>
+        <v>38.416</v>
       </c>
       <c r="C67" t="n">
-        <v>174.405</v>
+        <v>57.8502</v>
       </c>
       <c r="D67" t="n">
-        <v>360.257</v>
+        <v>85.1322</v>
       </c>
       <c r="E67" t="n">
-        <v>71.3562</v>
+        <v>32.6267</v>
       </c>
       <c r="F67" t="n">
-        <v>153.431</v>
+        <v>48.0412</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>68.6759</v>
+        <v>38.9214</v>
       </c>
       <c r="C68" t="n">
-        <v>167.007</v>
+        <v>57.3619</v>
       </c>
       <c r="D68" t="n">
-        <v>358.62</v>
+        <v>83.602</v>
       </c>
       <c r="E68" t="n">
-        <v>69.46259999999999</v>
+        <v>31.9536</v>
       </c>
       <c r="F68" t="n">
-        <v>150.391</v>
+        <v>47.145</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>67.3639</v>
+        <v>37.3716</v>
       </c>
       <c r="C69" t="n">
-        <v>166.632</v>
+        <v>56.3239</v>
       </c>
       <c r="D69" t="n">
-        <v>342.485</v>
+        <v>82.15389999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>67.4648</v>
+        <v>31.032</v>
       </c>
       <c r="F69" t="n">
-        <v>146.905</v>
+        <v>46.6977</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>65.4083</v>
+        <v>36.5242</v>
       </c>
       <c r="C70" t="n">
-        <v>157.107</v>
+        <v>55.4491</v>
       </c>
       <c r="D70" t="n">
-        <v>335.061</v>
+        <v>81.15479999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>66.08929999999999</v>
+        <v>30.5434</v>
       </c>
       <c r="F70" t="n">
-        <v>144.543</v>
+        <v>45.997</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>64.4834</v>
+        <v>35.9796</v>
       </c>
       <c r="C71" t="n">
-        <v>156.03</v>
+        <v>54.7214</v>
       </c>
       <c r="D71" t="n">
-        <v>336.178</v>
+        <v>80.30110000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>64.71299999999999</v>
+        <v>29.6307</v>
       </c>
       <c r="F71" t="n">
-        <v>140.374</v>
+        <v>45.3195</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>63.1747</v>
+        <v>35.911</v>
       </c>
       <c r="C72" t="n">
-        <v>154.347</v>
+        <v>53.6655</v>
       </c>
       <c r="D72" t="n">
-        <v>336.683</v>
+        <v>79.5753</v>
       </c>
       <c r="E72" t="n">
-        <v>63.1207</v>
+        <v>29.138</v>
       </c>
       <c r="F72" t="n">
-        <v>136.083</v>
+        <v>44.7888</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>61.9683</v>
+        <v>34.0906</v>
       </c>
       <c r="C73" t="n">
-        <v>152.995</v>
+        <v>53.4018</v>
       </c>
       <c r="D73" t="n">
-        <v>335.651</v>
+        <v>79.05029999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>61.6425</v>
+        <v>28.5575</v>
       </c>
       <c r="F73" t="n">
-        <v>125.299</v>
+        <v>44.2675</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>60.7928</v>
+        <v>35.0993</v>
       </c>
       <c r="C74" t="n">
-        <v>142.747</v>
+        <v>52.9474</v>
       </c>
       <c r="D74" t="n">
-        <v>334.224</v>
+        <v>78.6024</v>
       </c>
       <c r="E74" t="n">
-        <v>60.2557</v>
+        <v>27.715</v>
       </c>
       <c r="F74" t="n">
-        <v>129.227</v>
+        <v>43.8517</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>59.6687</v>
+        <v>33.3421</v>
       </c>
       <c r="C75" t="n">
-        <v>147.112</v>
+        <v>52.4158</v>
       </c>
       <c r="D75" t="n">
-        <v>336.522</v>
+        <v>78.31100000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>58.9167</v>
+        <v>27.46</v>
       </c>
       <c r="F75" t="n">
-        <v>129.01</v>
+        <v>43.3316</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>58.3184</v>
+        <v>32.8076</v>
       </c>
       <c r="C76" t="n">
-        <v>143.129</v>
+        <v>51.7545</v>
       </c>
       <c r="D76" t="n">
-        <v>332.271</v>
+        <v>78.1691</v>
       </c>
       <c r="E76" t="n">
-        <v>57.8554</v>
+        <v>27.2269</v>
       </c>
       <c r="F76" t="n">
-        <v>119.075</v>
+        <v>43.2024</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>57.5685</v>
+        <v>32.4364</v>
       </c>
       <c r="C77" t="n">
-        <v>134.81</v>
+        <v>51.8393</v>
       </c>
       <c r="D77" t="n">
-        <v>322.089</v>
+        <v>78.26130000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>56.7986</v>
+        <v>26.6738</v>
       </c>
       <c r="F77" t="n">
-        <v>121.785</v>
+        <v>42.8807</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>56.7273</v>
+        <v>31.3777</v>
       </c>
       <c r="C78" t="n">
-        <v>137.17</v>
+        <v>51.4155</v>
       </c>
       <c r="D78" t="n">
-        <v>633.129</v>
+        <v>128.182</v>
       </c>
       <c r="E78" t="n">
-        <v>56.4411</v>
+        <v>26.5013</v>
       </c>
       <c r="F78" t="n">
-        <v>118.946</v>
+        <v>42.9944</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>56.0905</v>
+        <v>31.0069</v>
       </c>
       <c r="C79" t="n">
-        <v>133.491</v>
+        <v>51.3294</v>
       </c>
       <c r="D79" t="n">
-        <v>604.97</v>
+        <v>126.099</v>
       </c>
       <c r="E79" t="n">
-        <v>55.8135</v>
+        <v>26.536</v>
       </c>
       <c r="F79" t="n">
-        <v>118.113</v>
+        <v>43.2228</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>55.4518</v>
+        <v>29.8432</v>
       </c>
       <c r="C80" t="n">
-        <v>132.855</v>
+        <v>51.1178</v>
       </c>
       <c r="D80" t="n">
-        <v>579.758</v>
+        <v>124.09</v>
       </c>
       <c r="E80" t="n">
-        <v>79.4815</v>
+        <v>43.1278</v>
       </c>
       <c r="F80" t="n">
-        <v>211.988</v>
+        <v>70.32550000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>75.3049</v>
+        <v>46.0523</v>
       </c>
       <c r="C81" t="n">
-        <v>244.479</v>
+        <v>82.4483</v>
       </c>
       <c r="D81" t="n">
-        <v>585.996</v>
+        <v>122.825</v>
       </c>
       <c r="E81" t="n">
-        <v>77.28270000000001</v>
+        <v>42.5295</v>
       </c>
       <c r="F81" t="n">
-        <v>223.939</v>
+        <v>70.77670000000001</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>74.5517</v>
+        <v>44.7894</v>
       </c>
       <c r="C82" t="n">
-        <v>246.521</v>
+        <v>82.8181</v>
       </c>
       <c r="D82" t="n">
-        <v>555.494</v>
+        <v>121.421</v>
       </c>
       <c r="E82" t="n">
-        <v>77.4246</v>
+        <v>41.6334</v>
       </c>
       <c r="F82" t="n">
-        <v>226.587</v>
+        <v>70.8815</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>76.7456</v>
+        <v>46.0457</v>
       </c>
       <c r="C83" t="n">
-        <v>243.981</v>
+        <v>82.74079999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>537.081</v>
+        <v>119.623</v>
       </c>
       <c r="E83" t="n">
-        <v>75.8417</v>
+        <v>40.7902</v>
       </c>
       <c r="F83" t="n">
-        <v>201.273</v>
+        <v>68.5873</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>75.8163</v>
+        <v>42.6619</v>
       </c>
       <c r="C84" t="n">
-        <v>238.938</v>
+        <v>82.7141</v>
       </c>
       <c r="D84" t="n">
-        <v>544.976</v>
+        <v>118.995</v>
       </c>
       <c r="E84" t="n">
-        <v>75.131</v>
+        <v>39.7923</v>
       </c>
       <c r="F84" t="n">
-        <v>213.742</v>
+        <v>67.3736</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>75.5716</v>
+        <v>44.3988</v>
       </c>
       <c r="C85" t="n">
-        <v>233.641</v>
+        <v>81.88890000000001</v>
       </c>
       <c r="D85" t="n">
-        <v>544.448</v>
+        <v>118.952</v>
       </c>
       <c r="E85" t="n">
-        <v>73.70910000000001</v>
+        <v>39.0814</v>
       </c>
       <c r="F85" t="n">
-        <v>198.34</v>
+        <v>66.6748</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>75.78740000000001</v>
+        <v>42.3874</v>
       </c>
       <c r="C86" t="n">
-        <v>227.524</v>
+        <v>80.63720000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>510.983</v>
+        <v>118.932</v>
       </c>
       <c r="E86" t="n">
-        <v>72.65819999999999</v>
+        <v>38.1772</v>
       </c>
       <c r="F86" t="n">
-        <v>200.152</v>
+        <v>65.2822</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>75.19629999999999</v>
+        <v>41.5738</v>
       </c>
       <c r="C87" t="n">
-        <v>218.841</v>
+        <v>80.789</v>
       </c>
       <c r="D87" t="n">
-        <v>524.422</v>
+        <v>119.341</v>
       </c>
       <c r="E87" t="n">
-        <v>71.3991</v>
+        <v>37.3734</v>
       </c>
       <c r="F87" t="n">
-        <v>176.79</v>
+        <v>65.7743</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>74.4149</v>
+        <v>41.4313</v>
       </c>
       <c r="C88" t="n">
-        <v>215.862</v>
+        <v>79.0355</v>
       </c>
       <c r="D88" t="n">
-        <v>511.942</v>
+        <v>120.206</v>
       </c>
       <c r="E88" t="n">
-        <v>69.6906</v>
+        <v>36.5498</v>
       </c>
       <c r="F88" t="n">
-        <v>186.629</v>
+        <v>64.6438</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>73.38630000000001</v>
+        <v>37.537</v>
       </c>
       <c r="C89" t="n">
-        <v>211.229</v>
+        <v>78.19710000000001</v>
       </c>
       <c r="D89" t="n">
-        <v>521.006</v>
+        <v>120.512</v>
       </c>
       <c r="E89" t="n">
-        <v>67.9559</v>
+        <v>35.7278</v>
       </c>
       <c r="F89" t="n">
-        <v>186.935</v>
+        <v>63.7806</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>73.0932</v>
+        <v>40.7945</v>
       </c>
       <c r="C90" t="n">
-        <v>207.985</v>
+        <v>76.2837</v>
       </c>
       <c r="D90" t="n">
-        <v>499.213</v>
+        <v>121.42</v>
       </c>
       <c r="E90" t="n">
-        <v>67.2058</v>
+        <v>34.7859</v>
       </c>
       <c r="F90" t="n">
-        <v>185.017</v>
+        <v>62.5092</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>73.2059</v>
+        <v>40.2393</v>
       </c>
       <c r="C91" t="n">
-        <v>204.668</v>
+        <v>75.89570000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>493.446</v>
+        <v>122.626</v>
       </c>
       <c r="E91" t="n">
-        <v>66.675</v>
+        <v>34.2984</v>
       </c>
       <c r="F91" t="n">
-        <v>174.609</v>
+        <v>60.9445</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>72.7462</v>
+        <v>40.3618</v>
       </c>
       <c r="C92" t="n">
-        <v>198.251</v>
+        <v>75.0427</v>
       </c>
       <c r="D92" t="n">
-        <v>822.404</v>
+        <v>185.035</v>
       </c>
       <c r="E92" t="n">
-        <v>64.95780000000001</v>
+        <v>33.9064</v>
       </c>
       <c r="F92" t="n">
-        <v>179.141</v>
+        <v>59.9628</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>72.73860000000001</v>
+        <v>38.4105</v>
       </c>
       <c r="C93" t="n">
-        <v>194.96</v>
+        <v>74.91289999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>827.191</v>
+        <v>185.018</v>
       </c>
       <c r="E93" t="n">
-        <v>63.7704</v>
+        <v>33.619</v>
       </c>
       <c r="F93" t="n">
-        <v>170.897</v>
+        <v>60.1533</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>71.75</v>
+        <v>37.7887</v>
       </c>
       <c r="C94" t="n">
-        <v>192.506</v>
+        <v>74.6022</v>
       </c>
       <c r="D94" t="n">
-        <v>773.228</v>
+        <v>183.452</v>
       </c>
       <c r="E94" t="n">
-        <v>96.7128</v>
+        <v>65.7296</v>
       </c>
       <c r="F94" t="n">
-        <v>326.623</v>
+        <v>119.558</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>91.3036</v>
+        <v>69.54470000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>362.776</v>
+        <v>116.646</v>
       </c>
       <c r="D95" t="n">
-        <v>784.832</v>
+        <v>181.971</v>
       </c>
       <c r="E95" t="n">
-        <v>95.3356</v>
+        <v>64.371</v>
       </c>
       <c r="F95" t="n">
-        <v>305.15</v>
+        <v>118.932</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>91.2704</v>
+        <v>67.43040000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>345.153</v>
+        <v>115.305</v>
       </c>
       <c r="D96" t="n">
-        <v>733.706</v>
+        <v>181.59</v>
       </c>
       <c r="E96" t="n">
-        <v>90.7</v>
+        <v>63.0305</v>
       </c>
       <c r="F96" t="n">
-        <v>290.849</v>
+        <v>114.631</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>92.82940000000001</v>
+        <v>70.1661</v>
       </c>
       <c r="C97" t="n">
-        <v>329.718</v>
+        <v>116.128</v>
       </c>
       <c r="D97" t="n">
-        <v>741.968</v>
+        <v>180.942</v>
       </c>
       <c r="E97" t="n">
-        <v>90.06619999999999</v>
+        <v>61.2009</v>
       </c>
       <c r="F97" t="n">
-        <v>293.722</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>94.9481</v>
+        <v>66.2732</v>
       </c>
       <c r="C98" t="n">
-        <v>337.069</v>
+        <v>112.789</v>
       </c>
       <c r="D98" t="n">
-        <v>723.9400000000001</v>
+        <v>180.224</v>
       </c>
       <c r="E98" t="n">
-        <v>90.6375</v>
+        <v>59.7469</v>
       </c>
       <c r="F98" t="n">
-        <v>283.488</v>
+        <v>111.763</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>94.40779999999999</v>
+        <v>66.0176</v>
       </c>
       <c r="C99" t="n">
-        <v>314.933</v>
+        <v>111.06</v>
       </c>
       <c r="D99" t="n">
-        <v>706.4349999999999</v>
+        <v>180.451</v>
       </c>
       <c r="E99" t="n">
-        <v>88.6242</v>
+        <v>57.9799</v>
       </c>
       <c r="F99" t="n">
-        <v>263.007</v>
+        <v>109.479</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>93.535</v>
+        <v>64.4675</v>
       </c>
       <c r="C100" t="n">
-        <v>314.283</v>
+        <v>112.32</v>
       </c>
       <c r="D100" t="n">
-        <v>690.802</v>
+        <v>180.656</v>
       </c>
       <c r="E100" t="n">
-        <v>91.63760000000001</v>
+        <v>56.5695</v>
       </c>
       <c r="F100" t="n">
-        <v>283.029</v>
+        <v>107.465</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>96.301</v>
+        <v>62.4014</v>
       </c>
       <c r="C101" t="n">
-        <v>321.945</v>
+        <v>109.262</v>
       </c>
       <c r="D101" t="n">
-        <v>677.6319999999999</v>
+        <v>180.871</v>
       </c>
       <c r="E101" t="n">
-        <v>87.98480000000001</v>
+        <v>54.9603</v>
       </c>
       <c r="F101" t="n">
-        <v>283.73</v>
+        <v>106.795</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>97.26139999999999</v>
+        <v>60.8549</v>
       </c>
       <c r="C102" t="n">
-        <v>315.033</v>
+        <v>106.319</v>
       </c>
       <c r="D102" t="n">
-        <v>666.763</v>
+        <v>180.987</v>
       </c>
       <c r="E102" t="n">
-        <v>88.5433</v>
+        <v>53.4983</v>
       </c>
       <c r="F102" t="n">
-        <v>280.64</v>
+        <v>105.73</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>97.4953</v>
+        <v>59.0571</v>
       </c>
       <c r="C103" t="n">
-        <v>312.435</v>
+        <v>105.104</v>
       </c>
       <c r="D103" t="n">
-        <v>655.678</v>
+        <v>181.886</v>
       </c>
       <c r="E103" t="n">
-        <v>89.357</v>
+        <v>52.2934</v>
       </c>
       <c r="F103" t="n">
-        <v>276.845</v>
+        <v>104.693</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>97.5234</v>
+        <v>60.0957</v>
       </c>
       <c r="C104" t="n">
-        <v>308.086</v>
+        <v>105.888</v>
       </c>
       <c r="D104" t="n">
-        <v>648.772</v>
+        <v>183.523</v>
       </c>
       <c r="E104" t="n">
-        <v>86.795</v>
+        <v>51.1942</v>
       </c>
       <c r="F104" t="n">
-        <v>266.888</v>
+        <v>103.957</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>98.011</v>
+        <v>57.2872</v>
       </c>
       <c r="C105" t="n">
-        <v>305.817</v>
+        <v>102.498</v>
       </c>
       <c r="D105" t="n">
-        <v>648.957</v>
+        <v>184.916</v>
       </c>
       <c r="E105" t="n">
-        <v>86.3278</v>
+        <v>50.0808</v>
       </c>
       <c r="F105" t="n">
-        <v>251.425</v>
+        <v>103.013</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>97.8621</v>
+        <v>56.5006</v>
       </c>
       <c r="C106" t="n">
-        <v>294.415</v>
+        <v>103.807</v>
       </c>
       <c r="D106" t="n">
-        <v>640.051</v>
+        <v>186.772</v>
       </c>
       <c r="E106" t="n">
-        <v>84.4992</v>
+        <v>49.1957</v>
       </c>
       <c r="F106" t="n">
-        <v>243.257</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>99.07510000000001</v>
+        <v>56.1657</v>
       </c>
       <c r="C107" t="n">
-        <v>284.368</v>
+        <v>104.195</v>
       </c>
       <c r="D107" t="n">
-        <v>948.856</v>
+        <v>253.178</v>
       </c>
       <c r="E107" t="n">
-        <v>86.2368</v>
+        <v>48.2741</v>
       </c>
       <c r="F107" t="n">
-        <v>252.955</v>
+        <v>99.0996</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>99.2903</v>
+        <v>56.3278</v>
       </c>
       <c r="C108" t="n">
-        <v>279.09</v>
+        <v>101.117</v>
       </c>
       <c r="D108" t="n">
-        <v>920.2569999999999</v>
+        <v>250.123</v>
       </c>
       <c r="E108" t="n">
-        <v>131.644</v>
+        <v>71.26519999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>405.79</v>
+        <v>254.938</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>104.534</v>
+        <v>45.8063</v>
       </c>
       <c r="C109" t="n">
-        <v>259.289</v>
+        <v>100.174</v>
       </c>
       <c r="D109" t="n">
-        <v>883.199</v>
+        <v>247.138</v>
       </c>
       <c r="E109" t="n">
-        <v>110.784</v>
+        <v>80.5997</v>
       </c>
       <c r="F109" t="n">
-        <v>414.829</v>
+        <v>255.641</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>145.822</v>
+        <v>89.1474</v>
       </c>
       <c r="C110" t="n">
-        <v>429.874</v>
+        <v>280.008</v>
       </c>
       <c r="D110" t="n">
-        <v>874.326</v>
+        <v>245.516</v>
       </c>
       <c r="E110" t="n">
-        <v>135.912</v>
+        <v>78.6155</v>
       </c>
       <c r="F110" t="n">
-        <v>403.514</v>
+        <v>254.183</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>145.53</v>
+        <v>79.20310000000001</v>
       </c>
       <c r="C111" t="n">
-        <v>419.983</v>
+        <v>277.709</v>
       </c>
       <c r="D111" t="n">
-        <v>849.875</v>
+        <v>246.704</v>
       </c>
       <c r="E111" t="n">
-        <v>126.193</v>
+        <v>76.3871</v>
       </c>
       <c r="F111" t="n">
-        <v>387.856</v>
+        <v>255.463</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>132.42</v>
+        <v>83.9866</v>
       </c>
       <c r="C112" t="n">
-        <v>413.462</v>
+        <v>278.075</v>
       </c>
       <c r="D112" t="n">
-        <v>824.83</v>
+        <v>244.6</v>
       </c>
       <c r="E112" t="n">
-        <v>109.463</v>
+        <v>65.2637</v>
       </c>
       <c r="F112" t="n">
-        <v>394.453</v>
+        <v>255.094</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>120.873</v>
+        <v>82.99250000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>420.324</v>
+        <v>276.102</v>
       </c>
       <c r="D113" t="n">
-        <v>829.837</v>
+        <v>245.193</v>
       </c>
       <c r="E113" t="n">
-        <v>111.575</v>
+        <v>63.8458</v>
       </c>
       <c r="F113" t="n">
-        <v>394.391</v>
+        <v>255.519</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>120.933</v>
+        <v>74.1721</v>
       </c>
       <c r="C114" t="n">
-        <v>416.752</v>
+        <v>276.222</v>
       </c>
       <c r="D114" t="n">
-        <v>820.755</v>
+        <v>253.89</v>
       </c>
       <c r="E114" t="n">
-        <v>111.521</v>
+        <v>70.58750000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>374.478</v>
+        <v>255.605</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>123.756</v>
+        <v>78.2427</v>
       </c>
       <c r="C115" t="n">
-        <v>401.304</v>
+        <v>275.838</v>
       </c>
       <c r="D115" t="n">
-        <v>801.424</v>
+        <v>248.178</v>
       </c>
       <c r="E115" t="n">
-        <v>111.627</v>
+        <v>68.8326</v>
       </c>
       <c r="F115" t="n">
-        <v>368.021</v>
+        <v>255.461</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>130.23</v>
+        <v>75.4706</v>
       </c>
       <c r="C116" t="n">
-        <v>397.092</v>
+        <v>276.472</v>
       </c>
       <c r="D116" t="n">
-        <v>773.022</v>
+        <v>252.523</v>
       </c>
       <c r="E116" t="n">
-        <v>110.943</v>
+        <v>67.1953</v>
       </c>
       <c r="F116" t="n">
-        <v>356.363</v>
+        <v>254.741</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>133.389</v>
+        <v>73.93510000000001</v>
       </c>
       <c r="C117" t="n">
-        <v>368.515</v>
+        <v>275.553</v>
       </c>
       <c r="D117" t="n">
-        <v>770.924</v>
+        <v>254.705</v>
       </c>
       <c r="E117" t="n">
-        <v>114.693</v>
+        <v>65.746</v>
       </c>
       <c r="F117" t="n">
-        <v>340.631</v>
+        <v>255.334</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>127.757</v>
+        <v>74.5154</v>
       </c>
       <c r="C118" t="n">
-        <v>358.36</v>
+        <v>274.941</v>
       </c>
       <c r="D118" t="n">
-        <v>750.99</v>
+        <v>240.249</v>
       </c>
       <c r="E118" t="n">
-        <v>110.636</v>
+        <v>57.3167</v>
       </c>
       <c r="F118" t="n">
-        <v>326.256</v>
+        <v>256.013</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>134.174</v>
+        <v>72.50239999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>344.272</v>
+        <v>274.549</v>
       </c>
       <c r="D119" t="n">
-        <v>740.463</v>
+        <v>241.287</v>
       </c>
       <c r="E119" t="n">
-        <v>116.989</v>
+        <v>56.3384</v>
       </c>
       <c r="F119" t="n">
-        <v>320.304</v>
+        <v>232.525</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>135.889</v>
+        <v>66.8954</v>
       </c>
       <c r="C120" t="n">
-        <v>344.316</v>
+        <v>203.833</v>
       </c>
       <c r="D120" t="n">
-        <v>739.275</v>
+        <v>242.28</v>
       </c>
       <c r="E120" t="n">
-        <v>124.199</v>
+        <v>55.5537</v>
       </c>
       <c r="F120" t="n">
-        <v>319.712</v>
+        <v>232.157</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>141.302</v>
+        <v>63.9337</v>
       </c>
       <c r="C121" t="n">
-        <v>352.078</v>
+        <v>274.437</v>
       </c>
       <c r="D121" t="n">
-        <v>1067.42</v>
+        <v>320.295</v>
       </c>
       <c r="E121" t="n">
-        <v>128.323</v>
+        <v>54.4233</v>
       </c>
       <c r="F121" t="n">
-        <v>315.438</v>
+        <v>108.616</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>141.669</v>
+        <v>63.5316</v>
       </c>
       <c r="C122" t="n">
-        <v>338.743</v>
+        <v>275.874</v>
       </c>
       <c r="D122" t="n">
-        <v>1061.1</v>
+        <v>315.476</v>
       </c>
       <c r="E122" t="n">
-        <v>128.388</v>
+        <v>53.9935</v>
       </c>
       <c r="F122" t="n">
-        <v>306.418</v>
+        <v>184.515</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>138.927</v>
+        <v>60.9071</v>
       </c>
       <c r="C123" t="n">
-        <v>334.528</v>
+        <v>277.014</v>
       </c>
       <c r="D123" t="n">
-        <v>1037.01</v>
+        <v>311.243</v>
       </c>
       <c r="E123" t="n">
-        <v>167.16</v>
+        <v>87.06180000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>468.798</v>
+        <v>308.544</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>171.939</v>
+        <v>99.4999</v>
       </c>
       <c r="C124" t="n">
-        <v>491.391</v>
+        <v>331.139</v>
       </c>
       <c r="D124" t="n">
-        <v>980.327</v>
+        <v>307.768</v>
       </c>
       <c r="E124" t="n">
-        <v>165.507</v>
+        <v>85.3112</v>
       </c>
       <c r="F124" t="n">
-        <v>449.206</v>
+        <v>307.439</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>169.487</v>
+        <v>97.2345</v>
       </c>
       <c r="C125" t="n">
-        <v>478.184</v>
+        <v>329.994</v>
       </c>
       <c r="D125" t="n">
-        <v>957.977</v>
+        <v>304.058</v>
       </c>
       <c r="E125" t="n">
-        <v>162.921</v>
+        <v>88.68940000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>444.175</v>
+        <v>308.26</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>175.318</v>
+        <v>91.3524</v>
       </c>
       <c r="C126" t="n">
-        <v>464.567</v>
+        <v>328.011</v>
       </c>
       <c r="D126" t="n">
-        <v>925.3099999999999</v>
+        <v>301.377</v>
       </c>
       <c r="E126" t="n">
-        <v>163.987</v>
+        <v>82.24460000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>436.013</v>
+        <v>305.33</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>176.667</v>
+        <v>90.0898</v>
       </c>
       <c r="C127" t="n">
-        <v>460.878</v>
+        <v>326.72</v>
       </c>
       <c r="D127" t="n">
-        <v>909.2809999999999</v>
+        <v>298.322</v>
       </c>
       <c r="E127" t="n">
-        <v>166.578</v>
+        <v>80.804</v>
       </c>
       <c r="F127" t="n">
-        <v>425.225</v>
+        <v>304.987</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>176.46</v>
+        <v>88.4156</v>
       </c>
       <c r="C128" t="n">
-        <v>468.211</v>
+        <v>327.438</v>
       </c>
       <c r="D128" t="n">
-        <v>905.457</v>
+        <v>295.843</v>
       </c>
       <c r="E128" t="n">
-        <v>167.627</v>
+        <v>79.29859999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>435.862</v>
+        <v>304.063</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>175.435</v>
+        <v>85.7786</v>
       </c>
       <c r="C129" t="n">
-        <v>457.03</v>
+        <v>324.091</v>
       </c>
       <c r="D129" t="n">
-        <v>880.011</v>
+        <v>293.814</v>
       </c>
       <c r="E129" t="n">
-        <v>164.842</v>
+        <v>77.97629999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>424.26</v>
+        <v>303.246</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>175.582</v>
+        <v>85.7864</v>
       </c>
       <c r="C130" t="n">
-        <v>446.557</v>
+        <v>322.982</v>
       </c>
       <c r="D130" t="n">
-        <v>856.965</v>
+        <v>292.479</v>
       </c>
       <c r="E130" t="n">
-        <v>170.25</v>
+        <v>76.5887</v>
       </c>
       <c r="F130" t="n">
-        <v>430.134</v>
+        <v>301.981</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>178.958</v>
+        <v>83.6746</v>
       </c>
       <c r="C131" t="n">
-        <v>451.95</v>
+        <v>321.808</v>
       </c>
       <c r="D131" t="n">
-        <v>857.982</v>
+        <v>291.343</v>
       </c>
       <c r="E131" t="n">
-        <v>168.982</v>
+        <v>75.5564</v>
       </c>
       <c r="F131" t="n">
-        <v>416.894</v>
+        <v>302.669</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>179.107</v>
+        <v>82.0299</v>
       </c>
       <c r="C132" t="n">
-        <v>434.46</v>
+        <v>321.162</v>
       </c>
       <c r="D132" t="n">
-        <v>841.148</v>
+        <v>290.348</v>
       </c>
       <c r="E132" t="n">
-        <v>163.615</v>
+        <v>74.31570000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>394.396</v>
+        <v>302.27</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>173.191</v>
+        <v>80.96169999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>419.144</v>
+        <v>320.612</v>
       </c>
       <c r="D133" t="n">
-        <v>825.29</v>
+        <v>290.024</v>
       </c>
       <c r="E133" t="n">
-        <v>162.347</v>
+        <v>76.6131</v>
       </c>
       <c r="F133" t="n">
-        <v>390.766</v>
+        <v>301.085</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>170.748</v>
+        <v>78.7863</v>
       </c>
       <c r="C134" t="n">
-        <v>412.389</v>
+        <v>320.622</v>
       </c>
       <c r="D134" t="n">
-        <v>810.617</v>
+        <v>285.478</v>
       </c>
       <c r="E134" t="n">
-        <v>161.505</v>
+        <v>66.3318</v>
       </c>
       <c r="F134" t="n">
-        <v>385.752</v>
+        <v>220.12</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>175.479</v>
+        <v>79.1542</v>
       </c>
       <c r="C135" t="n">
-        <v>404.261</v>
+        <v>319.413</v>
       </c>
       <c r="D135" t="n">
-        <v>1119.27</v>
+        <v>366.332</v>
       </c>
       <c r="E135" t="n">
-        <v>160.508</v>
+        <v>65.6009</v>
       </c>
       <c r="F135" t="n">
-        <v>376.678</v>
+        <v>273.833</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>170.937</v>
+        <v>77.2469</v>
       </c>
       <c r="C136" t="n">
-        <v>400.538</v>
+        <v>318.513</v>
       </c>
       <c r="D136" t="n">
-        <v>1137.43</v>
+        <v>359.814</v>
       </c>
       <c r="E136" t="n">
-        <v>165.869</v>
+        <v>64.95489999999999</v>
       </c>
       <c r="F136" t="n">
-        <v>381.517</v>
+        <v>300.799</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>175.901</v>
+        <v>78.2111</v>
       </c>
       <c r="C137" t="n">
-        <v>400.236</v>
+        <v>319.042</v>
       </c>
       <c r="D137" t="n">
-        <v>1082.51</v>
+        <v>353.904</v>
       </c>
       <c r="E137" t="n">
-        <v>207.93</v>
+        <v>98.7615</v>
       </c>
       <c r="F137" t="n">
-        <v>562.572</v>
+        <v>350.229</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>212.645</v>
+        <v>106.382</v>
       </c>
       <c r="C138" t="n">
-        <v>597.152</v>
+        <v>375.535</v>
       </c>
       <c r="D138" t="n">
-        <v>1078.42</v>
+        <v>348.667</v>
       </c>
       <c r="E138" t="n">
-        <v>207.483</v>
+        <v>97.26049999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>546.388</v>
+        <v>350.023</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>212.604</v>
+        <v>102.62</v>
       </c>
       <c r="C139" t="n">
-        <v>578.093</v>
+        <v>372.894</v>
       </c>
       <c r="D139" t="n">
-        <v>1062.04</v>
+        <v>343.798</v>
       </c>
       <c r="E139" t="n">
-        <v>203.311</v>
+        <v>96.0234</v>
       </c>
       <c r="F139" t="n">
-        <v>532.018</v>
+        <v>348.226</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>210.126</v>
+        <v>105.939</v>
       </c>
       <c r="C140" t="n">
-        <v>557.028</v>
+        <v>370.269</v>
       </c>
       <c r="D140" t="n">
-        <v>1004.22</v>
+        <v>340.979</v>
       </c>
       <c r="E140" t="n">
-        <v>197.567</v>
+        <v>94.3492</v>
       </c>
       <c r="F140" t="n">
-        <v>508.972</v>
+        <v>346.755</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>203.218</v>
+        <v>99.18049999999999</v>
       </c>
       <c r="C141" t="n">
-        <v>535.157</v>
+        <v>368.254</v>
       </c>
       <c r="D141" t="n">
-        <v>988.449</v>
+        <v>338.348</v>
       </c>
       <c r="E141" t="n">
-        <v>195.675</v>
+        <v>96.6591</v>
       </c>
       <c r="F141" t="n">
-        <v>496.584</v>
+        <v>345.541</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>201.344</v>
+        <v>97.07689999999999</v>
       </c>
       <c r="C142" t="n">
-        <v>527.324</v>
+        <v>366.212</v>
       </c>
       <c r="D142" t="n">
-        <v>965.428</v>
+        <v>337.221</v>
       </c>
       <c r="E142" t="n">
-        <v>193.797</v>
+        <v>91.7997</v>
       </c>
       <c r="F142" t="n">
-        <v>489.215</v>
+        <v>344.202</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>204.369</v>
+        <v>97.4192</v>
       </c>
       <c r="C143" t="n">
-        <v>518.773</v>
+        <v>365.106</v>
       </c>
       <c r="D143" t="n">
-        <v>959.448</v>
+        <v>334.839</v>
       </c>
       <c r="E143" t="n">
-        <v>196.474</v>
+        <v>90.42449999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>477.305</v>
+        <v>342.572</v>
       </c>
     </row>
   </sheetData>
